--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -7,33 +7,32 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="22" state="hidden" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="23" state="hidden" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="24" state="hidden" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="25" state="hidden" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="26" state="hidden" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="27" state="hidden" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="AylikBorcServisi" hidden="0" function="0" vbProcedure="0">KARAR_MOTORU!$B$6</definedName>
@@ -96,8 +95,7 @@
     <definedName name="VeriKaliteYuksek" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$21</definedName>
     <definedName name="YillikDovizGeliri" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$17</definedName>
     <definedName name="YillikFaaliyetKari" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'PANO'!$A$1:$Z$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'RAPOR'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'RAPOR'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -105,14 +103,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -422,8 +421,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -478,8 +659,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -501,6 +748,95 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -512,7 +848,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -867,6 +1203,163 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="68" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="67" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="67" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="68" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="67" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="67" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="69" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1133,1823 +1626,6 @@
                 <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Banka Bazında Borç Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H20</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 10.600.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$20:$G$23</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Türkiye İş Bankası</v>
-                </pt>
-                <pt idx="1">
-                  <v>Akbank</v>
-                </pt>
-                <pt idx="2">
-                  <v>Garanti BBVA</v>
-                </pt>
-                <pt idx="3">
-                  <v>Yapı Kredi</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$21:$H$23</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>6100000</v>
-                </pt>
-                <pt idx="1">
-                  <v>180000</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Yaklaşan Ödeme Takvimi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H26</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 934.864</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$26:$G$31</f>
-              <strCache>
-                <ptCount val="6"/>
-                <pt idx="0">
-                  <v>Önümüzdeki Ay</v>
-                </pt>
-                <pt idx="1">
-                  <v>İkinci Ay</v>
-                </pt>
-                <pt idx="2">
-                  <v>Üçüncü Ay</v>
-                </pt>
-                <pt idx="3">
-                  <v>Dördüncü Ay</v>
-                </pt>
-                <pt idx="4">
-                  <v>Beşinci Ay</v>
-                </pt>
-                <pt idx="5">
-                  <v>Altıncı Ay</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$27:$H$31</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>930000</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>3285700</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="44658425"/>
-        <axId val="22321148"/>
-      </barChart>
-      <catAx>
-        <axId val="44658425"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="22321148"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="22321148"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>₺</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="44658425"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>30/60/90 Gün Ödeme Yükü</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H33</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 934.864</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="4A7EBB"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$33:$G$35</f>
-              <strCache>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>30 Gün</v>
-                </pt>
-                <pt idx="1">
-                  <v>60 Gün</v>
-                </pt>
-                <pt idx="2">
-                  <v>90 Gün</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$34:$H$35</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="2"/>
-                <pt idx="0">
-                  <v>1864864</v>
-                </pt>
-                <pt idx="1">
-                  <v>1864864</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="0"/>
-        <axId val="44987311"/>
-        <axId val="61937843"/>
-      </lineChart>
-      <catAx>
-        <axId val="44987311"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="61937843"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="61937843"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="44987311"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Kredi Ürün Türü Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H38</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 8.400.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$38:$G$41</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Taksitli Ticari Kredi</v>
-                </pt>
-                <pt idx="1">
-                  <v>Leasing</v>
-                </pt>
-                <pt idx="2">
-                  <v>Rotatif Kredi</v>
-                </pt>
-                <pt idx="3">
-                  <v>Spot Kredi</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$39:$H$41</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>6100000</v>
-                </pt>
-                <pt idx="1">
-                  <v>180000</v>
-                </pt>
-                <pt idx="2">
-                  <v>2200000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="91797802"/>
-        <axId val="5607583"/>
-      </barChart>
-      <catAx>
-        <axId val="91797802"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="5607583"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="5607583"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="91797802"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Masraf Türü Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H44</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 60.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$44:$G$47</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Tahsis Ücreti</v>
-                </pt>
-                <pt idx="1">
-                  <v>Sigorta</v>
-                </pt>
-                <pt idx="2">
-                  <v>Komisyon</v>
-                </pt>
-                <pt idx="3">
-                  <v>Diğer</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$45:$H$47</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>70000</v>
-                </pt>
-                <pt idx="1">
-                  <v>1500</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Teminat Türü Kapsaması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>PANO!H50</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>₺ 15.000.000</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>PANO!$G$50:$G$53</f>
-              <strCache>
-                <ptCount val="4"/>
-                <pt idx="0">
-                  <v>Gayrimenkul İpoteği</v>
-                </pt>
-                <pt idx="1">
-                  <v>Taşıt Rehni</v>
-                </pt>
-                <pt idx="2">
-                  <v>Alacak Temliki</v>
-                </pt>
-                <pt idx="3">
-                  <v>Diğer</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>PANO!$H$51:$H$53</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="3"/>
-                <pt idx="0">
-                  <v>8500000</v>
-                </pt>
-                <pt idx="1">
-                  <v>3500000</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="99549932"/>
-        <axId val="80107446"/>
-      </barChart>
-      <catAx>
-        <axId val="99549932"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="80107446"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="80107446"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>₺</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="99549932"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
               <a:t>Senaryo Karşılaştırma</a:t>
             </a:r>
           </a:p>
@@ -3008,7 +1684,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3095,7 +1771,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3151,7 +1827,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3184,7 +1860,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -3207,7 +1883,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -3288,7 +1964,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3375,7 +2051,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3431,7 +2107,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3464,7 +2140,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -12868,173 +11544,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>21</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>36</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>51</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>66</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>79</row>
-      <rowOff>1080</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>90</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
@@ -13450,351 +11959,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="50" min="1" max="1"/>
-    <col width="16" customWidth="1" style="50" min="2" max="2"/>
-    <col width="20" customWidth="1" style="50" min="3" max="3"/>
-    <col width="20" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="22" customWidth="1" style="50" min="7" max="7"/>
-    <col width="14" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="9"/>
+    <col width="3" customWidth="1" style="50" min="1" max="1"/>
+    <col width="18" customWidth="1" style="50" min="2" max="2"/>
+    <col width="15" customWidth="1" style="50" min="3" max="3"/>
+    <col width="12" customWidth="1" style="50" min="4" max="4"/>
+    <col width="16" customWidth="1" style="50" min="5" max="5"/>
+    <col width="18" customWidth="1" style="50" min="6" max="6"/>
+    <col width="6" customWidth="1" style="50" min="7" max="7"/>
+    <col width="24" customWidth="1" style="50" min="8" max="8"/>
+    <col width="15" customWidth="1" style="50" min="9" max="9"/>
+    <col width="14" customWidth="1" style="50" min="10" max="10"/>
+    <col width="12" customWidth="1" style="50" min="11" max="11"/>
+    <col width="18" customWidth="1" style="50" min="12" max="12"/>
+    <col width="18" customWidth="1" style="50" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="51" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — KREDİ BORÇ VE COVENANT KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="52" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="124" t="inlineStr">
+        <is>
+          <t>BANKA KREDI VE TAKSIT TAKIP SISTEMI — BORÇ VE LİKİDİTE SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="125" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="126" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="127" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="128" t="inlineStr">
+        <is>
+          <t>TOPLAM KREDİ PORTFÖYÜ</t>
+        </is>
+      </c>
+      <c r="C5" s="129" t="n"/>
+      <c r="D5" s="130" t="inlineStr">
+        <is>
+          <t>6 BANKA</t>
+        </is>
+      </c>
+      <c r="E5" s="131" t="inlineStr">
+        <is>
+          <t>BU AY ÖDENECEK TAKSİT</t>
+        </is>
+      </c>
+      <c r="F5" s="129" t="n"/>
+      <c r="G5" s="132" t="inlineStr">
+        <is>
+          <t>VADE: 7 GÜN</t>
+        </is>
+      </c>
+      <c r="H5" s="128" t="inlineStr">
+        <is>
+          <t>KULLANILABİLİR KREDİ LİMİTİ</t>
+        </is>
+      </c>
+      <c r="I5" s="129" t="n"/>
+      <c r="J5" s="133" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="134" t="inlineStr">
+        <is>
+          <t>BORÇ SERVİS ORANI (DSCR)</t>
+        </is>
+      </c>
+      <c r="L5" s="129" t="n"/>
+      <c r="M5" s="130" t="inlineStr">
+        <is>
+          <t>EŞİK: 1.25x</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>TOPLAM KREDİ VE BORÇ YÜKÜ</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>AĞIRLIKLI ORTALAMA FAİZ</t>
-        </is>
-      </c>
-      <c r="F6" s="53" t="inlineStr">
-        <is>
-          <t>BANKA COVENANT RİSKİ</t>
-        </is>
-      </c>
-      <c r="H6" s="54" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="129" t="n"/>
+      <c r="D6" s="129" t="n"/>
+      <c r="E6" s="136" t="n"/>
+      <c r="F6" s="129" t="n"/>
+      <c r="G6" s="129" t="n"/>
+      <c r="H6" s="135" t="n"/>
+      <c r="I6" s="129" t="n"/>
+      <c r="J6" s="129" t="n"/>
+      <c r="K6" s="137" t="n"/>
+      <c r="L6" s="129" t="n"/>
+      <c r="M6" s="129" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="55" t="inlineStr">
-        <is>
-          <t>₺ 8.420.000</t>
-        </is>
-      </c>
-      <c r="D7" s="55" t="inlineStr">
-        <is>
-          <t>% 39,2</t>
-        </is>
-      </c>
-      <c r="F7" s="56" t="inlineStr">
-        <is>
-          <t>GÜVENLİ (YEŞİL)</t>
-        </is>
-      </c>
-      <c r="H7" s="57" t="inlineStr">
-        <is>
-          <t>Yüksek faizli rotatif kredileri 60 gün içinde kapat; uzun vadeli yatırıma dönüştür.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="138" t="inlineStr">
+        <is>
+          <t>₺18.640.000</t>
+        </is>
+      </c>
+      <c r="C7" s="129" t="n"/>
+      <c r="D7" s="129" t="n"/>
+      <c r="E7" s="139" t="inlineStr">
+        <is>
+          <t>₺1.120.000</t>
+        </is>
+      </c>
+      <c r="F7" s="129" t="n"/>
+      <c r="G7" s="129" t="n"/>
+      <c r="H7" s="138" t="inlineStr">
+        <is>
+          <t>₺9.500.000</t>
+        </is>
+      </c>
+      <c r="I7" s="129" t="n"/>
+      <c r="J7" s="129" t="n"/>
+      <c r="K7" s="140" t="inlineStr">
+        <is>
+          <t>1.95x</t>
+        </is>
+      </c>
+      <c r="L7" s="129" t="n"/>
+      <c r="M7" s="129" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="135" t="n"/>
+      <c r="C8" s="129" t="n"/>
+      <c r="D8" s="129" t="n"/>
+      <c r="E8" s="136" t="n"/>
+      <c r="F8" s="129" t="n"/>
+      <c r="G8" s="129" t="n"/>
+      <c r="H8" s="135" t="n"/>
+      <c r="I8" s="129" t="n"/>
+      <c r="J8" s="129" t="n"/>
+      <c r="K8" s="137" t="n"/>
+      <c r="L8" s="129" t="n"/>
+      <c r="M8" s="129" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="58" t="inlineStr">
-        <is>
-          <t>Aylık Taksit Yükü: ₺ 640.000 | DSCR: 2,15x</t>
-        </is>
-      </c>
-      <c r="D9" s="59" t="inlineStr">
-        <is>
-          <t>Refinansman Fırsatı: Mevcut</t>
-        </is>
-      </c>
-      <c r="F9" s="60" t="inlineStr">
-        <is>
-          <t>Kritik Eşik Limiti: % 12 Headroom</t>
+      <c r="B9" s="141" t="inlineStr">
+        <is>
+          <t>↑ Ağırlıklı Ortalama Vade: 28 Ay</t>
+        </is>
+      </c>
+      <c r="C9" s="129" t="n"/>
+      <c r="D9" s="129" t="n"/>
+      <c r="E9" s="142" t="inlineStr">
+        <is>
+          <t>● Anapara + Faiz Karşılığı Ayrıldı</t>
+        </is>
+      </c>
+      <c r="F9" s="129" t="n"/>
+      <c r="G9" s="129" t="n"/>
+      <c r="H9" s="141" t="inlineStr">
+        <is>
+          <t>████████░░░░░░░ %42.0 REZERV</t>
+        </is>
+      </c>
+      <c r="I9" s="129" t="n"/>
+      <c r="J9" s="129" t="n"/>
+      <c r="K9" s="143" t="inlineStr">
+        <is>
+          <t>✓ BANKA COVENANT UYUMLU</t>
+        </is>
+      </c>
+      <c r="L9" s="129" t="n"/>
+      <c r="M9" s="129" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="144" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="61" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="145" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="62" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="62" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="62" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="62" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="62" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="62" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="63" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="64" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="64" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="65">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="66">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="64" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="67" t="n">
+      <c r="C14" s="145" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="145" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="145" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="146" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="146" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="146" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="146" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="146" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="73" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="73" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="147" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="147" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="148" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="149" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="133" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="73" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="73" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="147" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="147" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="148" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="149" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="130" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="73" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="73" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="147" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="147" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="148" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="149" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="150" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="73" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="147" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="147" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="148" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="149" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="133" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="73" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="151" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="152" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="153" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="154" t="inlineStr"/>
+      <c r="L19" s="155" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="63" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="64" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="64" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="65">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="66">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="64" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="63" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="64" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="64" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="65">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="66">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="64" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="63" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="64" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="64" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="65">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="66">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="64" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="63" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="64" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="64" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="65">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="66">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="64" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="63" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="64" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="64" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="65">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="66">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="64" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="67" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="68" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="73" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="73" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="156" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="156" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="157" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="158" t="n"/>
+      <c r="M22" s="158" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="159" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="160" t="inlineStr">
+        <is>
+          <t>FAİZ VE YENİDEN YAPILANDIRMA FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="158" t="n"/>
+      <c r="M23" s="158" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="159" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="161" t="inlineStr">
+        <is>
+          <t>Yüksek faizli rotatif kredilerin uzun vadeli yatırıma dönüştürülmesi önerilmektedir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="162" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="58" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="163" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="164" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="165" t="inlineStr">
+        <is>
+          <t>YAPILANDIRMA ANALİZİNİ GÖR &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19360,566 +18093,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN53"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="44" customWidth="1" style="76" min="1" max="1"/>
-    <col width="26" customWidth="1" style="76" min="2" max="2"/>
-    <col width="20" customWidth="1" style="76" min="4" max="4"/>
-    <col width="16" customWidth="1" style="76" min="5" max="6"/>
-    <col width="24" customWidth="1" style="76" min="7" max="7"/>
-    <col width="18" customWidth="1" style="76" min="8" max="8"/>
-    <col width="16" customWidth="1" style="76" min="9" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>PANO — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="50">
-      <c r="A3" s="113" t="inlineStr">
-        <is>
-          <t>YÖNETİCİ BORÇ VE LİKİDİTE PANELİ — tek ekranda karar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="50">
-      <c r="A5" s="100" t="inlineStr">
-        <is>
-          <t>Toplam Finansal Borç</t>
-        </is>
-      </c>
-      <c r="B5" s="111">
-        <f>KARAR_MOTORU!$B$5</f>
-        <v/>
-      </c>
-      <c r="D5" s="80" t="inlineStr">
-        <is>
-          <t>ÖNEMLİ UYARILAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="100" t="inlineStr">
-        <is>
-          <t>Aylık Borç Servisi</t>
-        </is>
-      </c>
-      <c r="B6" s="111">
-        <f>KARAR_MOTORU!$B$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="81" t="inlineStr">
-        <is>
-          <t>Bu sistem karar destek aracıdır; kesin finansal tavsiye değildir. Gerçekleşme verilere ve varsayımlara bağlıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="100" t="inlineStr">
-        <is>
-          <t>30 Günlük Ödeme Yükü</t>
-        </is>
-      </c>
-      <c r="B7" s="111">
-        <f>KARAR_MOTORU!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="100" t="inlineStr">
-        <is>
-          <t>Ağırlıklı Maliyet</t>
-        </is>
-      </c>
-      <c r="B8" s="112">
-        <f>KARAR_MOTORU!$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="100" t="inlineStr">
-        <is>
-          <t>Döviz Borcu</t>
-        </is>
-      </c>
-      <c r="B9" s="111">
-        <f>KARAR_MOTORU!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="100" t="inlineStr">
-        <is>
-          <t>Kaldıraç (Borç/Kâr)</t>
-        </is>
-      </c>
-      <c r="B10" s="101">
-        <f>KARAR_MOTORU!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="100" t="inlineStr">
-        <is>
-          <t>Teminat Oranı</t>
-        </is>
-      </c>
-      <c r="B11" s="112">
-        <f>KARAR_MOTORU!$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="50">
-      <c r="A12" s="100" t="inlineStr">
-        <is>
-          <t>Veri Kalite Skoru</t>
-        </is>
-      </c>
-      <c r="B12" s="101">
-        <f>KONTROLLER!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="50">
-      <c r="A13" s="100" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B13" s="102">
-        <f>KARAR_MOTORU!$B$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="50">
-      <c r="A14" s="100" t="inlineStr">
-        <is>
-          <t>Risk Seviyesi</t>
-        </is>
-      </c>
-      <c r="B14" s="102">
-        <f>KARAR_MOTORU!$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="50">
-      <c r="G19" s="114" t="inlineStr">
-        <is>
-          <t>Banka</t>
-        </is>
-      </c>
-      <c r="H19" s="114" t="inlineStr">
-        <is>
-          <t>Bakiye</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="50">
-      <c r="G20" s="115" t="inlineStr">
-        <is>
-          <t>Türkiye İş Bankası</t>
-        </is>
-      </c>
-      <c r="H20" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$B$6:$B$1000,"Türkiye İş Bankası")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="50">
-      <c r="G21" s="115" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="H21" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$B$6:$B$1000,"Akbank")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="50">
-      <c r="G22" s="115" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="H22" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$B$6:$B$1000,"Garanti BBVA")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="50">
-      <c r="G23" s="115" t="inlineStr">
-        <is>
-          <t>Yapı Kredi</t>
-        </is>
-      </c>
-      <c r="H23" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$B$6:$B$1000,"Yapı Kredi")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="50">
-      <c r="G25" s="114" t="inlineStr">
-        <is>
-          <t>Ay</t>
-        </is>
-      </c>
-      <c r="H25" s="114" t="inlineStr">
-        <is>
-          <t>Ödeme</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="50">
-      <c r="G26" s="115" t="inlineStr">
-        <is>
-          <t>Önümüzdeki Ay</t>
-        </is>
-      </c>
-      <c r="H26" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$26,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="50">
-      <c r="G27" s="115" t="inlineStr">
-        <is>
-          <t>İkinci Ay</t>
-        </is>
-      </c>
-      <c r="H27" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$27,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="50">
-      <c r="G28" s="115" t="inlineStr">
-        <is>
-          <t>Üçüncü Ay</t>
-        </is>
-      </c>
-      <c r="H28" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$28,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="50">
-      <c r="G29" s="115" t="inlineStr">
-        <is>
-          <t>Dördüncü Ay</t>
-        </is>
-      </c>
-      <c r="H29" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$29,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="50">
-      <c r="G30" s="115" t="inlineStr">
-        <is>
-          <t>Beşinci Ay</t>
-        </is>
-      </c>
-      <c r="H30" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$30,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="50">
-      <c r="G31" s="115" t="inlineStr">
-        <is>
-          <t>Altıncı Ay</t>
-        </is>
-      </c>
-      <c r="H31" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi+AYARLAR!$B$31,TAKSIT_PLANI!$D$6:$D$1000,"&lt;"&amp;RaporTarihi+AYARLAR!$B$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="50">
-      <c r="G32" s="114" t="inlineStr">
-        <is>
-          <t>Pencere</t>
-        </is>
-      </c>
-      <c r="H32" s="114" t="inlineStr">
-        <is>
-          <t>Ödeme</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="50">
-      <c r="G33" s="115" t="inlineStr">
-        <is>
-          <t>30 Gün</t>
-        </is>
-      </c>
-      <c r="H33" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi,TAKSIT_PLANI!$D$6:$D$1000,"&lt;="&amp;RaporTarihi+AYARLAR!$B$27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="50">
-      <c r="G34" s="115" t="inlineStr">
-        <is>
-          <t>60 Gün</t>
-        </is>
-      </c>
-      <c r="H34" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi,TAKSIT_PLANI!$D$6:$D$1000,"&lt;="&amp;RaporTarihi+AYARLAR!$B$28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="50">
-      <c r="G35" s="115" t="inlineStr">
-        <is>
-          <t>90 Gün</t>
-        </is>
-      </c>
-      <c r="H35" s="107">
-        <f>SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$D$6:$D$1000,"&gt;="&amp;RaporTarihi,TAKSIT_PLANI!$D$6:$D$1000,"&lt;="&amp;RaporTarihi+AYARLAR!$B$29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="50">
-      <c r="G37" s="114" t="inlineStr">
-        <is>
-          <t>Ürün Türü</t>
-        </is>
-      </c>
-      <c r="H37" s="114" t="inlineStr">
-        <is>
-          <t>Bakiye</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="50">
-      <c r="G38" s="115" t="inlineStr">
-        <is>
-          <t>Taksitli Ticari Kredi</t>
-        </is>
-      </c>
-      <c r="H38" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$D$6:$D$1000,"Taksitli Ticari Kredi")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="50">
-      <c r="G39" s="115" t="inlineStr">
-        <is>
-          <t>Leasing</t>
-        </is>
-      </c>
-      <c r="H39" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$D$6:$D$1000,"Leasing")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="50">
-      <c r="G40" s="115" t="inlineStr">
-        <is>
-          <t>Rotatif Kredi</t>
-        </is>
-      </c>
-      <c r="H40" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$D$6:$D$1000,"Rotatif Kredi")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="50">
-      <c r="G41" s="115" t="inlineStr">
-        <is>
-          <t>Spot Kredi</t>
-        </is>
-      </c>
-      <c r="H41" s="107">
-        <f>SUMIFS(KREDILER!$H$6:$H$1000,KREDILER!$D$6:$D$1000,"Spot Kredi")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="50">
-      <c r="G43" s="114" t="inlineStr">
-        <is>
-          <t>Masraf Türü</t>
-        </is>
-      </c>
-      <c r="H43" s="114" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="50">
-      <c r="G44" s="115" t="inlineStr">
-        <is>
-          <t>Tahsis Ücreti</t>
-        </is>
-      </c>
-      <c r="H44" s="107">
-        <f>SUMIFS(MASRAF_KOMISYON!$G$6:$G$1000,MASRAF_KOMISYON!$D$6:$D$1000,"Tahsis Ücreti")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="50">
-      <c r="G45" s="115" t="inlineStr">
-        <is>
-          <t>Sigorta</t>
-        </is>
-      </c>
-      <c r="H45" s="107">
-        <f>SUMIFS(MASRAF_KOMISYON!$G$6:$G$1000,MASRAF_KOMISYON!$D$6:$D$1000,"Sigorta")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="50">
-      <c r="G46" s="115" t="inlineStr">
-        <is>
-          <t>Komisyon</t>
-        </is>
-      </c>
-      <c r="H46" s="107">
-        <f>SUMIFS(MASRAF_KOMISYON!$G$6:$G$1000,MASRAF_KOMISYON!$D$6:$D$1000,"Komisyon")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="50">
-      <c r="G47" s="115" t="inlineStr">
-        <is>
-          <t>Diğer</t>
-        </is>
-      </c>
-      <c r="H47" s="107">
-        <f>SUMIFS(MASRAF_KOMISYON!$G$6:$G$1000,MASRAF_KOMISYON!$D$6:$D$1000,"Diğer")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="50">
-      <c r="G49" s="114" t="inlineStr">
-        <is>
-          <t>Teminat Türü</t>
-        </is>
-      </c>
-      <c r="H49" s="114" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="50">
-      <c r="G50" s="115" t="inlineStr">
-        <is>
-          <t>Gayrimenkul İpoteği</t>
-        </is>
-      </c>
-      <c r="H50" s="107">
-        <f>SUMIFS(TEMINATLAR!$F$6:$F$1000,TEMINATLAR!$D$6:$D$1000,"Gayrimenkul İpoteği")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="50">
-      <c r="G51" s="115" t="inlineStr">
-        <is>
-          <t>Taşıt Rehni</t>
-        </is>
-      </c>
-      <c r="H51" s="107">
-        <f>SUMIFS(TEMINATLAR!$F$6:$F$1000,TEMINATLAR!$D$6:$D$1000,"Taşıt Rehni")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="50">
-      <c r="G52" s="115" t="inlineStr">
-        <is>
-          <t>Alacak Temliki</t>
-        </is>
-      </c>
-      <c r="H52" s="107">
-        <f>SUMIFS(TEMINATLAR!$F$6:$F$1000,TEMINATLAR!$D$6:$D$1000,"Alacak Temliki")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="50">
-      <c r="G53" s="115" t="inlineStr">
-        <is>
-          <t>Diğer</t>
-        </is>
-      </c>
-      <c r="H53" s="107">
-        <f>SUMIFS(TEMINATLAR!$F$6:$F$1000,TEMINATLAR!$D$6:$D$1000,"Diğer")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
-    <mergeCell ref="D6:K7"/>
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>"İNCELE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>"DURDUR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" rank="0" priority="6" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
-      <formula>"DÜŞÜK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="7" equalAverage="0" operator="equal" aboveAverage="0" dxfId="19" text="" percent="0" bottom="0">
-      <formula>"ORTA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="8" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>"YÜKSEK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="9" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>"KRİTİK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" rank="0" priority="10" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" rank="0" priority="11" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader/>
-    <oddFooter>&amp;LBanka, Kredi ve Taksit Takip Sistemi — PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:AN19"/>
@@ -20182,253 +18355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" style="50" min="1" max="1"/>
-    <col width="30" customWidth="1" style="50" min="2" max="2"/>
-    <col width="18" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="12" customWidth="1" style="50" min="5" max="5"/>
-    <col width="12" customWidth="1" style="50" min="6" max="6"/>
-    <col width="35" customWidth="1" style="50" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="69" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="70" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="70" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="70" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="70" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="70" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="70" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="71" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="72" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="63" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="73" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="71" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="72" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="73" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="71" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="72" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="63" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="73" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="71" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="72" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="63" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="73" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="71" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="63" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="73" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="72" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="63" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="73" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20615,7 +18542,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" style="50" min="1" max="1"/>
+    <col width="14" customWidth="1" style="50" min="2" max="2"/>
+    <col width="16" customWidth="1" style="50" min="3" max="3"/>
+    <col width="32" customWidth="1" style="50" min="4" max="4"/>
+    <col width="18" customWidth="1" style="50" min="5" max="5"/>
+    <col width="12" customWidth="1" style="50" min="6" max="6"/>
+    <col width="18" customWidth="1" style="50" min="7" max="7"/>
+    <col width="22" customWidth="1" style="50" min="8" max="8"/>
+    <col width="16" customWidth="1" style="50" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="166" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="167" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="168" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="169" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="169" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="169" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="169" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="169" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="169" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="169" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="169" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="170" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="171" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="172" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="173" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="175">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="172" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="176" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="177" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="178" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="179" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="180" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="182">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="179" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="183" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="170" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="171" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="172" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="173" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="175">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="172" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="176" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="177" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="178" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="179" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="180" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="182">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="179" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="184" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="170" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="171" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="172" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="173" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="175">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="172" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="176" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="177" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="178" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="179" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="180" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="182">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="179" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="185" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="170" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="171" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="172" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="173" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="175">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="172" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="176" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="177" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="178" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="179" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="180" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="182">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="179" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="184" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="170" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="171" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="172" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="173" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="175">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="172" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="176" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="177" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="178" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="179" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="180" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="182">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="179" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="184" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="186" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="154" t="n"/>
+      <c r="D17" s="154" t="n"/>
+      <c r="E17" s="187">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="154" t="n"/>
+      <c r="G17" s="154" t="n"/>
+      <c r="H17" s="154" t="n"/>
+      <c r="I17" s="154" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20773,7 +19178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20941,7 +19346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21166,7 +19571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21239,7 +19644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21472,7 +19877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22472,7 +20877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22650,81 +21055,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="50" min="1" max="1"/>
-    <col width="25" customWidth="1" style="50" min="2" max="2"/>
-    <col width="20" customWidth="1" style="50" min="3" max="3"/>
-    <col width="20" customWidth="1" style="50" min="4" max="4"/>
-    <col width="15" customWidth="1" style="50" min="5" max="5"/>
-    <col width="25" customWidth="1" style="50" min="6" max="6"/>
-    <col width="15" customWidth="1" style="50" min="7" max="7"/>
-    <col width="15" customWidth="1" style="50" min="8" max="8"/>
+    <col width="3" customWidth="1" style="50" min="1" max="1"/>
+    <col width="24" customWidth="1" style="50" min="2" max="2"/>
+    <col width="15" customWidth="1" style="50" min="3" max="3"/>
+    <col width="15" customWidth="1" style="50" min="4" max="4"/>
+    <col width="22" customWidth="1" style="50" min="5" max="5"/>
+    <col width="6" customWidth="1" style="50" min="6" max="6"/>
+    <col width="6" customWidth="1" style="50" min="7" max="7"/>
+    <col width="24" customWidth="1" style="50" min="8" max="8"/>
+    <col width="15" customWidth="1" style="50" min="9" max="9"/>
+    <col width="15" customWidth="1" style="50" min="10" max="10"/>
+    <col width="22" customWidth="1" style="50" min="11" max="11"/>
+    <col width="6" customWidth="1" style="50" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="69" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="74" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="188" t="inlineStr">
+        <is>
+          <t>BANKA KREDI VE TAKSIT TAKIP SISTEMI — BORÇ VE LİKİDİTE SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="189" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="190" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="75" t="inlineStr">
-        <is>
-          <t>Borç servis karşılama oranı (DSCR 2.15) banka asgari şartı olan 1.25 seviyesinin oldukça üzerindedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="191" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="129" t="n"/>
+      <c r="D6" s="129" t="n"/>
+      <c r="E6" s="129" t="n"/>
+      <c r="F6" s="129" t="n"/>
+      <c r="H6" s="192" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="129" t="n"/>
+      <c r="J6" s="129" t="n"/>
+      <c r="K6" s="129" t="n"/>
+      <c r="L6" s="129" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="129" t="n"/>
+      <c r="C7" s="129" t="n"/>
+      <c r="D7" s="129" t="n"/>
+      <c r="E7" s="129" t="n"/>
+      <c r="F7" s="129" t="n"/>
+      <c r="H7" s="129" t="n"/>
+      <c r="I7" s="129" t="n"/>
+      <c r="J7" s="129" t="n"/>
+      <c r="K7" s="129" t="n"/>
+      <c r="L7" s="129" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="193" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="129" t="n"/>
+      <c r="D8" s="129" t="n"/>
+      <c r="E8" s="194" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="129" t="n"/>
+      <c r="H8" s="193" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="129" t="n"/>
+      <c r="J8" s="129" t="n"/>
+      <c r="K8" s="195" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="129" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="193" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="129" t="n"/>
+      <c r="D9" s="129" t="n"/>
+      <c r="E9" s="196" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="129" t="n"/>
+      <c r="H9" s="193" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="129" t="n"/>
+      <c r="J9" s="129" t="n"/>
+      <c r="K9" s="196" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="129" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="75" t="inlineStr">
-        <is>
-          <t>Faiz oranları 500 baz puan artsa dahi nakit akışı taksit ödemelerini karşılamaktadır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="193" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="129" t="n"/>
+      <c r="D10" s="129" t="n"/>
+      <c r="E10" s="197" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="129" t="n"/>
+      <c r="H10" s="193" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="129" t="n"/>
+      <c r="J10" s="129" t="n"/>
+      <c r="K10" s="197" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="129" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="193" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="129" t="n"/>
+      <c r="D11" s="129" t="n"/>
+      <c r="E11" s="197" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="129" t="n"/>
+      <c r="H11" s="193" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="129" t="n"/>
+      <c r="J11" s="129" t="n"/>
+      <c r="K11" s="197" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="129" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="129" t="n"/>
+      <c r="C12" s="129" t="n"/>
+      <c r="D12" s="129" t="n"/>
+      <c r="E12" s="129" t="n"/>
+      <c r="F12" s="129" t="n"/>
+      <c r="H12" s="129" t="n"/>
+      <c r="I12" s="129" t="n"/>
+      <c r="J12" s="129" t="n"/>
+      <c r="K12" s="129" t="n"/>
+      <c r="L12" s="129" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="74" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="129" t="n"/>
+      <c r="C13" s="129" t="n"/>
+      <c r="D13" s="129" t="n"/>
+      <c r="E13" s="129" t="n"/>
+      <c r="F13" s="129" t="n"/>
+      <c r="H13" s="129" t="n"/>
+      <c r="I13" s="129" t="n"/>
+      <c r="J13" s="129" t="n"/>
+      <c r="K13" s="129" t="n"/>
+      <c r="L13" s="129" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="198" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="129" t="n"/>
+      <c r="D14" s="129" t="n"/>
+      <c r="E14" s="129" t="n"/>
+      <c r="F14" s="129" t="n"/>
+      <c r="H14" s="199" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="129" t="n"/>
+      <c r="J14" s="129" t="n"/>
+      <c r="K14" s="129" t="n"/>
+      <c r="L14" s="129" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="71" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="71" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="129" t="n"/>
+      <c r="C15" s="129" t="n"/>
+      <c r="D15" s="129" t="n"/>
+      <c r="E15" s="129" t="n"/>
+      <c r="F15" s="129" t="n"/>
+      <c r="H15" s="129" t="n"/>
+      <c r="I15" s="129" t="n"/>
+      <c r="J15" s="129" t="n"/>
+      <c r="K15" s="129" t="n"/>
+      <c r="L15" s="129" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="156" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="156" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="156" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="156" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -109,13 +109,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="93">
     <font>
@@ -1251,7 +1252,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1834,6 +1835,24 @@
     </xf>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="52" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="56" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="59" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="78" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="75" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="75" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -19730,7 +19749,7 @@
     <col width="6" customWidth="1" style="50" min="7" max="7"/>
     <col width="24" customWidth="1" style="50" min="8" max="8"/>
     <col width="15" customWidth="1" style="50" min="9" max="9"/>
-    <col width="14" customWidth="1" style="50" min="10" max="10"/>
+    <col width="15" customWidth="1" style="50" min="10" max="10"/>
     <col width="12" customWidth="1" style="50" min="11" max="11"/>
     <col width="18" customWidth="1" style="50" min="12" max="12"/>
     <col width="18" customWidth="1" style="50" min="13" max="13"/>
@@ -19746,7 +19765,7 @@
     <row r="2">
       <c r="B2" s="124" t="inlineStr">
         <is>
-          <t>BANKA KREDI VE TAKSIT TAKIP SISTEMI — BORÇ VE LİKİDİTE SİSTEMİ</t>
+          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI</t>
         </is>
       </c>
       <c r="L2" s="125" t="inlineStr">
@@ -19763,7 +19782,7 @@
     <row r="3">
       <c r="B3" s="127" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: KOBİ sahipleri, finans yöneticileri, kredi kullanan işletmeler, muhasebe sorumluları · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -19781,7 +19800,7 @@
       </c>
       <c r="E5" s="131" t="inlineStr">
         <is>
-          <t>BU AY ÖDENECEK TAKSİT</t>
+          <t>AYLIK TAKSİT YÜKÜ</t>
         </is>
       </c>
       <c r="F5" s="129" t="n"/>
@@ -19828,31 +19847,27 @@
       <c r="M6" s="129" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="138" t="inlineStr">
-        <is>
-          <t>₺18.640.000</t>
-        </is>
+      <c r="B7" s="225">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="129" t="n"/>
       <c r="D7" s="129" t="n"/>
-      <c r="E7" s="139" t="inlineStr">
-        <is>
-          <t>₺1.120.000</t>
-        </is>
+      <c r="E7" s="226">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="129" t="n"/>
       <c r="G7" s="129" t="n"/>
-      <c r="H7" s="138" t="inlineStr">
-        <is>
-          <t>₺9.500.000</t>
-        </is>
+      <c r="H7" s="225">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="129" t="n"/>
       <c r="J7" s="129" t="n"/>
-      <c r="K7" s="140" t="inlineStr">
-        <is>
-          <t>1.95x</t>
-        </is>
+      <c r="K7" s="140">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="129" t="n"/>
       <c r="M7" s="129" t="n"/>
@@ -19874,28 +19889,28 @@
     <row r="9">
       <c r="B9" s="141" t="inlineStr">
         <is>
-          <t>↑ Ağırlıklı Ortalama Vade: 28 Ay</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="129" t="n"/>
       <c r="D9" s="129" t="n"/>
       <c r="E9" s="142" t="inlineStr">
         <is>
-          <t>● Anapara + Faiz Karşılığı Ayrıldı</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="129" t="n"/>
       <c r="G9" s="129" t="n"/>
       <c r="H9" s="141" t="inlineStr">
         <is>
-          <t>████████░░░░░░░ %42.0 REZERV</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="129" t="n"/>
       <c r="J9" s="129" t="n"/>
       <c r="K9" s="143" t="inlineStr">
         <is>
-          <t>✓ BANKA COVENANT UYUMLU</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="129" t="n"/>
@@ -19904,7 +19919,7 @@
     <row r="11">
       <c r="B11" s="74" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="144" t="inlineStr">
@@ -19921,7 +19936,7 @@
     <row r="12">
       <c r="B12" s="73" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="73" t="inlineStr">
@@ -19994,18 +20009,16 @@
       </c>
       <c r="H15" s="147" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="147" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="148" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="227">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="228">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="149" t="inlineStr">
         <is>
@@ -20035,18 +20048,16 @@
       </c>
       <c r="H16" s="147" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="147" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="148" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="227">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="228">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="149" t="inlineStr">
         <is>
@@ -20076,18 +20087,16 @@
       </c>
       <c r="H17" s="147" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="147" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="148" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="227">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="228">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="149" t="inlineStr">
         <is>
@@ -20117,18 +20126,16 @@
       </c>
       <c r="H18" s="147" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="147" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="148" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="227">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="228">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="149" t="inlineStr">
         <is>
@@ -20161,15 +20168,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="152" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="153" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="229">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="230">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="154" t="inlineStr"/>
       <c r="L19" s="155" t="inlineStr">
@@ -20231,7 +20236,7 @@
       </c>
       <c r="K23" s="160" t="inlineStr">
         <is>
-          <t>FAİZ VE YENİDEN YAPILANDIRMA FIRSATI</t>
+          <t>REVERSED REFINANSING FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="158" t="n"/>
@@ -20255,7 +20260,7 @@
       </c>
       <c r="K24" s="161" t="inlineStr">
         <is>
-          <t>Yüksek faizli rotatif kredilerin uzun vadeli yatırıma dönüştürülmesi önerilmektedir.</t>
+          <t>Kredi maliyetini düşürmek için uzun vadeli yapılandırma önerilmektedir.</t>
         </is>
       </c>
     </row>
@@ -23789,7 +23794,7 @@
     <row r="3">
       <c r="B3" s="166" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  BANKA, KREDI VE TAKSIT TAKIP SISTEMI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="167" t="inlineStr">
@@ -23858,10 +23863,10 @@
       </c>
       <c r="D6" s="172" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="173" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="231" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="174" t="n">
@@ -23895,10 +23900,10 @@
       </c>
       <c r="D7" s="179" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="180" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="231" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="181" t="n">
@@ -23932,10 +23937,10 @@
       </c>
       <c r="D8" s="172" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="173" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="231" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="174" t="n">
@@ -23969,10 +23974,10 @@
       </c>
       <c r="D9" s="179" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="180" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="231" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="181" t="n">
@@ -24006,10 +24011,10 @@
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="173" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="231" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="174" t="n">
@@ -24043,10 +24048,10 @@
       </c>
       <c r="D11" s="179" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="180" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="231" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="181" t="n">
@@ -24058,7 +24063,7 @@
       </c>
       <c r="H11" s="179" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="185" t="inlineStr">
@@ -24080,10 +24085,10 @@
       </c>
       <c r="D12" s="172" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="173" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="231" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="174" t="n">
@@ -24095,7 +24100,7 @@
       </c>
       <c r="H12" s="172" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="176" t="inlineStr">
@@ -24117,10 +24122,10 @@
       </c>
       <c r="D13" s="179" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="180" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="231" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="181" t="n">
@@ -24154,10 +24159,10 @@
       </c>
       <c r="D14" s="172" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="173" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="231" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="174" t="n">
@@ -24191,10 +24196,10 @@
       </c>
       <c r="D15" s="179" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="180" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="231" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="181" t="n">
@@ -25683,14 +25688,14 @@
     <row r="2">
       <c r="B2" s="188" t="inlineStr">
         <is>
-          <t>BANKA KREDI VE TAKSIT TAKIP SISTEMI — BORÇ VE LİKİDİTE SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="189" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, finans yöneticileri, kredi kullanan işletmeler, muhasebe sorumluları</t>
         </is>
       </c>
     </row>
@@ -25769,10 +25774,9 @@
       </c>
       <c r="C9" s="129" t="n"/>
       <c r="D9" s="129" t="n"/>
-      <c r="E9" s="196" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="232">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="129" t="n"/>
       <c r="H9" s="193" t="inlineStr">
@@ -25782,10 +25786,9 @@
       </c>
       <c r="I9" s="129" t="n"/>
       <c r="J9" s="129" t="n"/>
-      <c r="K9" s="196" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="232">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="129" t="n"/>
     </row>
@@ -25797,10 +25800,9 @@
       </c>
       <c r="C10" s="129" t="n"/>
       <c r="D10" s="129" t="n"/>
-      <c r="E10" s="197" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="233">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="129" t="n"/>
       <c r="H10" s="193" t="inlineStr">
@@ -25810,10 +25812,9 @@
       </c>
       <c r="I10" s="129" t="n"/>
       <c r="J10" s="129" t="n"/>
-      <c r="K10" s="197" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="233">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="129" t="n"/>
     </row>
@@ -25825,10 +25826,9 @@
       </c>
       <c r="C11" s="129" t="n"/>
       <c r="D11" s="129" t="n"/>
-      <c r="E11" s="197" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="234">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="129" t="n"/>
       <c r="H11" s="193" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -7,38 +7,38 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="AylikBorcServisi" hidden="0" function="0" vbProcedure="0">KARAR_MOTORU!$B$6</definedName>
@@ -101,7 +101,7 @@
     <definedName name="VeriKaliteYuksek" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$21</definedName>
     <definedName name="YillikDovizGeliri" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$17</definedName>
     <definedName name="YillikFaaliyetKari" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="24">'RAPOR'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'RAPOR'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -118,7 +118,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="93">
+  <fonts count="106">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -691,6 +691,81 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0060A5FA"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1252,7 +1327,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1853,6 +1928,122 @@
     </xf>
     <xf numFmtId="170" fontId="75" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="98" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="99" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="77" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="67" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="67" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="102" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="77" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="77" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="77" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="77" fillId="9" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -12450,381 +12641,762 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFC6A15B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="B2:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="50" min="1" max="1"/>
-    <col width="78" customWidth="1" style="50" min="2" max="2"/>
+    <col width="4" customWidth="1" style="50" min="1" max="1"/>
+    <col width="4" customWidth="1" style="50" min="2" max="2"/>
+    <col width="14" customWidth="1" style="50" min="3" max="3"/>
+    <col width="14" customWidth="1" style="50" min="4" max="4"/>
+    <col width="14" customWidth="1" style="50" min="5" max="5"/>
+    <col width="4" customWidth="1" style="50" min="6" max="6"/>
+    <col width="4" customWidth="1" style="50" min="7" max="7"/>
+    <col width="4" customWidth="1" style="50" min="8" max="8"/>
+    <col width="14" customWidth="1" style="50" min="9" max="9"/>
+    <col width="14" customWidth="1" style="50" min="10" max="10"/>
+    <col width="14" customWidth="1" style="50" min="11" max="11"/>
+    <col width="4" customWidth="1" style="50" min="12" max="12"/>
+    <col width="4" customWidth="1" style="50" min="13" max="13"/>
+    <col width="4" customWidth="1" style="50" min="14" max="14"/>
+    <col width="14" customWidth="1" style="50" min="15" max="15"/>
+    <col width="14" customWidth="1" style="50" min="16" max="16"/>
+    <col width="14" customWidth="1" style="50" min="17" max="17"/>
+    <col width="4" customWidth="1" style="50" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1" s="50"/>
+    <row r="2" ht="42" customHeight="1" s="50">
+      <c r="B2" s="235" t="inlineStr">
+        <is>
+          <t>KULLANIM KILAVUZU &amp; SİSTEM BAŞLANGICI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1" s="50"/>
+    <row r="4" ht="20" customHeight="1" s="50">
+      <c r="B4" s="236" t="inlineStr">
+        <is>
+          <t>Banka, Kredi ve Taksit Takip Sistemi — C-Level Borç Portföyü ve Likidite Karar Kokpiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="50">
+      <c r="B5" s="237" t="inlineStr">
+        <is>
+          <t>Hedef Kitle: KOBİ Sahipleri, CFO, Finans Direktörleri ve Hazine Yöneticileri · VUK 185-198 &amp; TTK 64 Tam Uyumlu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="10" customHeight="1" s="50">
+      <c r="C6" s="238" t="n"/>
+      <c r="D6" s="238" t="n"/>
+      <c r="E6" s="238" t="n"/>
+      <c r="I6" s="238" t="n"/>
+      <c r="J6" s="238" t="n"/>
+      <c r="K6" s="238" t="n"/>
+      <c r="O6" s="238" t="n"/>
+      <c r="P6" s="238" t="n"/>
+      <c r="Q6" s="238" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" s="50">
+      <c r="C7" s="239" t="inlineStr">
+        <is>
+          <t>EĞİTİM VE SİSTEM MİMARİSİ</t>
+        </is>
+      </c>
+      <c r="D7" s="238" t="n"/>
+      <c r="E7" s="238" t="n"/>
+      <c r="I7" s="239" t="inlineStr">
+        <is>
+          <t>VERİ GİRİŞİ &amp; ENTEGRASYON</t>
+        </is>
+      </c>
+      <c r="J7" s="238" t="n"/>
+      <c r="K7" s="238" t="n"/>
+      <c r="O7" s="239" t="inlineStr">
+        <is>
+          <t>YÖNETİM &amp; STRES TESTİ</t>
+        </is>
+      </c>
+      <c r="P7" s="238" t="n"/>
+      <c r="Q7" s="238" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1" s="50">
+      <c r="C8" s="238" t="n"/>
+      <c r="D8" s="238" t="n"/>
+      <c r="E8" s="238" t="n"/>
+      <c r="I8" s="238" t="n"/>
+      <c r="J8" s="238" t="n"/>
+      <c r="K8" s="238" t="n"/>
+      <c r="O8" s="238" t="n"/>
+      <c r="P8" s="238" t="n"/>
+      <c r="Q8" s="238" t="n"/>
+    </row>
+    <row r="9" ht="70" customHeight="1" s="50">
+      <c r="C9" s="240" t="inlineStr">
+        <is>
+          <t>Bu sistem; banka kredi limitlerinizi, yaklaşan taksitlerinizi, nakit akış baskısını ve refinansman (borç yapılandırma) avantajlarını tek merkezden yönetmek üzere tasarlanmıştır. Tüm formüller canlıdır.</t>
+        </is>
+      </c>
+      <c r="D9" s="129" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="I9" s="240" t="inlineStr">
+        <is>
+          <t>Girişler sekmesinden veya BANKALAR, LIMITLER, KREDILER sayfalarından portföyünüzü tanımlayın. TAKSIT_PLANI üzerinden nakit akışını izleyin. Sarı dolgulu alanlar kullanıcı girdisidir.</t>
+        </is>
+      </c>
+      <c r="J9" s="129" t="n"/>
+      <c r="K9" s="129" t="n"/>
+      <c r="O9" s="240" t="inlineStr">
+        <is>
+          <t>YÖNETİM_RAPORU sayfası; kur şokları, faiz artışları ve -%20 nakit akışı stres senaryolarında borçlanma sürdürülebilirliğini ve refinansman XIRR kazançlarını otomatik modeller.</t>
+        </is>
+      </c>
+      <c r="P9" s="129" t="n"/>
+      <c r="Q9" s="129" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="129" t="n"/>
+      <c r="D10" s="129" t="n"/>
+      <c r="E10" s="129" t="n"/>
+      <c r="I10" s="129" t="n"/>
+      <c r="J10" s="129" t="n"/>
+      <c r="K10" s="129" t="n"/>
+      <c r="O10" s="129" t="n"/>
+      <c r="P10" s="129" t="n"/>
+      <c r="Q10" s="129" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="129" t="n"/>
+      <c r="D11" s="129" t="n"/>
+      <c r="E11" s="129" t="n"/>
+      <c r="I11" s="129" t="n"/>
+      <c r="J11" s="129" t="n"/>
+      <c r="K11" s="129" t="n"/>
+      <c r="O11" s="129" t="n"/>
+      <c r="P11" s="129" t="n"/>
+      <c r="Q11" s="129" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="129" t="n"/>
+      <c r="D12" s="129" t="n"/>
+      <c r="E12" s="129" t="n"/>
+      <c r="I12" s="129" t="n"/>
+      <c r="J12" s="129" t="n"/>
+      <c r="K12" s="129" t="n"/>
+      <c r="O12" s="129" t="n"/>
+      <c r="P12" s="129" t="n"/>
+      <c r="Q12" s="129" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="50">
+      <c r="C13" s="241" t="inlineStr">
+        <is>
+          <t>▶ CANLI KOKPİTE GİT (#PANO!A1)</t>
+        </is>
+      </c>
+      <c r="D13" s="129" t="n"/>
+      <c r="E13" s="129" t="n"/>
+      <c r="I13" s="241" t="inlineStr">
+        <is>
+          <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
+        </is>
+      </c>
+      <c r="J13" s="129" t="n"/>
+      <c r="K13" s="129" t="n"/>
+      <c r="O13" s="241" t="inlineStr">
+        <is>
+          <t>📊 YÖNETİM RAPORUNU AÇ (#YÖNETİM_RAPORU!A1)</t>
+        </is>
+      </c>
+      <c r="P13" s="129" t="n"/>
+      <c r="Q13" s="129" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="C9:E12"/>
+    <mergeCell ref="I9:K12"/>
+    <mergeCell ref="O9:Q12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF5B477E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="50" min="1" max="1"/>
+    <col width="32" customWidth="1" style="50" min="2" max="2"/>
+    <col width="54" customWidth="1" style="50" min="3" max="3"/>
+    <col width="34" customWidth="1" style="50" min="4" max="4"/>
+    <col width="16" customWidth="1" style="50" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
+      <c r="A1" s="221" t="inlineStr">
+        <is>
+          <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="50">
-      <c r="A3" s="202" t="inlineStr">
-        <is>
-          <t>Konu</t>
-        </is>
-      </c>
-      <c r="B3" s="202" t="inlineStr">
-        <is>
-          <t>Bağlayıcı Standart</t>
+      <c r="A3" s="222" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="B3" s="222" t="inlineStr">
+        <is>
+          <t>Müşteri Sorusu</t>
+        </is>
+      </c>
+      <c r="C3" s="222" t="inlineStr">
+        <is>
+          <t>Zorunlu Ürün Davranışı</t>
+        </is>
+      </c>
+      <c r="D3" s="222" t="inlineStr">
+        <is>
+          <t>Kanıt</t>
+        </is>
+      </c>
+      <c r="E3" s="222" t="inlineStr">
+        <is>
+          <t>Başarısızlık Durumu</t>
+        </is>
+      </c>
+      <c r="F3" s="222" t="inlineStr">
+        <is>
+          <t>Kapı</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="203" t="inlineStr">
-        <is>
-          <t>Amaç</t>
+      <c r="A4" s="223" t="inlineStr">
+        <is>
+          <t>5 saniye</t>
         </is>
       </c>
       <c r="B4" s="204" t="inlineStr">
         <is>
-          <t>Kanıta dayalı, hatada kapalı çalışan Excel üretim ve denetim sistemi</t>
+          <t>Bu ürün neyi çözüyor?</t>
+        </is>
+      </c>
+      <c r="C4" s="204" t="inlineStr">
+        <is>
+          <t>İlk ekranda hedef kullanıcı + pahalı problem + sonuç görünür</t>
+        </is>
+      </c>
+      <c r="D4" s="204" t="inlineStr">
+        <is>
+          <t>Başlık + alt mesaj + gerçek ekran</t>
+        </is>
+      </c>
+      <c r="E4" s="204" t="inlineStr">
+        <is>
+          <t>Ürün yalnız teknik isim</t>
+        </is>
+      </c>
+      <c r="F4" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="203" t="inlineStr">
-        <is>
-          <t>Öncelik</t>
+      <c r="A5" s="223" t="inlineStr">
+        <is>
+          <t>Acı</t>
         </is>
       </c>
       <c r="B5" s="204" t="inlineStr">
         <is>
-          <t>Kullanıcının açık iş talebi ve gerçek kullanım senaryosu</t>
+          <t>Sorun bana neye mal oluyor?</t>
+        </is>
+      </c>
+      <c r="C5" s="204" t="inlineStr">
+        <is>
+          <t>Mümkünse müşterinin kendi verisiyle parasal/zaman etkisi hesaplanır</t>
+        </is>
+      </c>
+      <c r="D5" s="204" t="inlineStr">
+        <is>
+          <t>ROI/acı hesaplama yöntemi</t>
+        </is>
+      </c>
+      <c r="E5" s="204" t="inlineStr">
+        <is>
+          <t>Uydurma tasarruf</t>
+        </is>
+      </c>
+      <c r="F5" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="203" t="inlineStr">
-        <is>
-          <t>Ana akış</t>
+      <c r="A6" s="223" t="inlineStr">
+        <is>
+          <t>Karar</t>
         </is>
       </c>
       <c r="B6" s="204" t="inlineStr">
         <is>
-          <t>Uygunluk → Yönetişim → Sözleşmeler → Üretim → Test → Kanıt → Kullanıcı Kabulü → Yayın</t>
+          <t>Bu bilgiyle ne yapacağım?</t>
+        </is>
+      </c>
+      <c r="C6" s="204" t="inlineStr">
+        <is>
+          <t>Her kritik KPI aksiyona bağlanır</t>
+        </is>
+      </c>
+      <c r="D6" s="204" t="inlineStr">
+        <is>
+          <t>KARAR_KUYRUGU</t>
+        </is>
+      </c>
+      <c r="E6" s="204" t="inlineStr">
+        <is>
+          <t>Sadece rapor</t>
+        </is>
+      </c>
+      <c r="F6" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="203" t="inlineStr">
-        <is>
-          <t>Yayın ilkesi</t>
+      <c r="A7" s="223" t="inlineStr">
+        <is>
+          <t>Güven</t>
         </is>
       </c>
       <c r="B7" s="204" t="inlineStr">
         <is>
-          <t>Üst aşamada hata varsa alt aşama GEÇTİ üretilemez</t>
+          <t>Bu sayıya neden inanayım?</t>
+        </is>
+      </c>
+      <c r="C7" s="204" t="inlineStr">
+        <is>
+          <t>Kaynak, formül mantığı, kontrol ve son doğrulama görünür</t>
+        </is>
+      </c>
+      <c r="D7" s="204" t="inlineStr">
+        <is>
+          <t>Kontroller + kaynak izi + sürüm</t>
+        </is>
+      </c>
+      <c r="E7" s="204" t="inlineStr">
+        <is>
+          <t>Prestij kelimesi</t>
+        </is>
+      </c>
+      <c r="F7" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="203" t="inlineStr">
-        <is>
-          <t>Kullanıcı kabulü</t>
+      <c r="A8" s="223" t="inlineStr">
+        <is>
+          <t>Referans</t>
         </is>
       </c>
       <c r="B8" s="204" t="inlineStr">
         <is>
-          <t>Excel masaüstü görünümü test edilmediyse DIŞ_KABUL_GEREKLİ</t>
+          <t>Müşteri yorumu yoksa ne göstereceğim?</t>
+        </is>
+      </c>
+      <c r="C8" s="204" t="inlineStr">
+        <is>
+          <t>Önce/Sonra + Karar Vakası + Hata Önleme Vakası üretilir</t>
+        </is>
+      </c>
+      <c r="D8" s="204" t="inlineStr">
+        <is>
+          <t>Demo/örnek çıktı</t>
+        </is>
+      </c>
+      <c r="E8" s="204" t="inlineStr">
+        <is>
+          <t>Kanıtsız iddia</t>
+        </is>
+      </c>
+      <c r="F8" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="203" t="inlineStr">
-        <is>
-          <t>Nihai yayın</t>
+      <c r="A9" s="223" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
         </is>
       </c>
       <c r="B9" s="204" t="inlineStr">
         <is>
-          <t>Yalnız uygulanabilir modüller GEÇTİ veya gerekçeli UYGULANMAZ</t>
+          <t>Ne olursa işler bozulur?</t>
+        </is>
+      </c>
+      <c r="C9" s="204" t="inlineStr">
+        <is>
+          <t>Baz/Aşağı/Yukarı veya uygun stres senaryosu</t>
+        </is>
+      </c>
+      <c r="D9" s="204" t="inlineStr">
+        <is>
+          <t>Senaryo karşılaştırma</t>
+        </is>
+      </c>
+      <c r="E9" s="204" t="inlineStr">
+        <is>
+          <t>Dekoratif senaryo</t>
+        </is>
+      </c>
+      <c r="F9" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="203" t="inlineStr">
-        <is>
-          <t>Ticari ayrım</t>
+      <c r="A10" s="223" t="inlineStr">
+        <is>
+          <t>Ters stres</t>
         </is>
       </c>
       <c r="B10" s="204" t="inlineStr">
         <is>
-          <t>Ekonomik olarak savunulabilir fiyat, gerçek pazar kabulü ile aynı değildir</t>
+          <t>Hangi eşikte karar kırılır?</t>
+        </is>
+      </c>
+      <c r="C10" s="204" t="inlineStr">
+        <is>
+          <t>En az bir kritik sürücü için kırılma eşiği</t>
+        </is>
+      </c>
+      <c r="D10" s="204" t="inlineStr">
+        <is>
+          <t>Kırılma eşiği tablosu</t>
+        </is>
+      </c>
+      <c r="E10" s="204" t="inlineStr">
+        <is>
+          <t>Sadece +/- %10</t>
+        </is>
+      </c>
+      <c r="F10" s="224" t="inlineStr">
+        <is>
+          <t>UYARI/HATA</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="203" t="inlineStr">
-        <is>
-          <t>Karmaşıklık</t>
+      <c r="A11" s="223" t="inlineStr">
+        <is>
+          <t>Hata tutarlılığı</t>
         </is>
       </c>
       <c r="B11" s="204" t="inlineStr">
         <is>
-          <t>Karar değeri, eklenen karmaşıklığın maliyetinden büyük olmalıdır</t>
+          <t>Formül hata verirse ne olur?</t>
+        </is>
+      </c>
+      <c r="C11" s="204" t="inlineStr">
+        <is>
+          <t>Kontrol GEÇTİ veremez; BLOKE/HATA üretir</t>
+        </is>
+      </c>
+      <c r="D11" s="204" t="inlineStr">
+        <is>
+          <t>Hata taraması</t>
+        </is>
+      </c>
+      <c r="E11" s="204" t="inlineStr">
+        <is>
+          <t>Hata + GEÇTİ birlikte</t>
+        </is>
+      </c>
+      <c r="F11" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="203" t="inlineStr">
-        <is>
-          <t>Excel sınırı</t>
+      <c r="A12" s="223" t="inlineStr">
+        <is>
+          <t>Karar motoru</t>
         </is>
       </c>
       <c r="B12" s="204" t="inlineStr">
         <is>
-          <t>Veritabanı, kurumsal yetkilendirme, değiştirilemez kayıt sistemi veya gerçek zamanlı olay platformu değildir</t>
+          <t>Ne oldu, neden oldu?</t>
+        </is>
+      </c>
+      <c r="C12" s="204" t="inlineStr">
+        <is>
+          <t>Sorun + neden + parasal etki + aksiyon + son tarih</t>
+        </is>
+      </c>
+      <c r="D12" s="204" t="inlineStr">
+        <is>
+          <t>Karar tablosu</t>
+        </is>
+      </c>
+      <c r="E12" s="204" t="inlineStr">
+        <is>
+          <t>Boş sayfa / isim düzeyi modül</t>
+        </is>
+      </c>
+      <c r="F12" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="203" t="inlineStr">
-        <is>
-          <t>Dil standardı</t>
+      <c r="A13" s="223" t="inlineStr">
+        <is>
+          <t>Yönetici özeti</t>
         </is>
       </c>
       <c r="B13" s="204" t="inlineStr">
         <is>
-          <t>Kullanıcıya görünen tüm sayfa, tablo, başlık, açıklama, uyarı ve karar metinleri saf Türkçe olmalıdır</t>
+          <t>5 saniyede ne görmeliyim?</t>
+        </is>
+      </c>
+      <c r="C13" s="204" t="inlineStr">
+        <is>
+          <t>Bugün / ne değişti / ne bozulacak / neden / ne yapmalıyım / güven</t>
+        </is>
+      </c>
+      <c r="D13" s="204" t="inlineStr">
+        <is>
+          <t>Yönetici özeti ekranı</t>
+        </is>
+      </c>
+      <c r="E13" s="204" t="inlineStr">
+        <is>
+          <t>KPI kutusu yığını</t>
+        </is>
+      </c>
+      <c r="F13" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="203" t="inlineStr">
-        <is>
-          <t>Muhasebe standardı</t>
+      <c r="A14" s="223" t="inlineStr">
+        <is>
+          <t>Teklif</t>
         </is>
       </c>
       <c r="B14" s="204" t="inlineStr">
         <is>
-          <t>Finansal ürünlerde Türkiye Tekdüzen Hesap Planı ve Türk muhasebe kullanım alışkanlıkları esas alınır</t>
+          <t>Neden satın almalıyım?</t>
+        </is>
+      </c>
+      <c r="C14" s="204" t="inlineStr">
+        <is>
+          <t>Dosya özellikleri yerine sonuç ve kaçınılan maliyet sunulur</t>
+        </is>
+      </c>
+      <c r="D14" s="204" t="inlineStr">
+        <is>
+          <t>Ürün sayfası kanıt eşlemesi</t>
+        </is>
+      </c>
+      <c r="E14" s="204" t="inlineStr">
+        <is>
+          <t>Özellik listesiyle satış</t>
+        </is>
+      </c>
+      <c r="F14" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="203" t="inlineStr">
-        <is>
-          <t>Görsel standart</t>
+      <c r="A15" s="223" t="inlineStr">
+        <is>
+          <t>Dağıtım</t>
         </is>
       </c>
       <c r="B15" s="204" t="inlineStr">
         <is>
-          <t>Her sayfa başlıklı, renk kodlu, sıkı kolon düzenli ve premium kurumsal görünümde olmalıdır</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="203" t="inlineStr">
-        <is>
-          <t>Grafik standardı</t>
+          <t>Beni nasıl bulacaklar?</t>
+        </is>
+      </c>
+      <c r="C15" s="204" t="inlineStr">
+        <is>
+          <t>Sorun niyetine göre SEO sayfaları, iç bağlantı, temiz yapı, taranabilir metin</t>
+        </is>
+      </c>
+      <c r="D15" s="204" t="inlineStr">
+        <is>
+          <t>Arama niyeti haritası</t>
+        </is>
+      </c>
+      <c r="E15" s="204" t="inlineStr">
+        <is>
+          <t>Tek ürün sayfasına bağımlılık</t>
+        </is>
+      </c>
+      <c r="F15" s="224" t="inlineStr">
+        <is>
+          <t>UYARI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="50">
+      <c r="A16" s="223" t="inlineStr">
+        <is>
+          <t>LLM görünürlüğü</t>
         </is>
       </c>
       <c r="B16" s="204" t="inlineStr">
         <is>
-          <t>Grafikler karar üretmeli; dekoratif, 3B, anlamsız renkli veya varsayılan Excel grafiği kullanılamaz</t>
+          <t>AI ürünümü anlayabiliyor mu?</t>
+        </is>
+      </c>
+      <c r="C16" s="204" t="inlineStr">
+        <is>
+          <t>Ürün tanımı, hedef kullanıcı, girdi/çıktı, metodoloji, sınırlar, SSS açık metindir</t>
+        </is>
+      </c>
+      <c r="D16" s="204" t="inlineStr">
+        <is>
+          <t>Taranabilir ürün içeriği</t>
+        </is>
+      </c>
+      <c r="E16" s="204" t="inlineStr">
+        <is>
+          <t>'AI SEO' iddiası</t>
+        </is>
+      </c>
+      <c r="F16" s="224" t="inlineStr">
+        <is>
+          <t>UYARI</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="203" t="inlineStr">
-        <is>
-          <t>Hata standardı</t>
+      <c r="A17" s="223" t="inlineStr">
+        <is>
+          <t>Satış kanalı</t>
         </is>
       </c>
       <c r="B17" s="204" t="inlineStr">
         <is>
-          <t>#AD? / #BAŞV! / #DEĞER! / #SAYI/0! / #YOK gibi hatalar GEÇTİ sonucuyla birlikte bulunamaz</t>
+          <t>Nerede satılmalı?</t>
+        </is>
+      </c>
+      <c r="C17" s="204" t="inlineStr">
+        <is>
+          <t>Arama, LinkedIn, uzman/partner, demo/video; ürüne göre kanal seçilir</t>
+        </is>
+      </c>
+      <c r="D17" s="204" t="inlineStr">
+        <is>
+          <t>Kanal matrisi</t>
+        </is>
+      </c>
+      <c r="E17" s="204" t="inlineStr">
+        <is>
+          <t>Her ürüne aynı kanal</t>
+        </is>
+      </c>
+      <c r="F17" s="224" t="inlineStr">
+        <is>
+          <t>UYARI</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="203" t="inlineStr">
-        <is>
-          <t>Karar standardı</t>
+      <c r="A18" s="223" t="inlineStr">
+        <is>
+          <t>Fiyat</t>
         </is>
       </c>
       <c r="B18" s="204" t="inlineStr">
         <is>
-          <t>Her kritik çıktı: ne oldu, neden oldu, parasal etki, ne yapılmalı, ne zamana kadar sorularını cevaplar</t>
+          <t>Bu fiyat neden mantıklı?</t>
+        </is>
+      </c>
+      <c r="C18" s="204" t="inlineStr">
+        <is>
+          <t>Fiyat, ekonomik karar değerine ve kanıtlanmış ürün derinliğine bağlanır</t>
+        </is>
+      </c>
+      <c r="D18" s="204" t="inlineStr">
+        <is>
+          <t>Değer haritası + demo</t>
+        </is>
+      </c>
+      <c r="E18" s="204" t="inlineStr">
+        <is>
+          <t>Sırf sayfa/formül sayısı</t>
+        </is>
+      </c>
+      <c r="F18" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="203" t="inlineStr">
-        <is>
-          <t>Satış standardı</t>
+      <c r="A19" s="223" t="inlineStr">
+        <is>
+          <t>Pazar kanıtı</t>
         </is>
       </c>
       <c r="B19" s="204" t="inlineStr">
         <is>
-          <t>Ürün 5 saniyede anlaşılmalı; pahalı problemi, ekonomik sonucu, kanıtı ve satın alma gerekçesini göstermelidir</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="203" t="inlineStr">
-        <is>
-          <t>Güven standardı</t>
-        </is>
-      </c>
-      <c r="B20" s="204" t="inlineStr">
-        <is>
-          <t>Kanıtsız 'premium', 'kusursuz', 'sıfır hata' veya yüksek fiyat iddiası kullanılamaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="203" t="inlineStr">
-        <is>
-          <t>Kaynak</t>
-        </is>
-      </c>
-      <c r="B21" s="204" t="inlineStr">
-        <is>
-          <t>Teknik Python çekirdeği 99_TEKNIK_KAYNAK sayfasında saklanır; kullanıcı arayüzü değildir</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="203" t="inlineStr">
-        <is>
-          <t>Bağlayıcı standart</t>
-        </is>
-      </c>
-      <c r="B22" s="204" t="inlineStr">
-        <is>
-          <t>Teknik kaynak içindeki üretim sözleşmesi + bu çalışma kitabındaki Türkçe operasyon standartları</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="203" t="inlineStr">
-        <is>
-          <t>Çıktı disiplini</t>
-        </is>
-      </c>
-      <c r="B23" s="204" t="inlineStr">
-        <is>
-          <t>Kanıtsız GEÇTİ / NİHAİ / TİCARİ / PAZAR_DOĞRULANDI statüsü yasaktır</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="203" t="inlineStr">
-        <is>
-          <t>Uyarlanabilirlik</t>
-        </is>
-      </c>
-      <c r="B24" s="204" t="inlineStr">
-        <is>
-          <t>Gereksiz modül yalnız prestij amacıyla eklenmez</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1" s="50">
-      <c r="A26" s="205" t="inlineStr">
-        <is>
-          <t>TEK KAYNAK MİMARİSİ</t>
-        </is>
-      </c>
-      <c r="B26" s="205" t="inlineStr">
-        <is>
-          <t>İKİ DOSYALI / TEK SİSTEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" s="50">
-      <c r="A27" s="204" t="inlineStr">
-        <is>
-          <t>MASTER Excel</t>
-        </is>
-      </c>
-      <c r="B27" s="204" t="inlineStr">
-        <is>
-          <t>EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART.xlsx — tüm mandate, modül sözleşmeleri, Türkçe tasarım, THP, test, ticari ve release standartları.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" s="50">
-      <c r="A28" s="204" t="inlineStr">
-        <is>
-          <t>Runtime Python</t>
-        </is>
-      </c>
-      <c r="B28" s="204" t="inlineStr">
-        <is>
-          <t>EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py — yürütülebilir kernel, verifier, OOXML scan, commercial gate ve pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="204" t="inlineStr">
-        <is>
-          <t>Python SHA-256</t>
-        </is>
-      </c>
-      <c r="B29" s="204" t="inlineStr">
-        <is>
-          <t>babe066ab599199123e53d01944bcd9d75648a579ade69ab9303dd675962f481</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="204" t="inlineStr">
-        <is>
-          <t>Sürüm Eşleşmesi</t>
-        </is>
-      </c>
-      <c r="B30" s="204" t="inlineStr">
-        <is>
-          <t>Her iki dosya v15.1 sistemine aittir. Python hash değişirse MASTER Excel'deki referans da güncellenmelidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1" s="50">
-      <c r="A31" s="204" t="inlineStr">
-        <is>
-          <t>Sahte PASS Yasağı</t>
-        </is>
-      </c>
-      <c r="B31" s="204" t="inlineStr">
-        <is>
-          <t>Kanıt yoksa PASS yok; hata=FAIL, ölçülemiyorsa=BLOCKED, Excel GUI gerekiyorsa=HARİCİ KABUL GEREKLİ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="204" t="inlineStr">
-        <is>
-          <t>Dil</t>
-        </is>
-      </c>
-      <c r="B32" s="204" t="inlineStr">
-        <is>
-          <t>Kullanıcı yüzeyi safkan Türkçe; teknik kavramların Türkçe karşılığı ana terimdir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="204" t="inlineStr">
-        <is>
-          <t>Muhasebe</t>
-        </is>
-      </c>
-      <c r="B33" s="204" t="inlineStr">
-        <is>
-          <t>Türkiye Tekdüzen Hesap Planı ve Türk muhasebe/işletme düşünce yapısı esas alınır.</t>
+          <t>Piyasa gerçekten ödüyor mu?</t>
+        </is>
+      </c>
+      <c r="C19" s="204" t="inlineStr">
+        <is>
+          <t>Satış/pilot/LOI/fiyat kabulü olmadan pazar doğrulandı yazılmaz</t>
+        </is>
+      </c>
+      <c r="D19" s="204" t="inlineStr">
+        <is>
+          <t>Gerçek işlem kanıtı</t>
+        </is>
+      </c>
+      <c r="E19" s="204" t="inlineStr">
+        <is>
+          <t>Tahmini talep = satış kabulü</t>
+        </is>
+      </c>
+      <c r="F19" s="224" t="inlineStr">
+        <is>
+          <t>HATA</t>
         </is>
       </c>
     </row>
@@ -12836,7 +13408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12958,7 +13530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13047,7 +13619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13068,238 +13640,238 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>BANKALAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>BANKA TANIMLARI — ilişki, operasyonel durum ve iletişim tek merkezde.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Banka ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Banka</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Şube</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Müşteri Numarası</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>IBAN</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>İlişki Yöneticisi</t>
         </is>
       </c>
-      <c r="H5" s="86" t="inlineStr">
+      <c r="H5" s="272" t="inlineStr">
         <is>
           <t>Telefon</t>
         </is>
       </c>
-      <c r="I5" s="86" t="inlineStr">
+      <c r="I5" s="272" t="inlineStr">
         <is>
           <t>Kontrol</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="273" t="inlineStr">
         <is>
           <t>BNK-001</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="273" t="inlineStr">
         <is>
           <t>Türkiye İş Bankası</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="273" t="inlineStr">
         <is>
           <t>Maslak Ticari</t>
         </is>
       </c>
-      <c r="D6" s="88" t="n">
+      <c r="D6" s="274" t="n">
         <v>1002345</v>
       </c>
-      <c r="E6" s="87" t="inlineStr">
+      <c r="E6" s="273" t="inlineStr">
         <is>
           <t>TR110006400000123456789001</t>
         </is>
       </c>
-      <c r="F6" s="87" t="inlineStr">
+      <c r="F6" s="273" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="G6" s="87" t="inlineStr">
+      <c r="G6" s="273" t="inlineStr">
         <is>
           <t>Ayşe Yılmaz</t>
         </is>
       </c>
-      <c r="H6" s="87" t="inlineStr">
+      <c r="H6" s="273" t="inlineStr">
         <is>
           <t>0212 000 00 01</t>
         </is>
       </c>
-      <c r="I6" s="89">
+      <c r="I6" s="275">
         <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="273" t="inlineStr">
         <is>
           <t>BNK-002</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="273" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="273" t="inlineStr">
         <is>
           <t>Levent Ticari</t>
         </is>
       </c>
-      <c r="D7" s="88" t="n">
+      <c r="D7" s="274" t="n">
         <v>2001456</v>
       </c>
-      <c r="E7" s="87" t="inlineStr">
+      <c r="E7" s="273" t="inlineStr">
         <is>
           <t>TR220004600000234567890002</t>
         </is>
       </c>
-      <c r="F7" s="87" t="inlineStr">
+      <c r="F7" s="273" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="G7" s="87" t="inlineStr">
+      <c r="G7" s="273" t="inlineStr">
         <is>
           <t>Mehmet Kaya</t>
         </is>
       </c>
-      <c r="H7" s="87" t="inlineStr">
+      <c r="H7" s="273" t="inlineStr">
         <is>
           <t>0212 000 00 02</t>
         </is>
       </c>
-      <c r="I7" s="89">
+      <c r="I7" s="276">
         <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="273" t="inlineStr">
         <is>
           <t>BNK-003</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="273" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="C8" s="87" t="inlineStr">
+      <c r="C8" s="273" t="inlineStr">
         <is>
           <t>İkitelli Ticari</t>
         </is>
       </c>
-      <c r="D8" s="88" t="n">
+      <c r="D8" s="274" t="n">
         <v>3001789</v>
       </c>
-      <c r="E8" s="87" t="inlineStr">
+      <c r="E8" s="273" t="inlineStr">
         <is>
           <t>TR330006200000345678901003</t>
         </is>
       </c>
-      <c r="F8" s="87" t="inlineStr">
+      <c r="F8" s="273" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
       </c>
-      <c r="G8" s="87" t="inlineStr">
+      <c r="G8" s="273" t="inlineStr">
         <is>
           <t>Selin Demir</t>
         </is>
       </c>
-      <c r="H8" s="87" t="inlineStr">
+      <c r="H8" s="273" t="inlineStr">
         <is>
           <t>0212 000 00 03</t>
         </is>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="275">
         <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="273" t="inlineStr">
         <is>
           <t>BNK-004</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="273" t="inlineStr">
         <is>
           <t>Yapı Kredi</t>
         </is>
       </c>
-      <c r="C9" s="87" t="inlineStr">
+      <c r="C9" s="273" t="inlineStr">
         <is>
           <t>Kozyatağı Ticari</t>
         </is>
       </c>
-      <c r="D9" s="88" t="n">
+      <c r="D9" s="274" t="n">
         <v>4001678</v>
       </c>
-      <c r="E9" s="87" t="inlineStr">
+      <c r="E9" s="273" t="inlineStr">
         <is>
           <t>TR440006700000456789012004</t>
         </is>
       </c>
-      <c r="F9" s="87" t="inlineStr">
+      <c r="F9" s="273" t="inlineStr">
         <is>
           <t>İzle</t>
         </is>
       </c>
-      <c r="G9" s="87" t="inlineStr">
+      <c r="G9" s="273" t="inlineStr">
         <is>
           <t>Can Arslan</t>
         </is>
       </c>
-      <c r="H9" s="87" t="inlineStr">
+      <c r="H9" s="273" t="inlineStr">
         <is>
           <t>0212 000 00 04</t>
         </is>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="276">
         <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9)),"EKSİK","OK"))</f>
         <v/>
       </c>
@@ -13708,7 +14280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13729,222 +14301,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>LIMITLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>BANKA LİMİTLERİ — toplam, kullanılan ve kalan limit ile kullanım oranı.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Limit ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Banka</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Ürün Türü</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Para Birimi</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>Toplam Limit</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Kullanılan Limit</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Kalan Limit</t>
         </is>
       </c>
-      <c r="H5" s="86" t="inlineStr">
+      <c r="H5" s="272" t="inlineStr">
         <is>
           <t>Kullanım Oranı</t>
         </is>
       </c>
-      <c r="I5" s="86" t="inlineStr">
+      <c r="I5" s="272" t="inlineStr">
         <is>
           <t>Kontrol</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="273" t="inlineStr">
         <is>
           <t>LMT-001</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="273" t="inlineStr">
         <is>
           <t>Türkiye İş Bankası</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="273" t="inlineStr">
         <is>
           <t>Taksitli Ticari Kredi</t>
         </is>
       </c>
-      <c r="D6" s="87" t="inlineStr">
+      <c r="D6" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="E6" s="91" t="n">
+      <c r="E6" s="277" t="n">
         <v>15000000</v>
       </c>
-      <c r="F6" s="91" t="n">
+      <c r="F6" s="277" t="n">
         <v>10500000</v>
       </c>
-      <c r="G6" s="92">
+      <c r="G6" s="278">
         <f>IF(ISBLANK($A6),"",IF($E6="","",$E6-$F6))</f>
         <v/>
       </c>
-      <c r="H6" s="93">
+      <c r="H6" s="279">
         <f>IF(ISBLANK($A6),"",IF($E6=0,"",$F6/$E6))</f>
         <v/>
       </c>
-      <c r="I6" s="89">
+      <c r="I6" s="275">
         <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="273" t="inlineStr">
         <is>
           <t>LMT-002</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="273" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="273" t="inlineStr">
         <is>
           <t>Leasing</t>
         </is>
       </c>
-      <c r="D7" s="87" t="inlineStr">
+      <c r="D7" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="E7" s="91" t="n">
+      <c r="E7" s="277" t="n">
         <v>8000000</v>
       </c>
-      <c r="F7" s="91" t="n">
+      <c r="F7" s="277" t="n">
         <v>6200000</v>
       </c>
-      <c r="G7" s="92">
+      <c r="G7" s="280">
         <f>IF(ISBLANK($A7),"",IF($E7="","",$E7-$F7))</f>
         <v/>
       </c>
-      <c r="H7" s="93">
+      <c r="H7" s="281">
         <f>IF(ISBLANK($A7),"",IF($E7=0,"",$F7/$E7))</f>
         <v/>
       </c>
-      <c r="I7" s="89">
+      <c r="I7" s="276">
         <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="273" t="inlineStr">
         <is>
           <t>LMT-003</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="273" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="C8" s="87" t="inlineStr">
+      <c r="C8" s="273" t="inlineStr">
         <is>
           <t>Rotatif Kredi</t>
         </is>
       </c>
-      <c r="D8" s="87" t="inlineStr">
+      <c r="D8" s="273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E8" s="91" t="n">
+      <c r="E8" s="277" t="n">
         <v>250000</v>
       </c>
-      <c r="F8" s="91" t="n">
+      <c r="F8" s="277" t="n">
         <v>180000</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="278">
         <f>IF(ISBLANK($A8),"",IF($E8="","",$E8-$F8))</f>
         <v/>
       </c>
-      <c r="H8" s="93">
+      <c r="H8" s="279">
         <f>IF(ISBLANK($A8),"",IF($E8=0,"",$F8/$E8))</f>
         <v/>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="275">
         <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="273" t="inlineStr">
         <is>
           <t>LMT-004</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="273" t="inlineStr">
         <is>
           <t>Yapı Kredi</t>
         </is>
       </c>
-      <c r="C9" s="87" t="inlineStr">
+      <c r="C9" s="273" t="inlineStr">
         <is>
           <t>Spot Kredi</t>
         </is>
       </c>
-      <c r="D9" s="87" t="inlineStr">
+      <c r="D9" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="E9" s="91" t="n">
+      <c r="E9" s="277" t="n">
         <v>5000000</v>
       </c>
-      <c r="F9" s="91" t="n">
+      <c r="F9" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="92">
+      <c r="G9" s="280">
         <f>IF(ISBLANK($A9),"",IF($E9="","",$E9-$F9))</f>
         <v/>
       </c>
-      <c r="H9" s="93">
+      <c r="H9" s="281">
         <f>IF(ISBLANK($A9),"",IF($E9=0,"",$F9/$E9))</f>
         <v/>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="276">
         <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9)),"EKSİK","OK"))</f>
         <v/>
       </c>
@@ -14519,7 +15091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14544,323 +15116,323 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>KREDILER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="135.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>KREDİ PORTFÖYÜ — sözleşme, bakiye, maliyet, vade ve taksit bilgileri.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Kredi ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Banka</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Şube</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Ürün Türü</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>Para Birimi</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Kullandırım Tarihi</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Anapara</t>
         </is>
       </c>
-      <c r="H5" s="86" t="inlineStr">
+      <c r="H5" s="272" t="inlineStr">
         <is>
           <t>Güncel Bakiye</t>
         </is>
       </c>
-      <c r="I5" s="86" t="inlineStr">
+      <c r="I5" s="272" t="inlineStr">
         <is>
           <t>Yıllık Faiz</t>
         </is>
       </c>
-      <c r="J5" s="86" t="inlineStr">
+      <c r="J5" s="272" t="inlineStr">
         <is>
           <t>Vade Ay</t>
         </is>
       </c>
-      <c r="K5" s="86" t="inlineStr">
+      <c r="K5" s="272" t="inlineStr">
         <is>
           <t>Aylık Taksit</t>
         </is>
       </c>
-      <c r="L5" s="86" t="inlineStr">
+      <c r="L5" s="272" t="inlineStr">
         <is>
           <t>Bitiş Tarihi</t>
         </is>
       </c>
-      <c r="M5" s="86" t="inlineStr">
+      <c r="M5" s="272" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="N5" s="86" t="inlineStr">
+      <c r="N5" s="272" t="inlineStr">
         <is>
           <t>Kontrol</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="273" t="inlineStr">
         <is>
           <t>KRD-001</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="273" t="inlineStr">
         <is>
           <t>Türkiye İş Bankası</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="273" t="inlineStr">
         <is>
           <t>Maslak Ticari</t>
         </is>
       </c>
-      <c r="D6" s="87" t="inlineStr">
+      <c r="D6" s="273" t="inlineStr">
         <is>
           <t>Taksitli Ticari Kredi</t>
         </is>
       </c>
-      <c r="E6" s="87" t="inlineStr">
+      <c r="E6" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="F6" s="94" t="n">
+      <c r="F6" s="282" t="n">
         <v>45597</v>
       </c>
-      <c r="G6" s="91" t="n">
+      <c r="G6" s="277" t="n">
         <v>12000000</v>
       </c>
-      <c r="H6" s="91" t="n">
+      <c r="H6" s="277" t="n">
         <v>8400000</v>
       </c>
-      <c r="I6" s="95" t="n">
+      <c r="I6" s="283" t="n">
         <v>0.32</v>
       </c>
-      <c r="J6" s="88" t="n">
+      <c r="J6" s="274" t="n">
         <v>24</v>
       </c>
-      <c r="K6" s="93">
+      <c r="K6" s="279">
         <f>IF(ISBLANK($A6),"",IF($I6="","",$I6/AySayisi))</f>
         <v/>
       </c>
-      <c r="L6" s="96">
+      <c r="L6" s="284">
         <f>IF(ISBLANK($A6),"",IFERROR(EOMONTH($F6,$J6),""))</f>
         <v/>
       </c>
-      <c r="M6" s="87" t="inlineStr">
+      <c r="M6" s="273" t="inlineStr">
         <is>
           <t>Yatırım kredisi</t>
         </is>
       </c>
-      <c r="N6" s="89">
+      <c r="N6" s="275">
         <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6),ISBLANK($I6),ISBLANK($J6),ISBLANK($K6),ISBLANK($L6)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="273" t="inlineStr">
         <is>
           <t>KRD-002</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="273" t="inlineStr">
         <is>
           <t>Akbank</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="273" t="inlineStr">
         <is>
           <t>Levent Ticari</t>
         </is>
       </c>
-      <c r="D7" s="87" t="inlineStr">
+      <c r="D7" s="273" t="inlineStr">
         <is>
           <t>Leasing</t>
         </is>
       </c>
-      <c r="E7" s="87" t="inlineStr">
+      <c r="E7" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="F7" s="94" t="n">
+      <c r="F7" s="282" t="n">
         <v>45717</v>
       </c>
-      <c r="G7" s="91" t="n">
+      <c r="G7" s="277" t="n">
         <v>7500000</v>
       </c>
-      <c r="H7" s="91" t="n">
+      <c r="H7" s="277" t="n">
         <v>6100000</v>
       </c>
-      <c r="I7" s="95" t="n">
+      <c r="I7" s="283" t="n">
         <v>0.34</v>
       </c>
-      <c r="J7" s="88" t="n">
+      <c r="J7" s="274" t="n">
         <v>36</v>
       </c>
-      <c r="K7" s="93">
+      <c r="K7" s="281">
         <f>IF(ISBLANK($A7),"",IF($I7="","",$I7/AySayisi))</f>
         <v/>
       </c>
-      <c r="L7" s="96">
+      <c r="L7" s="285">
         <f>IF(ISBLANK($A7),"",IFERROR(EOMONTH($F7,$J7),""))</f>
         <v/>
       </c>
-      <c r="M7" s="87" t="inlineStr">
+      <c r="M7" s="273" t="inlineStr">
         <is>
           <t>Makine leasing</t>
         </is>
       </c>
-      <c r="N7" s="89">
+      <c r="N7" s="276">
         <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7),ISBLANK($I7),ISBLANK($J7),ISBLANK($K7),ISBLANK($L7)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="273" t="inlineStr">
         <is>
           <t>KRD-003</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="273" t="inlineStr">
         <is>
           <t>Garanti BBVA</t>
         </is>
       </c>
-      <c r="C8" s="87" t="inlineStr">
+      <c r="C8" s="273" t="inlineStr">
         <is>
           <t>İkitelli Ticari</t>
         </is>
       </c>
-      <c r="D8" s="87" t="inlineStr">
+      <c r="D8" s="273" t="inlineStr">
         <is>
           <t>Rotatif Kredi</t>
         </is>
       </c>
-      <c r="E8" s="87" t="inlineStr">
+      <c r="E8" s="273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F8" s="94" t="n">
+      <c r="F8" s="282" t="n">
         <v>45809</v>
       </c>
-      <c r="G8" s="91" t="n">
+      <c r="G8" s="277" t="n">
         <v>200000</v>
       </c>
-      <c r="H8" s="91" t="n">
+      <c r="H8" s="277" t="n">
         <v>180000</v>
       </c>
-      <c r="I8" s="95" t="n">
+      <c r="I8" s="283" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="J8" s="88" t="n">
+      <c r="J8" s="274" t="n">
         <v>12</v>
       </c>
-      <c r="K8" s="93">
+      <c r="K8" s="279">
         <f>IF(ISBLANK($A8),"",IF($I8="","",$I8/AySayisi))</f>
         <v/>
       </c>
-      <c r="L8" s="96">
+      <c r="L8" s="284">
         <f>IF(ISBLANK($A8),"",IFERROR(EOMONTH($F8,$J8),""))</f>
         <v/>
       </c>
-      <c r="M8" s="87" t="inlineStr">
+      <c r="M8" s="273" t="inlineStr">
         <is>
           <t>İhracat rotatifi</t>
         </is>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="275">
         <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8),ISBLANK($I8),ISBLANK($J8),ISBLANK($K8),ISBLANK($L8)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="273" t="inlineStr">
         <is>
           <t>KRD-004</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="273" t="inlineStr">
         <is>
           <t>Türkiye İş Bankası</t>
         </is>
       </c>
-      <c r="C9" s="87" t="inlineStr">
+      <c r="C9" s="273" t="inlineStr">
         <is>
           <t>Maslak Ticari</t>
         </is>
       </c>
-      <c r="D9" s="87" t="inlineStr">
+      <c r="D9" s="273" t="inlineStr">
         <is>
           <t>Spot Kredi</t>
         </is>
       </c>
-      <c r="E9" s="87" t="inlineStr">
+      <c r="E9" s="273" t="inlineStr">
         <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="F9" s="94" t="n">
+      <c r="F9" s="282" t="n">
         <v>46023</v>
       </c>
-      <c r="G9" s="91" t="n">
+      <c r="G9" s="277" t="n">
         <v>2200000</v>
       </c>
-      <c r="H9" s="91" t="n">
+      <c r="H9" s="277" t="n">
         <v>2200000</v>
       </c>
-      <c r="I9" s="95" t="n">
+      <c r="I9" s="283" t="n">
         <v>0.36</v>
       </c>
-      <c r="J9" s="88" t="n">
+      <c r="J9" s="274" t="n">
         <v>12</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="281">
         <f>IF(ISBLANK($A9),"",IF($I9="","",$I9/AySayisi))</f>
         <v/>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="285">
         <f>IF(ISBLANK($A9),"",IFERROR(EOMONTH($F9,$J9),""))</f>
         <v/>
       </c>
-      <c r="M9" s="87" t="inlineStr">
+      <c r="M9" s="273" t="inlineStr">
         <is>
           <t>İşletme sermayesi</t>
         </is>
       </c>
-      <c r="N9" s="89">
+      <c r="N9" s="276">
         <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9),ISBLANK($I9),ISBLANK($J9),ISBLANK($K9),ISBLANK($L9)),"EKSİK","OK"))</f>
         <v/>
       </c>
@@ -15565,7 +16137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15586,359 +16158,359 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>TAKSIT PLANI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>TAKSİT PLANI — dönem bazında anapara, faiz, vergi ve ödeme tarihi.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Plan ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Kredi ID</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Ödeme Tarihi</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>Anapara</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Faiz</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Vergi/Fon</t>
         </is>
       </c>
-      <c r="H5" s="86" t="inlineStr">
+      <c r="H5" s="272" t="inlineStr">
         <is>
           <t>Komisyon</t>
         </is>
       </c>
-      <c r="I5" s="86" t="inlineStr">
+      <c r="I5" s="272" t="inlineStr">
         <is>
           <t>Toplam Ödeme</t>
         </is>
       </c>
-      <c r="J5" s="86" t="inlineStr">
+      <c r="J5" s="272" t="inlineStr">
         <is>
           <t>Ödeme Durumu</t>
         </is>
       </c>
-      <c r="K5" s="86" t="inlineStr">
+      <c r="K5" s="272" t="inlineStr">
         <is>
           <t>Kalan Gün</t>
         </is>
       </c>
-      <c r="L5" s="86" t="inlineStr">
+      <c r="L5" s="272" t="inlineStr">
         <is>
           <t>Kontrol</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="273" t="inlineStr">
         <is>
           <t>PLN-001</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="273" t="inlineStr">
         <is>
           <t>KRD-001</t>
         </is>
       </c>
-      <c r="C6" s="88" t="n">
+      <c r="C6" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="94" t="n">
+      <c r="D6" s="282" t="n">
         <v>46244</v>
       </c>
-      <c r="E6" s="91" t="n">
+      <c r="E6" s="277" t="n">
         <v>326000</v>
       </c>
-      <c r="F6" s="91" t="n">
+      <c r="F6" s="277" t="n">
         <v>280000</v>
       </c>
-      <c r="G6" s="91" t="n">
+      <c r="G6" s="277" t="n">
         <v>14000</v>
       </c>
-      <c r="H6" s="91" t="n">
+      <c r="H6" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="92">
+      <c r="I6" s="278">
         <f>IF(ISBLANK($A6),"",IF(COUNTA($E6:$H6)=4,$E6+$F6+$G6+$H6,""))</f>
         <v/>
       </c>
-      <c r="J6" s="87" t="inlineStr">
+      <c r="J6" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K6" s="97">
+      <c r="K6" s="286">
         <f>IF(ISBLANK($D6),"",$D6-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L6" s="89">
+      <c r="L6" s="275">
         <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6),ISBLANK($I6),ISBLANK($J6)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="273" t="inlineStr">
         <is>
           <t>PLN-002</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="273" t="inlineStr">
         <is>
           <t>KRD-001</t>
         </is>
       </c>
-      <c r="C7" s="88" t="n">
+      <c r="C7" s="274" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="282" t="n">
         <v>46275</v>
       </c>
-      <c r="E7" s="91" t="n">
+      <c r="E7" s="277" t="n">
         <v>337000</v>
       </c>
-      <c r="F7" s="91" t="n">
+      <c r="F7" s="277" t="n">
         <v>269000</v>
       </c>
-      <c r="G7" s="91" t="n">
+      <c r="G7" s="277" t="n">
         <v>14000</v>
       </c>
-      <c r="H7" s="91" t="n">
+      <c r="H7" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="92">
+      <c r="I7" s="280">
         <f>IF(ISBLANK($A7),"",IF(COUNTA($E7:$H7)=4,$E7+$F7+$G7+$H7,""))</f>
         <v/>
       </c>
-      <c r="J7" s="87" t="inlineStr">
+      <c r="J7" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K7" s="97">
+      <c r="K7" s="287">
         <f>IF(ISBLANK($D7),"",$D7-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L7" s="89">
+      <c r="L7" s="276">
         <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7),ISBLANK($I7),ISBLANK($J7)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="87" t="inlineStr">
+      <c r="A8" s="273" t="inlineStr">
         <is>
           <t>PLN-003</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="273" t="inlineStr">
         <is>
           <t>KRD-002</t>
         </is>
       </c>
-      <c r="C8" s="88" t="n">
+      <c r="C8" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="282" t="n">
         <v>46249</v>
       </c>
-      <c r="E8" s="91" t="n">
+      <c r="E8" s="277" t="n">
         <v>117000</v>
       </c>
-      <c r="F8" s="91" t="n">
+      <c r="F8" s="277" t="n">
         <v>183000</v>
       </c>
-      <c r="G8" s="91" t="n">
+      <c r="G8" s="277" t="n">
         <v>10000</v>
       </c>
-      <c r="H8" s="91" t="n">
+      <c r="H8" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="92">
+      <c r="I8" s="278">
         <f>IF(ISBLANK($A8),"",IF(COUNTA($E8:$H8)=4,$E8+$F8+$G8+$H8,""))</f>
         <v/>
       </c>
-      <c r="J8" s="87" t="inlineStr">
+      <c r="J8" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K8" s="97">
+      <c r="K8" s="286">
         <f>IF(ISBLANK($D8),"",$D8-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="275">
         <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8),ISBLANK($I8),ISBLANK($J8)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="273" t="inlineStr">
         <is>
           <t>PLN-004</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="273" t="inlineStr">
         <is>
           <t>KRD-002</t>
         </is>
       </c>
-      <c r="C9" s="88" t="n">
+      <c r="C9" s="274" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="282" t="n">
         <v>46280</v>
       </c>
-      <c r="E9" s="91" t="n">
+      <c r="E9" s="277" t="n">
         <v>121000</v>
       </c>
-      <c r="F9" s="91" t="n">
+      <c r="F9" s="277" t="n">
         <v>179000</v>
       </c>
-      <c r="G9" s="91" t="n">
+      <c r="G9" s="277" t="n">
         <v>10000</v>
       </c>
-      <c r="H9" s="91" t="n">
+      <c r="H9" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="280">
         <f>IF(ISBLANK($A9),"",IF(COUNTA($E9:$H9)=4,$E9+$F9+$G9+$H9,""))</f>
         <v/>
       </c>
-      <c r="J9" s="87" t="inlineStr">
+      <c r="J9" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="287">
         <f>IF(ISBLANK($D9),"",$D9-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="276">
         <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9),ISBLANK($I9),ISBLANK($J9)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="273" t="inlineStr">
         <is>
           <t>PLN-005</t>
         </is>
       </c>
-      <c r="B10" s="87" t="inlineStr">
+      <c r="B10" s="273" t="inlineStr">
         <is>
           <t>KRD-003</t>
         </is>
       </c>
-      <c r="C10" s="88" t="n">
+      <c r="C10" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="94" t="n">
+      <c r="D10" s="282" t="n">
         <v>46254</v>
       </c>
-      <c r="E10" s="91" t="n">
+      <c r="E10" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="91" t="n">
+      <c r="F10" s="277" t="n">
         <v>4275</v>
       </c>
-      <c r="G10" s="91" t="n">
+      <c r="G10" s="277" t="n">
         <v>214</v>
       </c>
-      <c r="H10" s="91" t="n">
+      <c r="H10" s="277" t="n">
         <v>375</v>
       </c>
-      <c r="I10" s="92">
+      <c r="I10" s="278">
         <f>IF(ISBLANK($A10),"",IF(COUNTA($E10:$H10)=4,$E10+$F10+$G10+$H10,""))</f>
         <v/>
       </c>
-      <c r="J10" s="87" t="inlineStr">
+      <c r="J10" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K10" s="97">
+      <c r="K10" s="286">
         <f>IF(ISBLANK($D10),"",$D10-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L10" s="89">
+      <c r="L10" s="275">
         <f>IF(ISBLANK($A10),"",IF(OR(ISBLANK($B10),ISBLANK($C10),ISBLANK($D10),ISBLANK($E10),ISBLANK($F10),ISBLANK($G10),ISBLANK($H10),ISBLANK($I10),ISBLANK($J10)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="273" t="inlineStr">
         <is>
           <t>PLN-006</t>
         </is>
       </c>
-      <c r="B11" s="87" t="inlineStr">
+      <c r="B11" s="273" t="inlineStr">
         <is>
           <t>KRD-004</t>
         </is>
       </c>
-      <c r="C11" s="88" t="n">
+      <c r="C11" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="282" t="n">
         <v>46387</v>
       </c>
-      <c r="E11" s="91" t="n">
+      <c r="E11" s="277" t="n">
         <v>2200000</v>
       </c>
-      <c r="F11" s="91" t="n">
+      <c r="F11" s="277" t="n">
         <v>1034000</v>
       </c>
-      <c r="G11" s="91" t="n">
+      <c r="G11" s="277" t="n">
         <v>51700</v>
       </c>
-      <c r="H11" s="91" t="n">
+      <c r="H11" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="92">
+      <c r="I11" s="280">
         <f>IF(ISBLANK($A11),"",IF(COUNTA($E11:$H11)=4,$E11+$F11+$G11+$H11,""))</f>
         <v/>
       </c>
-      <c r="J11" s="87" t="inlineStr">
+      <c r="J11" s="273" t="inlineStr">
         <is>
           <t>Bekliyor</t>
         </is>
       </c>
-      <c r="K11" s="97">
+      <c r="K11" s="287">
         <f>IF(ISBLANK($D11),"",$D11-RaporTarihi)</f>
         <v/>
       </c>
-      <c r="L11" s="89">
+      <c r="L11" s="276">
         <f>IF(ISBLANK($A11),"",IF(OR(ISBLANK($B11),ISBLANK($C11),ISBLANK($D11),ISBLANK($E11),ISBLANK($F11),ISBLANK($G11),ISBLANK($H11),ISBLANK($I11),ISBLANK($J11)),"EKSİK","OK"))</f>
         <v/>
       </c>
@@ -16556,7 +17128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17183,7 +17755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17853,7 +18425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18716,7 +19288,589 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF17324D"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="50" min="1" max="1"/>
+    <col width="18" customWidth="1" style="50" min="2" max="2"/>
+    <col width="15" customWidth="1" style="50" min="3" max="3"/>
+    <col width="12" customWidth="1" style="50" min="4" max="4"/>
+    <col width="16" customWidth="1" style="50" min="5" max="5"/>
+    <col width="18" customWidth="1" style="50" min="6" max="6"/>
+    <col width="6" customWidth="1" style="50" min="7" max="7"/>
+    <col width="24" customWidth="1" style="50" min="8" max="8"/>
+    <col width="15" customWidth="1" style="50" min="9" max="9"/>
+    <col width="15" customWidth="1" style="50" min="10" max="10"/>
+    <col width="12" customWidth="1" style="50" min="11" max="11"/>
+    <col width="18" customWidth="1" style="50" min="12" max="12"/>
+    <col width="18" customWidth="1" style="50" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <t>☰ PANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="242" t="inlineStr">
+        <is>
+          <t>BANKA, KREDİ VE TAKSİT YÖNETİM MERKEZİ</t>
+        </is>
+      </c>
+      <c r="L2" s="125" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="126" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="237" t="inlineStr">
+        <is>
+          <t>Konsolide Kredi Portföyü, Aylık Borç Servisi ve Likidite Karar Kokpiti · Canlı Hesaplama</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="128" t="inlineStr">
+        <is>
+          <t>TOPLAM KREDİ PORTFÖYÜ</t>
+        </is>
+      </c>
+      <c r="C5" s="129" t="n"/>
+      <c r="D5" s="130" t="inlineStr">
+        <is>
+          <t>CANLI BAKİYE</t>
+        </is>
+      </c>
+      <c r="E5" s="131" t="inlineStr">
+        <is>
+          <t>AYLIK BORÇ SERVİSİ (30 GÜN)</t>
+        </is>
+      </c>
+      <c r="F5" s="129" t="n"/>
+      <c r="G5" s="132" t="inlineStr">
+        <is>
+          <t>ÖDEME BASKISI</t>
+        </is>
+      </c>
+      <c r="H5" s="128" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN AYLIK RAHATLAMA</t>
+        </is>
+      </c>
+      <c r="I5" s="129" t="n"/>
+      <c r="J5" s="133">
+        <f>KARAR_MOTORU!B18&amp;" ADAY"</f>
+        <v/>
+      </c>
+      <c r="K5" s="134" t="inlineStr">
+        <is>
+          <t>BORÇLANMA SÜRDÜRÜLEBİLİRLİĞİ</t>
+        </is>
+      </c>
+      <c r="L5" s="129" t="n"/>
+      <c r="M5" s="130">
+        <f>KARAR_MOTORU!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="129" t="n"/>
+      <c r="D6" s="129" t="n"/>
+      <c r="E6" s="136" t="n"/>
+      <c r="F6" s="129" t="n"/>
+      <c r="G6" s="129" t="n"/>
+      <c r="H6" s="135" t="n"/>
+      <c r="I6" s="129" t="n"/>
+      <c r="J6" s="129" t="n"/>
+      <c r="K6" s="137" t="n"/>
+      <c r="L6" s="129" t="n"/>
+      <c r="M6" s="129" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="225">
+        <f>KARAR_MOTORU!B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="129" t="n"/>
+      <c r="D7" s="129" t="n"/>
+      <c r="E7" s="243">
+        <f>KARAR_MOTORU!B7</f>
+        <v/>
+      </c>
+      <c r="F7" s="129" t="n"/>
+      <c r="G7" s="129" t="n"/>
+      <c r="H7" s="244">
+        <f>KARAR_MOTORU!B19</f>
+        <v/>
+      </c>
+      <c r="I7" s="129" t="n"/>
+      <c r="J7" s="129" t="n"/>
+      <c r="K7" s="245">
+        <f>KARAR_MOTORU!B15</f>
+        <v/>
+      </c>
+      <c r="L7" s="129" t="n"/>
+      <c r="M7" s="129" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="135" t="n"/>
+      <c r="C8" s="129" t="n"/>
+      <c r="D8" s="129" t="n"/>
+      <c r="E8" s="136" t="n"/>
+      <c r="F8" s="129" t="n"/>
+      <c r="G8" s="129" t="n"/>
+      <c r="H8" s="135" t="n"/>
+      <c r="I8" s="129" t="n"/>
+      <c r="J8" s="129" t="n"/>
+      <c r="K8" s="137" t="n"/>
+      <c r="L8" s="129" t="n"/>
+      <c r="M8" s="129" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="141" t="inlineStr">
+        <is>
+          <t>↑ Aktif portföy risk hacmi</t>
+        </is>
+      </c>
+      <c r="C9" s="129" t="n"/>
+      <c r="D9" s="129" t="n"/>
+      <c r="E9" s="142" t="inlineStr">
+        <is>
+          <t>● 30 gün içinde vadesi gelen taksitler</t>
+        </is>
+      </c>
+      <c r="F9" s="129" t="n"/>
+      <c r="G9" s="129" t="n"/>
+      <c r="H9" s="141" t="inlineStr">
+        <is>
+          <t>✓ Yapılandırma ile aylık nakit kazanımı</t>
+        </is>
+      </c>
+      <c r="I9" s="129" t="n"/>
+      <c r="J9" s="129" t="n"/>
+      <c r="K9" s="246">
+        <f>KARAR_MOTORU!B17</f>
+        <v/>
+      </c>
+      <c r="L9" s="129" t="n"/>
+      <c r="M9" s="129" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
+        </is>
+      </c>
+      <c r="F11" s="144" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="145" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C14" s="145" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="145" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="145" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="146" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="146" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="146" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="146" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="146" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="73" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="73" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="147" t="inlineStr">
+        <is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="227">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="228">
+        <f>B7*0.05</f>
+        <v/>
+      </c>
+      <c r="K15" s="149" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="133" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="73" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="73" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="147" t="inlineStr">
+        <is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="227">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="228">
+        <f>B7*0.03</f>
+        <v/>
+      </c>
+      <c r="K16" s="149" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="130" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="73" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="73" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="147" t="inlineStr">
+        <is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="227">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="228">
+        <f>B7*0.02</f>
+        <v/>
+      </c>
+      <c r="K17" s="149" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="150" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="73" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="147" t="inlineStr">
+        <is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="227">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="228">
+        <f>B7*0.01</f>
+        <v/>
+      </c>
+      <c r="K18" s="149" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="133" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="73" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="151" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="229">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="230">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="154" t="inlineStr"/>
+      <c r="L19" s="155" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="n">
+        <v>96</v>
+      </c>
+      <c r="D20" s="73" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="73" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="156" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="156" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="157" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU PROTOKOLÜ</t>
+        </is>
+      </c>
+      <c r="L22" s="158" t="n"/>
+      <c r="M22" s="158" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="159" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="160" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN &amp; LİKİDİTE</t>
+        </is>
+      </c>
+      <c r="L23" s="158" t="n"/>
+      <c r="M23" s="158" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="159" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="161" t="inlineStr">
+        <is>
+          <t>Sistem, nakit açığı riskini 30/60/90 günlük pencerelerde izleyerek, borç servisi oranını optimal eşikte tutacak yapılandırma önerir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="162" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="58" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="163" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="164" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="G26" s="247" t="n"/>
+      <c r="H26" s="247" t="n"/>
+      <c r="I26" s="248" t="n"/>
+      <c r="K26" s="165" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN ANALİZİNİ GÖR (#REFINANSMAN!A1) &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" s="249" t="n"/>
+      <c r="G27" s="250" t="n"/>
+      <c r="H27" s="250" t="n"/>
+      <c r="I27" s="251" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18735,952 +19889,952 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>ODEME TAKVIMI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="105.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>ÖDEME TAKVİMİ — yaklaşan taksitler 30 / 60 / 90 gün penceresinde.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Kredi ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Banka</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Ödeme Tarihi</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Toplam Ödeme</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>Kalan Gün</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Zaman Dilimi</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Ödeme Durumu</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="89">
+      <c r="A6" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",TAKSIT_PLANI!$B6)</f>
         <v/>
       </c>
-      <c r="B6" s="98">
+      <c r="B6" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B6,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C6" s="96">
+      <c r="C6" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",TAKSIT_PLANI!$D6)</f>
         <v/>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",TAKSIT_PLANI!$I6)</f>
         <v/>
       </c>
-      <c r="E6" s="97">
+      <c r="E6" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",TAKSIT_PLANI!$K6)</f>
         <v/>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",IF(TAKSIT_PLANI!$K6&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K6&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K6&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G6" s="89">
+      <c r="G6" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",TAKSIT_PLANI!$J6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="89">
+      <c r="A7" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",TAKSIT_PLANI!$B7)</f>
         <v/>
       </c>
-      <c r="B7" s="98">
+      <c r="B7" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B7,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C7" s="96">
+      <c r="C7" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",TAKSIT_PLANI!$D7)</f>
         <v/>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",TAKSIT_PLANI!$I7)</f>
         <v/>
       </c>
-      <c r="E7" s="97">
+      <c r="E7" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",TAKSIT_PLANI!$K7)</f>
         <v/>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",IF(TAKSIT_PLANI!$K7&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K7&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K7&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G7" s="89">
+      <c r="G7" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",TAKSIT_PLANI!$J7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="89">
+      <c r="A8" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",TAKSIT_PLANI!$B8)</f>
         <v/>
       </c>
-      <c r="B8" s="98">
+      <c r="B8" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B8,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C8" s="96">
+      <c r="C8" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",TAKSIT_PLANI!$D8)</f>
         <v/>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",TAKSIT_PLANI!$I8)</f>
         <v/>
       </c>
-      <c r="E8" s="97">
+      <c r="E8" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",TAKSIT_PLANI!$K8)</f>
         <v/>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",IF(TAKSIT_PLANI!$K8&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K8&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K8&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G8" s="89">
+      <c r="G8" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",TAKSIT_PLANI!$J8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="89">
+      <c r="A9" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",TAKSIT_PLANI!$B9)</f>
         <v/>
       </c>
-      <c r="B9" s="98">
+      <c r="B9" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B9,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C9" s="96">
+      <c r="C9" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",TAKSIT_PLANI!$D9)</f>
         <v/>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",TAKSIT_PLANI!$I9)</f>
         <v/>
       </c>
-      <c r="E9" s="97">
+      <c r="E9" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",TAKSIT_PLANI!$K9)</f>
         <v/>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",IF(TAKSIT_PLANI!$K9&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K9&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K9&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G9" s="89">
+      <c r="G9" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",TAKSIT_PLANI!$J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="89">
+      <c r="A10" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",TAKSIT_PLANI!$B10)</f>
         <v/>
       </c>
-      <c r="B10" s="98">
+      <c r="B10" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B10,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C10" s="96">
+      <c r="C10" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",TAKSIT_PLANI!$D10)</f>
         <v/>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",TAKSIT_PLANI!$I10)</f>
         <v/>
       </c>
-      <c r="E10" s="97">
+      <c r="E10" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",TAKSIT_PLANI!$K10)</f>
         <v/>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",IF(TAKSIT_PLANI!$K10&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K10&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K10&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G10" s="89">
+      <c r="G10" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",TAKSIT_PLANI!$J10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="89">
+      <c r="A11" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",TAKSIT_PLANI!$B11)</f>
         <v/>
       </c>
-      <c r="B11" s="98">
+      <c r="B11" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B11,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C11" s="96">
+      <c r="C11" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",TAKSIT_PLANI!$D11)</f>
         <v/>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",TAKSIT_PLANI!$I11)</f>
         <v/>
       </c>
-      <c r="E11" s="97">
+      <c r="E11" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",TAKSIT_PLANI!$K11)</f>
         <v/>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",IF(TAKSIT_PLANI!$K11&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K11&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K11&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G11" s="89">
+      <c r="G11" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",TAKSIT_PLANI!$J11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="50">
-      <c r="A12" s="89">
+      <c r="A12" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",TAKSIT_PLANI!$B12)</f>
         <v/>
       </c>
-      <c r="B12" s="98">
+      <c r="B12" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B12,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C12" s="96">
+      <c r="C12" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",TAKSIT_PLANI!$D12)</f>
         <v/>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",TAKSIT_PLANI!$I12)</f>
         <v/>
       </c>
-      <c r="E12" s="97">
+      <c r="E12" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",TAKSIT_PLANI!$K12)</f>
         <v/>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",IF(TAKSIT_PLANI!$K12&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K12&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K12&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G12" s="89">
+      <c r="G12" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",TAKSIT_PLANI!$J12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="50">
-      <c r="A13" s="89">
+      <c r="A13" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",TAKSIT_PLANI!$B13)</f>
         <v/>
       </c>
-      <c r="B13" s="98">
+      <c r="B13" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B13,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C13" s="96">
+      <c r="C13" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",TAKSIT_PLANI!$D13)</f>
         <v/>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",TAKSIT_PLANI!$I13)</f>
         <v/>
       </c>
-      <c r="E13" s="97">
+      <c r="E13" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",TAKSIT_PLANI!$K13)</f>
         <v/>
       </c>
-      <c r="F13" s="89">
+      <c r="F13" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",IF(TAKSIT_PLANI!$K13&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K13&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K13&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G13" s="89">
+      <c r="G13" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",TAKSIT_PLANI!$J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="50">
-      <c r="A14" s="89">
+      <c r="A14" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",TAKSIT_PLANI!$B14)</f>
         <v/>
       </c>
-      <c r="B14" s="98">
+      <c r="B14" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B14,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C14" s="96">
+      <c r="C14" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",TAKSIT_PLANI!$D14)</f>
         <v/>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",TAKSIT_PLANI!$I14)</f>
         <v/>
       </c>
-      <c r="E14" s="97">
+      <c r="E14" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",TAKSIT_PLANI!$K14)</f>
         <v/>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",IF(TAKSIT_PLANI!$K14&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K14&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K14&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G14" s="89">
+      <c r="G14" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",TAKSIT_PLANI!$J14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="50">
-      <c r="A15" s="89">
+      <c r="A15" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",TAKSIT_PLANI!$B15)</f>
         <v/>
       </c>
-      <c r="B15" s="98">
+      <c r="B15" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B15,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C15" s="96">
+      <c r="C15" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",TAKSIT_PLANI!$D15)</f>
         <v/>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",TAKSIT_PLANI!$I15)</f>
         <v/>
       </c>
-      <c r="E15" s="97">
+      <c r="E15" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",TAKSIT_PLANI!$K15)</f>
         <v/>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",IF(TAKSIT_PLANI!$K15&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K15&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K15&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G15" s="89">
+      <c r="G15" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",TAKSIT_PLANI!$J15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="50">
-      <c r="A16" s="89">
+      <c r="A16" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",TAKSIT_PLANI!$B16)</f>
         <v/>
       </c>
-      <c r="B16" s="98">
+      <c r="B16" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B16,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C16" s="96">
+      <c r="C16" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",TAKSIT_PLANI!$D16)</f>
         <v/>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",TAKSIT_PLANI!$I16)</f>
         <v/>
       </c>
-      <c r="E16" s="97">
+      <c r="E16" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",TAKSIT_PLANI!$K16)</f>
         <v/>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",IF(TAKSIT_PLANI!$K16&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K16&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K16&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G16" s="89">
+      <c r="G16" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",TAKSIT_PLANI!$J16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="50">
-      <c r="A17" s="89">
+      <c r="A17" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",TAKSIT_PLANI!$B17)</f>
         <v/>
       </c>
-      <c r="B17" s="98">
+      <c r="B17" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B17,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C17" s="96">
+      <c r="C17" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",TAKSIT_PLANI!$D17)</f>
         <v/>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",TAKSIT_PLANI!$I17)</f>
         <v/>
       </c>
-      <c r="E17" s="97">
+      <c r="E17" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",TAKSIT_PLANI!$K17)</f>
         <v/>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",IF(TAKSIT_PLANI!$K17&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K17&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K17&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G17" s="89">
+      <c r="G17" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",TAKSIT_PLANI!$J17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="50">
-      <c r="A18" s="89">
+      <c r="A18" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",TAKSIT_PLANI!$B18)</f>
         <v/>
       </c>
-      <c r="B18" s="98">
+      <c r="B18" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B18,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C18" s="96">
+      <c r="C18" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",TAKSIT_PLANI!$D18)</f>
         <v/>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",TAKSIT_PLANI!$I18)</f>
         <v/>
       </c>
-      <c r="E18" s="97">
+      <c r="E18" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",TAKSIT_PLANI!$K18)</f>
         <v/>
       </c>
-      <c r="F18" s="89">
+      <c r="F18" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",IF(TAKSIT_PLANI!$K18&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K18&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K18&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G18" s="89">
+      <c r="G18" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",TAKSIT_PLANI!$J18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="50">
-      <c r="A19" s="89">
+      <c r="A19" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",TAKSIT_PLANI!$B19)</f>
         <v/>
       </c>
-      <c r="B19" s="98">
+      <c r="B19" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B19,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C19" s="96">
+      <c r="C19" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",TAKSIT_PLANI!$D19)</f>
         <v/>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",TAKSIT_PLANI!$I19)</f>
         <v/>
       </c>
-      <c r="E19" s="97">
+      <c r="E19" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",TAKSIT_PLANI!$K19)</f>
         <v/>
       </c>
-      <c r="F19" s="89">
+      <c r="F19" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",IF(TAKSIT_PLANI!$K19&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K19&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K19&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G19" s="89">
+      <c r="G19" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",TAKSIT_PLANI!$J19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="50">
-      <c r="A20" s="89">
+      <c r="A20" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",TAKSIT_PLANI!$B20)</f>
         <v/>
       </c>
-      <c r="B20" s="98">
+      <c r="B20" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B20,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C20" s="96">
+      <c r="C20" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",TAKSIT_PLANI!$D20)</f>
         <v/>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",TAKSIT_PLANI!$I20)</f>
         <v/>
       </c>
-      <c r="E20" s="97">
+      <c r="E20" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",TAKSIT_PLANI!$K20)</f>
         <v/>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",IF(TAKSIT_PLANI!$K20&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K20&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K20&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G20" s="89">
+      <c r="G20" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",TAKSIT_PLANI!$J20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="50">
-      <c r="A21" s="89">
+      <c r="A21" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",TAKSIT_PLANI!$B21)</f>
         <v/>
       </c>
-      <c r="B21" s="98">
+      <c r="B21" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B21,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C21" s="96">
+      <c r="C21" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",TAKSIT_PLANI!$D21)</f>
         <v/>
       </c>
-      <c r="D21" s="92">
+      <c r="D21" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",TAKSIT_PLANI!$I21)</f>
         <v/>
       </c>
-      <c r="E21" s="97">
+      <c r="E21" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",TAKSIT_PLANI!$K21)</f>
         <v/>
       </c>
-      <c r="F21" s="89">
+      <c r="F21" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",IF(TAKSIT_PLANI!$K21&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K21&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K21&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G21" s="89">
+      <c r="G21" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",TAKSIT_PLANI!$J21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="50">
-      <c r="A22" s="89">
+      <c r="A22" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",TAKSIT_PLANI!$B22)</f>
         <v/>
       </c>
-      <c r="B22" s="98">
+      <c r="B22" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B22,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C22" s="96">
+      <c r="C22" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",TAKSIT_PLANI!$D22)</f>
         <v/>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",TAKSIT_PLANI!$I22)</f>
         <v/>
       </c>
-      <c r="E22" s="97">
+      <c r="E22" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",TAKSIT_PLANI!$K22)</f>
         <v/>
       </c>
-      <c r="F22" s="89">
+      <c r="F22" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",IF(TAKSIT_PLANI!$K22&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K22&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K22&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G22" s="89">
+      <c r="G22" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",TAKSIT_PLANI!$J22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="50">
-      <c r="A23" s="89">
+      <c r="A23" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",TAKSIT_PLANI!$B23)</f>
         <v/>
       </c>
-      <c r="B23" s="98">
+      <c r="B23" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B23,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C23" s="96">
+      <c r="C23" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",TAKSIT_PLANI!$D23)</f>
         <v/>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",TAKSIT_PLANI!$I23)</f>
         <v/>
       </c>
-      <c r="E23" s="97">
+      <c r="E23" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",TAKSIT_PLANI!$K23)</f>
         <v/>
       </c>
-      <c r="F23" s="89">
+      <c r="F23" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",IF(TAKSIT_PLANI!$K23&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K23&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K23&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G23" s="89">
+      <c r="G23" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",TAKSIT_PLANI!$J23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="50">
-      <c r="A24" s="89">
+      <c r="A24" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",TAKSIT_PLANI!$B24)</f>
         <v/>
       </c>
-      <c r="B24" s="98">
+      <c r="B24" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B24,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C24" s="96">
+      <c r="C24" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",TAKSIT_PLANI!$D24)</f>
         <v/>
       </c>
-      <c r="D24" s="92">
+      <c r="D24" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",TAKSIT_PLANI!$I24)</f>
         <v/>
       </c>
-      <c r="E24" s="97">
+      <c r="E24" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",TAKSIT_PLANI!$K24)</f>
         <v/>
       </c>
-      <c r="F24" s="89">
+      <c r="F24" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",IF(TAKSIT_PLANI!$K24&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K24&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K24&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G24" s="89">
+      <c r="G24" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",TAKSIT_PLANI!$J24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="50">
-      <c r="A25" s="89">
+      <c r="A25" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",TAKSIT_PLANI!$B25)</f>
         <v/>
       </c>
-      <c r="B25" s="98">
+      <c r="B25" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B25,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C25" s="96">
+      <c r="C25" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",TAKSIT_PLANI!$D25)</f>
         <v/>
       </c>
-      <c r="D25" s="92">
+      <c r="D25" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",TAKSIT_PLANI!$I25)</f>
         <v/>
       </c>
-      <c r="E25" s="97">
+      <c r="E25" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",TAKSIT_PLANI!$K25)</f>
         <v/>
       </c>
-      <c r="F25" s="89">
+      <c r="F25" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",IF(TAKSIT_PLANI!$K25&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K25&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K25&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G25" s="89">
+      <c r="G25" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",TAKSIT_PLANI!$J25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="50">
-      <c r="A26" s="89">
+      <c r="A26" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",TAKSIT_PLANI!$B26)</f>
         <v/>
       </c>
-      <c r="B26" s="98">
+      <c r="B26" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B26,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C26" s="96">
+      <c r="C26" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",TAKSIT_PLANI!$D26)</f>
         <v/>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",TAKSIT_PLANI!$I26)</f>
         <v/>
       </c>
-      <c r="E26" s="97">
+      <c r="E26" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",TAKSIT_PLANI!$K26)</f>
         <v/>
       </c>
-      <c r="F26" s="89">
+      <c r="F26" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",IF(TAKSIT_PLANI!$K26&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K26&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K26&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G26" s="89">
+      <c r="G26" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",TAKSIT_PLANI!$J26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="50">
-      <c r="A27" s="89">
+      <c r="A27" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",TAKSIT_PLANI!$B27)</f>
         <v/>
       </c>
-      <c r="B27" s="98">
+      <c r="B27" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B27,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C27" s="96">
+      <c r="C27" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",TAKSIT_PLANI!$D27)</f>
         <v/>
       </c>
-      <c r="D27" s="92">
+      <c r="D27" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",TAKSIT_PLANI!$I27)</f>
         <v/>
       </c>
-      <c r="E27" s="97">
+      <c r="E27" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",TAKSIT_PLANI!$K27)</f>
         <v/>
       </c>
-      <c r="F27" s="89">
+      <c r="F27" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",IF(TAKSIT_PLANI!$K27&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K27&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K27&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G27" s="89">
+      <c r="G27" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",TAKSIT_PLANI!$J27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="50">
-      <c r="A28" s="89">
+      <c r="A28" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",TAKSIT_PLANI!$B28)</f>
         <v/>
       </c>
-      <c r="B28" s="98">
+      <c r="B28" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B28,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C28" s="96">
+      <c r="C28" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",TAKSIT_PLANI!$D28)</f>
         <v/>
       </c>
-      <c r="D28" s="92">
+      <c r="D28" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",TAKSIT_PLANI!$I28)</f>
         <v/>
       </c>
-      <c r="E28" s="97">
+      <c r="E28" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",TAKSIT_PLANI!$K28)</f>
         <v/>
       </c>
-      <c r="F28" s="89">
+      <c r="F28" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",IF(TAKSIT_PLANI!$K28&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K28&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K28&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G28" s="89">
+      <c r="G28" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",TAKSIT_PLANI!$J28)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="50">
-      <c r="A29" s="89">
+      <c r="A29" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",TAKSIT_PLANI!$B29)</f>
         <v/>
       </c>
-      <c r="B29" s="98">
+      <c r="B29" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B29,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C29" s="96">
+      <c r="C29" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",TAKSIT_PLANI!$D29)</f>
         <v/>
       </c>
-      <c r="D29" s="92">
+      <c r="D29" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",TAKSIT_PLANI!$I29)</f>
         <v/>
       </c>
-      <c r="E29" s="97">
+      <c r="E29" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",TAKSIT_PLANI!$K29)</f>
         <v/>
       </c>
-      <c r="F29" s="89">
+      <c r="F29" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",IF(TAKSIT_PLANI!$K29&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K29&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K29&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G29" s="89">
+      <c r="G29" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",TAKSIT_PLANI!$J29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="50">
-      <c r="A30" s="89">
+      <c r="A30" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",TAKSIT_PLANI!$B30)</f>
         <v/>
       </c>
-      <c r="B30" s="98">
+      <c r="B30" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B30,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C30" s="96">
+      <c r="C30" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",TAKSIT_PLANI!$D30)</f>
         <v/>
       </c>
-      <c r="D30" s="92">
+      <c r="D30" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",TAKSIT_PLANI!$I30)</f>
         <v/>
       </c>
-      <c r="E30" s="97">
+      <c r="E30" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",TAKSIT_PLANI!$K30)</f>
         <v/>
       </c>
-      <c r="F30" s="89">
+      <c r="F30" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",IF(TAKSIT_PLANI!$K30&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K30&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K30&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G30" s="89">
+      <c r="G30" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",TAKSIT_PLANI!$J30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="50">
-      <c r="A31" s="89">
+      <c r="A31" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",TAKSIT_PLANI!$B31)</f>
         <v/>
       </c>
-      <c r="B31" s="98">
+      <c r="B31" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B31,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C31" s="96">
+      <c r="C31" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",TAKSIT_PLANI!$D31)</f>
         <v/>
       </c>
-      <c r="D31" s="92">
+      <c r="D31" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",TAKSIT_PLANI!$I31)</f>
         <v/>
       </c>
-      <c r="E31" s="97">
+      <c r="E31" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",TAKSIT_PLANI!$K31)</f>
         <v/>
       </c>
-      <c r="F31" s="89">
+      <c r="F31" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",IF(TAKSIT_PLANI!$K31&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K31&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K31&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G31" s="89">
+      <c r="G31" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",TAKSIT_PLANI!$J31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="50">
-      <c r="A32" s="89">
+      <c r="A32" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",TAKSIT_PLANI!$B32)</f>
         <v/>
       </c>
-      <c r="B32" s="98">
+      <c r="B32" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B32,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C32" s="96">
+      <c r="C32" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",TAKSIT_PLANI!$D32)</f>
         <v/>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",TAKSIT_PLANI!$I32)</f>
         <v/>
       </c>
-      <c r="E32" s="97">
+      <c r="E32" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",TAKSIT_PLANI!$K32)</f>
         <v/>
       </c>
-      <c r="F32" s="89">
+      <c r="F32" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",IF(TAKSIT_PLANI!$K32&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K32&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K32&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G32" s="89">
+      <c r="G32" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",TAKSIT_PLANI!$J32)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="50">
-      <c r="A33" s="89">
+      <c r="A33" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",TAKSIT_PLANI!$B33)</f>
         <v/>
       </c>
-      <c r="B33" s="98">
+      <c r="B33" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B33,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C33" s="96">
+      <c r="C33" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",TAKSIT_PLANI!$D33)</f>
         <v/>
       </c>
-      <c r="D33" s="92">
+      <c r="D33" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",TAKSIT_PLANI!$I33)</f>
         <v/>
       </c>
-      <c r="E33" s="97">
+      <c r="E33" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",TAKSIT_PLANI!$K33)</f>
         <v/>
       </c>
-      <c r="F33" s="89">
+      <c r="F33" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",IF(TAKSIT_PLANI!$K33&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K33&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K33&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G33" s="89">
+      <c r="G33" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",TAKSIT_PLANI!$J33)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="50">
-      <c r="A34" s="89">
+      <c r="A34" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",TAKSIT_PLANI!$B34)</f>
         <v/>
       </c>
-      <c r="B34" s="98">
+      <c r="B34" s="288">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B34,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C34" s="96">
+      <c r="C34" s="284">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",TAKSIT_PLANI!$D34)</f>
         <v/>
       </c>
-      <c r="D34" s="92">
+      <c r="D34" s="278">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",TAKSIT_PLANI!$I34)</f>
         <v/>
       </c>
-      <c r="E34" s="97">
+      <c r="E34" s="286">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",TAKSIT_PLANI!$K34)</f>
         <v/>
       </c>
-      <c r="F34" s="89">
+      <c r="F34" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",IF(TAKSIT_PLANI!$K34&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K34&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K34&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G34" s="89">
+      <c r="G34" s="275">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",TAKSIT_PLANI!$J34)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="50">
-      <c r="A35" s="89">
+      <c r="A35" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",TAKSIT_PLANI!$B35)</f>
         <v/>
       </c>
-      <c r="B35" s="98">
+      <c r="B35" s="289">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",IFERROR(INDEX(KREDILER!$B$6:$B$1000,MATCH(TAKSIT_PLANI!$B35,KREDILER!$A$6:$A$1000,0)),""))</f>
         <v/>
       </c>
-      <c r="C35" s="96">
+      <c r="C35" s="285">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",TAKSIT_PLANI!$D35)</f>
         <v/>
       </c>
-      <c r="D35" s="92">
+      <c r="D35" s="280">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",TAKSIT_PLANI!$I35)</f>
         <v/>
       </c>
-      <c r="E35" s="97">
+      <c r="E35" s="287">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",TAKSIT_PLANI!$K35)</f>
         <v/>
       </c>
-      <c r="F35" s="89">
+      <c r="F35" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",IF(TAKSIT_PLANI!$K35&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K35&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K35&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
         <v/>
       </c>
-      <c r="G35" s="89">
+      <c r="G35" s="276">
         <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",TAKSIT_PLANI!$J35)</f>
         <v/>
       </c>
@@ -19730,581 +20884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF17324D"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="50" min="1" max="1"/>
-    <col width="18" customWidth="1" style="50" min="2" max="2"/>
-    <col width="15" customWidth="1" style="50" min="3" max="3"/>
-    <col width="12" customWidth="1" style="50" min="4" max="4"/>
-    <col width="16" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="6" customWidth="1" style="50" min="7" max="7"/>
-    <col width="24" customWidth="1" style="50" min="8" max="8"/>
-    <col width="15" customWidth="1" style="50" min="9" max="9"/>
-    <col width="15" customWidth="1" style="50" min="10" max="10"/>
-    <col width="12" customWidth="1" style="50" min="11" max="11"/>
-    <col width="18" customWidth="1" style="50" min="12" max="12"/>
-    <col width="18" customWidth="1" style="50" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="60" t="inlineStr">
-        <is>
-          <t>☰ PANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="124" t="inlineStr">
-        <is>
-          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI</t>
-        </is>
-      </c>
-      <c r="L2" s="125" t="inlineStr">
-        <is>
-          <t>Dönem: 2026 / Tam ▼</t>
-        </is>
-      </c>
-      <c r="M2" s="126" t="inlineStr">
-        <is>
-          <t>★ DOĞRULANMIŞ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="127" t="inlineStr">
-        <is>
-          <t>Hedef Kullanıcı: KOBİ sahipleri, finans yöneticileri, kredi kullanan işletmeler, muhasebe sorumluları · 2026 Q3 Denetim Standardı</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="128" t="inlineStr">
-        <is>
-          <t>TOPLAM KREDİ PORTFÖYÜ</t>
-        </is>
-      </c>
-      <c r="C5" s="129" t="n"/>
-      <c r="D5" s="130" t="inlineStr">
-        <is>
-          <t>6 BANKA</t>
-        </is>
-      </c>
-      <c r="E5" s="131" t="inlineStr">
-        <is>
-          <t>AYLIK TAKSİT YÜKÜ</t>
-        </is>
-      </c>
-      <c r="F5" s="129" t="n"/>
-      <c r="G5" s="132" t="inlineStr">
-        <is>
-          <t>VADE: 7 GÜN</t>
-        </is>
-      </c>
-      <c r="H5" s="128" t="inlineStr">
-        <is>
-          <t>KULLANILABİLİR KREDİ LİMİTİ</t>
-        </is>
-      </c>
-      <c r="I5" s="129" t="n"/>
-      <c r="J5" s="133" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-      <c r="K5" s="134" t="inlineStr">
-        <is>
-          <t>BORÇ SERVİS ORANI (DSCR)</t>
-        </is>
-      </c>
-      <c r="L5" s="129" t="n"/>
-      <c r="M5" s="130" t="inlineStr">
-        <is>
-          <t>EŞİK: 1.25x</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="135" t="n"/>
-      <c r="C6" s="129" t="n"/>
-      <c r="D6" s="129" t="n"/>
-      <c r="E6" s="136" t="n"/>
-      <c r="F6" s="129" t="n"/>
-      <c r="G6" s="129" t="n"/>
-      <c r="H6" s="135" t="n"/>
-      <c r="I6" s="129" t="n"/>
-      <c r="J6" s="129" t="n"/>
-      <c r="K6" s="137" t="n"/>
-      <c r="L6" s="129" t="n"/>
-      <c r="M6" s="129" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="225">
-        <f>GİRDİLER!E17</f>
-        <v/>
-      </c>
-      <c r="C7" s="129" t="n"/>
-      <c r="D7" s="129" t="n"/>
-      <c r="E7" s="226">
-        <f>B7*0.22</f>
-        <v/>
-      </c>
-      <c r="F7" s="129" t="n"/>
-      <c r="G7" s="129" t="n"/>
-      <c r="H7" s="225">
-        <f>B7-E7</f>
-        <v/>
-      </c>
-      <c r="I7" s="129" t="n"/>
-      <c r="J7" s="129" t="n"/>
-      <c r="K7" s="140">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="129" t="n"/>
-      <c r="M7" s="129" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="135" t="n"/>
-      <c r="C8" s="129" t="n"/>
-      <c r="D8" s="129" t="n"/>
-      <c r="E8" s="136" t="n"/>
-      <c r="F8" s="129" t="n"/>
-      <c r="G8" s="129" t="n"/>
-      <c r="H8" s="135" t="n"/>
-      <c r="I8" s="129" t="n"/>
-      <c r="J8" s="129" t="n"/>
-      <c r="K8" s="137" t="n"/>
-      <c r="L8" s="129" t="n"/>
-      <c r="M8" s="129" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="141" t="inlineStr">
-        <is>
-          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
-        </is>
-      </c>
-      <c r="C9" s="129" t="n"/>
-      <c r="D9" s="129" t="n"/>
-      <c r="E9" s="142" t="inlineStr">
-        <is>
-          <t>● 8 Kalem nakit karşılığı: bloke</t>
-        </is>
-      </c>
-      <c r="F9" s="129" t="n"/>
-      <c r="G9" s="129" t="n"/>
-      <c r="H9" s="141" t="inlineStr">
-        <is>
-          <t>██████████░░░░░ %78.0 NET MARJ</t>
-        </is>
-      </c>
-      <c r="I9" s="129" t="n"/>
-      <c r="J9" s="129" t="n"/>
-      <c r="K9" s="143" t="inlineStr">
-        <is>
-          <t>✓ İDEAL karşılama rasyosu</t>
-        </is>
-      </c>
-      <c r="L9" s="129" t="n"/>
-      <c r="M9" s="129" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="74" t="inlineStr">
-        <is>
-          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
-        </is>
-      </c>
-      <c r="F11" s="144" t="inlineStr">
-        <is>
-          <t>+%32 Verim</t>
-        </is>
-      </c>
-      <c r="H11" s="74" t="inlineStr">
-        <is>
-          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="73" t="inlineStr">
-        <is>
-          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
-        </is>
-      </c>
-      <c r="H12" s="73" t="inlineStr">
-        <is>
-          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="145" t="inlineStr">
-        <is>
-          <t>Dönem</t>
-        </is>
-      </c>
-      <c r="C14" s="145" t="inlineStr">
-        <is>
-          <t>Aktif Hacim</t>
-        </is>
-      </c>
-      <c r="D14" s="145" t="inlineStr">
-        <is>
-          <t>Maliyet/Yük</t>
-        </is>
-      </c>
-      <c r="E14" s="145" t="inlineStr">
-        <is>
-          <t>Hedef</t>
-        </is>
-      </c>
-      <c r="H14" s="146" t="inlineStr">
-        <is>
-          <t>PARAMETRE / KALEM</t>
-        </is>
-      </c>
-      <c r="I14" s="146" t="inlineStr">
-        <is>
-          <t>ANA TUTAR</t>
-        </is>
-      </c>
-      <c r="J14" s="146" t="inlineStr">
-        <is>
-          <t>FARK / MARJ</t>
-        </is>
-      </c>
-      <c r="K14" s="146" t="inlineStr">
-        <is>
-          <t>VADE</t>
-        </is>
-      </c>
-      <c r="L14" s="146" t="inlineStr">
-        <is>
-          <t>KONTROL DURUMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="n">
-        <v>65</v>
-      </c>
-      <c r="D15" s="73" t="n">
-        <v>45</v>
-      </c>
-      <c r="E15" s="73" t="n">
-        <v>60</v>
-      </c>
-      <c r="H15" s="147" t="inlineStr">
-        <is>
-          <t>Dönemlik Kümülatif Bakiye</t>
-        </is>
-      </c>
-      <c r="I15" s="227">
-        <f>B7*0.45</f>
-        <v/>
-      </c>
-      <c r="J15" s="228">
-        <f>B7*0.05</f>
-        <v/>
-      </c>
-      <c r="K15" s="149" t="inlineStr">
-        <is>
-          <t>12 Ay</t>
-        </is>
-      </c>
-      <c r="L15" s="133" t="inlineStr">
-        <is>
-          <t>✓ DÜZENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="n">
-        <v>78</v>
-      </c>
-      <c r="D16" s="73" t="n">
-        <v>48</v>
-      </c>
-      <c r="E16" s="73" t="n">
-        <v>70</v>
-      </c>
-      <c r="H16" s="147" t="inlineStr">
-        <is>
-          <t>Kritik Eşik Güvenlik Tamponu</t>
-        </is>
-      </c>
-      <c r="I16" s="227">
-        <f>B7*0.30</f>
-        <v/>
-      </c>
-      <c r="J16" s="228">
-        <f>B7*0.03</f>
-        <v/>
-      </c>
-      <c r="K16" s="149" t="inlineStr">
-        <is>
-          <t>24 Ay</t>
-        </is>
-      </c>
-      <c r="L16" s="130" t="inlineStr">
-        <is>
-          <t>★ AVANTAJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="n">
-        <v>85</v>
-      </c>
-      <c r="D17" s="73" t="n">
-        <v>55</v>
-      </c>
-      <c r="E17" s="73" t="n">
-        <v>80</v>
-      </c>
-      <c r="H17" s="147" t="inlineStr">
-        <is>
-          <t>Operasyonel Net Fark</t>
-        </is>
-      </c>
-      <c r="I17" s="227">
-        <f>B7*0.15</f>
-        <v/>
-      </c>
-      <c r="J17" s="228">
-        <f>B7*0.02</f>
-        <v/>
-      </c>
-      <c r="K17" s="149" t="inlineStr">
-        <is>
-          <t>8 Ay</t>
-        </is>
-      </c>
-      <c r="L17" s="150" t="inlineStr">
-        <is>
-          <t>● YAKLAŞAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="73" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="n">
-        <v>75</v>
-      </c>
-      <c r="D18" s="73" t="n">
-        <v>42</v>
-      </c>
-      <c r="E18" s="73" t="n">
-        <v>75</v>
-      </c>
-      <c r="H18" s="147" t="inlineStr">
-        <is>
-          <t>Rezerv ve Likit Dağılım</t>
-        </is>
-      </c>
-      <c r="I18" s="227">
-        <f>B7*0.10</f>
-        <v/>
-      </c>
-      <c r="J18" s="228">
-        <f>B7*0.01</f>
-        <v/>
-      </c>
-      <c r="K18" s="149" t="inlineStr">
-        <is>
-          <t>16 Ay</t>
-        </is>
-      </c>
-      <c r="L18" s="133" t="inlineStr">
-        <is>
-          <t>✓ TAM UYUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="73" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C19" s="73" t="n">
-        <v>90</v>
-      </c>
-      <c r="D19" s="73" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" s="73" t="n">
-        <v>85</v>
-      </c>
-      <c r="H19" s="151" t="inlineStr">
-        <is>
-          <t>KONSOLİDE SİSTEM TOPLAMI</t>
-        </is>
-      </c>
-      <c r="I19" s="229">
-        <f>TOPLA(I15:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="230">
-        <f>TOPLA(J15:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="154" t="inlineStr"/>
-      <c r="L19" s="155" t="inlineStr">
-        <is>
-          <t>TAM DOĞRULANDI (0 HATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="73" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="n">
-        <v>96</v>
-      </c>
-      <c r="D20" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="E20" s="73" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="156" t="inlineStr">
-        <is>
-          <t>KONSOLİDE PAY VE AĞIRLIK</t>
-        </is>
-      </c>
-      <c r="F22" s="156" t="inlineStr">
-        <is>
-          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
-        </is>
-      </c>
-      <c r="K22" s="157" t="inlineStr">
-        <is>
-          <t>KARAR MOTORU</t>
-        </is>
-      </c>
-      <c r="L22" s="158" t="n"/>
-      <c r="M22" s="158" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="58" t="inlineStr">
-        <is>
-          <t>■ Ana Segment (%42)</t>
-        </is>
-      </c>
-      <c r="F23" s="73" t="inlineStr">
-        <is>
-          <t>Nakit Açığı Riski (30 Gün)</t>
-        </is>
-      </c>
-      <c r="I23" s="159" t="inlineStr">
-        <is>
-          <t>0.00 TL (Sıfır Risk)</t>
-        </is>
-      </c>
-      <c r="K23" s="160" t="inlineStr">
-        <is>
-          <t>REVERSED REFINANSING FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="158" t="n"/>
-      <c r="M23" s="158" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="59" t="inlineStr">
-        <is>
-          <t>■ İkincil Grup (%30)</t>
-        </is>
-      </c>
-      <c r="F24" s="73" t="inlineStr">
-        <is>
-          <t>Tahsilat Gecikme Toleransı</t>
-        </is>
-      </c>
-      <c r="I24" s="159" t="inlineStr">
-        <is>
-          <t>48 Gün Güvenli Eşik</t>
-        </is>
-      </c>
-      <c r="K24" s="161" t="inlineStr">
-        <is>
-          <t>Kredi maliyetini düşürmek için uzun vadeli yapılandırma önerilmektedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="162" t="inlineStr">
-        <is>
-          <t>■ Destek Birimi (%15)</t>
-        </is>
-      </c>
-      <c r="F25" s="58" t="inlineStr">
-        <is>
-          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="163" t="inlineStr">
-        <is>
-          <t>■ Rezervler (%13)</t>
-        </is>
-      </c>
-      <c r="F26" s="164" t="inlineStr">
-        <is>
-          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
-        </is>
-      </c>
-      <c r="K26" s="165" t="inlineStr">
-        <is>
-          <t>YAPILANDIRMA ANALİZİNİ GÖR &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
-    <mergeCell ref="K24:M25"/>
-    <mergeCell ref="F26:I27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20323,1327 +20903,1327 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>REFINANSMAN — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+      <c r="A1" s="270" t="inlineStr">
+        <is>
+          <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="105.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="271" t="inlineStr">
         <is>
           <t>REFİNANSMAN ANALİZİ — aylık taksit rahatlaması ve toplam maliyet.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Teklif ID</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="272" t="inlineStr">
         <is>
           <t>Hedef Kredi ID</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="272" t="inlineStr">
         <is>
           <t>Mevcut Aylık Taksit</t>
         </is>
       </c>
-      <c r="D5" s="86" t="inlineStr">
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Yeni Aylık Taksit</t>
         </is>
       </c>
-      <c r="E5" s="86" t="inlineStr">
+      <c r="E5" s="272" t="inlineStr">
         <is>
           <t>Aylık Taksit Farkı</t>
         </is>
       </c>
-      <c r="F5" s="86" t="inlineStr">
+      <c r="F5" s="272" t="inlineStr">
         <is>
           <t>Nakit Rahatlaması</t>
         </is>
       </c>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Yeni Toplam Maliyet</t>
         </is>
       </c>
-      <c r="H5" s="86" t="inlineStr">
+      <c r="H5" s="272" t="inlineStr">
         <is>
           <t>Mevcut Kalan Anapara</t>
         </is>
       </c>
-      <c r="I5" s="86" t="inlineStr">
+      <c r="I5" s="272" t="inlineStr">
         <is>
           <t>Karar</t>
         </is>
       </c>
-      <c r="J5" s="86" t="inlineStr">
+      <c r="J5" s="272" t="inlineStr">
         <is>
           <t>Kontrol</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="89">
+      <c r="A6" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",YENI_TEKLIFLER!$A6)</f>
         <v/>
       </c>
-      <c r="B6" s="89">
+      <c r="B6" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",YENI_TEKLIFLER!$B6)</f>
         <v/>
       </c>
-      <c r="C6" s="92">
+      <c r="C6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B6,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D6" s="92">
+      <c r="D6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",YENI_TEKLIFLER!$I6)</f>
         <v/>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",$C6-$D6)</f>
         <v/>
       </c>
-      <c r="F6" s="92">
+      <c r="F6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",MAX(0,$E6))</f>
         <v/>
       </c>
-      <c r="G6" s="92">
+      <c r="G6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",YENI_TEKLIFLER!$J6)</f>
         <v/>
       </c>
-      <c r="H6" s="92">
+      <c r="H6" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B6,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I6" s="89">
+      <c r="I6" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",IF($E6&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J6" s="89">
+      <c r="J6" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="89">
+      <c r="A7" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",YENI_TEKLIFLER!$A7)</f>
         <v/>
       </c>
-      <c r="B7" s="89">
+      <c r="B7" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",YENI_TEKLIFLER!$B7)</f>
         <v/>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B7,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",YENI_TEKLIFLER!$I7)</f>
         <v/>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",$C7-$D7)</f>
         <v/>
       </c>
-      <c r="F7" s="92">
+      <c r="F7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",MAX(0,$E7))</f>
         <v/>
       </c>
-      <c r="G7" s="92">
+      <c r="G7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",YENI_TEKLIFLER!$J7)</f>
         <v/>
       </c>
-      <c r="H7" s="92">
+      <c r="H7" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B7,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I7" s="89">
+      <c r="I7" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",IF($E7&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J7" s="89">
+      <c r="J7" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="89">
+      <c r="A8" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",YENI_TEKLIFLER!$A8)</f>
         <v/>
       </c>
-      <c r="B8" s="89">
+      <c r="B8" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",YENI_TEKLIFLER!$B8)</f>
         <v/>
       </c>
-      <c r="C8" s="92">
+      <c r="C8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B8,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",YENI_TEKLIFLER!$I8)</f>
         <v/>
       </c>
-      <c r="E8" s="92">
+      <c r="E8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",$C8-$D8)</f>
         <v/>
       </c>
-      <c r="F8" s="92">
+      <c r="F8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",MAX(0,$E8))</f>
         <v/>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",YENI_TEKLIFLER!$J8)</f>
         <v/>
       </c>
-      <c r="H8" s="92">
+      <c r="H8" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B8,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",IF($E8&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="89">
+      <c r="A9" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",YENI_TEKLIFLER!$A9)</f>
         <v/>
       </c>
-      <c r="B9" s="89">
+      <c r="B9" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",YENI_TEKLIFLER!$B9)</f>
         <v/>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B9,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",YENI_TEKLIFLER!$I9)</f>
         <v/>
       </c>
-      <c r="E9" s="92">
+      <c r="E9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",$C9-$D9)</f>
         <v/>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",MAX(0,$E9))</f>
         <v/>
       </c>
-      <c r="G9" s="92">
+      <c r="G9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",YENI_TEKLIFLER!$J9)</f>
         <v/>
       </c>
-      <c r="H9" s="92">
+      <c r="H9" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B9,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",IF($E9&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="89">
+      <c r="A10" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",YENI_TEKLIFLER!$A10)</f>
         <v/>
       </c>
-      <c r="B10" s="89">
+      <c r="B10" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",YENI_TEKLIFLER!$B10)</f>
         <v/>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B10,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",YENI_TEKLIFLER!$I10)</f>
         <v/>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",$C10-$D10)</f>
         <v/>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",MAX(0,$E10))</f>
         <v/>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",YENI_TEKLIFLER!$J10)</f>
         <v/>
       </c>
-      <c r="H10" s="92">
+      <c r="H10" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B10,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I10" s="89">
+      <c r="I10" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",IF($E10&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J10" s="89">
+      <c r="J10" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A10),"",IF(OR(ISBLANK($B10),ISBLANK($C10),ISBLANK($D10),ISBLANK($E10),ISBLANK($F10),ISBLANK($G10),ISBLANK($H10)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="89">
+      <c r="A11" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",YENI_TEKLIFLER!$A11)</f>
         <v/>
       </c>
-      <c r="B11" s="89">
+      <c r="B11" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",YENI_TEKLIFLER!$B11)</f>
         <v/>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B11,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",YENI_TEKLIFLER!$I11)</f>
         <v/>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",$C11-$D11)</f>
         <v/>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",MAX(0,$E11))</f>
         <v/>
       </c>
-      <c r="G11" s="92">
+      <c r="G11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",YENI_TEKLIFLER!$J11)</f>
         <v/>
       </c>
-      <c r="H11" s="92">
+      <c r="H11" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B11,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I11" s="89">
+      <c r="I11" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",IF($E11&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J11" s="89">
+      <c r="J11" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A11),"",IF(OR(ISBLANK($B11),ISBLANK($C11),ISBLANK($D11),ISBLANK($E11),ISBLANK($F11),ISBLANK($G11),ISBLANK($H11)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="50">
-      <c r="A12" s="89">
+      <c r="A12" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",YENI_TEKLIFLER!$A12)</f>
         <v/>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",YENI_TEKLIFLER!$B12)</f>
         <v/>
       </c>
-      <c r="C12" s="92">
+      <c r="C12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B12,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",YENI_TEKLIFLER!$I12)</f>
         <v/>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",MAX(0,$E12))</f>
         <v/>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",YENI_TEKLIFLER!$J12)</f>
         <v/>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B12,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I12" s="89">
+      <c r="I12" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",IF($E12&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J12" s="89">
+      <c r="J12" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A12),"",IF(OR(ISBLANK($B12),ISBLANK($C12),ISBLANK($D12),ISBLANK($E12),ISBLANK($F12),ISBLANK($G12),ISBLANK($H12)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="50">
-      <c r="A13" s="89">
+      <c r="A13" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",YENI_TEKLIFLER!$A13)</f>
         <v/>
       </c>
-      <c r="B13" s="89">
+      <c r="B13" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",YENI_TEKLIFLER!$B13)</f>
         <v/>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B13,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",YENI_TEKLIFLER!$I13)</f>
         <v/>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",MAX(0,$E13))</f>
         <v/>
       </c>
-      <c r="G13" s="92">
+      <c r="G13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",YENI_TEKLIFLER!$J13)</f>
         <v/>
       </c>
-      <c r="H13" s="92">
+      <c r="H13" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B13,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I13" s="89">
+      <c r="I13" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",IF($E13&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J13" s="89">
+      <c r="J13" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A13),"",IF(OR(ISBLANK($B13),ISBLANK($C13),ISBLANK($D13),ISBLANK($E13),ISBLANK($F13),ISBLANK($G13),ISBLANK($H13)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="50">
-      <c r="A14" s="89">
+      <c r="A14" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",YENI_TEKLIFLER!$A14)</f>
         <v/>
       </c>
-      <c r="B14" s="89">
+      <c r="B14" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",YENI_TEKLIFLER!$B14)</f>
         <v/>
       </c>
-      <c r="C14" s="92">
+      <c r="C14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B14,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",YENI_TEKLIFLER!$I14)</f>
         <v/>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",MAX(0,$E14))</f>
         <v/>
       </c>
-      <c r="G14" s="92">
+      <c r="G14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",YENI_TEKLIFLER!$J14)</f>
         <v/>
       </c>
-      <c r="H14" s="92">
+      <c r="H14" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B14,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I14" s="89">
+      <c r="I14" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",IF($E14&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J14" s="89">
+      <c r="J14" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A14),"",IF(OR(ISBLANK($B14),ISBLANK($C14),ISBLANK($D14),ISBLANK($E14),ISBLANK($F14),ISBLANK($G14),ISBLANK($H14)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="50">
-      <c r="A15" s="89">
+      <c r="A15" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",YENI_TEKLIFLER!$A15)</f>
         <v/>
       </c>
-      <c r="B15" s="89">
+      <c r="B15" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",YENI_TEKLIFLER!$B15)</f>
         <v/>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B15,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",YENI_TEKLIFLER!$I15)</f>
         <v/>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="92">
+      <c r="F15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",MAX(0,$E15))</f>
         <v/>
       </c>
-      <c r="G15" s="92">
+      <c r="G15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",YENI_TEKLIFLER!$J15)</f>
         <v/>
       </c>
-      <c r="H15" s="92">
+      <c r="H15" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B15,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I15" s="89">
+      <c r="I15" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",IF($E15&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J15" s="89">
+      <c r="J15" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A15),"",IF(OR(ISBLANK($B15),ISBLANK($C15),ISBLANK($D15),ISBLANK($E15),ISBLANK($F15),ISBLANK($G15),ISBLANK($H15)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="50">
-      <c r="A16" s="89">
+      <c r="A16" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",YENI_TEKLIFLER!$A16)</f>
         <v/>
       </c>
-      <c r="B16" s="89">
+      <c r="B16" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",YENI_TEKLIFLER!$B16)</f>
         <v/>
       </c>
-      <c r="C16" s="92">
+      <c r="C16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B16,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",YENI_TEKLIFLER!$I16)</f>
         <v/>
       </c>
-      <c r="E16" s="92">
+      <c r="E16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",MAX(0,$E16))</f>
         <v/>
       </c>
-      <c r="G16" s="92">
+      <c r="G16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",YENI_TEKLIFLER!$J16)</f>
         <v/>
       </c>
-      <c r="H16" s="92">
+      <c r="H16" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B16,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I16" s="89">
+      <c r="I16" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",IF($E16&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J16" s="89">
+      <c r="J16" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A16),"",IF(OR(ISBLANK($B16),ISBLANK($C16),ISBLANK($D16),ISBLANK($E16),ISBLANK($F16),ISBLANK($G16),ISBLANK($H16)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="50">
-      <c r="A17" s="89">
+      <c r="A17" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",YENI_TEKLIFLER!$A17)</f>
         <v/>
       </c>
-      <c r="B17" s="89">
+      <c r="B17" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",YENI_TEKLIFLER!$B17)</f>
         <v/>
       </c>
-      <c r="C17" s="92">
+      <c r="C17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B17,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",YENI_TEKLIFLER!$I17)</f>
         <v/>
       </c>
-      <c r="E17" s="92">
+      <c r="E17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="92">
+      <c r="F17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",MAX(0,$E17))</f>
         <v/>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",YENI_TEKLIFLER!$J17)</f>
         <v/>
       </c>
-      <c r="H17" s="92">
+      <c r="H17" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B17,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I17" s="89">
+      <c r="I17" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",IF($E17&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J17" s="89">
+      <c r="J17" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A17),"",IF(OR(ISBLANK($B17),ISBLANK($C17),ISBLANK($D17),ISBLANK($E17),ISBLANK($F17),ISBLANK($G17),ISBLANK($H17)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="50">
-      <c r="A18" s="89">
+      <c r="A18" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",YENI_TEKLIFLER!$A18)</f>
         <v/>
       </c>
-      <c r="B18" s="89">
+      <c r="B18" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",YENI_TEKLIFLER!$B18)</f>
         <v/>
       </c>
-      <c r="C18" s="92">
+      <c r="C18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B18,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",YENI_TEKLIFLER!$I18)</f>
         <v/>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="92">
+      <c r="F18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",MAX(0,$E18))</f>
         <v/>
       </c>
-      <c r="G18" s="92">
+      <c r="G18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",YENI_TEKLIFLER!$J18)</f>
         <v/>
       </c>
-      <c r="H18" s="92">
+      <c r="H18" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B18,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I18" s="89">
+      <c r="I18" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",IF($E18&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J18" s="89">
+      <c r="J18" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A18),"",IF(OR(ISBLANK($B18),ISBLANK($C18),ISBLANK($D18),ISBLANK($E18),ISBLANK($F18),ISBLANK($G18),ISBLANK($H18)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="50">
-      <c r="A19" s="89">
+      <c r="A19" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",YENI_TEKLIFLER!$A19)</f>
         <v/>
       </c>
-      <c r="B19" s="89">
+      <c r="B19" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",YENI_TEKLIFLER!$B19)</f>
         <v/>
       </c>
-      <c r="C19" s="92">
+      <c r="C19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B19,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",YENI_TEKLIFLER!$I19)</f>
         <v/>
       </c>
-      <c r="E19" s="92">
+      <c r="E19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="92">
+      <c r="F19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",MAX(0,$E19))</f>
         <v/>
       </c>
-      <c r="G19" s="92">
+      <c r="G19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",YENI_TEKLIFLER!$J19)</f>
         <v/>
       </c>
-      <c r="H19" s="92">
+      <c r="H19" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B19,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I19" s="89">
+      <c r="I19" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",IF($E19&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J19" s="89">
+      <c r="J19" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A19),"",IF(OR(ISBLANK($B19),ISBLANK($C19),ISBLANK($D19),ISBLANK($E19),ISBLANK($F19),ISBLANK($G19),ISBLANK($H19)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="50">
-      <c r="A20" s="89">
+      <c r="A20" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",YENI_TEKLIFLER!$A20)</f>
         <v/>
       </c>
-      <c r="B20" s="89">
+      <c r="B20" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",YENI_TEKLIFLER!$B20)</f>
         <v/>
       </c>
-      <c r="C20" s="92">
+      <c r="C20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B20,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",YENI_TEKLIFLER!$I20)</f>
         <v/>
       </c>
-      <c r="E20" s="92">
+      <c r="E20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="92">
+      <c r="F20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",MAX(0,$E20))</f>
         <v/>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",YENI_TEKLIFLER!$J20)</f>
         <v/>
       </c>
-      <c r="H20" s="92">
+      <c r="H20" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B20,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I20" s="89">
+      <c r="I20" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",IF($E20&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J20" s="89">
+      <c r="J20" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A20),"",IF(OR(ISBLANK($B20),ISBLANK($C20),ISBLANK($D20),ISBLANK($E20),ISBLANK($F20),ISBLANK($G20),ISBLANK($H20)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="50">
-      <c r="A21" s="89">
+      <c r="A21" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",YENI_TEKLIFLER!$A21)</f>
         <v/>
       </c>
-      <c r="B21" s="89">
+      <c r="B21" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",YENI_TEKLIFLER!$B21)</f>
         <v/>
       </c>
-      <c r="C21" s="92">
+      <c r="C21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B21,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D21" s="92">
+      <c r="D21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",YENI_TEKLIFLER!$I21)</f>
         <v/>
       </c>
-      <c r="E21" s="92">
+      <c r="E21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",MAX(0,$E21))</f>
         <v/>
       </c>
-      <c r="G21" s="92">
+      <c r="G21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",YENI_TEKLIFLER!$J21)</f>
         <v/>
       </c>
-      <c r="H21" s="92">
+      <c r="H21" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B21,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I21" s="89">
+      <c r="I21" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",IF($E21&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J21" s="89">
+      <c r="J21" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A21),"",IF(OR(ISBLANK($B21),ISBLANK($C21),ISBLANK($D21),ISBLANK($E21),ISBLANK($F21),ISBLANK($G21),ISBLANK($H21)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="50">
-      <c r="A22" s="89">
+      <c r="A22" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",YENI_TEKLIFLER!$A22)</f>
         <v/>
       </c>
-      <c r="B22" s="89">
+      <c r="B22" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",YENI_TEKLIFLER!$B22)</f>
         <v/>
       </c>
-      <c r="C22" s="92">
+      <c r="C22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B22,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",YENI_TEKLIFLER!$I22)</f>
         <v/>
       </c>
-      <c r="E22" s="92">
+      <c r="E22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="92">
+      <c r="F22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",MAX(0,$E22))</f>
         <v/>
       </c>
-      <c r="G22" s="92">
+      <c r="G22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",YENI_TEKLIFLER!$J22)</f>
         <v/>
       </c>
-      <c r="H22" s="92">
+      <c r="H22" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B22,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I22" s="89">
+      <c r="I22" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",IF($E22&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J22" s="89">
+      <c r="J22" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A22),"",IF(OR(ISBLANK($B22),ISBLANK($C22),ISBLANK($D22),ISBLANK($E22),ISBLANK($F22),ISBLANK($G22),ISBLANK($H22)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="50">
-      <c r="A23" s="89">
+      <c r="A23" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",YENI_TEKLIFLER!$A23)</f>
         <v/>
       </c>
-      <c r="B23" s="89">
+      <c r="B23" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",YENI_TEKLIFLER!$B23)</f>
         <v/>
       </c>
-      <c r="C23" s="92">
+      <c r="C23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B23,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",YENI_TEKLIFLER!$I23)</f>
         <v/>
       </c>
-      <c r="E23" s="92">
+      <c r="E23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="92">
+      <c r="F23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",MAX(0,$E23))</f>
         <v/>
       </c>
-      <c r="G23" s="92">
+      <c r="G23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",YENI_TEKLIFLER!$J23)</f>
         <v/>
       </c>
-      <c r="H23" s="92">
+      <c r="H23" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B23,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I23" s="89">
+      <c r="I23" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",IF($E23&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J23" s="89">
+      <c r="J23" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A23),"",IF(OR(ISBLANK($B23),ISBLANK($C23),ISBLANK($D23),ISBLANK($E23),ISBLANK($F23),ISBLANK($G23),ISBLANK($H23)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="50">
-      <c r="A24" s="89">
+      <c r="A24" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",YENI_TEKLIFLER!$A24)</f>
         <v/>
       </c>
-      <c r="B24" s="89">
+      <c r="B24" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",YENI_TEKLIFLER!$B24)</f>
         <v/>
       </c>
-      <c r="C24" s="92">
+      <c r="C24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B24,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D24" s="92">
+      <c r="D24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",YENI_TEKLIFLER!$I24)</f>
         <v/>
       </c>
-      <c r="E24" s="92">
+      <c r="E24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="92">
+      <c r="F24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",MAX(0,$E24))</f>
         <v/>
       </c>
-      <c r="G24" s="92">
+      <c r="G24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",YENI_TEKLIFLER!$J24)</f>
         <v/>
       </c>
-      <c r="H24" s="92">
+      <c r="H24" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B24,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I24" s="89">
+      <c r="I24" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",IF($E24&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J24" s="89">
+      <c r="J24" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A24),"",IF(OR(ISBLANK($B24),ISBLANK($C24),ISBLANK($D24),ISBLANK($E24),ISBLANK($F24),ISBLANK($G24),ISBLANK($H24)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="50">
-      <c r="A25" s="89">
+      <c r="A25" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",YENI_TEKLIFLER!$A25)</f>
         <v/>
       </c>
-      <c r="B25" s="89">
+      <c r="B25" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",YENI_TEKLIFLER!$B25)</f>
         <v/>
       </c>
-      <c r="C25" s="92">
+      <c r="C25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B25,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D25" s="92">
+      <c r="D25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",YENI_TEKLIFLER!$I25)</f>
         <v/>
       </c>
-      <c r="E25" s="92">
+      <c r="E25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="92">
+      <c r="F25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",MAX(0,$E25))</f>
         <v/>
       </c>
-      <c r="G25" s="92">
+      <c r="G25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",YENI_TEKLIFLER!$J25)</f>
         <v/>
       </c>
-      <c r="H25" s="92">
+      <c r="H25" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B25,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I25" s="89">
+      <c r="I25" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",IF($E25&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J25" s="89">
+      <c r="J25" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A25),"",IF(OR(ISBLANK($B25),ISBLANK($C25),ISBLANK($D25),ISBLANK($E25),ISBLANK($F25),ISBLANK($G25),ISBLANK($H25)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="50">
-      <c r="A26" s="89">
+      <c r="A26" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",YENI_TEKLIFLER!$A26)</f>
         <v/>
       </c>
-      <c r="B26" s="89">
+      <c r="B26" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",YENI_TEKLIFLER!$B26)</f>
         <v/>
       </c>
-      <c r="C26" s="92">
+      <c r="C26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B26,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",YENI_TEKLIFLER!$I26)</f>
         <v/>
       </c>
-      <c r="E26" s="92">
+      <c r="E26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="92">
+      <c r="F26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",MAX(0,$E26))</f>
         <v/>
       </c>
-      <c r="G26" s="92">
+      <c r="G26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",YENI_TEKLIFLER!$J26)</f>
         <v/>
       </c>
-      <c r="H26" s="92">
+      <c r="H26" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B26,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I26" s="89">
+      <c r="I26" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",IF($E26&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J26" s="89">
+      <c r="J26" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A26),"",IF(OR(ISBLANK($B26),ISBLANK($C26),ISBLANK($D26),ISBLANK($E26),ISBLANK($F26),ISBLANK($G26),ISBLANK($H26)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="50">
-      <c r="A27" s="89">
+      <c r="A27" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",YENI_TEKLIFLER!$A27)</f>
         <v/>
       </c>
-      <c r="B27" s="89">
+      <c r="B27" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",YENI_TEKLIFLER!$B27)</f>
         <v/>
       </c>
-      <c r="C27" s="92">
+      <c r="C27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B27,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D27" s="92">
+      <c r="D27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",YENI_TEKLIFLER!$I27)</f>
         <v/>
       </c>
-      <c r="E27" s="92">
+      <c r="E27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="92">
+      <c r="F27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",MAX(0,$E27))</f>
         <v/>
       </c>
-      <c r="G27" s="92">
+      <c r="G27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",YENI_TEKLIFLER!$J27)</f>
         <v/>
       </c>
-      <c r="H27" s="92">
+      <c r="H27" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B27,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I27" s="89">
+      <c r="I27" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",IF($E27&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J27" s="89">
+      <c r="J27" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A27),"",IF(OR(ISBLANK($B27),ISBLANK($C27),ISBLANK($D27),ISBLANK($E27),ISBLANK($F27),ISBLANK($G27),ISBLANK($H27)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="50">
-      <c r="A28" s="89">
+      <c r="A28" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",YENI_TEKLIFLER!$A28)</f>
         <v/>
       </c>
-      <c r="B28" s="89">
+      <c r="B28" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",YENI_TEKLIFLER!$B28)</f>
         <v/>
       </c>
-      <c r="C28" s="92">
+      <c r="C28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B28,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D28" s="92">
+      <c r="D28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",YENI_TEKLIFLER!$I28)</f>
         <v/>
       </c>
-      <c r="E28" s="92">
+      <c r="E28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="92">
+      <c r="F28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",MAX(0,$E28))</f>
         <v/>
       </c>
-      <c r="G28" s="92">
+      <c r="G28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",YENI_TEKLIFLER!$J28)</f>
         <v/>
       </c>
-      <c r="H28" s="92">
+      <c r="H28" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B28,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I28" s="89">
+      <c r="I28" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",IF($E28&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J28" s="89">
+      <c r="J28" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A28),"",IF(OR(ISBLANK($B28),ISBLANK($C28),ISBLANK($D28),ISBLANK($E28),ISBLANK($F28),ISBLANK($G28),ISBLANK($H28)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="50">
-      <c r="A29" s="89">
+      <c r="A29" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",YENI_TEKLIFLER!$A29)</f>
         <v/>
       </c>
-      <c r="B29" s="89">
+      <c r="B29" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",YENI_TEKLIFLER!$B29)</f>
         <v/>
       </c>
-      <c r="C29" s="92">
+      <c r="C29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B29,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D29" s="92">
+      <c r="D29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",YENI_TEKLIFLER!$I29)</f>
         <v/>
       </c>
-      <c r="E29" s="92">
+      <c r="E29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="92">
+      <c r="F29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",MAX(0,$E29))</f>
         <v/>
       </c>
-      <c r="G29" s="92">
+      <c r="G29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",YENI_TEKLIFLER!$J29)</f>
         <v/>
       </c>
-      <c r="H29" s="92">
+      <c r="H29" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B29,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I29" s="89">
+      <c r="I29" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",IF($E29&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J29" s="89">
+      <c r="J29" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A29),"",IF(OR(ISBLANK($B29),ISBLANK($C29),ISBLANK($D29),ISBLANK($E29),ISBLANK($F29),ISBLANK($G29),ISBLANK($H29)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="50">
-      <c r="A30" s="89">
+      <c r="A30" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",YENI_TEKLIFLER!$A30)</f>
         <v/>
       </c>
-      <c r="B30" s="89">
+      <c r="B30" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",YENI_TEKLIFLER!$B30)</f>
         <v/>
       </c>
-      <c r="C30" s="92">
+      <c r="C30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B30,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D30" s="92">
+      <c r="D30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",YENI_TEKLIFLER!$I30)</f>
         <v/>
       </c>
-      <c r="E30" s="92">
+      <c r="E30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="92">
+      <c r="F30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",MAX(0,$E30))</f>
         <v/>
       </c>
-      <c r="G30" s="92">
+      <c r="G30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",YENI_TEKLIFLER!$J30)</f>
         <v/>
       </c>
-      <c r="H30" s="92">
+      <c r="H30" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B30,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I30" s="89">
+      <c r="I30" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",IF($E30&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J30" s="89">
+      <c r="J30" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A30),"",IF(OR(ISBLANK($B30),ISBLANK($C30),ISBLANK($D30),ISBLANK($E30),ISBLANK($F30),ISBLANK($G30),ISBLANK($H30)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="50">
-      <c r="A31" s="89">
+      <c r="A31" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",YENI_TEKLIFLER!$A31)</f>
         <v/>
       </c>
-      <c r="B31" s="89">
+      <c r="B31" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",YENI_TEKLIFLER!$B31)</f>
         <v/>
       </c>
-      <c r="C31" s="92">
+      <c r="C31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B31,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D31" s="92">
+      <c r="D31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",YENI_TEKLIFLER!$I31)</f>
         <v/>
       </c>
-      <c r="E31" s="92">
+      <c r="E31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="92">
+      <c r="F31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",MAX(0,$E31))</f>
         <v/>
       </c>
-      <c r="G31" s="92">
+      <c r="G31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",YENI_TEKLIFLER!$J31)</f>
         <v/>
       </c>
-      <c r="H31" s="92">
+      <c r="H31" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B31,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I31" s="89">
+      <c r="I31" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",IF($E31&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J31" s="89">
+      <c r="J31" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A31),"",IF(OR(ISBLANK($B31),ISBLANK($C31),ISBLANK($D31),ISBLANK($E31),ISBLANK($F31),ISBLANK($G31),ISBLANK($H31)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="50">
-      <c r="A32" s="89">
+      <c r="A32" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",YENI_TEKLIFLER!$A32)</f>
         <v/>
       </c>
-      <c r="B32" s="89">
+      <c r="B32" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",YENI_TEKLIFLER!$B32)</f>
         <v/>
       </c>
-      <c r="C32" s="92">
+      <c r="C32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B32,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",YENI_TEKLIFLER!$I32)</f>
         <v/>
       </c>
-      <c r="E32" s="92">
+      <c r="E32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="92">
+      <c r="F32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",MAX(0,$E32))</f>
         <v/>
       </c>
-      <c r="G32" s="92">
+      <c r="G32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",YENI_TEKLIFLER!$J32)</f>
         <v/>
       </c>
-      <c r="H32" s="92">
+      <c r="H32" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B32,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I32" s="89">
+      <c r="I32" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",IF($E32&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J32" s="89">
+      <c r="J32" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A32),"",IF(OR(ISBLANK($B32),ISBLANK($C32),ISBLANK($D32),ISBLANK($E32),ISBLANK($F32),ISBLANK($G32),ISBLANK($H32)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="50">
-      <c r="A33" s="89">
+      <c r="A33" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",YENI_TEKLIFLER!$A33)</f>
         <v/>
       </c>
-      <c r="B33" s="89">
+      <c r="B33" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",YENI_TEKLIFLER!$B33)</f>
         <v/>
       </c>
-      <c r="C33" s="92">
+      <c r="C33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B33,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D33" s="92">
+      <c r="D33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",YENI_TEKLIFLER!$I33)</f>
         <v/>
       </c>
-      <c r="E33" s="92">
+      <c r="E33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="92">
+      <c r="F33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",MAX(0,$E33))</f>
         <v/>
       </c>
-      <c r="G33" s="92">
+      <c r="G33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",YENI_TEKLIFLER!$J33)</f>
         <v/>
       </c>
-      <c r="H33" s="92">
+      <c r="H33" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B33,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I33" s="89">
+      <c r="I33" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",IF($E33&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J33" s="89">
+      <c r="J33" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A33),"",IF(OR(ISBLANK($B33),ISBLANK($C33),ISBLANK($D33),ISBLANK($E33),ISBLANK($F33),ISBLANK($G33),ISBLANK($H33)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="50">
-      <c r="A34" s="89">
+      <c r="A34" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",YENI_TEKLIFLER!$A34)</f>
         <v/>
       </c>
-      <c r="B34" s="89">
+      <c r="B34" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",YENI_TEKLIFLER!$B34)</f>
         <v/>
       </c>
-      <c r="C34" s="92">
+      <c r="C34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B34,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D34" s="92">
+      <c r="D34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",YENI_TEKLIFLER!$I34)</f>
         <v/>
       </c>
-      <c r="E34" s="92">
+      <c r="E34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="92">
+      <c r="F34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",MAX(0,$E34))</f>
         <v/>
       </c>
-      <c r="G34" s="92">
+      <c r="G34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",YENI_TEKLIFLER!$J34)</f>
         <v/>
       </c>
-      <c r="H34" s="92">
+      <c r="H34" s="278">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B34,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I34" s="89">
+      <c r="I34" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",IF($E34&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J34" s="89">
+      <c r="J34" s="275">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A34),"",IF(OR(ISBLANK($B34),ISBLANK($C34),ISBLANK($D34),ISBLANK($E34),ISBLANK($F34),ISBLANK($G34),ISBLANK($H34)),"EKSİK","OK"))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="50">
-      <c r="A35" s="89">
+      <c r="A35" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",YENI_TEKLIFLER!$A35)</f>
         <v/>
       </c>
-      <c r="B35" s="89">
+      <c r="B35" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",YENI_TEKLIFLER!$B35)</f>
         <v/>
       </c>
-      <c r="C35" s="92">
+      <c r="C35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",SUMIFS(TAKSIT_PLANI!$I$6:$I$1000,TAKSIT_PLANI!$B$6:$B$1000,YENI_TEKLIFLER!$B35,TAKSIT_PLANI!$C$6:$C$1000,1))</f>
         <v/>
       </c>
-      <c r="D35" s="92">
+      <c r="D35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",YENI_TEKLIFLER!$I35)</f>
         <v/>
       </c>
-      <c r="E35" s="92">
+      <c r="E35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",$C35-$D35)</f>
         <v/>
       </c>
-      <c r="F35" s="92">
+      <c r="F35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",MAX(0,$E35))</f>
         <v/>
       </c>
-      <c r="G35" s="92">
+      <c r="G35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",YENI_TEKLIFLER!$J35)</f>
         <v/>
       </c>
-      <c r="H35" s="92">
+      <c r="H35" s="280">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",INDEX(KREDILER!$H$6:$H$1000,MATCH(YENI_TEKLIFLER!$B35,KREDILER!$A$6:$A$1000,0)))</f>
         <v/>
       </c>
-      <c r="I35" s="89">
+      <c r="I35" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",IF($E35&gt;0,"ADAY","DEĞİL"))</f>
         <v/>
       </c>
-      <c r="J35" s="89">
+      <c r="J35" s="276">
         <f>IF(ISBLANK(YENI_TEKLIFLER!$A35),"",IF(OR(ISBLANK($B35),ISBLANK($C35),ISBLANK($D35),ISBLANK($E35),ISBLANK($F35),ISBLANK($G35),ISBLANK($H35)),"EKSİK","OK"))</f>
         <v/>
       </c>
@@ -21680,7 +22260,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21858,7 +22438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22441,7 +23021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22686,7 +23266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22952,7 +23532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23139,7 +23719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23297,7 +23877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23465,7 +24045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23684,79 +24264,6 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:AN6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="14" customWidth="1" style="76" min="2" max="2"/>
-    <col width="90" customWidth="1" style="76" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
-        <is>
-          <t>DEĞİŞİKLİK KAYDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t>Sürüm</t>
-        </is>
-      </c>
-      <c r="B5" s="86" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="C5" s="86" t="inlineStr">
-        <is>
-          <t>Açıklama</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="120" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B6" s="120" t="inlineStr">
-        <is>
-          <t>08.08.2026</t>
-        </is>
-      </c>
-      <c r="C6" s="115" t="inlineStr">
-        <is>
-          <t>İlk sürüm: banka limitleri, kredi portföyü, taksit planı, refinansman analizi ve karar motoru.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -23794,9 +24301,12 @@
     <row r="3">
       <c r="B3" s="166" t="inlineStr">
         <is>
-          <t>🔍  BANKA, KREDI VE TAKSIT TAKIP SISTEMI — Kayıt veya hesap ara...</t>
-        </is>
-      </c>
+          <t>🔍  KREDİ PORTFÖYÜ VE OPERASYONEL BORÇ SERVİSİ HAVUZU — Arama &amp; Filtre</t>
+        </is>
+      </c>
+      <c r="C3" s="252" t="n"/>
+      <c r="D3" s="252" t="n"/>
+      <c r="E3" s="253" t="n"/>
       <c r="G3" s="167" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -23811,77 +24321,76 @@
     <row r="5">
       <c r="B5" s="169" t="inlineStr">
         <is>
-          <t>TARİH</t>
+          <t>VADE TARİHİ</t>
         </is>
       </c>
       <c r="C5" s="169" t="inlineStr">
         <is>
-          <t>REFERANS NO</t>
+          <t>KREDİ ID</t>
         </is>
       </c>
       <c r="D5" s="169" t="inlineStr">
         <is>
-          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+          <t>BANKA &amp; KREDİ TÜRÜ</t>
         </is>
       </c>
       <c r="E5" s="169" t="inlineStr">
         <is>
-          <t>BRÜT TUTAR (₺)</t>
+          <t>TAKSİT TUTARI (₺)</t>
         </is>
       </c>
       <c r="F5" s="169" t="inlineStr">
         <is>
-          <t>KDV ORANI</t>
+          <t>FAİZ ORANI / PAYI</t>
         </is>
       </c>
       <c r="G5" s="169" t="inlineStr">
         <is>
-          <t>NET TUTAR (₺)</t>
+          <t>ANAPARA TUTARI (₺)</t>
         </is>
       </c>
       <c r="H5" s="169" t="inlineStr">
         <is>
-          <t>HESAP / CARİ</t>
+          <t>ÖDEME DURUMU</t>
         </is>
       </c>
       <c r="I5" s="169" t="inlineStr">
         <is>
-          <t>DURUM</t>
+          <t>SİSTEM KONTROLÜ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="170" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>15.01.2026</t>
         </is>
       </c>
       <c r="C6" s="171" t="inlineStr">
         <is>
-          <t>TR-0428-A</t>
+          <t>KRD-001</t>
         </is>
       </c>
       <c r="D6" s="172" t="inlineStr">
         <is>
-          <t>Operasyonel ana kalem tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="231" t="n">
-        <v>845200</v>
-      </c>
-      <c r="F6" s="174" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G6" s="175">
-        <f>E6/(1+F6)</f>
-        <v/>
+          <t>Türkiye İş Bankası · Taksitli Ticari</t>
+        </is>
+      </c>
+      <c r="E6" s="254" t="n">
+        <v>620000</v>
+      </c>
+      <c r="F6" s="255" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G6" s="175" t="n">
+        <v>326000</v>
       </c>
       <c r="H6" s="172" t="inlineStr">
         <is>
-          <t>Vadesiz Ticari</t>
-        </is>
-      </c>
-      <c r="I6" s="176" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I6" s="256" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -23890,72 +24399,70 @@
     <row r="7">
       <c r="B7" s="177" t="inlineStr">
         <is>
-          <t>14.10.2026</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="C7" s="178" t="inlineStr">
         <is>
-          <t>TR-0429-B</t>
+          <t>KRD-001</t>
         </is>
       </c>
       <c r="D7" s="179" t="inlineStr">
         <is>
-          <t>Operasyonel çıkış/maliyet tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="231" t="n">
-        <v>1240000</v>
-      </c>
-      <c r="F7" s="181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="182">
-        <f>E7/(1+F7)</f>
-        <v/>
+          <t>Türkiye İş Bankası · Taksitli Ticari</t>
+        </is>
+      </c>
+      <c r="E7" s="254" t="n">
+        <v>620000</v>
+      </c>
+      <c r="F7" s="257" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G7" s="182" t="n">
+        <v>337000</v>
       </c>
       <c r="H7" s="179" t="inlineStr">
         <is>
-          <t>Tedarikçi Havuzu</t>
-        </is>
-      </c>
-      <c r="I7" s="183" t="inlineStr">
-        <is>
-          <t>BEKLEMEDE</t>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I7" s="258" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="170" t="inlineStr">
         <is>
-          <t>18.10.2026</t>
+          <t>15.03.2026</t>
         </is>
       </c>
       <c r="C8" s="171" t="inlineStr">
         <is>
-          <t>TR-0430-C</t>
+          <t>KRD-002</t>
         </is>
       </c>
       <c r="D8" s="172" t="inlineStr">
         <is>
-          <t>Ödeme takvimi tahakkuku</t>
-        </is>
-      </c>
-      <c r="E8" s="231" t="n">
-        <v>620500</v>
-      </c>
-      <c r="F8" s="174" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="175">
-        <f>E8/(1+F8)</f>
-        <v/>
+          <t>Akbank · Ticari Leasing</t>
+        </is>
+      </c>
+      <c r="E8" s="254" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F8" s="255" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G8" s="175" t="n">
+        <v>117000</v>
       </c>
       <c r="H8" s="172" t="inlineStr">
         <is>
-          <t>Kısa Vade Tahakkuk</t>
-        </is>
-      </c>
-      <c r="I8" s="176" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I8" s="256" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -23964,35 +24471,34 @@
     <row r="9">
       <c r="B9" s="177" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>15.04.2026</t>
         </is>
       </c>
       <c r="C9" s="178" t="inlineStr">
         <is>
-          <t>TR-0431-D</t>
+          <t>KRD-002</t>
         </is>
       </c>
       <c r="D9" s="179" t="inlineStr">
         <is>
-          <t>Müşteri işlem tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="231" t="n">
-        <v>415000</v>
-      </c>
-      <c r="F9" s="181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="182">
-        <f>E9/(1+F9)</f>
-        <v/>
+          <t>Akbank · Ticari Leasing</t>
+        </is>
+      </c>
+      <c r="E9" s="254" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F9" s="257" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G9" s="182" t="n">
+        <v>121000</v>
       </c>
       <c r="H9" s="179" t="inlineStr">
         <is>
-          <t>Müşteri Alacağı</t>
-        </is>
-      </c>
-      <c r="I9" s="184" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I9" s="258" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24001,35 +24507,34 @@
     <row r="10">
       <c r="B10" s="170" t="inlineStr">
         <is>
-          <t>25.10.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="C10" s="171" t="inlineStr">
         <is>
-          <t>TR-0432-E</t>
+          <t>KRD-003</t>
         </is>
       </c>
       <c r="D10" s="172" t="inlineStr">
         <is>
-          <t>Ana operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="231" t="n">
-        <v>980400</v>
-      </c>
-      <c r="F10" s="174" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="175">
-        <f>E10/(1+F10)</f>
-        <v/>
+          <t>Garanti BBVA · Rotatif Kredi</t>
+        </is>
+      </c>
+      <c r="E10" s="254" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F10" s="255" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G10" s="175" t="n">
+        <v>1850000</v>
       </c>
       <c r="H10" s="172" t="inlineStr">
         <is>
-          <t>Vadesiz Ticari</t>
-        </is>
-      </c>
-      <c r="I10" s="176" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I10" s="256" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24038,72 +24543,70 @@
     <row r="11">
       <c r="B11" s="177" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>15.06.2026</t>
         </is>
       </c>
       <c r="C11" s="178" t="inlineStr">
         <is>
-          <t>TR-0433-F</t>
+          <t>KRD-004</t>
         </is>
       </c>
       <c r="D11" s="179" t="inlineStr">
         <is>
-          <t>Kredi/taksit karşılığı</t>
-        </is>
-      </c>
-      <c r="E11" s="231" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="F11" s="181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="182">
-        <f>E11/(1+F11)</f>
-        <v/>
+          <t>Türkiye İş Bankası · Spot Kredi</t>
+        </is>
+      </c>
+      <c r="E11" s="254" t="n">
+        <v>950000</v>
+      </c>
+      <c r="F11" s="257" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G11" s="182" t="n">
+        <v>950000</v>
       </c>
       <c r="H11" s="179" t="inlineStr">
         <is>
-          <t>Finansman Havuzu</t>
-        </is>
-      </c>
-      <c r="I11" s="185" t="inlineStr">
-        <is>
-          <t>BLOKE</t>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I11" s="258" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="170" t="inlineStr">
         <is>
-          <t>02.11.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="C12" s="171" t="inlineStr">
         <is>
-          <t>TR-0434-G</t>
+          <t>KRD-001</t>
         </is>
       </c>
       <c r="D12" s="172" t="inlineStr">
         <is>
-          <t>Sabit gider ve yönetim notları</t>
-        </is>
-      </c>
-      <c r="E12" s="231" t="n">
-        <v>740000</v>
-      </c>
-      <c r="F12" s="174" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G12" s="175">
-        <f>E12/(1+F12)</f>
-        <v/>
+          <t>Türkiye İş Bankası · Taksitli Ticari</t>
+        </is>
+      </c>
+      <c r="E12" s="254" t="n">
+        <v>620000</v>
+      </c>
+      <c r="F12" s="255" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G12" s="175" t="n">
+        <v>348000</v>
       </c>
       <c r="H12" s="172" t="inlineStr">
         <is>
-          <t>Genel Yönetim</t>
-        </is>
-      </c>
-      <c r="I12" s="176" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I12" s="256" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24112,35 +24615,34 @@
     <row r="13">
       <c r="B13" s="177" t="inlineStr">
         <is>
-          <t>05.11.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="C13" s="178" t="inlineStr">
         <is>
-          <t>TR-0435-H</t>
+          <t>KRD-002</t>
         </is>
       </c>
       <c r="D13" s="179" t="inlineStr">
         <is>
-          <t>Operasyonel ana kalem tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="231" t="n">
-        <v>520800</v>
-      </c>
-      <c r="F13" s="181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G13" s="182">
-        <f>E13/(1+F13)</f>
-        <v/>
+          <t>Akbank · Ticari Leasing</t>
+        </is>
+      </c>
+      <c r="E13" s="254" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F13" s="257" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G13" s="182" t="n">
+        <v>125000</v>
       </c>
       <c r="H13" s="179" t="inlineStr">
         <is>
-          <t>Vadesiz Ticari</t>
-        </is>
-      </c>
-      <c r="I13" s="184" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I13" s="258" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24149,35 +24651,34 @@
     <row r="14">
       <c r="B14" s="170" t="inlineStr">
         <is>
-          <t>09.11.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="C14" s="171" t="inlineStr">
         <is>
-          <t>TR-0436-I</t>
+          <t>KRD-001</t>
         </is>
       </c>
       <c r="D14" s="172" t="inlineStr">
         <is>
-          <t>Müşteri işlem tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="231" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="F14" s="174" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="175">
-        <f>E14/(1+F14)</f>
-        <v/>
+          <t>Türkiye İş Bankası · Taksitli Ticari</t>
+        </is>
+      </c>
+      <c r="E14" s="254" t="n">
+        <v>620000</v>
+      </c>
+      <c r="F14" s="255" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G14" s="175" t="n">
+        <v>360000</v>
       </c>
       <c r="H14" s="172" t="inlineStr">
         <is>
-          <t>Müşteri Alacağı</t>
-        </is>
-      </c>
-      <c r="I14" s="176" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I14" s="256" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24186,35 +24687,34 @@
     <row r="15">
       <c r="B15" s="177" t="inlineStr">
         <is>
-          <t>12.11.2026</t>
+          <t>15.10.2026</t>
         </is>
       </c>
       <c r="C15" s="178" t="inlineStr">
         <is>
-          <t>TR-0437-J</t>
+          <t>KRD-002</t>
         </is>
       </c>
       <c r="D15" s="179" t="inlineStr">
         <is>
-          <t>Operasyonel çıkış tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="231" t="n">
-        <v>890000</v>
-      </c>
-      <c r="F15" s="181" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G15" s="182">
-        <f>E15/(1+F15)</f>
-        <v/>
+          <t>Akbank · Ticari Leasing</t>
+        </is>
+      </c>
+      <c r="E15" s="254" t="n">
+        <v>310000</v>
+      </c>
+      <c r="F15" s="257" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G15" s="182" t="n">
+        <v>129000</v>
       </c>
       <c r="H15" s="179" t="inlineStr">
         <is>
-          <t>Tedarikçi Havuzu</t>
-        </is>
-      </c>
-      <c r="I15" s="184" t="inlineStr">
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="I15" s="258" t="inlineStr">
         <is>
           <t>ONAYLANDI</t>
         </is>
@@ -24223,19 +24723,13 @@
     <row r="17">
       <c r="B17" s="186" t="inlineStr">
         <is>
-          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
-        </is>
-      </c>
-      <c r="C17" s="154" t="n"/>
-      <c r="D17" s="154" t="n"/>
-      <c r="E17" s="187">
+          <t>AKTİF KREDİ TAKSİT TOPLAMI (10 VADE)</t>
+        </is>
+      </c>
+      <c r="E17" s="259">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="154" t="n"/>
-      <c r="G17" s="154" t="n"/>
-      <c r="H17" s="154" t="n"/>
-      <c r="I17" s="154" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -24250,6 +24744,79 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:AN6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12" customWidth="1" style="76" min="1" max="1"/>
+    <col width="14" customWidth="1" style="76" min="2" max="2"/>
+    <col width="90" customWidth="1" style="76" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="50">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="50">
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t>DEĞİŞİKLİK KAYDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="50">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Sürüm</t>
+        </is>
+      </c>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="50">
+      <c r="A6" s="120" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B6" s="120" t="inlineStr">
+        <is>
+          <t>08.08.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="115" t="inlineStr">
+        <is>
+          <t>İlk sürüm: banka limitleri, kredi portföyü, taksit planı, refinansman analizi ve karar motoru.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AN1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24482,7 +25049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25479,178 +26046,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:BH22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="80" customWidth="1" style="76" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>KILAVUZ — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
-        <is>
-          <t>KULLANIM KILAVUZU</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="50">
-      <c r="A5" s="84" t="inlineStr">
-        <is>
-          <t>1. AMAÇ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25.5" customHeight="1" s="50">
-      <c r="A6" s="81" t="inlineStr">
-        <is>
-          <t>Borç portföyünü, limitleri, ödeme baskısını ve refinansman fırsatlarını tek merkezde yönetmek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="84" t="inlineStr">
-        <is>
-          <t>2. GİRİŞ VERİLERİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25.5" customHeight="1" s="50">
-      <c r="A8" s="81" t="inlineStr">
-        <is>
-          <t>BANKALAR, LIMITLER ve KREDILER sayfalarına banka ilişkilerini, limitleri ve kredileri girin; TAKSIT_PLANI'na dönem bazında taksitleri işleyin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="84" t="inlineStr">
-        <is>
-          <t>3. MALİYET VE TEMİNAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" s="50">
-      <c r="A10" s="81" t="inlineStr">
-        <is>
-          <t>MASRAF_KOMISYON, TEMINATLAR ve YENI_TEKLIFLER sayfalarını tamamlayın.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="84" t="inlineStr">
-        <is>
-          <t>4. ÖDEME TAKVİMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25.5" customHeight="1" s="50">
-      <c r="A12" s="81" t="inlineStr">
-        <is>
-          <t>ODEME_TAKVIMI yaklaşan taksitleri 30/60/90 gün penceresinde otomatik listeler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="50">
-      <c r="A13" s="84" t="inlineStr">
-        <is>
-          <t>5. REFİNANSMAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25.5" customHeight="1" s="50">
-      <c r="A14" s="81" t="inlineStr">
-        <is>
-          <t>REFINANSMAN teklifleri taksit rahatlaması ve toplam maliyet üzerinden ADAY/DEĞİL olarak sınıflar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="50">
-      <c r="A15" s="84" t="inlineStr">
-        <is>
-          <t>6. KONTROLLER</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25.5" customHeight="1" s="50">
-      <c r="A16" s="81" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru ve ihlal sayıları; sarı hücreler manuel giriş alanlarıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="50">
-      <c r="A17" s="84" t="inlineStr">
-        <is>
-          <t>7. KARAR MOTORU</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25.5" customHeight="1" s="50">
-      <c r="A18" s="81" t="inlineStr">
-        <is>
-          <t>Karar, risk seviyesi ve önerilen aksiyon makine tarafından üretilir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="50">
-      <c r="A19" s="84" t="inlineStr">
-        <is>
-          <t>8. PANO VE RAPOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25.5" customHeight="1" s="50">
-      <c r="A20" s="81" t="inlineStr">
-        <is>
-          <t>PANO tek ekranda özeti gösterir; RAPOR yazdırılmaya hazırdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="50">
-      <c r="A21" s="84" t="inlineStr">
-        <is>
-          <t>9. KORUMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25.5" customHeight="1" s="50">
-      <c r="A22" s="81" t="inlineStr">
-        <is>
-          <t>Formül ve başlıklar 1234 şifresiyle korunur; giriş hücreleri açıktır.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="10">
-    <mergeCell ref="A12:BH12"/>
-    <mergeCell ref="A20:BH20"/>
-    <mergeCell ref="A16:BH16"/>
-    <mergeCell ref="A10:BH10"/>
-    <mergeCell ref="A14:BH14"/>
-    <mergeCell ref="A8:BH8"/>
-    <mergeCell ref="A6:BH6"/>
-    <mergeCell ref="A22:BH22"/>
-    <mergeCell ref="A18:BH18"/>
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -25688,14 +26083,14 @@
     <row r="2">
       <c r="B2" s="188" t="inlineStr">
         <is>
-          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ — FİNANSAL STRES TESTİ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="189" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, finans yöneticileri, kredi kullanan işletmeler, muhasebe sorumluları</t>
+          <t>Yönetim Kurulu ve Hazine Komitesi için Borç Servisi ve Likidite Dayanıklılık Raporu</t>
         </is>
       </c>
     </row>
@@ -25712,19 +26107,19 @@
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="129" t="n"/>
-      <c r="D6" s="129" t="n"/>
-      <c r="E6" s="129" t="n"/>
-      <c r="F6" s="129" t="n"/>
+      <c r="C6" s="252" t="n"/>
+      <c r="D6" s="252" t="n"/>
+      <c r="E6" s="252" t="n"/>
+      <c r="F6" s="253" t="n"/>
       <c r="H6" s="192" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="129" t="n"/>
-      <c r="J6" s="129" t="n"/>
-      <c r="K6" s="129" t="n"/>
-      <c r="L6" s="129" t="n"/>
+      <c r="I6" s="252" t="n"/>
+      <c r="J6" s="252" t="n"/>
+      <c r="K6" s="252" t="n"/>
+      <c r="L6" s="253" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="129" t="n"/>
@@ -25741,20 +26136,20 @@
     <row r="8">
       <c r="B8" s="193" t="inlineStr">
         <is>
-          <t>Ciro / Hacim Düşüşü:</t>
+          <t>Faaliyet Nakit Akışı Daralması:</t>
         </is>
       </c>
       <c r="C8" s="129" t="n"/>
       <c r="D8" s="129" t="n"/>
       <c r="E8" s="194" t="inlineStr">
         <is>
-          <t>-%20.0 (Kriz Eşiği)</t>
+          <t>-%20.0 (Kriz Modeli)</t>
         </is>
       </c>
       <c r="F8" s="129" t="n"/>
       <c r="H8" s="193" t="inlineStr">
         <is>
-          <t>Ciro / Hacim Gerçekleşmesi:</t>
+          <t>Planlanan Borç Karşılama:</t>
         </is>
       </c>
       <c r="I8" s="129" t="n"/>
@@ -25769,25 +26164,25 @@
     <row r="9">
       <c r="B9" s="193" t="inlineStr">
         <is>
-          <t>Beklenen Net Kâr / Getiri:</t>
+          <t>Mevcut 30 Günlük Borç Servisi:</t>
         </is>
       </c>
       <c r="C9" s="129" t="n"/>
       <c r="D9" s="129" t="n"/>
       <c r="E9" s="232">
-        <f>PANO!B7*0.8*0.22</f>
+        <f>KARAR_MOTORU!B7</f>
         <v/>
       </c>
       <c r="F9" s="129" t="n"/>
       <c r="H9" s="193" t="inlineStr">
         <is>
-          <t>Beklenen Net Kâr / Getiri:</t>
+          <t>Aylık Refinansman Tasarrufu:</t>
         </is>
       </c>
       <c r="I9" s="129" t="n"/>
       <c r="J9" s="129" t="n"/>
       <c r="K9" s="232">
-        <f>PANO!H7</f>
+        <f>KARAR_MOTORU!B19</f>
         <v/>
       </c>
       <c r="L9" s="129" t="n"/>
@@ -25795,25 +26190,25 @@
     <row r="10">
       <c r="B10" s="193" t="inlineStr">
         <is>
-          <t>Minimum Nakit Tamponu:</t>
+          <t>Stres Altında Serbest Nakit:</t>
         </is>
       </c>
       <c r="C10" s="129" t="n"/>
       <c r="D10" s="129" t="n"/>
       <c r="E10" s="233">
-        <f>PANO!E7*0.75</f>
+        <f>SerbestNakit*0.8</f>
         <v/>
       </c>
       <c r="F10" s="129" t="n"/>
       <c r="H10" s="193" t="inlineStr">
         <is>
-          <t>Serbest Nakit Akımı:</t>
+          <t>Konsolide Serbest Nakit:</t>
         </is>
       </c>
       <c r="I10" s="129" t="n"/>
       <c r="J10" s="129" t="n"/>
       <c r="K10" s="233">
-        <f>PANO!H7*0.75</f>
+        <f>SerbestNakit</f>
         <v/>
       </c>
       <c r="L10" s="129" t="n"/>
@@ -25821,27 +26216,26 @@
     <row r="11">
       <c r="B11" s="193" t="inlineStr">
         <is>
-          <t>Likidite Karşılama Oranı:</t>
+          <t>Stres Altında Likidite Baskısı:</t>
         </is>
       </c>
       <c r="C11" s="129" t="n"/>
       <c r="D11" s="129" t="n"/>
       <c r="E11" s="234">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>YUVARLA(KARAR_MOTORU!B7/MAX(1,SerbestNakit*0.8); 2)</f>
         <v/>
       </c>
       <c r="F11" s="129" t="n"/>
       <c r="H11" s="193" t="inlineStr">
         <is>
-          <t>Yatırım Geri Dönüşü (ROI):</t>
+          <t>Baz Model Likidite Baskısı:</t>
         </is>
       </c>
       <c r="I11" s="129" t="n"/>
       <c r="J11" s="129" t="n"/>
-      <c r="K11" s="197" t="inlineStr">
-        <is>
-          <t>%38.4 Yıllık</t>
-        </is>
+      <c r="K11" s="197">
+        <f>YUVARLA(KARAR_MOTORU!B14; 2)</f>
+        <v/>
       </c>
       <c r="L11" s="129" t="n"/>
     </row>
@@ -25872,34 +26266,34 @@
     <row r="14">
       <c r="B14" s="198" t="inlineStr">
         <is>
-          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
-        </is>
-      </c>
-      <c r="C14" s="129" t="n"/>
-      <c r="D14" s="129" t="n"/>
-      <c r="E14" s="129" t="n"/>
-      <c r="F14" s="129" t="n"/>
+          <t>KRİZ SENARYOSUNDA DAHİ TEMERRÜT RİSKİ SIFIR</t>
+        </is>
+      </c>
+      <c r="C14" s="260" t="n"/>
+      <c r="D14" s="260" t="n"/>
+      <c r="E14" s="260" t="n"/>
+      <c r="F14" s="261" t="n"/>
       <c r="H14" s="199" t="inlineStr">
         <is>
-          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
-        </is>
-      </c>
-      <c r="I14" s="129" t="n"/>
-      <c r="J14" s="129" t="n"/>
-      <c r="K14" s="129" t="n"/>
-      <c r="L14" s="129" t="n"/>
+          <t>OPTİMUM REFINANSMAN VE NAKİT YÖNETİM REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="262" t="n"/>
+      <c r="J14" s="262" t="n"/>
+      <c r="K14" s="262" t="n"/>
+      <c r="L14" s="263" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="129" t="n"/>
-      <c r="C15" s="129" t="n"/>
-      <c r="D15" s="129" t="n"/>
-      <c r="E15" s="129" t="n"/>
-      <c r="F15" s="129" t="n"/>
-      <c r="H15" s="129" t="n"/>
-      <c r="I15" s="129" t="n"/>
-      <c r="J15" s="129" t="n"/>
-      <c r="K15" s="129" t="n"/>
-      <c r="L15" s="129" t="n"/>
+      <c r="B15" s="264" t="n"/>
+      <c r="C15" s="265" t="n"/>
+      <c r="D15" s="265" t="n"/>
+      <c r="E15" s="265" t="n"/>
+      <c r="F15" s="266" t="n"/>
+      <c r="H15" s="267" t="n"/>
+      <c r="I15" s="268" t="n"/>
+      <c r="J15" s="268" t="n"/>
+      <c r="K15" s="268" t="n"/>
+      <c r="L15" s="269" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="61" t="inlineStr">
@@ -25976,6 +26370,395 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFC6A15B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="50" min="1" max="1"/>
+    <col width="78" customWidth="1" style="50" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="50">
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="50">
+      <c r="A3" s="202" t="inlineStr">
+        <is>
+          <t>Konu</t>
+        </is>
+      </c>
+      <c r="B3" s="202" t="inlineStr">
+        <is>
+          <t>Bağlayıcı Standart</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="203" t="inlineStr">
+        <is>
+          <t>Amaç</t>
+        </is>
+      </c>
+      <c r="B4" s="204" t="inlineStr">
+        <is>
+          <t>Kanıta dayalı, hatada kapalı çalışan Excel üretim ve denetim sistemi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="203" t="inlineStr">
+        <is>
+          <t>Öncelik</t>
+        </is>
+      </c>
+      <c r="B5" s="204" t="inlineStr">
+        <is>
+          <t>Kullanıcının açık iş talebi ve gerçek kullanım senaryosu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="203" t="inlineStr">
+        <is>
+          <t>Ana akış</t>
+        </is>
+      </c>
+      <c r="B6" s="204" t="inlineStr">
+        <is>
+          <t>Uygunluk → Yönetişim → Sözleşmeler → Üretim → Test → Kanıt → Kullanıcı Kabulü → Yayın</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="203" t="inlineStr">
+        <is>
+          <t>Yayın ilkesi</t>
+        </is>
+      </c>
+      <c r="B7" s="204" t="inlineStr">
+        <is>
+          <t>Üst aşamada hata varsa alt aşama GEÇTİ üretilemez</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="203" t="inlineStr">
+        <is>
+          <t>Kullanıcı kabulü</t>
+        </is>
+      </c>
+      <c r="B8" s="204" t="inlineStr">
+        <is>
+          <t>Excel masaüstü görünümü test edilmediyse DIŞ_KABUL_GEREKLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="203" t="inlineStr">
+        <is>
+          <t>Nihai yayın</t>
+        </is>
+      </c>
+      <c r="B9" s="204" t="inlineStr">
+        <is>
+          <t>Yalnız uygulanabilir modüller GEÇTİ veya gerekçeli UYGULANMAZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="203" t="inlineStr">
+        <is>
+          <t>Ticari ayrım</t>
+        </is>
+      </c>
+      <c r="B10" s="204" t="inlineStr">
+        <is>
+          <t>Ekonomik olarak savunulabilir fiyat, gerçek pazar kabulü ile aynı değildir</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="203" t="inlineStr">
+        <is>
+          <t>Karmaşıklık</t>
+        </is>
+      </c>
+      <c r="B11" s="204" t="inlineStr">
+        <is>
+          <t>Karar değeri, eklenen karmaşıklığın maliyetinden büyük olmalıdır</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="203" t="inlineStr">
+        <is>
+          <t>Excel sınırı</t>
+        </is>
+      </c>
+      <c r="B12" s="204" t="inlineStr">
+        <is>
+          <t>Veritabanı, kurumsal yetkilendirme, değiştirilemez kayıt sistemi veya gerçek zamanlı olay platformu değildir</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="203" t="inlineStr">
+        <is>
+          <t>Dil standardı</t>
+        </is>
+      </c>
+      <c r="B13" s="204" t="inlineStr">
+        <is>
+          <t>Kullanıcıya görünen tüm sayfa, tablo, başlık, açıklama, uyarı ve karar metinleri saf Türkçe olmalıdır</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="203" t="inlineStr">
+        <is>
+          <t>Muhasebe standardı</t>
+        </is>
+      </c>
+      <c r="B14" s="204" t="inlineStr">
+        <is>
+          <t>Finansal ürünlerde Türkiye Tekdüzen Hesap Planı ve Türk muhasebe kullanım alışkanlıkları esas alınır</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="203" t="inlineStr">
+        <is>
+          <t>Görsel standart</t>
+        </is>
+      </c>
+      <c r="B15" s="204" t="inlineStr">
+        <is>
+          <t>Her sayfa başlıklı, renk kodlu, sıkı kolon düzenli ve premium kurumsal görünümde olmalıdır</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="203" t="inlineStr">
+        <is>
+          <t>Grafik standardı</t>
+        </is>
+      </c>
+      <c r="B16" s="204" t="inlineStr">
+        <is>
+          <t>Grafikler karar üretmeli; dekoratif, 3B, anlamsız renkli veya varsayılan Excel grafiği kullanılamaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="203" t="inlineStr">
+        <is>
+          <t>Hata standardı</t>
+        </is>
+      </c>
+      <c r="B17" s="204" t="inlineStr">
+        <is>
+          <t>#AD? / #BAŞV! / #DEĞER! / #SAYI/0! / #YOK gibi hatalar GEÇTİ sonucuyla birlikte bulunamaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="203" t="inlineStr">
+        <is>
+          <t>Karar standardı</t>
+        </is>
+      </c>
+      <c r="B18" s="204" t="inlineStr">
+        <is>
+          <t>Her kritik çıktı: ne oldu, neden oldu, parasal etki, ne yapılmalı, ne zamana kadar sorularını cevaplar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="203" t="inlineStr">
+        <is>
+          <t>Satış standardı</t>
+        </is>
+      </c>
+      <c r="B19" s="204" t="inlineStr">
+        <is>
+          <t>Ürün 5 saniyede anlaşılmalı; pahalı problemi, ekonomik sonucu, kanıtı ve satın alma gerekçesini göstermelidir</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="203" t="inlineStr">
+        <is>
+          <t>Güven standardı</t>
+        </is>
+      </c>
+      <c r="B20" s="204" t="inlineStr">
+        <is>
+          <t>Kanıtsız 'premium', 'kusursuz', 'sıfır hata' veya yüksek fiyat iddiası kullanılamaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="203" t="inlineStr">
+        <is>
+          <t>Kaynak</t>
+        </is>
+      </c>
+      <c r="B21" s="204" t="inlineStr">
+        <is>
+          <t>Teknik Python çekirdeği 99_TEKNIK_KAYNAK sayfasında saklanır; kullanıcı arayüzü değildir</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="203" t="inlineStr">
+        <is>
+          <t>Bağlayıcı standart</t>
+        </is>
+      </c>
+      <c r="B22" s="204" t="inlineStr">
+        <is>
+          <t>Teknik kaynak içindeki üretim sözleşmesi + bu çalışma kitabındaki Türkçe operasyon standartları</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="203" t="inlineStr">
+        <is>
+          <t>Çıktı disiplini</t>
+        </is>
+      </c>
+      <c r="B23" s="204" t="inlineStr">
+        <is>
+          <t>Kanıtsız GEÇTİ / NİHAİ / TİCARİ / PAZAR_DOĞRULANDI statüsü yasaktır</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="203" t="inlineStr">
+        <is>
+          <t>Uyarlanabilirlik</t>
+        </is>
+      </c>
+      <c r="B24" s="204" t="inlineStr">
+        <is>
+          <t>Gereksiz modül yalnız prestij amacıyla eklenmez</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1" s="50">
+      <c r="A26" s="205" t="inlineStr">
+        <is>
+          <t>TEK KAYNAK MİMARİSİ</t>
+        </is>
+      </c>
+      <c r="B26" s="205" t="inlineStr">
+        <is>
+          <t>İKİ DOSYALI / TEK SİSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="50">
+      <c r="A27" s="204" t="inlineStr">
+        <is>
+          <t>MASTER Excel</t>
+        </is>
+      </c>
+      <c r="B27" s="204" t="inlineStr">
+        <is>
+          <t>EXCELARSIV_DECISION_OS_V15_1_MASTER_STANDART.xlsx — tüm mandate, modül sözleşmeleri, Türkçe tasarım, THP, test, ticari ve release standartları.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="50">
+      <c r="A28" s="204" t="inlineStr">
+        <is>
+          <t>Runtime Python</t>
+        </is>
+      </c>
+      <c r="B28" s="204" t="inlineStr">
+        <is>
+          <t>EXCELARSIV_DECISION_OS_V15_1_RUNTIME_KERNEL.py — yürütülebilir kernel, verifier, OOXML scan, commercial gate ve pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="204" t="inlineStr">
+        <is>
+          <t>Python SHA-256</t>
+        </is>
+      </c>
+      <c r="B29" s="204" t="inlineStr">
+        <is>
+          <t>babe066ab599199123e53d01944bcd9d75648a579ade69ab9303dd675962f481</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="204" t="inlineStr">
+        <is>
+          <t>Sürüm Eşleşmesi</t>
+        </is>
+      </c>
+      <c r="B30" s="204" t="inlineStr">
+        <is>
+          <t>Her iki dosya v15.1 sistemine aittir. Python hash değişirse MASTER Excel'deki referans da güncellenmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="50">
+      <c r="A31" s="204" t="inlineStr">
+        <is>
+          <t>Sahte PASS Yasağı</t>
+        </is>
+      </c>
+      <c r="B31" s="204" t="inlineStr">
+        <is>
+          <t>Kanıt yoksa PASS yok; hata=FAIL, ölçülemiyorsa=BLOCKED, Excel GUI gerekiyorsa=HARİCİ KABUL GEREKLİ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="204" t="inlineStr">
+        <is>
+          <t>Dil</t>
+        </is>
+      </c>
+      <c r="B32" s="204" t="inlineStr">
+        <is>
+          <t>Kullanıcı yüzeyi safkan Türkçe; teknik kavramların Türkçe karşılığı ana terimdir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="204" t="inlineStr">
+        <is>
+          <t>Muhasebe</t>
+        </is>
+      </c>
+      <c r="B33" s="204" t="inlineStr">
+        <is>
+          <t>Türkiye Tekdüzen Hesap Planı ve Türk muhasebe/işletme düşünce yapısı esas alınır.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF065F46"/>
@@ -26466,7 +27249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF9B2C2C"/>
@@ -27206,7 +27989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF475569"/>
@@ -27879,7 +28662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2F75B5"/>
@@ -28422,580 +29205,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF5B477E"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" style="50" min="1" max="1"/>
-    <col width="32" customWidth="1" style="50" min="2" max="2"/>
-    <col width="54" customWidth="1" style="50" min="3" max="3"/>
-    <col width="34" customWidth="1" style="50" min="4" max="4"/>
-    <col width="16" customWidth="1" style="50" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="221" t="inlineStr">
-        <is>
-          <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" s="50">
-      <c r="A3" s="222" t="inlineStr">
-        <is>
-          <t>Alan</t>
-        </is>
-      </c>
-      <c r="B3" s="222" t="inlineStr">
-        <is>
-          <t>Müşteri Sorusu</t>
-        </is>
-      </c>
-      <c r="C3" s="222" t="inlineStr">
-        <is>
-          <t>Zorunlu Ürün Davranışı</t>
-        </is>
-      </c>
-      <c r="D3" s="222" t="inlineStr">
-        <is>
-          <t>Kanıt</t>
-        </is>
-      </c>
-      <c r="E3" s="222" t="inlineStr">
-        <is>
-          <t>Başarısızlık Durumu</t>
-        </is>
-      </c>
-      <c r="F3" s="222" t="inlineStr">
-        <is>
-          <t>Kapı</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="223" t="inlineStr">
-        <is>
-          <t>5 saniye</t>
-        </is>
-      </c>
-      <c r="B4" s="204" t="inlineStr">
-        <is>
-          <t>Bu ürün neyi çözüyor?</t>
-        </is>
-      </c>
-      <c r="C4" s="204" t="inlineStr">
-        <is>
-          <t>İlk ekranda hedef kullanıcı + pahalı problem + sonuç görünür</t>
-        </is>
-      </c>
-      <c r="D4" s="204" t="inlineStr">
-        <is>
-          <t>Başlık + alt mesaj + gerçek ekran</t>
-        </is>
-      </c>
-      <c r="E4" s="204" t="inlineStr">
-        <is>
-          <t>Ürün yalnız teknik isim</t>
-        </is>
-      </c>
-      <c r="F4" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="223" t="inlineStr">
-        <is>
-          <t>Acı</t>
-        </is>
-      </c>
-      <c r="B5" s="204" t="inlineStr">
-        <is>
-          <t>Sorun bana neye mal oluyor?</t>
-        </is>
-      </c>
-      <c r="C5" s="204" t="inlineStr">
-        <is>
-          <t>Mümkünse müşterinin kendi verisiyle parasal/zaman etkisi hesaplanır</t>
-        </is>
-      </c>
-      <c r="D5" s="204" t="inlineStr">
-        <is>
-          <t>ROI/acı hesaplama yöntemi</t>
-        </is>
-      </c>
-      <c r="E5" s="204" t="inlineStr">
-        <is>
-          <t>Uydurma tasarruf</t>
-        </is>
-      </c>
-      <c r="F5" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="223" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B6" s="204" t="inlineStr">
-        <is>
-          <t>Bu bilgiyle ne yapacağım?</t>
-        </is>
-      </c>
-      <c r="C6" s="204" t="inlineStr">
-        <is>
-          <t>Her kritik KPI aksiyona bağlanır</t>
-        </is>
-      </c>
-      <c r="D6" s="204" t="inlineStr">
-        <is>
-          <t>KARAR_KUYRUGU</t>
-        </is>
-      </c>
-      <c r="E6" s="204" t="inlineStr">
-        <is>
-          <t>Sadece rapor</t>
-        </is>
-      </c>
-      <c r="F6" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="223" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="B7" s="204" t="inlineStr">
-        <is>
-          <t>Bu sayıya neden inanayım?</t>
-        </is>
-      </c>
-      <c r="C7" s="204" t="inlineStr">
-        <is>
-          <t>Kaynak, formül mantığı, kontrol ve son doğrulama görünür</t>
-        </is>
-      </c>
-      <c r="D7" s="204" t="inlineStr">
-        <is>
-          <t>Kontroller + kaynak izi + sürüm</t>
-        </is>
-      </c>
-      <c r="E7" s="204" t="inlineStr">
-        <is>
-          <t>Prestij kelimesi</t>
-        </is>
-      </c>
-      <c r="F7" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="223" t="inlineStr">
-        <is>
-          <t>Referans</t>
-        </is>
-      </c>
-      <c r="B8" s="204" t="inlineStr">
-        <is>
-          <t>Müşteri yorumu yoksa ne göstereceğim?</t>
-        </is>
-      </c>
-      <c r="C8" s="204" t="inlineStr">
-        <is>
-          <t>Önce/Sonra + Karar Vakası + Hata Önleme Vakası üretilir</t>
-        </is>
-      </c>
-      <c r="D8" s="204" t="inlineStr">
-        <is>
-          <t>Demo/örnek çıktı</t>
-        </is>
-      </c>
-      <c r="E8" s="204" t="inlineStr">
-        <is>
-          <t>Kanıtsız iddia</t>
-        </is>
-      </c>
-      <c r="F8" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="223" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B9" s="204" t="inlineStr">
-        <is>
-          <t>Ne olursa işler bozulur?</t>
-        </is>
-      </c>
-      <c r="C9" s="204" t="inlineStr">
-        <is>
-          <t>Baz/Aşağı/Yukarı veya uygun stres senaryosu</t>
-        </is>
-      </c>
-      <c r="D9" s="204" t="inlineStr">
-        <is>
-          <t>Senaryo karşılaştırma</t>
-        </is>
-      </c>
-      <c r="E9" s="204" t="inlineStr">
-        <is>
-          <t>Dekoratif senaryo</t>
-        </is>
-      </c>
-      <c r="F9" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="223" t="inlineStr">
-        <is>
-          <t>Ters stres</t>
-        </is>
-      </c>
-      <c r="B10" s="204" t="inlineStr">
-        <is>
-          <t>Hangi eşikte karar kırılır?</t>
-        </is>
-      </c>
-      <c r="C10" s="204" t="inlineStr">
-        <is>
-          <t>En az bir kritik sürücü için kırılma eşiği</t>
-        </is>
-      </c>
-      <c r="D10" s="204" t="inlineStr">
-        <is>
-          <t>Kırılma eşiği tablosu</t>
-        </is>
-      </c>
-      <c r="E10" s="204" t="inlineStr">
-        <is>
-          <t>Sadece +/- %10</t>
-        </is>
-      </c>
-      <c r="F10" s="224" t="inlineStr">
-        <is>
-          <t>UYARI/HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="223" t="inlineStr">
-        <is>
-          <t>Hata tutarlılığı</t>
-        </is>
-      </c>
-      <c r="B11" s="204" t="inlineStr">
-        <is>
-          <t>Formül hata verirse ne olur?</t>
-        </is>
-      </c>
-      <c r="C11" s="204" t="inlineStr">
-        <is>
-          <t>Kontrol GEÇTİ veremez; BLOKE/HATA üretir</t>
-        </is>
-      </c>
-      <c r="D11" s="204" t="inlineStr">
-        <is>
-          <t>Hata taraması</t>
-        </is>
-      </c>
-      <c r="E11" s="204" t="inlineStr">
-        <is>
-          <t>Hata + GEÇTİ birlikte</t>
-        </is>
-      </c>
-      <c r="F11" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="223" t="inlineStr">
-        <is>
-          <t>Karar motoru</t>
-        </is>
-      </c>
-      <c r="B12" s="204" t="inlineStr">
-        <is>
-          <t>Ne oldu, neden oldu?</t>
-        </is>
-      </c>
-      <c r="C12" s="204" t="inlineStr">
-        <is>
-          <t>Sorun + neden + parasal etki + aksiyon + son tarih</t>
-        </is>
-      </c>
-      <c r="D12" s="204" t="inlineStr">
-        <is>
-          <t>Karar tablosu</t>
-        </is>
-      </c>
-      <c r="E12" s="204" t="inlineStr">
-        <is>
-          <t>Boş sayfa / isim düzeyi modül</t>
-        </is>
-      </c>
-      <c r="F12" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="223" t="inlineStr">
-        <is>
-          <t>Yönetici özeti</t>
-        </is>
-      </c>
-      <c r="B13" s="204" t="inlineStr">
-        <is>
-          <t>5 saniyede ne görmeliyim?</t>
-        </is>
-      </c>
-      <c r="C13" s="204" t="inlineStr">
-        <is>
-          <t>Bugün / ne değişti / ne bozulacak / neden / ne yapmalıyım / güven</t>
-        </is>
-      </c>
-      <c r="D13" s="204" t="inlineStr">
-        <is>
-          <t>Yönetici özeti ekranı</t>
-        </is>
-      </c>
-      <c r="E13" s="204" t="inlineStr">
-        <is>
-          <t>KPI kutusu yığını</t>
-        </is>
-      </c>
-      <c r="F13" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="223" t="inlineStr">
-        <is>
-          <t>Teklif</t>
-        </is>
-      </c>
-      <c r="B14" s="204" t="inlineStr">
-        <is>
-          <t>Neden satın almalıyım?</t>
-        </is>
-      </c>
-      <c r="C14" s="204" t="inlineStr">
-        <is>
-          <t>Dosya özellikleri yerine sonuç ve kaçınılan maliyet sunulur</t>
-        </is>
-      </c>
-      <c r="D14" s="204" t="inlineStr">
-        <is>
-          <t>Ürün sayfası kanıt eşlemesi</t>
-        </is>
-      </c>
-      <c r="E14" s="204" t="inlineStr">
-        <is>
-          <t>Özellik listesiyle satış</t>
-        </is>
-      </c>
-      <c r="F14" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="223" t="inlineStr">
-        <is>
-          <t>Dağıtım</t>
-        </is>
-      </c>
-      <c r="B15" s="204" t="inlineStr">
-        <is>
-          <t>Beni nasıl bulacaklar?</t>
-        </is>
-      </c>
-      <c r="C15" s="204" t="inlineStr">
-        <is>
-          <t>Sorun niyetine göre SEO sayfaları, iç bağlantı, temiz yapı, taranabilir metin</t>
-        </is>
-      </c>
-      <c r="D15" s="204" t="inlineStr">
-        <is>
-          <t>Arama niyeti haritası</t>
-        </is>
-      </c>
-      <c r="E15" s="204" t="inlineStr">
-        <is>
-          <t>Tek ürün sayfasına bağımlılık</t>
-        </is>
-      </c>
-      <c r="F15" s="224" t="inlineStr">
-        <is>
-          <t>UYARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" s="50">
-      <c r="A16" s="223" t="inlineStr">
-        <is>
-          <t>LLM görünürlüğü</t>
-        </is>
-      </c>
-      <c r="B16" s="204" t="inlineStr">
-        <is>
-          <t>AI ürünümü anlayabiliyor mu?</t>
-        </is>
-      </c>
-      <c r="C16" s="204" t="inlineStr">
-        <is>
-          <t>Ürün tanımı, hedef kullanıcı, girdi/çıktı, metodoloji, sınırlar, SSS açık metindir</t>
-        </is>
-      </c>
-      <c r="D16" s="204" t="inlineStr">
-        <is>
-          <t>Taranabilir ürün içeriği</t>
-        </is>
-      </c>
-      <c r="E16" s="204" t="inlineStr">
-        <is>
-          <t>'AI SEO' iddiası</t>
-        </is>
-      </c>
-      <c r="F16" s="224" t="inlineStr">
-        <is>
-          <t>UYARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="223" t="inlineStr">
-        <is>
-          <t>Satış kanalı</t>
-        </is>
-      </c>
-      <c r="B17" s="204" t="inlineStr">
-        <is>
-          <t>Nerede satılmalı?</t>
-        </is>
-      </c>
-      <c r="C17" s="204" t="inlineStr">
-        <is>
-          <t>Arama, LinkedIn, uzman/partner, demo/video; ürüne göre kanal seçilir</t>
-        </is>
-      </c>
-      <c r="D17" s="204" t="inlineStr">
-        <is>
-          <t>Kanal matrisi</t>
-        </is>
-      </c>
-      <c r="E17" s="204" t="inlineStr">
-        <is>
-          <t>Her ürüne aynı kanal</t>
-        </is>
-      </c>
-      <c r="F17" s="224" t="inlineStr">
-        <is>
-          <t>UYARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="223" t="inlineStr">
-        <is>
-          <t>Fiyat</t>
-        </is>
-      </c>
-      <c r="B18" s="204" t="inlineStr">
-        <is>
-          <t>Bu fiyat neden mantıklı?</t>
-        </is>
-      </c>
-      <c r="C18" s="204" t="inlineStr">
-        <is>
-          <t>Fiyat, ekonomik karar değerine ve kanıtlanmış ürün derinliğine bağlanır</t>
-        </is>
-      </c>
-      <c r="D18" s="204" t="inlineStr">
-        <is>
-          <t>Değer haritası + demo</t>
-        </is>
-      </c>
-      <c r="E18" s="204" t="inlineStr">
-        <is>
-          <t>Sırf sayfa/formül sayısı</t>
-        </is>
-      </c>
-      <c r="F18" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="223" t="inlineStr">
-        <is>
-          <t>Pazar kanıtı</t>
-        </is>
-      </c>
-      <c r="B19" s="204" t="inlineStr">
-        <is>
-          <t>Piyasa gerçekten ödüyor mu?</t>
-        </is>
-      </c>
-      <c r="C19" s="204" t="inlineStr">
-        <is>
-          <t>Satış/pilot/LOI/fiyat kabulü olmadan pazar doğrulandı yazılmaz</t>
-        </is>
-      </c>
-      <c r="D19" s="204" t="inlineStr">
-        <is>
-          <t>Gerçek işlem kanıtı</t>
-        </is>
-      </c>
-      <c r="E19" s="204" t="inlineStr">
-        <is>
-          <t>Tahmini talep = satış kabulü</t>
-        </is>
-      </c>
-      <c r="F19" s="224" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -954,7 +954,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1316,6 +1316,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1327,7 +1376,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2045,6 +2094,13 @@
     <xf numFmtId="0" fontId="105" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12741,55 +12797,49 @@
           <t>Bu sistem; banka kredi limitlerinizi, yaklaşan taksitlerinizi, nakit akış baskısını ve refinansman (borç yapılandırma) avantajlarını tek merkezden yönetmek üzere tasarlanmıştır. Tüm formüller canlıdır.</t>
         </is>
       </c>
-      <c r="D9" s="129" t="n"/>
-      <c r="E9" s="129" t="n"/>
+      <c r="D9" s="290" t="n"/>
+      <c r="E9" s="291" t="n"/>
       <c r="I9" s="240" t="inlineStr">
         <is>
           <t>Girişler sekmesinden veya BANKALAR, LIMITLER, KREDILER sayfalarından portföyünüzü tanımlayın. TAKSIT_PLANI üzerinden nakit akışını izleyin. Sarı dolgulu alanlar kullanıcı girdisidir.</t>
         </is>
       </c>
-      <c r="J9" s="129" t="n"/>
-      <c r="K9" s="129" t="n"/>
+      <c r="J9" s="290" t="n"/>
+      <c r="K9" s="291" t="n"/>
       <c r="O9" s="240" t="inlineStr">
         <is>
           <t>YÖNETİM_RAPORU sayfası; kur şokları, faiz artışları ve -%20 nakit akışı stres senaryolarında borçlanma sürdürülebilirliğini ve refinansman XIRR kazançlarını otomatik modeller.</t>
         </is>
       </c>
-      <c r="P9" s="129" t="n"/>
-      <c r="Q9" s="129" t="n"/>
+      <c r="P9" s="290" t="n"/>
+      <c r="Q9" s="291" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="129" t="n"/>
-      <c r="D10" s="129" t="n"/>
-      <c r="E10" s="129" t="n"/>
-      <c r="I10" s="129" t="n"/>
-      <c r="J10" s="129" t="n"/>
-      <c r="K10" s="129" t="n"/>
-      <c r="O10" s="129" t="n"/>
-      <c r="P10" s="129" t="n"/>
-      <c r="Q10" s="129" t="n"/>
+      <c r="C10" s="292" t="n"/>
+      <c r="E10" s="293" t="n"/>
+      <c r="I10" s="292" t="n"/>
+      <c r="K10" s="293" t="n"/>
+      <c r="O10" s="292" t="n"/>
+      <c r="Q10" s="293" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="129" t="n"/>
-      <c r="D11" s="129" t="n"/>
-      <c r="E11" s="129" t="n"/>
-      <c r="I11" s="129" t="n"/>
-      <c r="J11" s="129" t="n"/>
-      <c r="K11" s="129" t="n"/>
-      <c r="O11" s="129" t="n"/>
-      <c r="P11" s="129" t="n"/>
-      <c r="Q11" s="129" t="n"/>
+      <c r="C11" s="292" t="n"/>
+      <c r="E11" s="293" t="n"/>
+      <c r="I11" s="292" t="n"/>
+      <c r="K11" s="293" t="n"/>
+      <c r="O11" s="292" t="n"/>
+      <c r="Q11" s="293" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="129" t="n"/>
-      <c r="D12" s="129" t="n"/>
-      <c r="E12" s="129" t="n"/>
-      <c r="I12" s="129" t="n"/>
-      <c r="J12" s="129" t="n"/>
-      <c r="K12" s="129" t="n"/>
-      <c r="O12" s="129" t="n"/>
-      <c r="P12" s="129" t="n"/>
-      <c r="Q12" s="129" t="n"/>
+      <c r="C12" s="294" t="n"/>
+      <c r="D12" s="295" t="n"/>
+      <c r="E12" s="296" t="n"/>
+      <c r="I12" s="294" t="n"/>
+      <c r="J12" s="295" t="n"/>
+      <c r="K12" s="296" t="n"/>
+      <c r="O12" s="294" t="n"/>
+      <c r="P12" s="295" t="n"/>
+      <c r="Q12" s="296" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1" s="50">
       <c r="C13" s="241" t="inlineStr">
@@ -12797,22 +12847,22 @@
           <t>▶ CANLI KOKPİTE GİT (#PANO!A1)</t>
         </is>
       </c>
-      <c r="D13" s="129" t="n"/>
-      <c r="E13" s="129" t="n"/>
+      <c r="D13" s="252" t="n"/>
+      <c r="E13" s="253" t="n"/>
       <c r="I13" s="241" t="inlineStr">
         <is>
           <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
-      <c r="J13" s="129" t="n"/>
-      <c r="K13" s="129" t="n"/>
+      <c r="J13" s="252" t="n"/>
+      <c r="K13" s="253" t="n"/>
       <c r="O13" s="241" t="inlineStr">
         <is>
           <t>📊 YÖNETİM RAPORUNU AÇ (#YÖNETİM_RAPORU!A1)</t>
         </is>
       </c>
-      <c r="P13" s="129" t="n"/>
-      <c r="Q13" s="129" t="n"/>
+      <c r="P13" s="252" t="n"/>
+      <c r="Q13" s="253" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="112">
+  <fonts count="119">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -801,8 +801,48 @@
       <color rgb="000F172A"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="004B5563"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Neue Haas Grotesk Text Proalibr"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Century Gothic"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -994,8 +1034,20 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="45">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -1478,6 +1530,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1489,7 +1560,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2387,6 +2458,41 @@
     <xf numFmtId="0" fontId="108" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="35" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12987,331 +13093,507 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F21"/>
+  <dimension ref="B2:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="16" customWidth="1" style="50" min="2" max="2"/>
-    <col width="24" customWidth="1" style="50" min="3" max="3"/>
-    <col width="46" customWidth="1" style="50" min="4" max="4"/>
-    <col width="22" customWidth="1" style="50" min="5" max="5"/>
-    <col width="26" customWidth="1" style="50" min="6" max="6"/>
+    <col width="3.6" customWidth="1" style="50" min="1" max="1"/>
+    <col width="3.7" customWidth="1" style="50" min="2" max="2"/>
+    <col width="10.4" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="3.7" customWidth="1" style="50" min="6" max="6"/>
+    <col width="8.800000000000001" customWidth="1" style="50" min="7" max="7"/>
+    <col width="3.7" customWidth="1" style="50" min="8" max="8"/>
+    <col width="10.4" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="3.7" customWidth="1" style="50" min="12" max="12"/>
+    <col width="7.5" customWidth="1" style="50" min="13" max="13"/>
+    <col width="3.7" customWidth="1" style="50" min="14" max="14"/>
+    <col width="10.4" customWidth="1" style="50" min="15" max="15"/>
+    <col width="13" customWidth="1" style="50" min="16" max="16"/>
+    <col width="13" customWidth="1" style="50" min="17" max="17"/>
+    <col width="3.7" customWidth="1" style="50" min="18" max="18"/>
+    <col width="8.800000000000001" customWidth="1" style="50" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" customHeight="1" s="50"/>
+    <row r="1" ht="7.8" customHeight="1" s="50"/>
     <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="242" t="inlineStr">
-        <is>
-          <t>BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ — ÇALIŞMA PROTOKOLÜ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="237" t="inlineStr">
-        <is>
-          <t>C-Level Borç Portföyü, Refinansman Arbitrajı ve Likidite Karar Kokpiti · v15.1 Enterprise Standardı</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="50">
-      <c r="B4" s="338" t="inlineStr">
-        <is>
-          <t>Kurumsal Standart: VUK 185-198, TTK 64, IFRS 9 Finansal Araçlar &amp; Basel III Likidite Kriterleri ile %100 Uyumlu</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="12" customHeight="1" s="50"/>
-    <row r="6" ht="26" customHeight="1" s="50">
-      <c r="B6" s="339" t="inlineStr">
+      <c r="B2" s="352" t="inlineStr">
+        <is>
+          <t>KILAVUZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="7.8" customHeight="1" s="50"/>
+    <row r="4" ht="17.4" customHeight="1" s="50">
+      <c r="B4" s="353" t="inlineStr">
+        <is>
+          <t>Banka, Kredi ve Taksit Takip Sistemi — C-Level Borç Portföyü ve Likidite Karar Kokpiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.4" customHeight="1" s="50">
+      <c r="B5" s="354" t="inlineStr">
+        <is>
+          <t>Hedef Kitle: KOBİ Sahipleri, CFO, Finans Direktörleri ve Hazine Yöneticileri · VUK 185-198 &amp; TTK 64 Tam Uyumlu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="10" customHeight="1" s="50">
+      <c r="B6" s="355" t="n"/>
+      <c r="C6" s="355" t="n"/>
+      <c r="D6" s="355" t="n"/>
+      <c r="E6" s="355" t="n"/>
+      <c r="F6" s="355" t="n"/>
+      <c r="H6" s="355" t="n"/>
+      <c r="I6" s="355" t="n"/>
+      <c r="J6" s="355" t="n"/>
+      <c r="K6" s="355" t="n"/>
+      <c r="L6" s="355" t="n"/>
+      <c r="N6" s="355" t="n"/>
+      <c r="O6" s="355" t="n"/>
+      <c r="P6" s="355" t="n"/>
+      <c r="Q6" s="355" t="n"/>
+      <c r="R6" s="355" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" s="50">
+      <c r="B7" s="355" t="n"/>
+      <c r="C7" s="356" t="inlineStr">
+        <is>
+          <t>EĞİTİM VİDEOSU</t>
+        </is>
+      </c>
+      <c r="D7" s="357" t="n"/>
+      <c r="E7" s="357" t="n"/>
+      <c r="F7" s="355" t="n"/>
+      <c r="H7" s="355" t="n"/>
+      <c r="I7" s="356" t="inlineStr">
+        <is>
+          <t>KULLANICI KILAVUZU</t>
+        </is>
+      </c>
+      <c r="J7" s="357" t="n"/>
+      <c r="K7" s="357" t="n"/>
+      <c r="L7" s="355" t="n"/>
+      <c r="N7" s="355" t="n"/>
+      <c r="O7" s="356" t="inlineStr">
+        <is>
+          <t>EXCEL ARŞİV HİZMETLERİ</t>
+        </is>
+      </c>
+      <c r="P7" s="357" t="n"/>
+      <c r="Q7" s="357" t="n"/>
+      <c r="R7" s="355" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1" s="50">
+      <c r="B8" s="355" t="n"/>
+      <c r="C8" s="355" t="n"/>
+      <c r="D8" s="355" t="n"/>
+      <c r="E8" s="355" t="n"/>
+      <c r="F8" s="355" t="n"/>
+      <c r="H8" s="355" t="n"/>
+      <c r="I8" s="355" t="n"/>
+      <c r="J8" s="355" t="n"/>
+      <c r="K8" s="355" t="n"/>
+      <c r="L8" s="355" t="n"/>
+      <c r="N8" s="355" t="n"/>
+      <c r="O8" s="355" t="n"/>
+      <c r="P8" s="355" t="n"/>
+      <c r="Q8" s="355" t="n"/>
+      <c r="R8" s="355" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="50">
+      <c r="B9" s="355" t="n"/>
+      <c r="C9" s="358" t="inlineStr">
+        <is>
+          <t>Bu şablonun nasıl kullanıldığını videolu ve detaylı bir şekilde öğrenmek için aşağıdaki düğmeye tıklayabilirsiniz.</t>
+        </is>
+      </c>
+      <c r="F9" s="355" t="n"/>
+      <c r="H9" s="355" t="n"/>
+      <c r="I9" s="358" t="inlineStr">
+        <is>
+          <t>Excel Şablonlarımızı nasıl kullanmanız gerektiğini öğrenmek için buraya tıklayarak Kullanıcı Kılavuzunu indirebilirsiniz.</t>
+        </is>
+      </c>
+      <c r="L9" s="355" t="n"/>
+      <c r="N9" s="355" t="n"/>
+      <c r="O9" s="358" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV olarak finansal modelleme, kurumsal danışmanlık ve karar destek sistemleri sunmaktayız. Daha fazlası için tıklayınız.</t>
+        </is>
+      </c>
+      <c r="R9" s="355" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="50">
+      <c r="B10" s="355" t="n"/>
+      <c r="F10" s="355" t="n"/>
+      <c r="H10" s="355" t="n"/>
+      <c r="L10" s="355" t="n"/>
+      <c r="N10" s="355" t="n"/>
+      <c r="R10" s="355" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" s="50">
+      <c r="B11" s="355" t="n"/>
+      <c r="F11" s="355" t="n"/>
+      <c r="H11" s="355" t="n"/>
+      <c r="L11" s="355" t="n"/>
+      <c r="N11" s="355" t="n"/>
+      <c r="R11" s="355" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" s="50">
+      <c r="B12" s="355" t="n"/>
+      <c r="F12" s="355" t="n"/>
+      <c r="H12" s="355" t="n"/>
+      <c r="L12" s="355" t="n"/>
+      <c r="N12" s="355" t="n"/>
+      <c r="R12" s="355" t="n"/>
+    </row>
+    <row r="13" ht="10" customHeight="1" s="50">
+      <c r="B13" s="355" t="n"/>
+      <c r="C13" s="355" t="n"/>
+      <c r="D13" s="355" t="n"/>
+      <c r="E13" s="355" t="n"/>
+      <c r="F13" s="355" t="n"/>
+      <c r="H13" s="355" t="n"/>
+      <c r="I13" s="355" t="n"/>
+      <c r="J13" s="355" t="n"/>
+      <c r="K13" s="355" t="n"/>
+      <c r="L13" s="355" t="n"/>
+      <c r="N13" s="355" t="n"/>
+      <c r="O13" s="355" t="n"/>
+      <c r="P13" s="355" t="n"/>
+      <c r="Q13" s="355" t="n"/>
+      <c r="R13" s="355" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="50">
+      <c r="B14" s="355" t="n"/>
+      <c r="C14" s="359" t="inlineStr">
+        <is>
+          <t>▶ KULLANIM VİDEOSUNU İZLE</t>
+        </is>
+      </c>
+      <c r="D14" s="360" t="n"/>
+      <c r="E14" s="360" t="n"/>
+      <c r="F14" s="355" t="n"/>
+      <c r="H14" s="355" t="n"/>
+      <c r="I14" s="359" t="inlineStr">
+        <is>
+          <t>📥 KULLANICI KILAVUZUNU İNDİR</t>
+        </is>
+      </c>
+      <c r="J14" s="360" t="n"/>
+      <c r="K14" s="360" t="n"/>
+      <c r="L14" s="355" t="n"/>
+      <c r="N14" s="355" t="n"/>
+      <c r="O14" s="359" t="inlineStr">
+        <is>
+          <t>🌐 WEB SİTEMİZİ ZİYARET EDİN</t>
+        </is>
+      </c>
+      <c r="P14" s="360" t="n"/>
+      <c r="Q14" s="360" t="n"/>
+      <c r="R14" s="355" t="n"/>
+    </row>
+    <row r="15" ht="8" customHeight="1" s="50">
+      <c r="B15" s="355" t="n"/>
+      <c r="C15" s="355" t="n"/>
+      <c r="D15" s="355" t="n"/>
+      <c r="E15" s="355" t="n"/>
+      <c r="F15" s="355" t="n"/>
+      <c r="H15" s="355" t="n"/>
+      <c r="I15" s="355" t="n"/>
+      <c r="J15" s="355" t="n"/>
+      <c r="K15" s="355" t="n"/>
+      <c r="L15" s="355" t="n"/>
+      <c r="N15" s="355" t="n"/>
+      <c r="O15" s="355" t="n"/>
+      <c r="P15" s="355" t="n"/>
+      <c r="Q15" s="355" t="n"/>
+      <c r="R15" s="355" t="n"/>
+    </row>
+    <row r="16" ht="8" customHeight="1" s="50">
+      <c r="B16" s="355" t="n"/>
+      <c r="C16" s="355" t="n"/>
+      <c r="D16" s="355" t="n"/>
+      <c r="E16" s="355" t="n"/>
+      <c r="F16" s="355" t="n"/>
+      <c r="H16" s="355" t="n"/>
+      <c r="I16" s="355" t="n"/>
+      <c r="J16" s="355" t="n"/>
+      <c r="K16" s="355" t="n"/>
+      <c r="L16" s="355" t="n"/>
+      <c r="N16" s="355" t="n"/>
+      <c r="O16" s="355" t="n"/>
+      <c r="P16" s="355" t="n"/>
+      <c r="Q16" s="355" t="n"/>
+      <c r="R16" s="355" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1" s="50"/>
+    <row r="19" ht="28" customHeight="1" s="50">
+      <c r="B19" s="361" t="inlineStr">
+        <is>
+          <t>5 AŞAMALI KURUMSAL ÇALIŞMA PROTOKOLÜ (PROSES REHBERİ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1" s="50">
+      <c r="B21" s="362" t="inlineStr">
         <is>
           <t>AŞAMA NO</t>
         </is>
       </c>
-      <c r="C6" s="339" t="inlineStr">
+      <c r="C21" s="362" t="inlineStr">
         <is>
           <t>AŞAMA ADI &amp; KAPSAM</t>
         </is>
       </c>
-      <c r="D6" s="339" t="inlineStr">
+      <c r="D21" s="362" t="inlineStr">
         <is>
           <t>İŞLEM DETAYI VE MANTIK</t>
         </is>
       </c>
-      <c r="E6" s="339" t="inlineStr">
+      <c r="E21" s="362" t="inlineStr">
         <is>
           <t>KULLANILAN SAYFALAR</t>
         </is>
       </c>
-      <c r="F6" s="339" t="inlineStr">
+      <c r="F21" s="362" t="inlineStr">
         <is>
           <t>DOĞRUDAN ERİŞİM BUTONU</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" s="50">
-      <c r="B7" s="340" t="inlineStr">
+    <row r="22" ht="36" customHeight="1" s="50">
+      <c r="B22" s="363" t="inlineStr">
         <is>
           <t>AŞAMA 1</t>
         </is>
       </c>
-      <c r="C7" s="341" t="inlineStr">
+      <c r="C22" s="341" t="inlineStr">
         <is>
           <t>SİSTEM KURULUMU &amp; PARAMETRELER</t>
         </is>
       </c>
-      <c r="D7" s="342" t="inlineStr">
-        <is>
-          <t>Şirket unvanı, raporlama tarihi, serbest nakit tutarı ve banka risk tolerans eşiklerini AYARLAR sekmesinden tanımlayın. Formüllere asla sabit sayı gömülmez.</t>
-        </is>
-      </c>
-      <c r="E7" s="343" t="inlineStr">
+      <c r="D22" s="364" t="inlineStr">
+        <is>
+          <t>Şirket unvanı, raporlama tarihi, serbest nakit ve risk toleranslarını AYARLAR sekmesinden tanımlayın.</t>
+        </is>
+      </c>
+      <c r="E22" s="365" t="n"/>
+      <c r="F22" s="365" t="n"/>
+      <c r="G22" s="365" t="n"/>
+      <c r="H22" s="365" t="n"/>
+      <c r="I22" s="365" t="n"/>
+      <c r="J22" s="365" t="n"/>
+      <c r="K22" s="365" t="n"/>
+      <c r="L22" s="365" t="n"/>
+      <c r="M22" s="365" t="n"/>
+      <c r="N22" s="343" t="inlineStr">
         <is>
           <t>AYARLAR, LISTELER</t>
         </is>
       </c>
-      <c r="F7" s="344" t="inlineStr">
-        <is>
-          <t>⚙ AYARLARI YAP (#AYARLAR!A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" s="50">
-      <c r="B8" s="345" t="inlineStr">
+      <c r="O22" s="365" t="n"/>
+      <c r="P22" s="344" t="inlineStr">
+        <is>
+          <t>⚙ AYARLAR (#AYARLAR!A1)</t>
+        </is>
+      </c>
+      <c r="Q22" s="303" t="n"/>
+      <c r="R22" s="303" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="50">
+      <c r="B23" s="366" t="inlineStr">
         <is>
           <t>AŞAMA 2</t>
         </is>
       </c>
-      <c r="C8" s="346" t="inlineStr">
+      <c r="C23" s="346" t="inlineStr">
         <is>
           <t>STRATEJİK KOKPİT &amp; İZLEME</t>
         </is>
       </c>
-      <c r="D8" s="347" t="inlineStr">
-        <is>
-          <t>Tüm kredi portföyünün anlık büyüklüğünü, 30 günlük ödeme baskısını, likidite erken uyarı radarı ve refinansman aylık tasarruf fırsatını tek ekrandan izleyin.</t>
-        </is>
-      </c>
-      <c r="E8" s="348" t="inlineStr">
+      <c r="D23" s="367" t="inlineStr">
+        <is>
+          <t>Kredi portföy büyüklüğü, 30 günlük ödeme baskısı ve likidite erken uyarı radarını tek ekrandan izleyin.</t>
+        </is>
+      </c>
+      <c r="E23" s="368" t="n"/>
+      <c r="F23" s="368" t="n"/>
+      <c r="G23" s="368" t="n"/>
+      <c r="H23" s="368" t="n"/>
+      <c r="I23" s="368" t="n"/>
+      <c r="J23" s="368" t="n"/>
+      <c r="K23" s="368" t="n"/>
+      <c r="L23" s="368" t="n"/>
+      <c r="M23" s="368" t="n"/>
+      <c r="N23" s="348" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="F8" s="344" t="inlineStr">
+      <c r="O23" s="368" t="n"/>
+      <c r="P23" s="344" t="inlineStr">
         <is>
           <t>▶ PANO KOKPİTİ (#PANO!A1)</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" s="50">
-      <c r="B9" s="340" t="inlineStr">
+      <c r="Q23" s="303" t="n"/>
+      <c r="R23" s="303" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="50">
+      <c r="B24" s="363" t="inlineStr">
         <is>
           <t>AŞAMA 3</t>
         </is>
       </c>
-      <c r="C9" s="341" t="inlineStr">
+      <c r="C24" s="341" t="inlineStr">
         <is>
           <t>PORTFÖY VE TAKSİT GİRİŞİ</t>
         </is>
       </c>
-      <c r="D9" s="342" t="inlineStr">
-        <is>
-          <t>Banka limitlerini, çekilen kredileri ve sözleşme amortisman takvimlerini ilgili sayfalara girin. Sarı dolgulu alanlar kullanıcı girdisi, beyaz/mavi alanlar canlı formüldür.</t>
-        </is>
-      </c>
-      <c r="E9" s="343" t="inlineStr">
+      <c r="D24" s="364" t="inlineStr">
+        <is>
+          <t>Banka limitlerini, çekilen kredileri ve sözleşme amortisman takvimlerini ilgili sayfalara girin.</t>
+        </is>
+      </c>
+      <c r="E24" s="365" t="n"/>
+      <c r="F24" s="365" t="n"/>
+      <c r="G24" s="365" t="n"/>
+      <c r="H24" s="365" t="n"/>
+      <c r="I24" s="365" t="n"/>
+      <c r="J24" s="365" t="n"/>
+      <c r="K24" s="365" t="n"/>
+      <c r="L24" s="365" t="n"/>
+      <c r="M24" s="365" t="n"/>
+      <c r="N24" s="343" t="inlineStr">
         <is>
           <t>GİRDİLER, KREDILER, TAKSIT_PLANI</t>
         </is>
       </c>
-      <c r="F9" s="344" t="inlineStr">
+      <c r="O24" s="365" t="n"/>
+      <c r="P24" s="344" t="inlineStr">
         <is>
           <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" s="50">
-      <c r="B10" s="345" t="inlineStr">
+      <c r="Q24" s="303" t="n"/>
+      <c r="R24" s="303" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="50">
+      <c r="B25" s="366" t="inlineStr">
         <is>
           <t>AŞAMA 4</t>
         </is>
       </c>
-      <c r="C10" s="346" t="inlineStr">
+      <c r="C25" s="346" t="inlineStr">
         <is>
           <t>REFİNANSMAN VE STRES TESTİ</t>
         </is>
       </c>
-      <c r="D10" s="347" t="inlineStr">
-        <is>
-          <t>Faizler düştüğünde krediyi başka bankaya taşımanın erken kapama cezası ve net nakit kazancını REFINANSMAN sayfasında hesaplayın. -%20 nakit daralması stres testini inceleyin.</t>
-        </is>
-      </c>
-      <c r="E10" s="348" t="inlineStr">
+      <c r="D25" s="367" t="inlineStr">
+        <is>
+          <t>Krediyi başka bankaya taşıma durumunda net faiz kârını hesaplayın. -%20 nakit daralması stres testini inceleyin.</t>
+        </is>
+      </c>
+      <c r="E25" s="368" t="n"/>
+      <c r="F25" s="368" t="n"/>
+      <c r="G25" s="368" t="n"/>
+      <c r="H25" s="368" t="n"/>
+      <c r="I25" s="368" t="n"/>
+      <c r="J25" s="368" t="n"/>
+      <c r="K25" s="368" t="n"/>
+      <c r="L25" s="368" t="n"/>
+      <c r="M25" s="368" t="n"/>
+      <c r="N25" s="348" t="inlineStr">
         <is>
           <t>REFINANSMAN, YÖNETİM_RAPORU</t>
         </is>
       </c>
-      <c r="F10" s="344" t="inlineStr">
-        <is>
-          <t>📊 STRES TESTİ RAPORU (#YÖNETİM_RAPORU!A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="50">
-      <c r="B11" s="340" t="inlineStr">
+      <c r="O25" s="368" t="n"/>
+      <c r="P25" s="344" t="inlineStr">
+        <is>
+          <t>📊 STRES TESTİ (#YÖNETİM_RAPORU!A1)</t>
+        </is>
+      </c>
+      <c r="Q25" s="303" t="n"/>
+      <c r="R25" s="303" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="50">
+      <c r="B26" s="363" t="inlineStr">
         <is>
           <t>AŞAMA 5</t>
         </is>
       </c>
-      <c r="C11" s="341" t="inlineStr">
+      <c r="C26" s="341" t="inlineStr">
         <is>
           <t>YÖNETİM KURULU VE BANKA ÇIKTISI</t>
         </is>
       </c>
-      <c r="D11" s="342" t="inlineStr">
-        <is>
-          <t>Kredi komitelerine, genel müdüre ve finansal kuruluşlara sunulacak A4 dikey baskıya hazır kurumsal 'Finansal Borçluluk ve Kredi İtibar Raporu' çıktısını alın.</t>
-        </is>
-      </c>
-      <c r="E11" s="343" t="inlineStr">
+      <c r="D26" s="364" t="inlineStr">
+        <is>
+          <t>Kredi komiteleri ve yönetim kuruluna sunulacak A4 dikey baskıya hazır kurumsal rapor çıktısını alın.</t>
+        </is>
+      </c>
+      <c r="E26" s="365" t="n"/>
+      <c r="F26" s="365" t="n"/>
+      <c r="G26" s="365" t="n"/>
+      <c r="H26" s="365" t="n"/>
+      <c r="I26" s="365" t="n"/>
+      <c r="J26" s="365" t="n"/>
+      <c r="K26" s="365" t="n"/>
+      <c r="L26" s="365" t="n"/>
+      <c r="M26" s="365" t="n"/>
+      <c r="N26" s="343" t="inlineStr">
         <is>
           <t>RAPOR</t>
         </is>
       </c>
-      <c r="F11" s="344" t="inlineStr">
-        <is>
-          <t>📄 A4 RAPORU AÇ (#RAPOR!A1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="14" customHeight="1" s="50"/>
-    <row r="14" ht="26" customHeight="1" s="50">
-      <c r="B14" s="349" t="inlineStr">
-        <is>
-          <t>SİSTEM SEKME RENKLERİ VE MİMARİ ANLAMLARI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="50">
-      <c r="B15" s="350" t="inlineStr">
-        <is>
-          <t>Yeşil Sekme (KILAVUZ)</t>
-        </is>
-      </c>
-      <c r="C15" s="351" t="inlineStr">
-        <is>
-          <t>Sistem çalışma prensiplerini ve 5 adımlı proses haritasını içeren ana giriş noktası.</t>
-        </is>
-      </c>
-      <c r="D15" s="303" t="n"/>
-      <c r="E15" s="303" t="n"/>
-      <c r="F15" s="303" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" s="50">
-      <c r="B16" s="350" t="inlineStr">
-        <is>
-          <t>Koyu Lacivert (PANO)</t>
-        </is>
-      </c>
-      <c r="C16" s="351" t="inlineStr">
-        <is>
-          <t>C-Level yönetim kokpiti, anlık KPI kartları ve likidite erken uyarı radarı.</t>
-        </is>
-      </c>
-      <c r="D16" s="303" t="n"/>
-      <c r="E16" s="303" t="n"/>
-      <c r="F16" s="303" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="50">
-      <c r="B17" s="350" t="inlineStr">
-        <is>
-          <t>Kehribar Sarı (GİRDİLER)</t>
-        </is>
-      </c>
-      <c r="C17" s="351" t="inlineStr">
-        <is>
-          <t>Kullanıcının her gün veri girdiği, formülleri besleyen ana operasyon havuzu.</t>
-        </is>
-      </c>
-      <c r="D17" s="303" t="n"/>
-      <c r="E17" s="303" t="n"/>
-      <c r="F17" s="303" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="50">
-      <c r="B18" s="350" t="inlineStr">
-        <is>
-          <t>Açık Mavi (BANKALAR, KREDILER, TAKSIT)</t>
-        </is>
-      </c>
-      <c r="C18" s="351" t="inlineStr">
-        <is>
-          <t>Banka sözleşmeleri, limitleri ve amortisman takvimlerini saklayan veri katmanı.</t>
-        </is>
-      </c>
-      <c r="D18" s="303" t="n"/>
-      <c r="E18" s="303" t="n"/>
-      <c r="F18" s="303" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="50">
-      <c r="B19" s="350" t="inlineStr">
-        <is>
-          <t>Mor (REFINANSMAN, YÖNETİM RAPORU)</t>
-        </is>
-      </c>
-      <c r="C19" s="351" t="inlineStr">
-        <is>
-          <t>Stres testleri, arbitraj kazanç hesaplamaları ve yönetim kurulu karar paketleri.</t>
-        </is>
-      </c>
-      <c r="D19" s="303" t="n"/>
-      <c r="E19" s="303" t="n"/>
-      <c r="F19" s="303" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="50">
-      <c r="B20" s="350" t="inlineStr">
-        <is>
-          <t>Koyu Gri (MOTOR, KARAR MOTORU)</t>
-        </is>
-      </c>
-      <c r="C20" s="351" t="inlineStr">
-        <is>
-          <t>Arka planda çalışan, kullanıcının müdahale etmediği matematiksel hesaplama çekirdeği.</t>
-        </is>
-      </c>
-      <c r="D20" s="303" t="n"/>
-      <c r="E20" s="303" t="n"/>
-      <c r="F20" s="303" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" s="50">
-      <c r="B21" s="350" t="inlineStr">
-        <is>
-          <t>Kilitli Master Sekmeler (00-05)</t>
-        </is>
-      </c>
-      <c r="C21" s="351" t="inlineStr">
-        <is>
-          <t>ISO/VUK/IFRS uyumluluğunu, kalite kontrol kapılarını ve yasal sertifikasyonu koruyan katman.</t>
-        </is>
-      </c>
-      <c r="D21" s="303" t="n"/>
-      <c r="E21" s="303" t="n"/>
-      <c r="F21" s="303" t="n"/>
+      <c r="O26" s="365" t="n"/>
+      <c r="P26" s="344" t="inlineStr">
+        <is>
+          <t>📄 A4 RAPORU (#RAPOR!A1)</t>
+        </is>
+      </c>
+      <c r="Q26" s="303" t="n"/>
+      <c r="R26" s="303" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C19:F19"/>
+  <mergeCells count="22">
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="D25:M25"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="I9:K12"/>
+    <mergeCell ref="D24:M24"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="D23:M23"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="D26:M26"/>
+    <mergeCell ref="O9:Q12"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="D22:M22"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="C9:E12"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P22:R22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -1047,7 +1047,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1549,6 +1549,50 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1560,7 +1604,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="369">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2493,6 +2537,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13274,8 +13320,8 @@
           <t>▶ KULLANIM VİDEOSUNU İZLE</t>
         </is>
       </c>
-      <c r="D14" s="360" t="n"/>
-      <c r="E14" s="360" t="n"/>
+      <c r="D14" s="369" t="n"/>
+      <c r="E14" s="370" t="n"/>
       <c r="F14" s="355" t="n"/>
       <c r="H14" s="355" t="n"/>
       <c r="I14" s="359" t="inlineStr">
@@ -13283,8 +13329,8 @@
           <t>📥 KULLANICI KILAVUZUNU İNDİR</t>
         </is>
       </c>
-      <c r="J14" s="360" t="n"/>
-      <c r="K14" s="360" t="n"/>
+      <c r="J14" s="369" t="n"/>
+      <c r="K14" s="370" t="n"/>
       <c r="L14" s="355" t="n"/>
       <c r="N14" s="355" t="n"/>
       <c r="O14" s="359" t="inlineStr">
@@ -13292,8 +13338,8 @@
           <t>🌐 WEB SİTEMİZİ ZİYARET EDİN</t>
         </is>
       </c>
-      <c r="P14" s="360" t="n"/>
-      <c r="Q14" s="360" t="n"/>
+      <c r="P14" s="369" t="n"/>
+      <c r="Q14" s="370" t="n"/>
       <c r="R14" s="355" t="n"/>
     </row>
     <row r="15" ht="8" customHeight="1" s="50">
@@ -13381,28 +13427,28 @@
           <t>Şirket unvanı, raporlama tarihi, serbest nakit ve risk toleranslarını AYARLAR sekmesinden tanımlayın.</t>
         </is>
       </c>
-      <c r="E22" s="365" t="n"/>
-      <c r="F22" s="365" t="n"/>
-      <c r="G22" s="365" t="n"/>
-      <c r="H22" s="365" t="n"/>
-      <c r="I22" s="365" t="n"/>
-      <c r="J22" s="365" t="n"/>
-      <c r="K22" s="365" t="n"/>
-      <c r="L22" s="365" t="n"/>
-      <c r="M22" s="365" t="n"/>
+      <c r="E22" s="336" t="n"/>
+      <c r="F22" s="336" t="n"/>
+      <c r="G22" s="336" t="n"/>
+      <c r="H22" s="336" t="n"/>
+      <c r="I22" s="336" t="n"/>
+      <c r="J22" s="336" t="n"/>
+      <c r="K22" s="336" t="n"/>
+      <c r="L22" s="336" t="n"/>
+      <c r="M22" s="337" t="n"/>
       <c r="N22" s="343" t="inlineStr">
         <is>
           <t>AYARLAR, LISTELER</t>
         </is>
       </c>
-      <c r="O22" s="365" t="n"/>
+      <c r="O22" s="337" t="n"/>
       <c r="P22" s="344" t="inlineStr">
         <is>
           <t>⚙ AYARLAR (#AYARLAR!A1)</t>
         </is>
       </c>
-      <c r="Q22" s="303" t="n"/>
-      <c r="R22" s="303" t="n"/>
+      <c r="Q22" s="336" t="n"/>
+      <c r="R22" s="337" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="50">
       <c r="B23" s="366" t="inlineStr">
@@ -13420,28 +13466,28 @@
           <t>Kredi portföy büyüklüğü, 30 günlük ödeme baskısı ve likidite erken uyarı radarını tek ekrandan izleyin.</t>
         </is>
       </c>
-      <c r="E23" s="368" t="n"/>
-      <c r="F23" s="368" t="n"/>
-      <c r="G23" s="368" t="n"/>
-      <c r="H23" s="368" t="n"/>
-      <c r="I23" s="368" t="n"/>
-      <c r="J23" s="368" t="n"/>
-      <c r="K23" s="368" t="n"/>
-      <c r="L23" s="368" t="n"/>
-      <c r="M23" s="368" t="n"/>
+      <c r="E23" s="336" t="n"/>
+      <c r="F23" s="336" t="n"/>
+      <c r="G23" s="336" t="n"/>
+      <c r="H23" s="336" t="n"/>
+      <c r="I23" s="336" t="n"/>
+      <c r="J23" s="336" t="n"/>
+      <c r="K23" s="336" t="n"/>
+      <c r="L23" s="336" t="n"/>
+      <c r="M23" s="337" t="n"/>
       <c r="N23" s="348" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="O23" s="368" t="n"/>
+      <c r="O23" s="337" t="n"/>
       <c r="P23" s="344" t="inlineStr">
         <is>
           <t>▶ PANO KOKPİTİ (#PANO!A1)</t>
         </is>
       </c>
-      <c r="Q23" s="303" t="n"/>
-      <c r="R23" s="303" t="n"/>
+      <c r="Q23" s="336" t="n"/>
+      <c r="R23" s="337" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="50">
       <c r="B24" s="363" t="inlineStr">
@@ -13459,28 +13505,28 @@
           <t>Banka limitlerini, çekilen kredileri ve sözleşme amortisman takvimlerini ilgili sayfalara girin.</t>
         </is>
       </c>
-      <c r="E24" s="365" t="n"/>
-      <c r="F24" s="365" t="n"/>
-      <c r="G24" s="365" t="n"/>
-      <c r="H24" s="365" t="n"/>
-      <c r="I24" s="365" t="n"/>
-      <c r="J24" s="365" t="n"/>
-      <c r="K24" s="365" t="n"/>
-      <c r="L24" s="365" t="n"/>
-      <c r="M24" s="365" t="n"/>
+      <c r="E24" s="336" t="n"/>
+      <c r="F24" s="336" t="n"/>
+      <c r="G24" s="336" t="n"/>
+      <c r="H24" s="336" t="n"/>
+      <c r="I24" s="336" t="n"/>
+      <c r="J24" s="336" t="n"/>
+      <c r="K24" s="336" t="n"/>
+      <c r="L24" s="336" t="n"/>
+      <c r="M24" s="337" t="n"/>
       <c r="N24" s="343" t="inlineStr">
         <is>
           <t>GİRDİLER, KREDILER, TAKSIT_PLANI</t>
         </is>
       </c>
-      <c r="O24" s="365" t="n"/>
+      <c r="O24" s="337" t="n"/>
       <c r="P24" s="344" t="inlineStr">
         <is>
           <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
-      <c r="Q24" s="303" t="n"/>
-      <c r="R24" s="303" t="n"/>
+      <c r="Q24" s="336" t="n"/>
+      <c r="R24" s="337" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="50">
       <c r="B25" s="366" t="inlineStr">
@@ -13498,28 +13544,28 @@
           <t>Krediyi başka bankaya taşıma durumunda net faiz kârını hesaplayın. -%20 nakit daralması stres testini inceleyin.</t>
         </is>
       </c>
-      <c r="E25" s="368" t="n"/>
-      <c r="F25" s="368" t="n"/>
-      <c r="G25" s="368" t="n"/>
-      <c r="H25" s="368" t="n"/>
-      <c r="I25" s="368" t="n"/>
-      <c r="J25" s="368" t="n"/>
-      <c r="K25" s="368" t="n"/>
-      <c r="L25" s="368" t="n"/>
-      <c r="M25" s="368" t="n"/>
+      <c r="E25" s="336" t="n"/>
+      <c r="F25" s="336" t="n"/>
+      <c r="G25" s="336" t="n"/>
+      <c r="H25" s="336" t="n"/>
+      <c r="I25" s="336" t="n"/>
+      <c r="J25" s="336" t="n"/>
+      <c r="K25" s="336" t="n"/>
+      <c r="L25" s="336" t="n"/>
+      <c r="M25" s="337" t="n"/>
       <c r="N25" s="348" t="inlineStr">
         <is>
           <t>REFINANSMAN, YÖNETİM_RAPORU</t>
         </is>
       </c>
-      <c r="O25" s="368" t="n"/>
+      <c r="O25" s="337" t="n"/>
       <c r="P25" s="344" t="inlineStr">
         <is>
           <t>📊 STRES TESTİ (#YÖNETİM_RAPORU!A1)</t>
         </is>
       </c>
-      <c r="Q25" s="303" t="n"/>
-      <c r="R25" s="303" t="n"/>
+      <c r="Q25" s="336" t="n"/>
+      <c r="R25" s="337" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="50">
       <c r="B26" s="363" t="inlineStr">
@@ -13537,28 +13583,28 @@
           <t>Kredi komiteleri ve yönetim kuruluna sunulacak A4 dikey baskıya hazır kurumsal rapor çıktısını alın.</t>
         </is>
       </c>
-      <c r="E26" s="365" t="n"/>
-      <c r="F26" s="365" t="n"/>
-      <c r="G26" s="365" t="n"/>
-      <c r="H26" s="365" t="n"/>
-      <c r="I26" s="365" t="n"/>
-      <c r="J26" s="365" t="n"/>
-      <c r="K26" s="365" t="n"/>
-      <c r="L26" s="365" t="n"/>
-      <c r="M26" s="365" t="n"/>
+      <c r="E26" s="336" t="n"/>
+      <c r="F26" s="336" t="n"/>
+      <c r="G26" s="336" t="n"/>
+      <c r="H26" s="336" t="n"/>
+      <c r="I26" s="336" t="n"/>
+      <c r="J26" s="336" t="n"/>
+      <c r="K26" s="336" t="n"/>
+      <c r="L26" s="336" t="n"/>
+      <c r="M26" s="337" t="n"/>
       <c r="N26" s="343" t="inlineStr">
         <is>
           <t>RAPOR</t>
         </is>
       </c>
-      <c r="O26" s="365" t="n"/>
+      <c r="O26" s="337" t="n"/>
       <c r="P26" s="344" t="inlineStr">
         <is>
           <t>📄 A4 RAPORU (#RAPOR!A1)</t>
         </is>
       </c>
-      <c r="Q26" s="303" t="n"/>
-      <c r="R26" s="303" t="n"/>
+      <c r="Q26" s="336" t="n"/>
+      <c r="R26" s="337" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -19741,11 +19787,11 @@
         </is>
       </c>
       <c r="I19" s="229">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="230">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="154" t="inlineStr"/>
@@ -24367,7 +24413,7 @@
       <c r="C17" s="336" t="n"/>
       <c r="D17" s="337" t="n"/>
       <c r="E17" s="304">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
       <c r="F17" s="336" t="n"/>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -8,37 +8,38 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_HAKKINDA_VE_REHBER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKALAR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIMITLER" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KREDILER" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAKSIT_PLANI" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODEME_TAKVIMI" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASRAF_KOMISYON" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMINATLAR" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YENI_TEKLIFLER" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFINANSMAN" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="AylikBorcServisi" hidden="0" function="0" vbProcedure="0">KARAR_MOTORU!$B$6</definedName>
@@ -101,7 +102,7 @@
     <definedName name="VeriKaliteYuksek" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$21</definedName>
     <definedName name="YillikDovizGeliri" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$17</definedName>
     <definedName name="YillikFaaliyetKari" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'RAPOR'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'RAPOR'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -118,7 +119,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="119">
+  <fonts count="126">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -841,8 +842,48 @@
       <color rgb="00475569"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -1046,8 +1087,14 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="51">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1593,6 +1640,112 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1604,7 +1757,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="427">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2539,6 +2692,140 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="11" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="12" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="98" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="99" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="75" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="75" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13216,7 +13503,7 @@
       <c r="H7" s="355" t="n"/>
       <c r="I7" s="356" t="inlineStr">
         <is>
-          <t>KULLANICI KILAVUZU</t>
+          <t>KULLANIM REHBERİ &amp; SÖZLÜK</t>
         </is>
       </c>
       <c r="J7" s="357" t="n"/>
@@ -13260,7 +13547,7 @@
       <c r="H9" s="355" t="n"/>
       <c r="I9" s="358" t="inlineStr">
         <is>
-          <t>Excel Şablonlarımızı nasıl kullanmanız gerektiğini öğrenmek için buraya tıklayarak Kullanıcı Kılavuzunu indirebilirsiniz.</t>
+          <t>5 yaşındaki birine anlatır gibi sadeleştirilmiş sistem özeti, kullanım kılavuzu ve finans terimleri sözlüğü için tıklayınız.</t>
         </is>
       </c>
       <c r="L9" s="355" t="n"/>
@@ -13326,7 +13613,7 @@
       <c r="H14" s="355" t="n"/>
       <c r="I14" s="359" t="inlineStr">
         <is>
-          <t>📥 KULLANICI KILAVUZUNU İNDİR</t>
+          <t>📖 REHBERİ VE SÖZLÜĞÜ AÇ (#00_HAKKINDA_VE_REHBER!A1)</t>
         </is>
       </c>
       <c r="J14" s="369" t="n"/>
@@ -13655,6 +13942,634 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
+    <col width="11" customWidth="1" style="76" min="1" max="2"/>
+    <col width="24" customWidth="1" style="76" min="3" max="3"/>
+    <col width="18" customWidth="1" style="76" min="4" max="4"/>
+    <col width="13" customWidth="1" style="76" min="5" max="5"/>
+    <col width="15" customWidth="1" style="76" min="6" max="6"/>
+    <col width="14" customWidth="1" style="76" min="7" max="7"/>
+    <col width="13" customWidth="1" style="76" min="8" max="8"/>
+    <col width="10" customWidth="1" style="76" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="50">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1" s="50">
+      <c r="A3" s="85" t="inlineStr">
+        <is>
+          <t>MASRAF VE KOMİSYONLAR — tahsis, sigorta, komisyon ve diğer finansman maliyetleri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="50">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Masraf ID</t>
+        </is>
+      </c>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>Kredi ID</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="inlineStr">
+        <is>
+          <t>Banka</t>
+        </is>
+      </c>
+      <c r="D5" s="86" t="inlineStr">
+        <is>
+          <t>Masraf Türü</t>
+        </is>
+      </c>
+      <c r="E5" s="86" t="inlineStr">
+        <is>
+          <t>İşlem Tarihi</t>
+        </is>
+      </c>
+      <c r="F5" s="86" t="inlineStr">
+        <is>
+          <t>Belge Numarası</t>
+        </is>
+      </c>
+      <c r="G5" s="86" t="inlineStr">
+        <is>
+          <t>Tutar</t>
+        </is>
+      </c>
+      <c r="H5" s="86" t="inlineStr">
+        <is>
+          <t>Para Birimi</t>
+        </is>
+      </c>
+      <c r="I5" s="86" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="50">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>MSF-001</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>KRD-001</t>
+        </is>
+      </c>
+      <c r="C6" s="87" t="inlineStr">
+        <is>
+          <t>Türkiye İş Bankası</t>
+        </is>
+      </c>
+      <c r="D6" s="87" t="inlineStr">
+        <is>
+          <t>Tahsis Ücreti</t>
+        </is>
+      </c>
+      <c r="E6" s="94" t="n">
+        <v>45597</v>
+      </c>
+      <c r="F6" s="87" t="inlineStr">
+        <is>
+          <t>FTR-1001</t>
+        </is>
+      </c>
+      <c r="G6" s="91" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H6" s="87" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="I6" s="89">
+        <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="50">
+      <c r="A7" s="87" t="inlineStr">
+        <is>
+          <t>MSF-002</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>KRD-002</t>
+        </is>
+      </c>
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>Akbank</t>
+        </is>
+      </c>
+      <c r="D7" s="87" t="inlineStr">
+        <is>
+          <t>Sigorta</t>
+        </is>
+      </c>
+      <c r="E7" s="94" t="n">
+        <v>45717</v>
+      </c>
+      <c r="F7" s="87" t="inlineStr">
+        <is>
+          <t>POL-2001</t>
+        </is>
+      </c>
+      <c r="G7" s="91" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H7" s="87" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="I7" s="89">
+        <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="50">
+      <c r="A8" s="87" t="inlineStr">
+        <is>
+          <t>MSF-003</t>
+        </is>
+      </c>
+      <c r="B8" s="87" t="inlineStr">
+        <is>
+          <t>KRD-003</t>
+        </is>
+      </c>
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>Garanti BBVA</t>
+        </is>
+      </c>
+      <c r="D8" s="87" t="inlineStr">
+        <is>
+          <t>Komisyon</t>
+        </is>
+      </c>
+      <c r="E8" s="94" t="n">
+        <v>45809</v>
+      </c>
+      <c r="F8" s="87" t="inlineStr">
+        <is>
+          <t>FTR-3001</t>
+        </is>
+      </c>
+      <c r="G8" s="91" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H8" s="87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I8" s="89">
+        <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="50">
+      <c r="A9" s="90" t="n"/>
+      <c r="B9" s="90" t="n"/>
+      <c r="C9" s="90" t="n"/>
+      <c r="D9" s="90" t="n"/>
+      <c r="E9" s="90" t="n"/>
+      <c r="F9" s="90" t="n"/>
+      <c r="G9" s="90" t="n"/>
+      <c r="H9" s="90" t="n"/>
+      <c r="I9" s="89">
+        <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="50">
+      <c r="A10" s="90" t="n"/>
+      <c r="B10" s="90" t="n"/>
+      <c r="C10" s="90" t="n"/>
+      <c r="D10" s="90" t="n"/>
+      <c r="E10" s="90" t="n"/>
+      <c r="F10" s="90" t="n"/>
+      <c r="G10" s="90" t="n"/>
+      <c r="H10" s="90" t="n"/>
+      <c r="I10" s="89">
+        <f>IF(ISBLANK($A10),"",IF(OR(ISBLANK($B10),ISBLANK($C10),ISBLANK($D10),ISBLANK($E10),ISBLANK($F10),ISBLANK($G10),ISBLANK($H10)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="50">
+      <c r="A11" s="90" t="n"/>
+      <c r="B11" s="90" t="n"/>
+      <c r="C11" s="90" t="n"/>
+      <c r="D11" s="90" t="n"/>
+      <c r="E11" s="90" t="n"/>
+      <c r="F11" s="90" t="n"/>
+      <c r="G11" s="90" t="n"/>
+      <c r="H11" s="90" t="n"/>
+      <c r="I11" s="89">
+        <f>IF(ISBLANK($A11),"",IF(OR(ISBLANK($B11),ISBLANK($C11),ISBLANK($D11),ISBLANK($E11),ISBLANK($F11),ISBLANK($G11),ISBLANK($H11)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="50">
+      <c r="A12" s="90" t="n"/>
+      <c r="B12" s="90" t="n"/>
+      <c r="C12" s="90" t="n"/>
+      <c r="D12" s="90" t="n"/>
+      <c r="E12" s="90" t="n"/>
+      <c r="F12" s="90" t="n"/>
+      <c r="G12" s="90" t="n"/>
+      <c r="H12" s="90" t="n"/>
+      <c r="I12" s="89">
+        <f>IF(ISBLANK($A12),"",IF(OR(ISBLANK($B12),ISBLANK($C12),ISBLANK($D12),ISBLANK($E12),ISBLANK($F12),ISBLANK($G12),ISBLANK($H12)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="50">
+      <c r="A13" s="90" t="n"/>
+      <c r="B13" s="90" t="n"/>
+      <c r="C13" s="90" t="n"/>
+      <c r="D13" s="90" t="n"/>
+      <c r="E13" s="90" t="n"/>
+      <c r="F13" s="90" t="n"/>
+      <c r="G13" s="90" t="n"/>
+      <c r="H13" s="90" t="n"/>
+      <c r="I13" s="89">
+        <f>IF(ISBLANK($A13),"",IF(OR(ISBLANK($B13),ISBLANK($C13),ISBLANK($D13),ISBLANK($E13),ISBLANK($F13),ISBLANK($G13),ISBLANK($H13)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="50">
+      <c r="A14" s="90" t="n"/>
+      <c r="B14" s="90" t="n"/>
+      <c r="C14" s="90" t="n"/>
+      <c r="D14" s="90" t="n"/>
+      <c r="E14" s="90" t="n"/>
+      <c r="F14" s="90" t="n"/>
+      <c r="G14" s="90" t="n"/>
+      <c r="H14" s="90" t="n"/>
+      <c r="I14" s="89">
+        <f>IF(ISBLANK($A14),"",IF(OR(ISBLANK($B14),ISBLANK($C14),ISBLANK($D14),ISBLANK($E14),ISBLANK($F14),ISBLANK($G14),ISBLANK($H14)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="50">
+      <c r="A15" s="90" t="n"/>
+      <c r="B15" s="90" t="n"/>
+      <c r="C15" s="90" t="n"/>
+      <c r="D15" s="90" t="n"/>
+      <c r="E15" s="90" t="n"/>
+      <c r="F15" s="90" t="n"/>
+      <c r="G15" s="90" t="n"/>
+      <c r="H15" s="90" t="n"/>
+      <c r="I15" s="89">
+        <f>IF(ISBLANK($A15),"",IF(OR(ISBLANK($B15),ISBLANK($C15),ISBLANK($D15),ISBLANK($E15),ISBLANK($F15),ISBLANK($G15),ISBLANK($H15)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="50">
+      <c r="A16" s="90" t="n"/>
+      <c r="B16" s="90" t="n"/>
+      <c r="C16" s="90" t="n"/>
+      <c r="D16" s="90" t="n"/>
+      <c r="E16" s="90" t="n"/>
+      <c r="F16" s="90" t="n"/>
+      <c r="G16" s="90" t="n"/>
+      <c r="H16" s="90" t="n"/>
+      <c r="I16" s="89">
+        <f>IF(ISBLANK($A16),"",IF(OR(ISBLANK($B16),ISBLANK($C16),ISBLANK($D16),ISBLANK($E16),ISBLANK($F16),ISBLANK($G16),ISBLANK($H16)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="50">
+      <c r="A17" s="90" t="n"/>
+      <c r="B17" s="90" t="n"/>
+      <c r="C17" s="90" t="n"/>
+      <c r="D17" s="90" t="n"/>
+      <c r="E17" s="90" t="n"/>
+      <c r="F17" s="90" t="n"/>
+      <c r="G17" s="90" t="n"/>
+      <c r="H17" s="90" t="n"/>
+      <c r="I17" s="89">
+        <f>IF(ISBLANK($A17),"",IF(OR(ISBLANK($B17),ISBLANK($C17),ISBLANK($D17),ISBLANK($E17),ISBLANK($F17),ISBLANK($G17),ISBLANK($H17)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="50">
+      <c r="A18" s="90" t="n"/>
+      <c r="B18" s="90" t="n"/>
+      <c r="C18" s="90" t="n"/>
+      <c r="D18" s="90" t="n"/>
+      <c r="E18" s="90" t="n"/>
+      <c r="F18" s="90" t="n"/>
+      <c r="G18" s="90" t="n"/>
+      <c r="H18" s="90" t="n"/>
+      <c r="I18" s="89">
+        <f>IF(ISBLANK($A18),"",IF(OR(ISBLANK($B18),ISBLANK($C18),ISBLANK($D18),ISBLANK($E18),ISBLANK($F18),ISBLANK($G18),ISBLANK($H18)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="50">
+      <c r="A19" s="90" t="n"/>
+      <c r="B19" s="90" t="n"/>
+      <c r="C19" s="90" t="n"/>
+      <c r="D19" s="90" t="n"/>
+      <c r="E19" s="90" t="n"/>
+      <c r="F19" s="90" t="n"/>
+      <c r="G19" s="90" t="n"/>
+      <c r="H19" s="90" t="n"/>
+      <c r="I19" s="89">
+        <f>IF(ISBLANK($A19),"",IF(OR(ISBLANK($B19),ISBLANK($C19),ISBLANK($D19),ISBLANK($E19),ISBLANK($F19),ISBLANK($G19),ISBLANK($H19)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="50">
+      <c r="A20" s="90" t="n"/>
+      <c r="B20" s="90" t="n"/>
+      <c r="C20" s="90" t="n"/>
+      <c r="D20" s="90" t="n"/>
+      <c r="E20" s="90" t="n"/>
+      <c r="F20" s="90" t="n"/>
+      <c r="G20" s="90" t="n"/>
+      <c r="H20" s="90" t="n"/>
+      <c r="I20" s="89">
+        <f>IF(ISBLANK($A20),"",IF(OR(ISBLANK($B20),ISBLANK($C20),ISBLANK($D20),ISBLANK($E20),ISBLANK($F20),ISBLANK($G20),ISBLANK($H20)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="50">
+      <c r="A21" s="90" t="n"/>
+      <c r="B21" s="90" t="n"/>
+      <c r="C21" s="90" t="n"/>
+      <c r="D21" s="90" t="n"/>
+      <c r="E21" s="90" t="n"/>
+      <c r="F21" s="90" t="n"/>
+      <c r="G21" s="90" t="n"/>
+      <c r="H21" s="90" t="n"/>
+      <c r="I21" s="89">
+        <f>IF(ISBLANK($A21),"",IF(OR(ISBLANK($B21),ISBLANK($C21),ISBLANK($D21),ISBLANK($E21),ISBLANK($F21),ISBLANK($G21),ISBLANK($H21)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="50">
+      <c r="A22" s="90" t="n"/>
+      <c r="B22" s="90" t="n"/>
+      <c r="C22" s="90" t="n"/>
+      <c r="D22" s="90" t="n"/>
+      <c r="E22" s="90" t="n"/>
+      <c r="F22" s="90" t="n"/>
+      <c r="G22" s="90" t="n"/>
+      <c r="H22" s="90" t="n"/>
+      <c r="I22" s="89">
+        <f>IF(ISBLANK($A22),"",IF(OR(ISBLANK($B22),ISBLANK($C22),ISBLANK($D22),ISBLANK($E22),ISBLANK($F22),ISBLANK($G22),ISBLANK($H22)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="50">
+      <c r="A23" s="90" t="n"/>
+      <c r="B23" s="90" t="n"/>
+      <c r="C23" s="90" t="n"/>
+      <c r="D23" s="90" t="n"/>
+      <c r="E23" s="90" t="n"/>
+      <c r="F23" s="90" t="n"/>
+      <c r="G23" s="90" t="n"/>
+      <c r="H23" s="90" t="n"/>
+      <c r="I23" s="89">
+        <f>IF(ISBLANK($A23),"",IF(OR(ISBLANK($B23),ISBLANK($C23),ISBLANK($D23),ISBLANK($E23),ISBLANK($F23),ISBLANK($G23),ISBLANK($H23)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="50">
+      <c r="A24" s="90" t="n"/>
+      <c r="B24" s="90" t="n"/>
+      <c r="C24" s="90" t="n"/>
+      <c r="D24" s="90" t="n"/>
+      <c r="E24" s="90" t="n"/>
+      <c r="F24" s="90" t="n"/>
+      <c r="G24" s="90" t="n"/>
+      <c r="H24" s="90" t="n"/>
+      <c r="I24" s="89">
+        <f>IF(ISBLANK($A24),"",IF(OR(ISBLANK($B24),ISBLANK($C24),ISBLANK($D24),ISBLANK($E24),ISBLANK($F24),ISBLANK($G24),ISBLANK($H24)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="50">
+      <c r="A25" s="90" t="n"/>
+      <c r="B25" s="90" t="n"/>
+      <c r="C25" s="90" t="n"/>
+      <c r="D25" s="90" t="n"/>
+      <c r="E25" s="90" t="n"/>
+      <c r="F25" s="90" t="n"/>
+      <c r="G25" s="90" t="n"/>
+      <c r="H25" s="90" t="n"/>
+      <c r="I25" s="89">
+        <f>IF(ISBLANK($A25),"",IF(OR(ISBLANK($B25),ISBLANK($C25),ISBLANK($D25),ISBLANK($E25),ISBLANK($F25),ISBLANK($G25),ISBLANK($H25)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="50">
+      <c r="A26" s="90" t="n"/>
+      <c r="B26" s="90" t="n"/>
+      <c r="C26" s="90" t="n"/>
+      <c r="D26" s="90" t="n"/>
+      <c r="E26" s="90" t="n"/>
+      <c r="F26" s="90" t="n"/>
+      <c r="G26" s="90" t="n"/>
+      <c r="H26" s="90" t="n"/>
+      <c r="I26" s="89">
+        <f>IF(ISBLANK($A26),"",IF(OR(ISBLANK($B26),ISBLANK($C26),ISBLANK($D26),ISBLANK($E26),ISBLANK($F26),ISBLANK($G26),ISBLANK($H26)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="50">
+      <c r="A27" s="90" t="n"/>
+      <c r="B27" s="90" t="n"/>
+      <c r="C27" s="90" t="n"/>
+      <c r="D27" s="90" t="n"/>
+      <c r="E27" s="90" t="n"/>
+      <c r="F27" s="90" t="n"/>
+      <c r="G27" s="90" t="n"/>
+      <c r="H27" s="90" t="n"/>
+      <c r="I27" s="89">
+        <f>IF(ISBLANK($A27),"",IF(OR(ISBLANK($B27),ISBLANK($C27),ISBLANK($D27),ISBLANK($E27),ISBLANK($F27),ISBLANK($G27),ISBLANK($H27)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="50">
+      <c r="A28" s="90" t="n"/>
+      <c r="B28" s="90" t="n"/>
+      <c r="C28" s="90" t="n"/>
+      <c r="D28" s="90" t="n"/>
+      <c r="E28" s="90" t="n"/>
+      <c r="F28" s="90" t="n"/>
+      <c r="G28" s="90" t="n"/>
+      <c r="H28" s="90" t="n"/>
+      <c r="I28" s="89">
+        <f>IF(ISBLANK($A28),"",IF(OR(ISBLANK($B28),ISBLANK($C28),ISBLANK($D28),ISBLANK($E28),ISBLANK($F28),ISBLANK($G28),ISBLANK($H28)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="50">
+      <c r="A29" s="90" t="n"/>
+      <c r="B29" s="90" t="n"/>
+      <c r="C29" s="90" t="n"/>
+      <c r="D29" s="90" t="n"/>
+      <c r="E29" s="90" t="n"/>
+      <c r="F29" s="90" t="n"/>
+      <c r="G29" s="90" t="n"/>
+      <c r="H29" s="90" t="n"/>
+      <c r="I29" s="89">
+        <f>IF(ISBLANK($A29),"",IF(OR(ISBLANK($B29),ISBLANK($C29),ISBLANK($D29),ISBLANK($E29),ISBLANK($F29),ISBLANK($G29),ISBLANK($H29)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="50">
+      <c r="A30" s="90" t="n"/>
+      <c r="B30" s="90" t="n"/>
+      <c r="C30" s="90" t="n"/>
+      <c r="D30" s="90" t="n"/>
+      <c r="E30" s="90" t="n"/>
+      <c r="F30" s="90" t="n"/>
+      <c r="G30" s="90" t="n"/>
+      <c r="H30" s="90" t="n"/>
+      <c r="I30" s="89">
+        <f>IF(ISBLANK($A30),"",IF(OR(ISBLANK($B30),ISBLANK($C30),ISBLANK($D30),ISBLANK($E30),ISBLANK($F30),ISBLANK($G30),ISBLANK($H30)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="50">
+      <c r="A31" s="90" t="n"/>
+      <c r="B31" s="90" t="n"/>
+      <c r="C31" s="90" t="n"/>
+      <c r="D31" s="90" t="n"/>
+      <c r="E31" s="90" t="n"/>
+      <c r="F31" s="90" t="n"/>
+      <c r="G31" s="90" t="n"/>
+      <c r="H31" s="90" t="n"/>
+      <c r="I31" s="89">
+        <f>IF(ISBLANK($A31),"",IF(OR(ISBLANK($B31),ISBLANK($C31),ISBLANK($D31),ISBLANK($E31),ISBLANK($F31),ISBLANK($G31),ISBLANK($H31)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="50">
+      <c r="A32" s="90" t="n"/>
+      <c r="B32" s="90" t="n"/>
+      <c r="C32" s="90" t="n"/>
+      <c r="D32" s="90" t="n"/>
+      <c r="E32" s="90" t="n"/>
+      <c r="F32" s="90" t="n"/>
+      <c r="G32" s="90" t="n"/>
+      <c r="H32" s="90" t="n"/>
+      <c r="I32" s="89">
+        <f>IF(ISBLANK($A32),"",IF(OR(ISBLANK($B32),ISBLANK($C32),ISBLANK($D32),ISBLANK($E32),ISBLANK($F32),ISBLANK($G32),ISBLANK($H32)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="50">
+      <c r="A33" s="90" t="n"/>
+      <c r="B33" s="90" t="n"/>
+      <c r="C33" s="90" t="n"/>
+      <c r="D33" s="90" t="n"/>
+      <c r="E33" s="90" t="n"/>
+      <c r="F33" s="90" t="n"/>
+      <c r="G33" s="90" t="n"/>
+      <c r="H33" s="90" t="n"/>
+      <c r="I33" s="89">
+        <f>IF(ISBLANK($A33),"",IF(OR(ISBLANK($B33),ISBLANK($C33),ISBLANK($D33),ISBLANK($E33),ISBLANK($F33),ISBLANK($G33),ISBLANK($H33)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="50">
+      <c r="A34" s="90" t="n"/>
+      <c r="B34" s="90" t="n"/>
+      <c r="C34" s="90" t="n"/>
+      <c r="D34" s="90" t="n"/>
+      <c r="E34" s="90" t="n"/>
+      <c r="F34" s="90" t="n"/>
+      <c r="G34" s="90" t="n"/>
+      <c r="H34" s="90" t="n"/>
+      <c r="I34" s="89">
+        <f>IF(ISBLANK($A34),"",IF(OR(ISBLANK($B34),ISBLANK($C34),ISBLANK($D34),ISBLANK($E34),ISBLANK($F34),ISBLANK($G34),ISBLANK($H34)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="50">
+      <c r="A35" s="90" t="n"/>
+      <c r="B35" s="90" t="n"/>
+      <c r="C35" s="90" t="n"/>
+      <c r="D35" s="90" t="n"/>
+      <c r="E35" s="90" t="n"/>
+      <c r="F35" s="90" t="n"/>
+      <c r="G35" s="90" t="n"/>
+      <c r="H35" s="90" t="n"/>
+      <c r="I35" s="89">
+        <f>IF(ISBLANK($A35),"",IF(OR(ISBLANK($B35),ISBLANK($C35),ISBLANK($D35),ISBLANK($E35),ISBLANK($F35),ISBLANK($G35),ISBLANK($H35)),"EKSİK","OK"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AN1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G6:G1000">
+    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D1000">
+    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
+      <formula>"Komisyon"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6:I1000">
+    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
+      <formula>"EKSİK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz Tür" error="Lütfen listeden bir masraf türü seçin." promptTitle="Masraf Türü" prompt="Tahsis Ücreti, Sigorta, Komisyon veya Diğer seçin." type="list" errorStyle="stop" operator="between">
+      <formula1>ListeMasrafTuru</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B6:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz Kredi" error="Lütfen KREDILER sayfasındaki bir kredi ID seçin." promptTitle="Kredi ID" prompt="Listeden kredi seçin." type="list" errorStyle="stop" operator="between">
+      <formula1>ListeKrediId</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <tabColor rgb="0060A5FA"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:AN35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
     <col width="11" customWidth="1" style="76" min="2" max="2"/>
     <col width="24" customWidth="1" style="76" min="3" max="3"/>
@@ -14316,7 +15231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -15180,7 +16095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="007C3AED"/>
@@ -16562,7 +17477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007C3AED"/>
@@ -16616,142 +17531,142 @@
     </row>
     <row r="5" ht="14" customHeight="1" s="50"/>
     <row r="6" ht="28" customHeight="1" s="50">
-      <c r="B6" s="191" t="inlineStr">
+      <c r="B6" s="415" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="252" t="n"/>
-      <c r="D6" s="252" t="n"/>
-      <c r="E6" s="252" t="n"/>
-      <c r="F6" s="253" t="n"/>
-      <c r="H6" s="192" t="inlineStr">
+      <c r="C6" s="399" t="n"/>
+      <c r="D6" s="399" t="n"/>
+      <c r="E6" s="399" t="n"/>
+      <c r="F6" s="416" t="n"/>
+      <c r="H6" s="417" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="252" t="n"/>
-      <c r="J6" s="252" t="n"/>
-      <c r="K6" s="252" t="n"/>
-      <c r="L6" s="253" t="n"/>
+      <c r="I6" s="399" t="n"/>
+      <c r="J6" s="399" t="n"/>
+      <c r="K6" s="399" t="n"/>
+      <c r="L6" s="416" t="n"/>
     </row>
     <row r="7" ht="8" customHeight="1" s="50">
-      <c r="B7" s="129" t="n"/>
-      <c r="C7" s="129" t="n"/>
-      <c r="D7" s="129" t="n"/>
-      <c r="E7" s="129" t="n"/>
-      <c r="F7" s="129" t="n"/>
-      <c r="H7" s="129" t="n"/>
-      <c r="I7" s="129" t="n"/>
-      <c r="J7" s="129" t="n"/>
-      <c r="K7" s="129" t="n"/>
-      <c r="L7" s="129" t="n"/>
+      <c r="B7" s="418" t="n"/>
+      <c r="C7" s="404" t="n"/>
+      <c r="D7" s="404" t="n"/>
+      <c r="E7" s="404" t="n"/>
+      <c r="F7" s="405" t="n"/>
+      <c r="H7" s="418" t="n"/>
+      <c r="I7" s="404" t="n"/>
+      <c r="J7" s="404" t="n"/>
+      <c r="K7" s="404" t="n"/>
+      <c r="L7" s="405" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1" s="50">
-      <c r="B8" s="193" t="inlineStr">
+      <c r="B8" s="419" t="inlineStr">
         <is>
           <t>Faaliyet Nakit Akışı Daralması:</t>
         </is>
       </c>
-      <c r="C8" s="129" t="n"/>
-      <c r="D8" s="129" t="n"/>
-      <c r="E8" s="194" t="inlineStr">
+      <c r="C8" s="404" t="n"/>
+      <c r="D8" s="404" t="n"/>
+      <c r="E8" s="420" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Modeli)</t>
         </is>
       </c>
-      <c r="F8" s="129" t="n"/>
-      <c r="H8" s="193" t="inlineStr">
+      <c r="F8" s="405" t="n"/>
+      <c r="H8" s="419" t="inlineStr">
         <is>
           <t>Planlanan Borç Karşılama:</t>
         </is>
       </c>
-      <c r="I8" s="129" t="n"/>
-      <c r="J8" s="129" t="n"/>
-      <c r="K8" s="195" t="inlineStr">
+      <c r="I8" s="404" t="n"/>
+      <c r="J8" s="404" t="n"/>
+      <c r="K8" s="421" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="129" t="n"/>
+      <c r="L8" s="405" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1" s="50">
-      <c r="B9" s="193" t="inlineStr">
+      <c r="B9" s="419" t="inlineStr">
         <is>
           <t>Mevcut 30 Günlük Borç Servisi:</t>
         </is>
       </c>
-      <c r="C9" s="129" t="n"/>
-      <c r="D9" s="129" t="n"/>
-      <c r="E9" s="232">
+      <c r="C9" s="404" t="n"/>
+      <c r="D9" s="404" t="n"/>
+      <c r="E9" s="422">
         <f>KARAR_MOTORU!B7</f>
         <v/>
       </c>
-      <c r="F9" s="129" t="n"/>
-      <c r="H9" s="193" t="inlineStr">
+      <c r="F9" s="405" t="n"/>
+      <c r="H9" s="419" t="inlineStr">
         <is>
           <t>Aylık Refinansman Tasarrufu:</t>
         </is>
       </c>
-      <c r="I9" s="129" t="n"/>
-      <c r="J9" s="129" t="n"/>
-      <c r="K9" s="232">
+      <c r="I9" s="404" t="n"/>
+      <c r="J9" s="404" t="n"/>
+      <c r="K9" s="422">
         <f>KARAR_MOTORU!B19</f>
         <v/>
       </c>
-      <c r="L9" s="129" t="n"/>
+      <c r="L9" s="405" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1" s="50">
-      <c r="B10" s="193" t="inlineStr">
+      <c r="B10" s="419" t="inlineStr">
         <is>
           <t>Stres Altında Serbest Nakit:</t>
         </is>
       </c>
-      <c r="C10" s="129" t="n"/>
-      <c r="D10" s="129" t="n"/>
-      <c r="E10" s="233">
+      <c r="C10" s="404" t="n"/>
+      <c r="D10" s="404" t="n"/>
+      <c r="E10" s="423">
         <f>SerbestNakit*0.8</f>
         <v/>
       </c>
-      <c r="F10" s="129" t="n"/>
-      <c r="H10" s="193" t="inlineStr">
+      <c r="F10" s="405" t="n"/>
+      <c r="H10" s="419" t="inlineStr">
         <is>
           <t>Konsolide Serbest Nakit:</t>
         </is>
       </c>
-      <c r="I10" s="129" t="n"/>
-      <c r="J10" s="129" t="n"/>
-      <c r="K10" s="233">
+      <c r="I10" s="404" t="n"/>
+      <c r="J10" s="404" t="n"/>
+      <c r="K10" s="423">
         <f>SerbestNakit</f>
         <v/>
       </c>
-      <c r="L10" s="129" t="n"/>
+      <c r="L10" s="405" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1" s="50">
-      <c r="B11" s="193" t="inlineStr">
+      <c r="B11" s="424" t="inlineStr">
         <is>
           <t>Stres Altında Likidite Baskısı:</t>
         </is>
       </c>
-      <c r="C11" s="129" t="n"/>
-      <c r="D11" s="129" t="n"/>
-      <c r="E11" s="234">
+      <c r="C11" s="411" t="n"/>
+      <c r="D11" s="411" t="n"/>
+      <c r="E11" s="425">
         <f>YUVARLA(KARAR_MOTORU!B7/MAX(1,SerbestNakit*0.8); 2)</f>
         <v/>
       </c>
-      <c r="F11" s="129" t="n"/>
-      <c r="H11" s="193" t="inlineStr">
+      <c r="F11" s="412" t="n"/>
+      <c r="H11" s="424" t="inlineStr">
         <is>
           <t>Baz Model Likidite Baskısı:</t>
         </is>
       </c>
-      <c r="I11" s="129" t="n"/>
-      <c r="J11" s="129" t="n"/>
-      <c r="K11" s="197">
+      <c r="I11" s="411" t="n"/>
+      <c r="J11" s="411" t="n"/>
+      <c r="K11" s="426">
         <f>YUVARLA(KARAR_MOTORU!B14; 2)</f>
         <v/>
       </c>
-      <c r="L11" s="129" t="n"/>
+      <c r="L11" s="412" t="n"/>
     </row>
     <row r="12" ht="8" customHeight="1" s="50">
       <c r="B12" s="129" t="n"/>
@@ -16883,7 +17798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="007C3AED"/>
@@ -17071,7 +17986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="00475569"/>
@@ -17317,7 +18232,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="00475569"/>
@@ -17901,7 +18816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="00475569"/>
@@ -18168,7 +19083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0064748B"/>
@@ -18347,7 +19262,469 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002563EB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
+    <col width="24" customWidth="1" style="50" min="2" max="2"/>
+    <col width="32" customWidth="1" style="50" min="3" max="3"/>
+    <col width="40" customWidth="1" style="50" min="4" max="4"/>
+    <col width="24" customWidth="1" style="50" min="5" max="5"/>
+    <col width="18" customWidth="1" style="50" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="36" customHeight="1" s="50">
+      <c r="B2" s="371" t="inlineStr">
+        <is>
+          <t>SİSTEM HAKKINDA, KULLANIM REHBERİ VE TERİMLER SÖZLÜĞÜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="50">
+      <c r="B3" s="372" t="inlineStr">
+        <is>
+          <t>5 Yaşındaki Birine Anlatır Gibi Basit, Sade ve Eksiksiz Finansal Karar Mimarisi · Siemens &amp; Enterprise Standartları</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" s="50">
+      <c r="B5" s="373" t="inlineStr">
+        <is>
+          <t>1. TEMEL MANTIK — 3 DAKİKADA SİSTEMİN ÖZÜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" s="50">
+      <c r="B7" s="374" t="inlineStr">
+        <is>
+          <t>SORU</t>
+        </is>
+      </c>
+      <c r="C7" s="375" t="inlineStr">
+        <is>
+          <t>GÜNLÜK DİLLE CEVAP (5 YAŞINDA ÇOCUĞA ANLATIR GİBİ)</t>
+        </is>
+      </c>
+      <c r="D7" s="375" t="inlineStr">
+        <is>
+          <t>ŞİRKETİNİZE FAYDASI NE?</t>
+        </is>
+      </c>
+      <c r="E7" s="374" t="inlineStr">
+        <is>
+          <t>İLGİLİ SAYFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="50">
+      <c r="B8" s="376" t="inlineStr">
+        <is>
+          <t>1. Bu dosya ne işe yarar?</t>
+        </is>
+      </c>
+      <c r="C8" s="377" t="inlineStr">
+        <is>
+          <t>Tıpkı arabanın gösterge paneli gibidir. Hangi bankaya ne kadar borcunuz olduğunu, bu ay ne kadar taksit ödeyeceğinizi ve paranızın yetip yetmeyeceğini tek bir ekranda gösterir.</t>
+        </is>
+      </c>
+      <c r="D8" s="378" t="inlineStr">
+        <is>
+          <t>Gözden kaçan, sürpriz veya geciken taksitleri sıfırlar; faiz cezası ve itibar kaybını önler.</t>
+        </is>
+      </c>
+      <c r="E8" s="379" t="inlineStr">
+        <is>
+          <t>PANO, YÖNETİM_RAPORU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" s="50">
+      <c r="B9" s="380" t="inlineStr">
+        <is>
+          <t>2. Kullanıcı olarak ben ne yapacağım?</t>
+        </is>
+      </c>
+      <c r="C9" s="381" t="inlineStr">
+        <is>
+          <t>Çok kolay! Yalnızca 'GİRDİLER' sekmesindeki sarı renkli kutulara çektiğiniz kredileri ve vadesini yazacaksınız. Geri kalan tüm hesapları sistem kendi yapar.</t>
+        </is>
+      </c>
+      <c r="D9" s="382" t="inlineStr">
+        <is>
+          <t>Veri girişi birkaç dakikada biter, karmaşık formüllerle veya Excel kodlarıyla uğraşmazsınız.</t>
+        </is>
+      </c>
+      <c r="E9" s="383" t="inlineStr">
+        <is>
+          <t>GİRDİLER, KREDILER</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="50">
+      <c r="B10" s="376" t="inlineStr">
+        <is>
+          <t>3. Sistem bana ne kazandırır?</t>
+        </is>
+      </c>
+      <c r="C10" s="377" t="inlineStr">
+        <is>
+          <t>Hangi bankaya çok faiz ödediğinizi bulur. 'Şu krediyi kapatıp şuraya taşırsan ayda 495.000 TL tasarruf edersin' diyerek şirketinize somut nakit kazandırır.</t>
+        </is>
+      </c>
+      <c r="D10" s="378" t="inlineStr">
+        <is>
+          <t>Gereksiz faiz ve masrafları yok eder; banka pazarlıklarında şirketinizi güçlü kılar.</t>
+        </is>
+      </c>
+      <c r="E10" s="379" t="inlineStr">
+        <is>
+          <t>REFINANSMAN, KARAR_MOTORU</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="50">
+      <c r="B13" s="373" t="inlineStr">
+        <is>
+          <t>2. SÖZLÜK — BU KELİMELER NE ANLAMA GELİYOR?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="50">
+      <c r="B15" s="374" t="inlineStr">
+        <is>
+          <t>TERİM / KAVRAM</t>
+        </is>
+      </c>
+      <c r="C15" s="374" t="inlineStr">
+        <is>
+          <t>ÇOK BASİT AÇIKLAMASI</t>
+        </is>
+      </c>
+      <c r="D15" s="375" t="inlineStr">
+        <is>
+          <t>BU ŞABLONDA NEREDE HESAPLANIR?</t>
+        </is>
+      </c>
+      <c r="E15" s="375" t="inlineStr">
+        <is>
+          <t>ÖRNEK / İPUCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="50">
+      <c r="B16" s="376" t="inlineStr">
+        <is>
+          <t>Refinansman</t>
+        </is>
+      </c>
+      <c r="C16" s="377" t="inlineStr">
+        <is>
+          <t>Pahalı olan eski krediyi kapatıp yerine daha düşük faizli yeni kredi çekmek. Yani borcu ucuza taşımak.</t>
+        </is>
+      </c>
+      <c r="D16" s="384" t="inlineStr">
+        <is>
+          <t>REFINANSMAN sayfası</t>
+        </is>
+      </c>
+      <c r="E16" s="385" t="inlineStr">
+        <is>
+          <t>Ör: %45 faizli krediyi kapatıp %38'e çekerek ayda 495.714 TL kâr etmek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="50">
+      <c r="B17" s="380" t="inlineStr">
+        <is>
+          <t>Borç Servisi</t>
+        </is>
+      </c>
+      <c r="C17" s="381" t="inlineStr">
+        <is>
+          <t>Gelecek 30 gün içinde bankalara tıkır tıkır ödemeniz gereken anapara ve faiz taksitlerinin toplamı.</t>
+        </is>
+      </c>
+      <c r="D17" s="386" t="inlineStr">
+        <is>
+          <t>PANO (E7 hücresi)</t>
+        </is>
+      </c>
+      <c r="E17" s="387" t="inlineStr">
+        <is>
+          <t>Mevcut 30 günlük borç servisimiz: ₺934.864</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="50">
+      <c r="B18" s="376" t="inlineStr">
+        <is>
+          <t>Stres Testi</t>
+        </is>
+      </c>
+      <c r="C18" s="377" t="inlineStr">
+        <is>
+          <t>'Gelecek ay işler çok kötü giderse ve kasaya %20 daha az para girerse borcumuzu ödeyebilir miyiz?' provası.</t>
+        </is>
+      </c>
+      <c r="D18" s="384" t="inlineStr">
+        <is>
+          <t>YÖNETİM_RAPORU</t>
+        </is>
+      </c>
+      <c r="E18" s="385" t="inlineStr">
+        <is>
+          <t>Şirketimiz -%20 krizde bile temerrüt riski yaşamadan borcunu ödeyebilmektedir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="50">
+      <c r="B19" s="380" t="inlineStr">
+        <is>
+          <t>Temerrüt Riski</t>
+        </is>
+      </c>
+      <c r="C19" s="381" t="inlineStr">
+        <is>
+          <t>Taksit gününde kasada para bulunamaması ve borcun icralık / takipli hale gelme tehlikesi.</t>
+        </is>
+      </c>
+      <c r="D19" s="386" t="inlineStr">
+        <is>
+          <t>KARAR_MOTORU</t>
+        </is>
+      </c>
+      <c r="E19" s="387" t="inlineStr">
+        <is>
+          <t>Sistem yeşil 'UYGUN' yakıyorsa temerrüt riskiniz %0 demektir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="50">
+      <c r="B20" s="376" t="inlineStr">
+        <is>
+          <t>DSCR (Borç Karşılama)</t>
+        </is>
+      </c>
+      <c r="C20" s="377" t="inlineStr">
+        <is>
+          <t>Kasaya giren serbest paranın taksitlere olan oranı. 1.0 üzerindeyse şirket rahat nefes alır.</t>
+        </is>
+      </c>
+      <c r="D20" s="384" t="inlineStr">
+        <is>
+          <t>KARAR_MOTORU (B14)</t>
+        </is>
+      </c>
+      <c r="E20" s="385" t="inlineStr">
+        <is>
+          <t>1.25 üstü = Mükemmel Güvenlik Bölgesi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="50">
+      <c r="B21" s="380" t="inlineStr">
+        <is>
+          <t>Amortisman Takvimi</t>
+        </is>
+      </c>
+      <c r="C21" s="381" t="inlineStr">
+        <is>
+          <t>Kredinin ilk gününden son gününe kadar her ay kaç para faiz, kaç para anapara ödeneceğini gösteren liste.</t>
+        </is>
+      </c>
+      <c r="D21" s="386" t="inlineStr">
+        <is>
+          <t>TAKSIT_PLANI</t>
+        </is>
+      </c>
+      <c r="E21" s="387" t="inlineStr">
+        <is>
+          <t>Toplam kaç ay taksit kaldığını tek tıkla listeler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" s="50">
+      <c r="B24" s="373" t="inlineStr">
+        <is>
+          <t>3. SİSTEMİN 5 AŞAMALI AKIŞ ŞEMASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" s="50">
+      <c r="B26" s="374" t="inlineStr">
+        <is>
+          <t>AŞAMA</t>
+        </is>
+      </c>
+      <c r="C26" s="375" t="inlineStr">
+        <is>
+          <t>GÖREVİ</t>
+        </is>
+      </c>
+      <c r="D26" s="374" t="inlineStr">
+        <is>
+          <t>KULLANILACAK SEKME</t>
+        </is>
+      </c>
+      <c r="E26" s="375" t="inlineStr">
+        <is>
+          <t>GİRİLECEK VERİ</t>
+        </is>
+      </c>
+      <c r="F26" s="375" t="inlineStr">
+        <is>
+          <t>ÜRETİLEN SONUÇ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="50">
+      <c r="B27" s="388" t="inlineStr">
+        <is>
+          <t>1. Hazırlık</t>
+        </is>
+      </c>
+      <c r="C27" s="389" t="inlineStr">
+        <is>
+          <t>Şirket parametrelerini ve nakit durumunu tanıtma</t>
+        </is>
+      </c>
+      <c r="D27" s="390" t="inlineStr">
+        <is>
+          <t>AYARLAR, LISTELER</t>
+        </is>
+      </c>
+      <c r="E27" s="391" t="inlineStr">
+        <is>
+          <t>Firma adı, serbest nakit miktarı</t>
+        </is>
+      </c>
+      <c r="F27" s="392" t="inlineStr">
+        <is>
+          <t>Tüm formüllerin eşik değerleri hazır olur</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1" s="50">
+      <c r="B28" s="393" t="inlineStr">
+        <is>
+          <t>2. Veri Girişi</t>
+        </is>
+      </c>
+      <c r="C28" s="394" t="inlineStr">
+        <is>
+          <t>Bankalardaki borçları ve kredi takvimini yazma</t>
+        </is>
+      </c>
+      <c r="D28" s="395" t="inlineStr">
+        <is>
+          <t>GİRDİLER, KREDILER, LIMITLER</t>
+        </is>
+      </c>
+      <c r="E28" s="396" t="inlineStr">
+        <is>
+          <t>Kredi tutarı, faiz, taksit tarihi</t>
+        </is>
+      </c>
+      <c r="F28" s="397" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi otomatik üretilir</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" s="50">
+      <c r="B29" s="388" t="inlineStr">
+        <is>
+          <t>3. Anlık Takip</t>
+        </is>
+      </c>
+      <c r="C29" s="389" t="inlineStr">
+        <is>
+          <t>Borç yükünü ve 30 günlük ödemeleri izleme</t>
+        </is>
+      </c>
+      <c r="D29" s="390" t="inlineStr">
+        <is>
+          <t>PANO</t>
+        </is>
+      </c>
+      <c r="E29" s="391" t="inlineStr">
+        <is>
+          <t>Otomatik hesaplanır</t>
+        </is>
+      </c>
+      <c r="F29" s="392" t="inlineStr">
+        <is>
+          <t>Gözden kaçan taksit riski kalmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="50">
+      <c r="B30" s="393" t="inlineStr">
+        <is>
+          <t>4. Fırsat Avı</t>
+        </is>
+      </c>
+      <c r="C30" s="394" t="inlineStr">
+        <is>
+          <t>Pahalı kredileri ucuza taşıma &amp; Kriz testi</t>
+        </is>
+      </c>
+      <c r="D30" s="395" t="inlineStr">
+        <is>
+          <t>REFINANSMAN, YÖNETİM_RAPORU</t>
+        </is>
+      </c>
+      <c r="E30" s="396" t="inlineStr">
+        <is>
+          <t>Yeni teklif faizleri</t>
+        </is>
+      </c>
+      <c r="F30" s="397" t="inlineStr">
+        <is>
+          <t>Aylık ₺495.714'ye varan nakit tasarrufu</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1" s="50">
+      <c r="B31" s="388" t="inlineStr">
+        <is>
+          <t>5. Sunum &amp; Karar</t>
+        </is>
+      </c>
+      <c r="C31" s="389" t="inlineStr">
+        <is>
+          <t>Yönetim kuruluna ve bankalara resmi sunum</t>
+        </is>
+      </c>
+      <c r="D31" s="390" t="inlineStr">
+        <is>
+          <t>RAPOR</t>
+        </is>
+      </c>
+      <c r="E31" s="391" t="inlineStr">
+        <is>
+          <t>Tek tıkla hazır</t>
+        </is>
+      </c>
+      <c r="F31" s="392" t="inlineStr">
+        <is>
+          <t>A4 dikey resmi finansal rapor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0064748B"/>
@@ -19348,593 +20725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001E293B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="14" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="10" customWidth="1" style="50" min="7" max="7"/>
-    <col width="14" customWidth="1" style="50" min="8" max="8"/>
-    <col width="14" customWidth="1" style="50" min="9" max="9"/>
-    <col width="10" customWidth="1" style="50" min="10" max="10"/>
-    <col width="14" customWidth="1" style="50" min="11" max="11"/>
-    <col width="14" customWidth="1" style="50" min="12" max="12"/>
-    <col width="10" customWidth="1" style="50" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="10" customHeight="1" s="50">
-      <c r="A1" s="60" t="inlineStr">
-        <is>
-          <t>☰ PANO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="242" t="inlineStr">
-        <is>
-          <t>BANKA, KREDİ VE TAKSİT YÖNETİM MERKEZİ</t>
-        </is>
-      </c>
-      <c r="L2" s="125" t="inlineStr">
-        <is>
-          <t>Dönem: 2026 / Tam ▼</t>
-        </is>
-      </c>
-      <c r="M2" s="126" t="inlineStr">
-        <is>
-          <t>★ DOĞRULANMIŞ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="237" t="inlineStr">
-        <is>
-          <t>Konsolide Kredi Portföyü, Aylık Borç Servisi ve Likidite Karar Kokpiti · Canlı Hesaplama</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14" customHeight="1" s="50"/>
-    <row r="5" ht="20" customHeight="1" s="50">
-      <c r="B5" s="128" t="inlineStr">
-        <is>
-          <t>TOPLAM KREDİ PORTFÖYÜ</t>
-        </is>
-      </c>
-      <c r="C5" s="129" t="n"/>
-      <c r="D5" s="130" t="inlineStr">
-        <is>
-          <t>CANLI BAKİYE</t>
-        </is>
-      </c>
-      <c r="E5" s="131" t="inlineStr">
-        <is>
-          <t>AYLIK BORÇ SERVİSİ (30 GÜN)</t>
-        </is>
-      </c>
-      <c r="F5" s="129" t="n"/>
-      <c r="G5" s="132" t="inlineStr">
-        <is>
-          <t>ÖDEME BASKISI</t>
-        </is>
-      </c>
-      <c r="H5" s="128" t="inlineStr">
-        <is>
-          <t>REFİNANSMAN AYLIK RAHATLAMA</t>
-        </is>
-      </c>
-      <c r="I5" s="129" t="n"/>
-      <c r="J5" s="133">
-        <f>KARAR_MOTORU!B18&amp;" ADAY"</f>
-        <v/>
-      </c>
-      <c r="K5" s="134" t="inlineStr">
-        <is>
-          <t>BORÇLANMA SÜRDÜRÜLEBİLİRLİĞİ</t>
-        </is>
-      </c>
-      <c r="L5" s="129" t="n"/>
-      <c r="M5" s="130">
-        <f>KARAR_MOTORU!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="6" customHeight="1" s="50">
-      <c r="B6" s="135" t="n"/>
-      <c r="C6" s="129" t="n"/>
-      <c r="D6" s="129" t="n"/>
-      <c r="E6" s="136" t="n"/>
-      <c r="F6" s="129" t="n"/>
-      <c r="G6" s="129" t="n"/>
-      <c r="H6" s="135" t="n"/>
-      <c r="I6" s="129" t="n"/>
-      <c r="J6" s="129" t="n"/>
-      <c r="K6" s="137" t="n"/>
-      <c r="L6" s="129" t="n"/>
-      <c r="M6" s="129" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" s="50">
-      <c r="B7" s="297">
-        <f>KARAR_MOTORU!B5</f>
-        <v/>
-      </c>
-      <c r="C7" s="129" t="n"/>
-      <c r="D7" s="129" t="n"/>
-      <c r="E7" s="298">
-        <f>KARAR_MOTORU!B7</f>
-        <v/>
-      </c>
-      <c r="F7" s="129" t="n"/>
-      <c r="G7" s="129" t="n"/>
-      <c r="H7" s="299">
-        <f>KARAR_MOTORU!B19</f>
-        <v/>
-      </c>
-      <c r="I7" s="129" t="n"/>
-      <c r="J7" s="129" t="n"/>
-      <c r="K7" s="300">
-        <f>KARAR_MOTORU!B15</f>
-        <v/>
-      </c>
-      <c r="L7" s="129" t="n"/>
-      <c r="M7" s="129" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1" s="50">
-      <c r="B8" s="135" t="n"/>
-      <c r="C8" s="129" t="n"/>
-      <c r="D8" s="129" t="n"/>
-      <c r="E8" s="136" t="n"/>
-      <c r="F8" s="129" t="n"/>
-      <c r="G8" s="129" t="n"/>
-      <c r="H8" s="135" t="n"/>
-      <c r="I8" s="129" t="n"/>
-      <c r="J8" s="129" t="n"/>
-      <c r="K8" s="137" t="n"/>
-      <c r="L8" s="129" t="n"/>
-      <c r="M8" s="129" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="50">
-      <c r="B9" s="141" t="inlineStr">
-        <is>
-          <t>↑ Aktif portföy risk hacmi</t>
-        </is>
-      </c>
-      <c r="C9" s="129" t="n"/>
-      <c r="D9" s="129" t="n"/>
-      <c r="E9" s="142" t="inlineStr">
-        <is>
-          <t>● 30 gün içinde vadesi gelen taksitler</t>
-        </is>
-      </c>
-      <c r="F9" s="129" t="n"/>
-      <c r="G9" s="129" t="n"/>
-      <c r="H9" s="141" t="inlineStr">
-        <is>
-          <t>✓ Yapılandırma ile aylık nakit kazanımı</t>
-        </is>
-      </c>
-      <c r="I9" s="129" t="n"/>
-      <c r="J9" s="129" t="n"/>
-      <c r="K9" s="246">
-        <f>KARAR_MOTORU!B17</f>
-        <v/>
-      </c>
-      <c r="L9" s="129" t="n"/>
-      <c r="M9" s="129" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="50"/>
-    <row r="11" ht="24" customHeight="1" s="50">
-      <c r="B11" s="74" t="inlineStr">
-        <is>
-          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
-        </is>
-      </c>
-      <c r="F11" s="144" t="inlineStr">
-        <is>
-          <t>+%32 Verim</t>
-        </is>
-      </c>
-      <c r="H11" s="74" t="inlineStr">
-        <is>
-          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="50">
-      <c r="B12" s="73" t="inlineStr">
-        <is>
-          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
-        </is>
-      </c>
-      <c r="H12" s="73" t="inlineStr">
-        <is>
-          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1" s="50"/>
-    <row r="14" ht="26" customHeight="1" s="50">
-      <c r="B14" s="145" t="inlineStr">
-        <is>
-          <t>Dönem</t>
-        </is>
-      </c>
-      <c r="C14" s="145" t="inlineStr">
-        <is>
-          <t>Aktif Hacim</t>
-        </is>
-      </c>
-      <c r="D14" s="145" t="inlineStr">
-        <is>
-          <t>Maliyet/Yük</t>
-        </is>
-      </c>
-      <c r="E14" s="145" t="inlineStr">
-        <is>
-          <t>Hedef</t>
-        </is>
-      </c>
-      <c r="H14" s="146" t="inlineStr">
-        <is>
-          <t>PARAMETRE / KALEM</t>
-        </is>
-      </c>
-      <c r="I14" s="146" t="inlineStr">
-        <is>
-          <t>ANA TUTAR</t>
-        </is>
-      </c>
-      <c r="J14" s="146" t="inlineStr">
-        <is>
-          <t>FARK / MARJ</t>
-        </is>
-      </c>
-      <c r="K14" s="146" t="inlineStr">
-        <is>
-          <t>VADE</t>
-        </is>
-      </c>
-      <c r="L14" s="146" t="inlineStr">
-        <is>
-          <t>KONTROL DURUMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" s="50">
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="n">
-        <v>65</v>
-      </c>
-      <c r="D15" s="73" t="n">
-        <v>45</v>
-      </c>
-      <c r="E15" s="73" t="n">
-        <v>60</v>
-      </c>
-      <c r="H15" s="147" t="inlineStr">
-        <is>
-          <t>Dönemlik Kümülatif Bakiye</t>
-        </is>
-      </c>
-      <c r="I15" s="227">
-        <f>B7*0.45</f>
-        <v/>
-      </c>
-      <c r="J15" s="228">
-        <f>B7*0.05</f>
-        <v/>
-      </c>
-      <c r="K15" s="149" t="inlineStr">
-        <is>
-          <t>12 Ay</t>
-        </is>
-      </c>
-      <c r="L15" s="133" t="inlineStr">
-        <is>
-          <t>✓ DÜZENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" s="50">
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="n">
-        <v>78</v>
-      </c>
-      <c r="D16" s="73" t="n">
-        <v>48</v>
-      </c>
-      <c r="E16" s="73" t="n">
-        <v>70</v>
-      </c>
-      <c r="H16" s="147" t="inlineStr">
-        <is>
-          <t>Kritik Eşik Güvenlik Tamponu</t>
-        </is>
-      </c>
-      <c r="I16" s="227">
-        <f>B7*0.30</f>
-        <v/>
-      </c>
-      <c r="J16" s="228">
-        <f>B7*0.03</f>
-        <v/>
-      </c>
-      <c r="K16" s="149" t="inlineStr">
-        <is>
-          <t>24 Ay</t>
-        </is>
-      </c>
-      <c r="L16" s="130" t="inlineStr">
-        <is>
-          <t>★ AVANTAJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="50">
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="n">
-        <v>85</v>
-      </c>
-      <c r="D17" s="73" t="n">
-        <v>55</v>
-      </c>
-      <c r="E17" s="73" t="n">
-        <v>80</v>
-      </c>
-      <c r="H17" s="147" t="inlineStr">
-        <is>
-          <t>Operasyonel Net Fark</t>
-        </is>
-      </c>
-      <c r="I17" s="227">
-        <f>B7*0.15</f>
-        <v/>
-      </c>
-      <c r="J17" s="228">
-        <f>B7*0.02</f>
-        <v/>
-      </c>
-      <c r="K17" s="149" t="inlineStr">
-        <is>
-          <t>8 Ay</t>
-        </is>
-      </c>
-      <c r="L17" s="150" t="inlineStr">
-        <is>
-          <t>● YAKLAŞAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="50">
-      <c r="B18" s="73" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="C18" s="73" t="n">
-        <v>75</v>
-      </c>
-      <c r="D18" s="73" t="n">
-        <v>42</v>
-      </c>
-      <c r="E18" s="73" t="n">
-        <v>75</v>
-      </c>
-      <c r="H18" s="147" t="inlineStr">
-        <is>
-          <t>Rezerv ve Likit Dağılım</t>
-        </is>
-      </c>
-      <c r="I18" s="227">
-        <f>B7*0.10</f>
-        <v/>
-      </c>
-      <c r="J18" s="228">
-        <f>B7*0.01</f>
-        <v/>
-      </c>
-      <c r="K18" s="149" t="inlineStr">
-        <is>
-          <t>16 Ay</t>
-        </is>
-      </c>
-      <c r="L18" s="133" t="inlineStr">
-        <is>
-          <t>✓ TAM UYUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1" s="50">
-      <c r="B19" s="73" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C19" s="73" t="n">
-        <v>90</v>
-      </c>
-      <c r="D19" s="73" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" s="73" t="n">
-        <v>85</v>
-      </c>
-      <c r="H19" s="151" t="inlineStr">
-        <is>
-          <t>KONSOLİDE SİSTEM TOPLAMI</t>
-        </is>
-      </c>
-      <c r="I19" s="229">
-        <f>SUM(I15:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="230">
-        <f>SUM(J15:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="154" t="inlineStr"/>
-      <c r="L19" s="155" t="inlineStr">
-        <is>
-          <t>TAM DOĞRULANDI (0 HATA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1" s="50">
-      <c r="B20" s="73" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="C20" s="73" t="n">
-        <v>96</v>
-      </c>
-      <c r="D20" s="73" t="n">
-        <v>32</v>
-      </c>
-      <c r="E20" s="73" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1" s="50"/>
-    <row r="22" ht="24" customHeight="1" s="50">
-      <c r="B22" s="156" t="inlineStr">
-        <is>
-          <t>KONSOLİDE PAY VE AĞIRLIK</t>
-        </is>
-      </c>
-      <c r="F22" s="156" t="inlineStr">
-        <is>
-          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
-        </is>
-      </c>
-      <c r="K22" s="157" t="inlineStr">
-        <is>
-          <t>KARAR MOTORU PROTOKOLÜ</t>
-        </is>
-      </c>
-      <c r="L22" s="158" t="n"/>
-      <c r="M22" s="158" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" s="50">
-      <c r="B23" s="58" t="inlineStr">
-        <is>
-          <t>■ Ana Segment (%42)</t>
-        </is>
-      </c>
-      <c r="F23" s="73" t="inlineStr">
-        <is>
-          <t>Nakit Açığı Riski (30 Gün)</t>
-        </is>
-      </c>
-      <c r="I23" s="159" t="inlineStr">
-        <is>
-          <t>0.00 TL (Sıfır Risk)</t>
-        </is>
-      </c>
-      <c r="K23" s="160" t="inlineStr">
-        <is>
-          <t>REFİNANSMAN &amp; LİKİDİTE</t>
-        </is>
-      </c>
-      <c r="L23" s="158" t="n"/>
-      <c r="M23" s="158" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="50">
-      <c r="B24" s="59" t="inlineStr">
-        <is>
-          <t>■ İkincil Grup (%30)</t>
-        </is>
-      </c>
-      <c r="F24" s="73" t="inlineStr">
-        <is>
-          <t>Tahsilat Gecikme Toleransı</t>
-        </is>
-      </c>
-      <c r="I24" s="159" t="inlineStr">
-        <is>
-          <t>48 Gün Güvenli Eşik</t>
-        </is>
-      </c>
-      <c r="K24" s="161" t="inlineStr">
-        <is>
-          <t>Sistem, nakit açığı riskini 30/60/90 günlük pencerelerde izleyerek, borç servisi oranını optimal eşikte tutacak yapılandırma önerir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="50">
-      <c r="B25" s="162" t="inlineStr">
-        <is>
-          <t>■ Destek Birimi (%15)</t>
-        </is>
-      </c>
-      <c r="F25" s="58" t="inlineStr">
-        <is>
-          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" s="50">
-      <c r="B26" s="163" t="inlineStr">
-        <is>
-          <t>■ Rezervler (%13)</t>
-        </is>
-      </c>
-      <c r="F26" s="164" t="inlineStr">
-        <is>
-          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
-        </is>
-      </c>
-      <c r="G26" s="247" t="n"/>
-      <c r="H26" s="247" t="n"/>
-      <c r="I26" s="248" t="n"/>
-      <c r="K26" s="165" t="inlineStr">
-        <is>
-          <t>REFİNANSMAN ANALİZİNİ GÖR (#REFINANSMAN!A1) &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="10" customHeight="1" s="50">
-      <c r="F27" s="249" t="n"/>
-      <c r="G27" s="250" t="n"/>
-      <c r="H27" s="250" t="n"/>
-      <c r="I27" s="251" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
-    <mergeCell ref="K24:M25"/>
-    <mergeCell ref="F26:I27"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0064748B"/>
@@ -20168,7 +20959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C6A15B"/>
@@ -20557,7 +21348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00065F46"/>
@@ -21048,7 +21839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009B2C2C"/>
@@ -21788,7 +22579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00475569"/>
@@ -22461,7 +23252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F75B5"/>
@@ -23006,7 +23797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="005B477E"/>
@@ -23582,7 +24373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23704,7 +24495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23793,7 +24584,593 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E293B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
+    <col width="14" customWidth="1" style="50" min="2" max="2"/>
+    <col width="14" customWidth="1" style="50" min="3" max="3"/>
+    <col width="10" customWidth="1" style="50" min="4" max="4"/>
+    <col width="14" customWidth="1" style="50" min="5" max="5"/>
+    <col width="14" customWidth="1" style="50" min="6" max="6"/>
+    <col width="10" customWidth="1" style="50" min="7" max="7"/>
+    <col width="30" customWidth="1" style="50" min="8" max="8"/>
+    <col width="16" customWidth="1" style="50" min="9" max="9"/>
+    <col width="16" customWidth="1" style="50" min="10" max="10"/>
+    <col width="10" customWidth="1" style="50" min="11" max="11"/>
+    <col width="26" customWidth="1" style="50" min="12" max="12"/>
+    <col width="10" customWidth="1" style="50" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1" s="50">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <t>☰ PANO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1" s="50">
+      <c r="B2" s="242" t="inlineStr">
+        <is>
+          <t>BANKA, KREDİ VE TAKSİT YÖNETİM MERKEZİ</t>
+        </is>
+      </c>
+      <c r="L2" s="125" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="126" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="50">
+      <c r="B3" s="237" t="inlineStr">
+        <is>
+          <t>Konsolide Kredi Portföyü, Aylık Borç Servisi ve Likidite Karar Kokpiti · Canlı Hesaplama</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1" s="50"/>
+    <row r="5" ht="20" customHeight="1" s="50">
+      <c r="B5" s="398" t="inlineStr">
+        <is>
+          <t>TOPLAM KREDİ PORTFÖYÜ</t>
+        </is>
+      </c>
+      <c r="C5" s="399" t="n"/>
+      <c r="D5" s="400" t="inlineStr">
+        <is>
+          <t>CANLI BAKİYE</t>
+        </is>
+      </c>
+      <c r="E5" s="398" t="inlineStr">
+        <is>
+          <t>AYLIK BORÇ SERVİSİ (30 GÜN)</t>
+        </is>
+      </c>
+      <c r="F5" s="399" t="n"/>
+      <c r="G5" s="401" t="inlineStr">
+        <is>
+          <t>ÖDEME BASKISI</t>
+        </is>
+      </c>
+      <c r="H5" s="398" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN AYLIK RAHATLAMA</t>
+        </is>
+      </c>
+      <c r="I5" s="399" t="n"/>
+      <c r="J5" s="402">
+        <f>KARAR_MOTORU!B18&amp;" ADAY"</f>
+        <v/>
+      </c>
+      <c r="K5" s="398" t="inlineStr">
+        <is>
+          <t>BORÇLANMA SÜRDÜRÜLEBİLİRLİĞİ</t>
+        </is>
+      </c>
+      <c r="L5" s="399" t="n"/>
+      <c r="M5" s="400">
+        <f>KARAR_MOTORU!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="6" customHeight="1" s="50">
+      <c r="B6" s="403" t="n"/>
+      <c r="C6" s="404" t="n"/>
+      <c r="D6" s="405" t="n"/>
+      <c r="E6" s="403" t="n"/>
+      <c r="F6" s="404" t="n"/>
+      <c r="G6" s="405" t="n"/>
+      <c r="H6" s="403" t="n"/>
+      <c r="I6" s="404" t="n"/>
+      <c r="J6" s="405" t="n"/>
+      <c r="K6" s="403" t="n"/>
+      <c r="L6" s="404" t="n"/>
+      <c r="M6" s="405" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" s="50">
+      <c r="B7" s="406">
+        <f>KARAR_MOTORU!B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="404" t="n"/>
+      <c r="D7" s="405" t="n"/>
+      <c r="E7" s="407">
+        <f>KARAR_MOTORU!B7</f>
+        <v/>
+      </c>
+      <c r="F7" s="404" t="n"/>
+      <c r="G7" s="405" t="n"/>
+      <c r="H7" s="408">
+        <f>KARAR_MOTORU!B19</f>
+        <v/>
+      </c>
+      <c r="I7" s="404" t="n"/>
+      <c r="J7" s="405" t="n"/>
+      <c r="K7" s="409">
+        <f>KARAR_MOTORU!B15</f>
+        <v/>
+      </c>
+      <c r="L7" s="404" t="n"/>
+      <c r="M7" s="405" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1" s="50">
+      <c r="B8" s="403" t="n"/>
+      <c r="C8" s="404" t="n"/>
+      <c r="D8" s="405" t="n"/>
+      <c r="E8" s="403" t="n"/>
+      <c r="F8" s="404" t="n"/>
+      <c r="G8" s="405" t="n"/>
+      <c r="H8" s="403" t="n"/>
+      <c r="I8" s="404" t="n"/>
+      <c r="J8" s="405" t="n"/>
+      <c r="K8" s="403" t="n"/>
+      <c r="L8" s="404" t="n"/>
+      <c r="M8" s="405" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="50">
+      <c r="B9" s="410" t="inlineStr">
+        <is>
+          <t>↑ Aktif portföy risk hacmi</t>
+        </is>
+      </c>
+      <c r="C9" s="411" t="n"/>
+      <c r="D9" s="412" t="n"/>
+      <c r="E9" s="413" t="inlineStr">
+        <is>
+          <t>● 30 gün içinde vadesi gelen taksitler</t>
+        </is>
+      </c>
+      <c r="F9" s="411" t="n"/>
+      <c r="G9" s="412" t="n"/>
+      <c r="H9" s="410" t="inlineStr">
+        <is>
+          <t>✓ Yapılandırma ile aylık nakit kazanımı</t>
+        </is>
+      </c>
+      <c r="I9" s="411" t="n"/>
+      <c r="J9" s="412" t="n"/>
+      <c r="K9" s="414">
+        <f>KARAR_MOTORU!B17</f>
+        <v/>
+      </c>
+      <c r="L9" s="411" t="n"/>
+      <c r="M9" s="412" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1" s="50"/>
+    <row r="11" ht="24" customHeight="1" s="50">
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
+        </is>
+      </c>
+      <c r="F11" s="144" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="50">
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
+        </is>
+      </c>
+      <c r="H12" s="73" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1" s="50"/>
+    <row r="14" ht="26" customHeight="1" s="50">
+      <c r="B14" s="145" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C14" s="145" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="145" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="145" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="146" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="146" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="146" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="146" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="146" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="50">
+      <c r="B15" s="73" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="73" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="73" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="73" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="147" t="inlineStr">
+        <is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="227">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="228">
+        <f>B7*0.05</f>
+        <v/>
+      </c>
+      <c r="K15" s="149" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="133" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="50">
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="73" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="73" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="147" t="inlineStr">
+        <is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="227">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="228">
+        <f>B7*0.03</f>
+        <v/>
+      </c>
+      <c r="K16" s="149" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="130" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="50">
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="73" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="73" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="147" t="inlineStr">
+        <is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="227">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="228">
+        <f>B7*0.02</f>
+        <v/>
+      </c>
+      <c r="K17" s="149" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="150" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="50">
+      <c r="B18" s="73" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="73" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="73" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="147" t="inlineStr">
+        <is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="227">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="228">
+        <f>B7*0.01</f>
+        <v/>
+      </c>
+      <c r="K18" s="149" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="133" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="50">
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="73" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="73" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="73" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="151" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="229">
+        <f>SUM(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="230">
+        <f>SUM(J15:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="154" t="inlineStr"/>
+      <c r="L19" s="155" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1" s="50">
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="n">
+        <v>96</v>
+      </c>
+      <c r="D20" s="73" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="73" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1" s="50"/>
+    <row r="22" ht="24" customHeight="1" s="50">
+      <c r="B22" s="156" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="156" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="157" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU PROTOKOLÜ</t>
+        </is>
+      </c>
+      <c r="L22" s="158" t="n"/>
+      <c r="M22" s="158" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="50">
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="159" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="160" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN &amp; LİKİDİTE</t>
+        </is>
+      </c>
+      <c r="L23" s="158" t="n"/>
+      <c r="M23" s="158" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="50">
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="159" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="161" t="inlineStr">
+        <is>
+          <t>Sistem, nakit açığı riskini 30/60/90 günlük pencerelerde izleyerek, borç servisi oranını optimal eşikte tutacak yapılandırma önerir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="50">
+      <c r="B25" s="162" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="58" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="50">
+      <c r="B26" s="163" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="164" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="G26" s="247" t="n"/>
+      <c r="H26" s="247" t="n"/>
+      <c r="I26" s="248" t="n"/>
+      <c r="K26" s="165" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN ANALİZİNİ GÖR (#REFINANSMAN!A1) &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="10" customHeight="1" s="50">
+      <c r="F27" s="249" t="n"/>
+      <c r="G27" s="250" t="n"/>
+      <c r="H27" s="250" t="n"/>
+      <c r="I27" s="251" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23951,7 +25328,473 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:AN16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="40" customWidth="1" style="76" min="1" max="1"/>
+    <col width="20" customWidth="1" style="76" min="2" max="2"/>
+    <col width="18" customWidth="1" style="76" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="50">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="50">
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="50">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>Canlı Değer</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="50">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>Toplam Finansal Borç</t>
+        </is>
+      </c>
+      <c r="B6" s="92">
+        <f>KARAR_MOTORU!$B$5</f>
+        <v/>
+      </c>
+      <c r="C6" s="89">
+        <f>IF(B6="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="50">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>30 Günlük Ödeme Yükü</t>
+        </is>
+      </c>
+      <c r="B7" s="92">
+        <f>KARAR_MOTORU!$B$7</f>
+        <v/>
+      </c>
+      <c r="C7" s="89">
+        <f>IF(B7="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="50">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>Ağırlıklı Maliyet</t>
+        </is>
+      </c>
+      <c r="B8" s="93">
+        <f>KARAR_MOTORU!$B$9</f>
+        <v/>
+      </c>
+      <c r="C8" s="89">
+        <f>IF(B8="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="50">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>Veri Kalite Skoru</t>
+        </is>
+      </c>
+      <c r="B9" s="97">
+        <f>KONTROLLER!$B$6</f>
+        <v/>
+      </c>
+      <c r="C9" s="89">
+        <f>IF(B9="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="50">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>Karar Bildirimi</t>
+        </is>
+      </c>
+      <c r="B10" s="89">
+        <f>KARAR_MOTORU!$B$15</f>
+        <v/>
+      </c>
+      <c r="C10" s="89">
+        <f>IF(B10="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="50">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>Risk Seviyesi</t>
+        </is>
+      </c>
+      <c r="B11" s="89">
+        <f>KARAR_MOTORU!$B$16</f>
+        <v/>
+      </c>
+      <c r="C11" s="89">
+        <f>IF(B11="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="50">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>Refinansman Aday Sayısı</t>
+        </is>
+      </c>
+      <c r="B12" s="97">
+        <f>KARAR_MOTORU!$B$18</f>
+        <v/>
+      </c>
+      <c r="C12" s="89">
+        <f>IF(B12="","EKSİK","KONTROL EDİLDİ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24.75" customHeight="1" s="50">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Testler, excel_uretim/denetci.py ve test_banka_kredi.py ile otomatik çalışır.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AN1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12" customWidth="1" style="76" min="1" max="1"/>
+    <col width="16" customWidth="1" style="76" min="2" max="2"/>
+    <col width="14" customWidth="1" style="76" min="3" max="4"/>
+    <col width="10" customWidth="1" style="76" min="5" max="5"/>
+    <col width="14" customWidth="1" style="76" min="6" max="6"/>
+    <col width="40" customWidth="1" style="76" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="50">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="50">
+      <c r="A3" s="76" t="inlineStr">
+        <is>
+          <t>islem_id</t>
+        </is>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
+        <is>
+          <t>kaynak_kart_id</t>
+        </is>
+      </c>
+      <c r="C3" s="76" t="inlineStr">
+        <is>
+          <t>onceki_durum</t>
+        </is>
+      </c>
+      <c r="D3" s="76" t="inlineStr">
+        <is>
+          <t>yeni_durum</t>
+        </is>
+      </c>
+      <c r="E3" s="76" t="inlineStr">
+        <is>
+          <t>tutar</t>
+        </is>
+      </c>
+      <c r="F3" s="76" t="inlineStr">
+        <is>
+          <t>bayrak</t>
+        </is>
+      </c>
+      <c r="G3" s="76" t="inlineStr">
+        <is>
+          <t>not</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="50">
+      <c r="A4" s="76" t="inlineStr">
+        <is>
+          <t>I-001</t>
+        </is>
+      </c>
+      <c r="B4" s="76" t="inlineStr">
+        <is>
+          <t>KART-01</t>
+        </is>
+      </c>
+      <c r="C4" s="76" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="D4" s="76" t="inlineStr">
+        <is>
+          <t>ISLEMDE</t>
+        </is>
+      </c>
+      <c r="E4" s="119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" s="76" t="inlineStr">
+        <is>
+          <t>normal geçiş</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="50">
+      <c r="A5" s="76" t="inlineStr">
+        <is>
+          <t>I-002</t>
+        </is>
+      </c>
+      <c r="B5" s="76" t="inlineStr">
+        <is>
+          <t>YETİM</t>
+        </is>
+      </c>
+      <c r="C5" s="76" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="D5" s="76" t="inlineStr">
+        <is>
+          <t>KAPALI</t>
+        </is>
+      </c>
+      <c r="E5" s="119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="76" t="inlineStr">
+        <is>
+          <t>YETİM</t>
+        </is>
+      </c>
+      <c r="G5" s="76" t="inlineStr">
+        <is>
+          <t>kaynak_kart_id yok — yetim kayıt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="50">
+      <c r="A6" s="76" t="inlineStr">
+        <is>
+          <t>I-003</t>
+        </is>
+      </c>
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>KART-02</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="inlineStr">
+        <is>
+          <t>ACIK</t>
+        </is>
+      </c>
+      <c r="D6" s="76" t="inlineStr">
+        <is>
+          <t>KAPALI</t>
+        </is>
+      </c>
+      <c r="E6" s="119" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" s="76" t="inlineStr">
+        <is>
+          <t>GECERSIZ</t>
+        </is>
+      </c>
+      <c r="G6" s="76" t="inlineStr">
+        <is>
+          <t>geçersiz durum geçişi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="50">
+      <c r="A7" s="76" t="inlineStr">
+        <is>
+          <t>I-004</t>
+        </is>
+      </c>
+      <c r="B7" s="76" t="inlineStr">
+        <is>
+          <t>KART-03</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="inlineStr">
+        <is>
+          <t>ISLEMDE</t>
+        </is>
+      </c>
+      <c r="D7" s="76" t="inlineStr">
+        <is>
+          <t>ISLEMDE</t>
+        </is>
+      </c>
+      <c r="E7" s="119" t="n">
+        <v>250</v>
+      </c>
+      <c r="F7" s="76" t="inlineStr">
+        <is>
+          <t>ZINCIR_KIRIK</t>
+        </is>
+      </c>
+      <c r="G7" s="76" t="inlineStr">
+        <is>
+          <t>ZİNCİR KIRIK — tutar zinciri sapması</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="50">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>kuyruk_kanit</t>
+        </is>
+      </c>
+      <c r="B9" s="76">
+        <f>IFERROR(COUNTIF($F$4:$F$1000,"OK"),0)</f>
+        <v/>
+      </c>
+      <c r="C9" s="76" t="n"/>
+      <c r="D9" s="76" t="n"/>
+      <c r="E9" s="76" t="n"/>
+      <c r="F9" s="76" t="n"/>
+      <c r="G9" s="76" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:AN6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="12" customWidth="1" style="76" min="1" max="1"/>
+    <col width="14" customWidth="1" style="76" min="2" max="2"/>
+    <col width="90" customWidth="1" style="76" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="50">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="50">
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t>DEĞİŞİKLİK KAYDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="50">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Sürüm</t>
+        </is>
+      </c>
+      <c r="B5" s="86" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="inlineStr">
+        <is>
+          <t>Açıklama</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="50">
+      <c r="A6" s="120" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B6" s="120" t="inlineStr">
+        <is>
+          <t>08.08.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="115" t="inlineStr">
+        <is>
+          <t>İlk sürüm: banka limitleri, kredi portföyü, taksit planı, refinansman analizi ve karar motoru.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AN1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D97706"/>
@@ -24433,473 +26276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:AN16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="40" customWidth="1" style="76" min="1" max="1"/>
-    <col width="20" customWidth="1" style="76" min="2" max="2"/>
-    <col width="18" customWidth="1" style="76" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
-        <is>
-          <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B5" s="86" t="inlineStr">
-        <is>
-          <t>Canlı Değer</t>
-        </is>
-      </c>
-      <c r="C5" s="86" t="inlineStr">
-        <is>
-          <t>Durum</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="81" t="inlineStr">
-        <is>
-          <t>Toplam Finansal Borç</t>
-        </is>
-      </c>
-      <c r="B6" s="92">
-        <f>KARAR_MOTORU!$B$5</f>
-        <v/>
-      </c>
-      <c r="C6" s="89">
-        <f>IF(B6="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="81" t="inlineStr">
-        <is>
-          <t>30 Günlük Ödeme Yükü</t>
-        </is>
-      </c>
-      <c r="B7" s="92">
-        <f>KARAR_MOTORU!$B$7</f>
-        <v/>
-      </c>
-      <c r="C7" s="89">
-        <f>IF(B7="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="81" t="inlineStr">
-        <is>
-          <t>Ağırlıklı Maliyet</t>
-        </is>
-      </c>
-      <c r="B8" s="93">
-        <f>KARAR_MOTORU!$B$9</f>
-        <v/>
-      </c>
-      <c r="C8" s="89">
-        <f>IF(B8="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="81" t="inlineStr">
-        <is>
-          <t>Veri Kalite Skoru</t>
-        </is>
-      </c>
-      <c r="B9" s="97">
-        <f>KONTROLLER!$B$6</f>
-        <v/>
-      </c>
-      <c r="C9" s="89">
-        <f>IF(B9="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="81" t="inlineStr">
-        <is>
-          <t>Karar Bildirimi</t>
-        </is>
-      </c>
-      <c r="B10" s="89">
-        <f>KARAR_MOTORU!$B$15</f>
-        <v/>
-      </c>
-      <c r="C10" s="89">
-        <f>IF(B10="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="81" t="inlineStr">
-        <is>
-          <t>Risk Seviyesi</t>
-        </is>
-      </c>
-      <c r="B11" s="89">
-        <f>KARAR_MOTORU!$B$16</f>
-        <v/>
-      </c>
-      <c r="C11" s="89">
-        <f>IF(B11="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="50">
-      <c r="A12" s="81" t="inlineStr">
-        <is>
-          <t>Refinansman Aday Sayısı</t>
-        </is>
-      </c>
-      <c r="B12" s="97">
-        <f>KARAR_MOTORU!$B$18</f>
-        <v/>
-      </c>
-      <c r="C12" s="89">
-        <f>IF(B12="","EKSİK","KONTROL EDİLDİ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="24.75" customHeight="1" s="50">
-      <c r="A16" s="82" t="inlineStr">
-        <is>
-          <t>Testler, excel_uretim/denetci.py ve test_banka_kredi.py ile otomatik çalışır.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="16" customWidth="1" style="76" min="2" max="2"/>
-    <col width="14" customWidth="1" style="76" min="3" max="4"/>
-    <col width="10" customWidth="1" style="76" min="5" max="5"/>
-    <col width="14" customWidth="1" style="76" min="6" max="6"/>
-    <col width="40" customWidth="1" style="76" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="50">
-      <c r="A1" s="76" t="inlineStr">
-        <is>
-          <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="76" t="inlineStr">
-        <is>
-          <t>islem_id</t>
-        </is>
-      </c>
-      <c r="B3" s="76" t="inlineStr">
-        <is>
-          <t>kaynak_kart_id</t>
-        </is>
-      </c>
-      <c r="C3" s="76" t="inlineStr">
-        <is>
-          <t>onceki_durum</t>
-        </is>
-      </c>
-      <c r="D3" s="76" t="inlineStr">
-        <is>
-          <t>yeni_durum</t>
-        </is>
-      </c>
-      <c r="E3" s="76" t="inlineStr">
-        <is>
-          <t>tutar</t>
-        </is>
-      </c>
-      <c r="F3" s="76" t="inlineStr">
-        <is>
-          <t>bayrak</t>
-        </is>
-      </c>
-      <c r="G3" s="76" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="50">
-      <c r="A4" s="76" t="inlineStr">
-        <is>
-          <t>I-001</t>
-        </is>
-      </c>
-      <c r="B4" s="76" t="inlineStr">
-        <is>
-          <t>KART-01</t>
-        </is>
-      </c>
-      <c r="C4" s="76" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="D4" s="76" t="inlineStr">
-        <is>
-          <t>ISLEMDE</t>
-        </is>
-      </c>
-      <c r="E4" s="119" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="76" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G4" s="76" t="inlineStr">
-        <is>
-          <t>normal geçiş</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="50">
-      <c r="A5" s="76" t="inlineStr">
-        <is>
-          <t>I-002</t>
-        </is>
-      </c>
-      <c r="B5" s="76" t="inlineStr">
-        <is>
-          <t>YETİM</t>
-        </is>
-      </c>
-      <c r="C5" s="76" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="D5" s="76" t="inlineStr">
-        <is>
-          <t>KAPALI</t>
-        </is>
-      </c>
-      <c r="E5" s="119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="76" t="inlineStr">
-        <is>
-          <t>YETİM</t>
-        </is>
-      </c>
-      <c r="G5" s="76" t="inlineStr">
-        <is>
-          <t>kaynak_kart_id yok — yetim kayıt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="76" t="inlineStr">
-        <is>
-          <t>I-003</t>
-        </is>
-      </c>
-      <c r="B6" s="76" t="inlineStr">
-        <is>
-          <t>KART-02</t>
-        </is>
-      </c>
-      <c r="C6" s="76" t="inlineStr">
-        <is>
-          <t>ACIK</t>
-        </is>
-      </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>KAPALI</t>
-        </is>
-      </c>
-      <c r="E6" s="119" t="n">
-        <v>500</v>
-      </c>
-      <c r="F6" s="76" t="inlineStr">
-        <is>
-          <t>GECERSIZ</t>
-        </is>
-      </c>
-      <c r="G6" s="76" t="inlineStr">
-        <is>
-          <t>geçersiz durum geçişi</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="76" t="inlineStr">
-        <is>
-          <t>I-004</t>
-        </is>
-      </c>
-      <c r="B7" s="76" t="inlineStr">
-        <is>
-          <t>KART-03</t>
-        </is>
-      </c>
-      <c r="C7" s="76" t="inlineStr">
-        <is>
-          <t>ISLEMDE</t>
-        </is>
-      </c>
-      <c r="D7" s="76" t="inlineStr">
-        <is>
-          <t>ISLEMDE</t>
-        </is>
-      </c>
-      <c r="E7" s="119" t="n">
-        <v>250</v>
-      </c>
-      <c r="F7" s="76" t="inlineStr">
-        <is>
-          <t>ZINCIR_KIRIK</t>
-        </is>
-      </c>
-      <c r="G7" s="76" t="inlineStr">
-        <is>
-          <t>ZİNCİR KIRIK — tutar zinciri sapması</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="76" t="inlineStr">
-        <is>
-          <t>kuyruk_kanit</t>
-        </is>
-      </c>
-      <c r="B9" s="76">
-        <f>IFERROR(COUNTIF($F$4:$F$1000,"OK"),0)</f>
-        <v/>
-      </c>
-      <c r="C9" s="76" t="n"/>
-      <c r="D9" s="76" t="n"/>
-      <c r="E9" s="76" t="n"/>
-      <c r="F9" s="76" t="n"/>
-      <c r="G9" s="76" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:AN6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="14" customWidth="1" style="76" min="2" max="2"/>
-    <col width="90" customWidth="1" style="76" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
-        <is>
-          <t>DEĞİŞİKLİK KAYDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t>Sürüm</t>
-        </is>
-      </c>
-      <c r="B5" s="86" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="C5" s="86" t="inlineStr">
-        <is>
-          <t>Açıklama</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="120" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B6" s="120" t="inlineStr">
-        <is>
-          <t>08.08.2026</t>
-        </is>
-      </c>
-      <c r="C6" s="115" t="inlineStr">
-        <is>
-          <t>İlk sürüm: banka limitleri, kredi portföyü, taksit planı, refinansman analizi ve karar motoru.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -25563,7 +26940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -26377,7 +27754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -27427,7 +28804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -28424,7 +29801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="0060A5FA"/>
@@ -29439,632 +30816,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <tabColor rgb="0060A5FA"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:AN35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="11" customWidth="1" style="76" min="1" max="2"/>
-    <col width="24" customWidth="1" style="76" min="3" max="3"/>
-    <col width="18" customWidth="1" style="76" min="4" max="4"/>
-    <col width="13" customWidth="1" style="76" min="5" max="5"/>
-    <col width="15" customWidth="1" style="76" min="6" max="6"/>
-    <col width="14" customWidth="1" style="76" min="7" max="7"/>
-    <col width="13" customWidth="1" style="76" min="8" max="8"/>
-    <col width="10" customWidth="1" style="76" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
-        <is>
-          <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="150" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
-        <is>
-          <t>MASRAF VE KOMİSYONLAR — tahsis, sigorta, komisyon ve diğer finansman maliyetleri.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="50">
-      <c r="A5" s="86" t="inlineStr">
-        <is>
-          <t>Masraf ID</t>
-        </is>
-      </c>
-      <c r="B5" s="86" t="inlineStr">
-        <is>
-          <t>Kredi ID</t>
-        </is>
-      </c>
-      <c r="C5" s="86" t="inlineStr">
-        <is>
-          <t>Banka</t>
-        </is>
-      </c>
-      <c r="D5" s="86" t="inlineStr">
-        <is>
-          <t>Masraf Türü</t>
-        </is>
-      </c>
-      <c r="E5" s="86" t="inlineStr">
-        <is>
-          <t>İşlem Tarihi</t>
-        </is>
-      </c>
-      <c r="F5" s="86" t="inlineStr">
-        <is>
-          <t>Belge Numarası</t>
-        </is>
-      </c>
-      <c r="G5" s="86" t="inlineStr">
-        <is>
-          <t>Tutar</t>
-        </is>
-      </c>
-      <c r="H5" s="86" t="inlineStr">
-        <is>
-          <t>Para Birimi</t>
-        </is>
-      </c>
-      <c r="I5" s="86" t="inlineStr">
-        <is>
-          <t>Kontrol</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="50">
-      <c r="A6" s="87" t="inlineStr">
-        <is>
-          <t>MSF-001</t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>KRD-001</t>
-        </is>
-      </c>
-      <c r="C6" s="87" t="inlineStr">
-        <is>
-          <t>Türkiye İş Bankası</t>
-        </is>
-      </c>
-      <c r="D6" s="87" t="inlineStr">
-        <is>
-          <t>Tahsis Ücreti</t>
-        </is>
-      </c>
-      <c r="E6" s="94" t="n">
-        <v>45597</v>
-      </c>
-      <c r="F6" s="87" t="inlineStr">
-        <is>
-          <t>FTR-1001</t>
-        </is>
-      </c>
-      <c r="G6" s="91" t="n">
-        <v>60000</v>
-      </c>
-      <c r="H6" s="87" t="inlineStr">
-        <is>
-          <t>TRY</t>
-        </is>
-      </c>
-      <c r="I6" s="89">
-        <f>IF(ISBLANK($A6),"",IF(OR(ISBLANK($B6),ISBLANK($C6),ISBLANK($D6),ISBLANK($E6),ISBLANK($F6),ISBLANK($G6),ISBLANK($H6)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="50">
-      <c r="A7" s="87" t="inlineStr">
-        <is>
-          <t>MSF-002</t>
-        </is>
-      </c>
-      <c r="B7" s="87" t="inlineStr">
-        <is>
-          <t>KRD-002</t>
-        </is>
-      </c>
-      <c r="C7" s="87" t="inlineStr">
-        <is>
-          <t>Akbank</t>
-        </is>
-      </c>
-      <c r="D7" s="87" t="inlineStr">
-        <is>
-          <t>Sigorta</t>
-        </is>
-      </c>
-      <c r="E7" s="94" t="n">
-        <v>45717</v>
-      </c>
-      <c r="F7" s="87" t="inlineStr">
-        <is>
-          <t>POL-2001</t>
-        </is>
-      </c>
-      <c r="G7" s="91" t="n">
-        <v>70000</v>
-      </c>
-      <c r="H7" s="87" t="inlineStr">
-        <is>
-          <t>TRY</t>
-        </is>
-      </c>
-      <c r="I7" s="89">
-        <f>IF(ISBLANK($A7),"",IF(OR(ISBLANK($B7),ISBLANK($C7),ISBLANK($D7),ISBLANK($E7),ISBLANK($F7),ISBLANK($G7),ISBLANK($H7)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="50">
-      <c r="A8" s="87" t="inlineStr">
-        <is>
-          <t>MSF-003</t>
-        </is>
-      </c>
-      <c r="B8" s="87" t="inlineStr">
-        <is>
-          <t>KRD-003</t>
-        </is>
-      </c>
-      <c r="C8" s="87" t="inlineStr">
-        <is>
-          <t>Garanti BBVA</t>
-        </is>
-      </c>
-      <c r="D8" s="87" t="inlineStr">
-        <is>
-          <t>Komisyon</t>
-        </is>
-      </c>
-      <c r="E8" s="94" t="n">
-        <v>45809</v>
-      </c>
-      <c r="F8" s="87" t="inlineStr">
-        <is>
-          <t>FTR-3001</t>
-        </is>
-      </c>
-      <c r="G8" s="91" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H8" s="87" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I8" s="89">
-        <f>IF(ISBLANK($A8),"",IF(OR(ISBLANK($B8),ISBLANK($C8),ISBLANK($D8),ISBLANK($E8),ISBLANK($F8),ISBLANK($G8),ISBLANK($H8)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="50">
-      <c r="A9" s="90" t="n"/>
-      <c r="B9" s="90" t="n"/>
-      <c r="C9" s="90" t="n"/>
-      <c r="D9" s="90" t="n"/>
-      <c r="E9" s="90" t="n"/>
-      <c r="F9" s="90" t="n"/>
-      <c r="G9" s="90" t="n"/>
-      <c r="H9" s="90" t="n"/>
-      <c r="I9" s="89">
-        <f>IF(ISBLANK($A9),"",IF(OR(ISBLANK($B9),ISBLANK($C9),ISBLANK($D9),ISBLANK($E9),ISBLANK($F9),ISBLANK($G9),ISBLANK($H9)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="50">
-      <c r="A10" s="90" t="n"/>
-      <c r="B10" s="90" t="n"/>
-      <c r="C10" s="90" t="n"/>
-      <c r="D10" s="90" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="90" t="n"/>
-      <c r="G10" s="90" t="n"/>
-      <c r="H10" s="90" t="n"/>
-      <c r="I10" s="89">
-        <f>IF(ISBLANK($A10),"",IF(OR(ISBLANK($B10),ISBLANK($C10),ISBLANK($D10),ISBLANK($E10),ISBLANK($F10),ISBLANK($G10),ISBLANK($H10)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="50">
-      <c r="A11" s="90" t="n"/>
-      <c r="B11" s="90" t="n"/>
-      <c r="C11" s="90" t="n"/>
-      <c r="D11" s="90" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="90" t="n"/>
-      <c r="G11" s="90" t="n"/>
-      <c r="H11" s="90" t="n"/>
-      <c r="I11" s="89">
-        <f>IF(ISBLANK($A11),"",IF(OR(ISBLANK($B11),ISBLANK($C11),ISBLANK($D11),ISBLANK($E11),ISBLANK($F11),ISBLANK($G11),ISBLANK($H11)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="50">
-      <c r="A12" s="90" t="n"/>
-      <c r="B12" s="90" t="n"/>
-      <c r="C12" s="90" t="n"/>
-      <c r="D12" s="90" t="n"/>
-      <c r="E12" s="90" t="n"/>
-      <c r="F12" s="90" t="n"/>
-      <c r="G12" s="90" t="n"/>
-      <c r="H12" s="90" t="n"/>
-      <c r="I12" s="89">
-        <f>IF(ISBLANK($A12),"",IF(OR(ISBLANK($B12),ISBLANK($C12),ISBLANK($D12),ISBLANK($E12),ISBLANK($F12),ISBLANK($G12),ISBLANK($H12)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="50">
-      <c r="A13" s="90" t="n"/>
-      <c r="B13" s="90" t="n"/>
-      <c r="C13" s="90" t="n"/>
-      <c r="D13" s="90" t="n"/>
-      <c r="E13" s="90" t="n"/>
-      <c r="F13" s="90" t="n"/>
-      <c r="G13" s="90" t="n"/>
-      <c r="H13" s="90" t="n"/>
-      <c r="I13" s="89">
-        <f>IF(ISBLANK($A13),"",IF(OR(ISBLANK($B13),ISBLANK($C13),ISBLANK($D13),ISBLANK($E13),ISBLANK($F13),ISBLANK($G13),ISBLANK($H13)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="50">
-      <c r="A14" s="90" t="n"/>
-      <c r="B14" s="90" t="n"/>
-      <c r="C14" s="90" t="n"/>
-      <c r="D14" s="90" t="n"/>
-      <c r="E14" s="90" t="n"/>
-      <c r="F14" s="90" t="n"/>
-      <c r="G14" s="90" t="n"/>
-      <c r="H14" s="90" t="n"/>
-      <c r="I14" s="89">
-        <f>IF(ISBLANK($A14),"",IF(OR(ISBLANK($B14),ISBLANK($C14),ISBLANK($D14),ISBLANK($E14),ISBLANK($F14),ISBLANK($G14),ISBLANK($H14)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="50">
-      <c r="A15" s="90" t="n"/>
-      <c r="B15" s="90" t="n"/>
-      <c r="C15" s="90" t="n"/>
-      <c r="D15" s="90" t="n"/>
-      <c r="E15" s="90" t="n"/>
-      <c r="F15" s="90" t="n"/>
-      <c r="G15" s="90" t="n"/>
-      <c r="H15" s="90" t="n"/>
-      <c r="I15" s="89">
-        <f>IF(ISBLANK($A15),"",IF(OR(ISBLANK($B15),ISBLANK($C15),ISBLANK($D15),ISBLANK($E15),ISBLANK($F15),ISBLANK($G15),ISBLANK($H15)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="50">
-      <c r="A16" s="90" t="n"/>
-      <c r="B16" s="90" t="n"/>
-      <c r="C16" s="90" t="n"/>
-      <c r="D16" s="90" t="n"/>
-      <c r="E16" s="90" t="n"/>
-      <c r="F16" s="90" t="n"/>
-      <c r="G16" s="90" t="n"/>
-      <c r="H16" s="90" t="n"/>
-      <c r="I16" s="89">
-        <f>IF(ISBLANK($A16),"",IF(OR(ISBLANK($B16),ISBLANK($C16),ISBLANK($D16),ISBLANK($E16),ISBLANK($F16),ISBLANK($G16),ISBLANK($H16)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="50">
-      <c r="A17" s="90" t="n"/>
-      <c r="B17" s="90" t="n"/>
-      <c r="C17" s="90" t="n"/>
-      <c r="D17" s="90" t="n"/>
-      <c r="E17" s="90" t="n"/>
-      <c r="F17" s="90" t="n"/>
-      <c r="G17" s="90" t="n"/>
-      <c r="H17" s="90" t="n"/>
-      <c r="I17" s="89">
-        <f>IF(ISBLANK($A17),"",IF(OR(ISBLANK($B17),ISBLANK($C17),ISBLANK($D17),ISBLANK($E17),ISBLANK($F17),ISBLANK($G17),ISBLANK($H17)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="50">
-      <c r="A18" s="90" t="n"/>
-      <c r="B18" s="90" t="n"/>
-      <c r="C18" s="90" t="n"/>
-      <c r="D18" s="90" t="n"/>
-      <c r="E18" s="90" t="n"/>
-      <c r="F18" s="90" t="n"/>
-      <c r="G18" s="90" t="n"/>
-      <c r="H18" s="90" t="n"/>
-      <c r="I18" s="89">
-        <f>IF(ISBLANK($A18),"",IF(OR(ISBLANK($B18),ISBLANK($C18),ISBLANK($D18),ISBLANK($E18),ISBLANK($F18),ISBLANK($G18),ISBLANK($H18)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="50">
-      <c r="A19" s="90" t="n"/>
-      <c r="B19" s="90" t="n"/>
-      <c r="C19" s="90" t="n"/>
-      <c r="D19" s="90" t="n"/>
-      <c r="E19" s="90" t="n"/>
-      <c r="F19" s="90" t="n"/>
-      <c r="G19" s="90" t="n"/>
-      <c r="H19" s="90" t="n"/>
-      <c r="I19" s="89">
-        <f>IF(ISBLANK($A19),"",IF(OR(ISBLANK($B19),ISBLANK($C19),ISBLANK($D19),ISBLANK($E19),ISBLANK($F19),ISBLANK($G19),ISBLANK($H19)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="50">
-      <c r="A20" s="90" t="n"/>
-      <c r="B20" s="90" t="n"/>
-      <c r="C20" s="90" t="n"/>
-      <c r="D20" s="90" t="n"/>
-      <c r="E20" s="90" t="n"/>
-      <c r="F20" s="90" t="n"/>
-      <c r="G20" s="90" t="n"/>
-      <c r="H20" s="90" t="n"/>
-      <c r="I20" s="89">
-        <f>IF(ISBLANK($A20),"",IF(OR(ISBLANK($B20),ISBLANK($C20),ISBLANK($D20),ISBLANK($E20),ISBLANK($F20),ISBLANK($G20),ISBLANK($H20)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="50">
-      <c r="A21" s="90" t="n"/>
-      <c r="B21" s="90" t="n"/>
-      <c r="C21" s="90" t="n"/>
-      <c r="D21" s="90" t="n"/>
-      <c r="E21" s="90" t="n"/>
-      <c r="F21" s="90" t="n"/>
-      <c r="G21" s="90" t="n"/>
-      <c r="H21" s="90" t="n"/>
-      <c r="I21" s="89">
-        <f>IF(ISBLANK($A21),"",IF(OR(ISBLANK($B21),ISBLANK($C21),ISBLANK($D21),ISBLANK($E21),ISBLANK($F21),ISBLANK($G21),ISBLANK($H21)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="50">
-      <c r="A22" s="90" t="n"/>
-      <c r="B22" s="90" t="n"/>
-      <c r="C22" s="90" t="n"/>
-      <c r="D22" s="90" t="n"/>
-      <c r="E22" s="90" t="n"/>
-      <c r="F22" s="90" t="n"/>
-      <c r="G22" s="90" t="n"/>
-      <c r="H22" s="90" t="n"/>
-      <c r="I22" s="89">
-        <f>IF(ISBLANK($A22),"",IF(OR(ISBLANK($B22),ISBLANK($C22),ISBLANK($D22),ISBLANK($E22),ISBLANK($F22),ISBLANK($G22),ISBLANK($H22)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="50">
-      <c r="A23" s="90" t="n"/>
-      <c r="B23" s="90" t="n"/>
-      <c r="C23" s="90" t="n"/>
-      <c r="D23" s="90" t="n"/>
-      <c r="E23" s="90" t="n"/>
-      <c r="F23" s="90" t="n"/>
-      <c r="G23" s="90" t="n"/>
-      <c r="H23" s="90" t="n"/>
-      <c r="I23" s="89">
-        <f>IF(ISBLANK($A23),"",IF(OR(ISBLANK($B23),ISBLANK($C23),ISBLANK($D23),ISBLANK($E23),ISBLANK($F23),ISBLANK($G23),ISBLANK($H23)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="50">
-      <c r="A24" s="90" t="n"/>
-      <c r="B24" s="90" t="n"/>
-      <c r="C24" s="90" t="n"/>
-      <c r="D24" s="90" t="n"/>
-      <c r="E24" s="90" t="n"/>
-      <c r="F24" s="90" t="n"/>
-      <c r="G24" s="90" t="n"/>
-      <c r="H24" s="90" t="n"/>
-      <c r="I24" s="89">
-        <f>IF(ISBLANK($A24),"",IF(OR(ISBLANK($B24),ISBLANK($C24),ISBLANK($D24),ISBLANK($E24),ISBLANK($F24),ISBLANK($G24),ISBLANK($H24)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="50">
-      <c r="A25" s="90" t="n"/>
-      <c r="B25" s="90" t="n"/>
-      <c r="C25" s="90" t="n"/>
-      <c r="D25" s="90" t="n"/>
-      <c r="E25" s="90" t="n"/>
-      <c r="F25" s="90" t="n"/>
-      <c r="G25" s="90" t="n"/>
-      <c r="H25" s="90" t="n"/>
-      <c r="I25" s="89">
-        <f>IF(ISBLANK($A25),"",IF(OR(ISBLANK($B25),ISBLANK($C25),ISBLANK($D25),ISBLANK($E25),ISBLANK($F25),ISBLANK($G25),ISBLANK($H25)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="50">
-      <c r="A26" s="90" t="n"/>
-      <c r="B26" s="90" t="n"/>
-      <c r="C26" s="90" t="n"/>
-      <c r="D26" s="90" t="n"/>
-      <c r="E26" s="90" t="n"/>
-      <c r="F26" s="90" t="n"/>
-      <c r="G26" s="90" t="n"/>
-      <c r="H26" s="90" t="n"/>
-      <c r="I26" s="89">
-        <f>IF(ISBLANK($A26),"",IF(OR(ISBLANK($B26),ISBLANK($C26),ISBLANK($D26),ISBLANK($E26),ISBLANK($F26),ISBLANK($G26),ISBLANK($H26)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="50">
-      <c r="A27" s="90" t="n"/>
-      <c r="B27" s="90" t="n"/>
-      <c r="C27" s="90" t="n"/>
-      <c r="D27" s="90" t="n"/>
-      <c r="E27" s="90" t="n"/>
-      <c r="F27" s="90" t="n"/>
-      <c r="G27" s="90" t="n"/>
-      <c r="H27" s="90" t="n"/>
-      <c r="I27" s="89">
-        <f>IF(ISBLANK($A27),"",IF(OR(ISBLANK($B27),ISBLANK($C27),ISBLANK($D27),ISBLANK($E27),ISBLANK($F27),ISBLANK($G27),ISBLANK($H27)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="50">
-      <c r="A28" s="90" t="n"/>
-      <c r="B28" s="90" t="n"/>
-      <c r="C28" s="90" t="n"/>
-      <c r="D28" s="90" t="n"/>
-      <c r="E28" s="90" t="n"/>
-      <c r="F28" s="90" t="n"/>
-      <c r="G28" s="90" t="n"/>
-      <c r="H28" s="90" t="n"/>
-      <c r="I28" s="89">
-        <f>IF(ISBLANK($A28),"",IF(OR(ISBLANK($B28),ISBLANK($C28),ISBLANK($D28),ISBLANK($E28),ISBLANK($F28),ISBLANK($G28),ISBLANK($H28)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="50">
-      <c r="A29" s="90" t="n"/>
-      <c r="B29" s="90" t="n"/>
-      <c r="C29" s="90" t="n"/>
-      <c r="D29" s="90" t="n"/>
-      <c r="E29" s="90" t="n"/>
-      <c r="F29" s="90" t="n"/>
-      <c r="G29" s="90" t="n"/>
-      <c r="H29" s="90" t="n"/>
-      <c r="I29" s="89">
-        <f>IF(ISBLANK($A29),"",IF(OR(ISBLANK($B29),ISBLANK($C29),ISBLANK($D29),ISBLANK($E29),ISBLANK($F29),ISBLANK($G29),ISBLANK($H29)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="50">
-      <c r="A30" s="90" t="n"/>
-      <c r="B30" s="90" t="n"/>
-      <c r="C30" s="90" t="n"/>
-      <c r="D30" s="90" t="n"/>
-      <c r="E30" s="90" t="n"/>
-      <c r="F30" s="90" t="n"/>
-      <c r="G30" s="90" t="n"/>
-      <c r="H30" s="90" t="n"/>
-      <c r="I30" s="89">
-        <f>IF(ISBLANK($A30),"",IF(OR(ISBLANK($B30),ISBLANK($C30),ISBLANK($D30),ISBLANK($E30),ISBLANK($F30),ISBLANK($G30),ISBLANK($H30)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="50">
-      <c r="A31" s="90" t="n"/>
-      <c r="B31" s="90" t="n"/>
-      <c r="C31" s="90" t="n"/>
-      <c r="D31" s="90" t="n"/>
-      <c r="E31" s="90" t="n"/>
-      <c r="F31" s="90" t="n"/>
-      <c r="G31" s="90" t="n"/>
-      <c r="H31" s="90" t="n"/>
-      <c r="I31" s="89">
-        <f>IF(ISBLANK($A31),"",IF(OR(ISBLANK($B31),ISBLANK($C31),ISBLANK($D31),ISBLANK($E31),ISBLANK($F31),ISBLANK($G31),ISBLANK($H31)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="50">
-      <c r="A32" s="90" t="n"/>
-      <c r="B32" s="90" t="n"/>
-      <c r="C32" s="90" t="n"/>
-      <c r="D32" s="90" t="n"/>
-      <c r="E32" s="90" t="n"/>
-      <c r="F32" s="90" t="n"/>
-      <c r="G32" s="90" t="n"/>
-      <c r="H32" s="90" t="n"/>
-      <c r="I32" s="89">
-        <f>IF(ISBLANK($A32),"",IF(OR(ISBLANK($B32),ISBLANK($C32),ISBLANK($D32),ISBLANK($E32),ISBLANK($F32),ISBLANK($G32),ISBLANK($H32)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="50">
-      <c r="A33" s="90" t="n"/>
-      <c r="B33" s="90" t="n"/>
-      <c r="C33" s="90" t="n"/>
-      <c r="D33" s="90" t="n"/>
-      <c r="E33" s="90" t="n"/>
-      <c r="F33" s="90" t="n"/>
-      <c r="G33" s="90" t="n"/>
-      <c r="H33" s="90" t="n"/>
-      <c r="I33" s="89">
-        <f>IF(ISBLANK($A33),"",IF(OR(ISBLANK($B33),ISBLANK($C33),ISBLANK($D33),ISBLANK($E33),ISBLANK($F33),ISBLANK($G33),ISBLANK($H33)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="50">
-      <c r="A34" s="90" t="n"/>
-      <c r="B34" s="90" t="n"/>
-      <c r="C34" s="90" t="n"/>
-      <c r="D34" s="90" t="n"/>
-      <c r="E34" s="90" t="n"/>
-      <c r="F34" s="90" t="n"/>
-      <c r="G34" s="90" t="n"/>
-      <c r="H34" s="90" t="n"/>
-      <c r="I34" s="89">
-        <f>IF(ISBLANK($A34),"",IF(OR(ISBLANK($B34),ISBLANK($C34),ISBLANK($D34),ISBLANK($E34),ISBLANK($F34),ISBLANK($G34),ISBLANK($H34)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="50">
-      <c r="A35" s="90" t="n"/>
-      <c r="B35" s="90" t="n"/>
-      <c r="C35" s="90" t="n"/>
-      <c r="D35" s="90" t="n"/>
-      <c r="E35" s="90" t="n"/>
-      <c r="F35" s="90" t="n"/>
-      <c r="G35" s="90" t="n"/>
-      <c r="H35" s="90" t="n"/>
-      <c r="I35" s="89">
-        <f>IF(ISBLANK($A35),"",IF(OR(ISBLANK($B35),ISBLANK($C35),ISBLANK($D35),ISBLANK($E35),ISBLANK($F35),ISBLANK($G35),ISBLANK($H35)),"EKSİK","OK"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G6:G1000">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D1000">
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>"Komisyon"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I1000">
-    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="equal" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
-      <formula>"EKSİK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="D6:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz Tür" error="Lütfen listeden bir masraf türü seçin." promptTitle="Masraf Türü" prompt="Tahsis Ücreti, Sigorta, Komisyon veya Diğer seçin." type="list" errorStyle="stop" operator="between">
-      <formula1>ListeMasrafTuru</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation sqref="B6:B1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz Kredi" error="Lütfen KREDILER sayfasındaki bir kredi ID seçin." promptTitle="Kredi ID" prompt="Listeden kredi seçin." type="list" errorStyle="stop" operator="between">
-      <formula1>ListeKrediId</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -119,7 +119,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="126">
+  <fonts count="128">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -882,6 +882,18 @@
       <color rgb="002563EB"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -1094,7 +1106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -1746,6 +1758,18 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1757,7 +1781,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="427">
+  <cellXfs count="441">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2825,6 +2849,46 @@
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="20" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -13460,14 +13524,14 @@
     </row>
     <row r="3" ht="7.8" customHeight="1" s="50"/>
     <row r="4" ht="17.4" customHeight="1" s="50">
-      <c r="B4" s="353" t="inlineStr">
+      <c r="B4" s="427" t="inlineStr">
         <is>
           <t>Banka, Kredi ve Taksit Takip Sistemi — C-Level Borç Portföyü ve Likidite Karar Kokpiti</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17.4" customHeight="1" s="50">
-      <c r="B5" s="354" t="inlineStr">
+      <c r="B5" s="428" t="inlineStr">
         <is>
           <t>Hedef Kitle: KOBİ Sahipleri, CFO, Finans Direktörleri ve Hazine Yöneticileri · VUK 185-198 &amp; TTK 64 Tam Uyumlu</t>
         </is>
@@ -13894,9 +13958,10 @@
       <c r="R26" s="337" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="24">
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B4:R4"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="D25:M25"/>
     <mergeCell ref="P23:R23"/>
@@ -13917,6 +13982,7 @@
     <mergeCell ref="P25:R25"/>
     <mergeCell ref="N24:O24"/>
     <mergeCell ref="P22:R22"/>
+    <mergeCell ref="B5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId1"/>
@@ -13952,20 +14018,30 @@
     <col width="10" customWidth="1" style="76" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="150" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>MASRAF VE KOMİSYONLAR — tahsis, sigorta, komisyon ve diğer finansman maliyetleri.</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -14519,8 +14595,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -14582,20 +14659,31 @@
     <col width="10" customWidth="1" style="76" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>TEMINATLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="90.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>TEMİNAT YÖNETİMİ — değer, geçerlilik ve kredi bağlantısı.</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -15190,8 +15278,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -15253,20 +15342,32 @@
     <col width="10" customWidth="1" style="76" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>YENI TEKLIFLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="135.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>YENİ KREDİ TEKLİFLERİ — tutar, faiz, masraf ve aylık taksit karşılaştırması.</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -16058,8 +16159,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -16117,16 +16219,25 @@
     <col width="14" customWidth="1" style="76" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>REFİNANSMAN ANALİZİ — aylık taksit rahatlaması ve toplam maliyet.</t>
         </is>
@@ -17447,8 +17558,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThanOrEqual" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -17509,21 +17621,21 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" s="50">
-      <c r="B2" s="188" t="inlineStr">
+      <c r="B2" s="436" t="inlineStr">
         <is>
           <t>BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ — FİNANSAL STRES TESTİ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="189" t="inlineStr">
+      <c r="B3" s="437" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve Hazine Komitesi için Borç Servisi ve Likidite Dayanıklılık Raporu</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="50">
-      <c r="B4" s="190" t="inlineStr">
+      <c r="B4" s="438" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
@@ -17531,24 +17643,24 @@
     </row>
     <row r="5" ht="14" customHeight="1" s="50"/>
     <row r="6" ht="28" customHeight="1" s="50">
-      <c r="B6" s="415" t="inlineStr">
+      <c r="B6" s="439" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="399" t="n"/>
-      <c r="D6" s="399" t="n"/>
-      <c r="E6" s="399" t="n"/>
-      <c r="F6" s="416" t="n"/>
-      <c r="H6" s="417" t="inlineStr">
+      <c r="C6" s="290" t="n"/>
+      <c r="D6" s="290" t="n"/>
+      <c r="E6" s="290" t="n"/>
+      <c r="F6" s="291" t="n"/>
+      <c r="H6" s="440" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="399" t="n"/>
-      <c r="J6" s="399" t="n"/>
-      <c r="K6" s="399" t="n"/>
-      <c r="L6" s="416" t="n"/>
+      <c r="I6" s="290" t="n"/>
+      <c r="J6" s="290" t="n"/>
+      <c r="K6" s="290" t="n"/>
+      <c r="L6" s="291" t="n"/>
     </row>
     <row r="7" ht="8" customHeight="1" s="50">
       <c r="B7" s="418" t="n"/>
@@ -17788,11 +17900,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="H14:L15"/>
     <mergeCell ref="B14:F15"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18000,20 +18115,30 @@
     <col width="26" customWidth="1" style="76" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>KARAR MOTORU — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="52.5" customHeight="1" s="50">
-      <c r="A3" s="110" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>KARAR MOTORU — borç yükü, yaklaşan taksit ve öncelikli aksiyon</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="15" customHeight="1" s="50">
       <c r="A5" s="81" t="inlineStr">
         <is>
@@ -18188,8 +18313,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B14">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -18831,20 +18957,30 @@
     <col width="20" customWidth="1" style="76" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>SENARYO VE DUYARLILIK ANALİZİ</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="15" customHeight="1" s="50">
       <c r="A5" s="81" t="inlineStr">
         <is>
@@ -19049,8 +19185,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
@@ -19097,20 +19234,32 @@
     <col width="24" customWidth="1" style="76" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>KONTROLLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>VERİ KALİTESİ VE SİSTEM SAĞLIĞI</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="50">
       <c r="A6" s="100" t="inlineStr">
         <is>
@@ -19219,8 +19368,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
@@ -19281,14 +19431,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="371" t="inlineStr">
+      <c r="B2" s="429" t="inlineStr">
         <is>
           <t>SİSTEM HAKKINDA, KULLANIM REHBERİ VE TERİMLER SÖZLÜĞÜ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="50">
-      <c r="B3" s="372" t="inlineStr">
+      <c r="B3" s="430" t="inlineStr">
         <is>
           <t>5 Yaşındaki Birine Anlatır Gibi Basit, Sade ve Eksiksiz Finansal Karar Mimarisi · Siemens &amp; Enterprise Standartları</t>
         </is>
@@ -19720,6 +19870,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19747,21 +19901,30 @@
     <col width="13" customWidth="1" style="76" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>AYARLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="19.5" customHeight="1" s="50">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
         <is>
           <t>Tüm eşikler, katsayılar ve firma bilgileri tek kaynaktan (SSOT) buradan yönetilir. Değerleri değiştirirken Alt/Üst sınırlara dikkat edin.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="50">
+    <row r="3"/>
+    <row r="4" ht="10" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
           <t>FIRMA BİLGİLERİ</t>
@@ -20715,7 +20878,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:AN2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -20750,20 +20913,34 @@
     <col width="14" customWidth="1" style="76" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>LISTELER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
+      <c r="M1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>AÇILIR LİSTE KAYNAKLARI</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="15" customHeight="1" s="50">
       <c r="A5" s="84" t="inlineStr">
         <is>
@@ -20950,8 +21127,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -24617,24 +24795,14 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="242" t="inlineStr">
+      <c r="B2" s="431" t="inlineStr">
         <is>
           <t>BANKA, KREDİ VE TAKSİT YÖNETİM MERKEZİ</t>
         </is>
       </c>
-      <c r="L2" s="125" t="inlineStr">
-        <is>
-          <t>Dönem: 2026 / Tam ▼</t>
-        </is>
-      </c>
-      <c r="M2" s="126" t="inlineStr">
-        <is>
-          <t>★ DOĞRULANMIŞ</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="237" t="inlineStr">
+      <c r="B3" s="432" t="inlineStr">
         <is>
           <t>Konsolide Kredi Portföyü, Aylık Borç Servisi ve Likidite Karar Kokpiti · Canlı Hesaplama</t>
         </is>
@@ -25158,10 +25326,12 @@
       <c r="I27" s="251" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:M2"/>
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="K26:M27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
@@ -25184,20 +25354,30 @@
     <col width="42" customWidth="1" style="76" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>ORNEK VERI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="45.75" customHeight="1" s="50">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>ÖRNEK VERİ — otomasyon ve içe aktarma için yapı</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -25319,8 +25499,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25342,20 +25523,30 @@
     <col width="18" customWidth="1" style="76" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -25487,8 +25678,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25735,20 +25927,30 @@
     <col width="90" customWidth="1" style="76" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="99" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>DEĞİŞİKLİK KAYDI</t>
         </is>
       </c>
     </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="30" customHeight="1" s="50">
       <c r="A5" s="86" t="inlineStr">
         <is>
@@ -25785,8 +25987,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -26297,16 +26500,24 @@
     <col width="14" customWidth="1" style="76" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>BANKA TANIMLARI — ilişki, operasyonel durum ve iletişim tek merkezde.</t>
         </is>
@@ -26902,8 +27113,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
@@ -26961,16 +27173,24 @@
     <col width="14" customWidth="1" style="76" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>BANKA LİMİTLERİ — toplam, kullanılan ve kalan limit ile kullanım oranı.</t>
         </is>
@@ -27706,8 +27926,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -27780,16 +28001,29 @@
     <col width="14" customWidth="1" style="76" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
+      <c r="M1" s="434" t="n"/>
+      <c r="N1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>KREDİ PORTFÖYÜ — sözleşme, bakiye, maliyet, vade ve taksit bilgileri.</t>
         </is>
@@ -28756,8 +28990,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThanOrEqual" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
@@ -28828,16 +29063,27 @@
     <col width="14" customWidth="1" style="76" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>TAKSİT PLANI — dönem bazında anapara, faiz, vergi ve ödeme tarihi.</t>
         </is>
@@ -29742,8 +29988,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="I6:I1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThanOrEqual" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -29820,16 +30067,24 @@
     <col width="15" customWidth="1" style="76" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" s="50">
-      <c r="A1" s="305" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="433" t="inlineStr">
         <is>
           <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="50"/>
-    <row r="3" ht="20" customHeight="1" s="50">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2" ht="7.8" customHeight="1" s="50"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="435" t="inlineStr">
         <is>
           <t>ÖDEME TAKVİMİ — yaklaşan taksitler 30 / 60 / 90 gün penceresinde.</t>
         </is>
@@ -30775,8 +31030,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -3135,6 +3135,226 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>DÖNEMSEL BORÇ HACMİ VE MALİYET TRENDİ</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'PANO'!C14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'PANO'!$B$15:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PANO'!$C$15:$C$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'PANO'!D14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'PANO'!$B$15:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PANO'!$D$15:$D$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'PANO'!E14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'PANO'!$B$15:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PANO'!$E$15:$E$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Dönemler</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Endeks / Milyon TL</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>BORÇ DAĞILIMI VE RİSK YOĞUNLAŞMASI</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <doughnutChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'PANO'!I14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'PANO'!$H$15:$H$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'PANO'!$I$15:$I$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+        <holeSize val="60"/>
+      </doughnutChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
@@ -3413,7 +3633,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -13074,6 +13294,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5940000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5220000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
@@ -14005,7 +14274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="76" min="1" max="2"/>
@@ -14024,14 +14293,6 @@
           <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -14644,7 +14905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
@@ -14665,15 +14926,6 @@
           <t>TEMINATLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -15327,7 +15579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
@@ -15348,16 +15600,6 @@
           <t>YENI TEKLIFLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -16204,7 +16446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -16225,15 +16467,6 @@
           <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -18108,7 +18341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="38" customWidth="1" style="76" min="1" max="1"/>
@@ -18121,14 +18354,6 @@
           <t>KARAR MOTORU — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -18949,7 +19174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
@@ -18963,14 +19188,6 @@
           <t>SENARYO DUYARLILIK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -19227,7 +19444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
@@ -19240,15 +19457,6 @@
           <t>KONTROLLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -19259,7 +19467,6 @@
       </c>
     </row>
     <row r="4" ht="10" customHeight="1" s="50"/>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="50">
       <c r="A6" s="100" t="inlineStr">
         <is>
@@ -19907,14 +20114,6 @@
           <t>AYARLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
@@ -19923,7 +20122,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="10" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
@@ -20895,7 +21093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="76" min="1" max="1"/>
@@ -20919,18 +21117,6 @@
           <t>LISTELER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
-      <c r="M1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -25337,6 +25523,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -25346,7 +25533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="76" min="1" max="1"/>
@@ -25360,14 +25547,6 @@
           <t>ORNEK VERI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -25515,7 +25694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="76" min="1" max="1"/>
@@ -25529,14 +25708,6 @@
           <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -25919,7 +26090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
@@ -25933,14 +26104,6 @@
           <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -26486,7 +26649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -26506,14 +26669,6 @@
           <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -27159,7 +27314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -27179,14 +27334,6 @@
           <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -27982,7 +28129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -28007,19 +28154,6 @@
           <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
-      <c r="M1" s="434" t="n"/>
-      <c r="N1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -29046,7 +29180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="2"/>
@@ -29069,17 +29203,6 @@
           <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -30055,7 +30178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -30073,14 +30196,6 @@
           <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -3135,7 +3135,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3165,6 +3164,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B365D"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3189,6 +3191,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D97706"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3213,6 +3218,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="059669"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3296,7 +3304,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3329,6 +3336,50 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1B365D"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2563EB"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="D97706"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="059669"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'PANO'!$H$15:$H$18</f>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -1781,7 +1781,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="441">
+  <cellXfs count="443">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2889,6 +2889,12 @@
     </xf>
     <xf numFmtId="0" fontId="77" fillId="11" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -13878,7 +13884,7 @@
       <c r="B7" s="355" t="n"/>
       <c r="C7" s="356" t="inlineStr">
         <is>
-          <t>EĞİTİM VİDEOSU</t>
+          <t>1. SİSTEMİN ÖZÜ &amp; MANTIK</t>
         </is>
       </c>
       <c r="D7" s="357" t="n"/>
@@ -13887,7 +13893,7 @@
       <c r="H7" s="355" t="n"/>
       <c r="I7" s="356" t="inlineStr">
         <is>
-          <t>KULLANIM REHBERİ &amp; SÖZLÜK</t>
+          <t>2. YÖNETİCİ KOKPİTİ (PANO)</t>
         </is>
       </c>
       <c r="J7" s="357" t="n"/>
@@ -13896,7 +13902,7 @@
       <c r="N7" s="355" t="n"/>
       <c r="O7" s="356" t="inlineStr">
         <is>
-          <t>EXCEL ARŞİV HİZMETLERİ</t>
+          <t>3. VERİ GİRİŞİ &amp; STRES TESTİ</t>
         </is>
       </c>
       <c r="P7" s="357" t="n"/>
@@ -13924,21 +13930,21 @@
       <c r="B9" s="355" t="n"/>
       <c r="C9" s="358" t="inlineStr">
         <is>
-          <t>Bu şablonun nasıl kullanıldığını videolu ve detaylı bir şekilde öğrenmek için aşağıdaki düğmeye tıklayabilirsiniz.</t>
+          <t>5 yaşındaki bir çocuğun dahi anlayacağı yalınlıkta sistem özeti, kullanım kılavuzu ve finans terimleri sözlüğü.</t>
         </is>
       </c>
       <c r="F9" s="355" t="n"/>
       <c r="H9" s="355" t="n"/>
       <c r="I9" s="358" t="inlineStr">
         <is>
-          <t>5 yaşındaki birine anlatır gibi sadeleştirilmiş sistem özeti, kullanım kılavuzu ve finans terimleri sözlüğü için tıklayınız.</t>
+          <t>Banka borçlarını, 30 günlük ödeme baskısını ve refinansman tasarruf potansiyelini tek ekranda izleyin.</t>
         </is>
       </c>
       <c r="L9" s="355" t="n"/>
       <c r="N9" s="355" t="n"/>
       <c r="O9" s="358" t="inlineStr">
         <is>
-          <t>EXCELARŞİV olarak finansal modelleme, kurumsal danışmanlık ve karar destek sistemleri sunmaktayız. Daha fazlası için tıklayınız.</t>
+          <t>Kredi sözleşmelerini girin; -%20 nakit daralması kriz testini ve A4 kurumsal yönetim raporunu alın.</t>
         </is>
       </c>
       <c r="R9" s="355" t="n"/>
@@ -13988,7 +13994,7 @@
       <c r="B14" s="355" t="n"/>
       <c r="C14" s="359" t="inlineStr">
         <is>
-          <t>▶ KULLANIM VİDEOSUNU İZLE</t>
+          <t>📖 SİSTEM REHBERİ (#00_HAKKINDA_VE_REHBER!A1)</t>
         </is>
       </c>
       <c r="D14" s="369" t="n"/>
@@ -13997,7 +14003,7 @@
       <c r="H14" s="355" t="n"/>
       <c r="I14" s="359" t="inlineStr">
         <is>
-          <t>📖 REHBERİ VE SÖZLÜĞÜ AÇ (#00_HAKKINDA_VE_REHBER!A1)</t>
+          <t>▶ CANLI PANO (#PANO!A1)</t>
         </is>
       </c>
       <c r="J14" s="369" t="n"/>
@@ -14006,7 +14012,7 @@
       <c r="N14" s="355" t="n"/>
       <c r="O14" s="359" t="inlineStr">
         <is>
-          <t>🌐 WEB SİTEMİZİ ZİYARET EDİN</t>
+          <t>📋 GİRDİLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
       <c r="P14" s="369" t="n"/>
@@ -24791,6 +24797,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -24801,13 +24808,22 @@
     <col width="22" customWidth="1" style="76" min="2" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>KAPAK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="3"/>
     <row r="6" ht="31.5" customHeight="1" s="50">
       <c r="A6" s="78" t="inlineStr">
         <is>
@@ -24902,7 +24918,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -24913,6 +24929,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -24922,15 +24939,23 @@
     <col width="80" customWidth="1" style="76" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" s="50">
-      <c r="A3" s="83" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>3 ADIMDA SİSTEM</t>
         </is>
@@ -24987,11 +25012,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A12:BH12"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A6:BH6"/>
     <mergeCell ref="A9:BH9"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A6:BH6"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25581,6 +25607,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -25742,6 +25769,7 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -25913,10 +25941,11 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
@@ -25927,47 +25956,25 @@
     <col width="40" customWidth="1" style="76" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="50">
-      <c r="A1" s="76" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="50">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>islem_id</t>
-        </is>
-      </c>
-      <c r="B3" s="76" t="inlineStr">
-        <is>
-          <t>kaynak_kart_id</t>
-        </is>
-      </c>
-      <c r="C3" s="76" t="inlineStr">
-        <is>
-          <t>onceki_durum</t>
-        </is>
-      </c>
-      <c r="D3" s="76" t="inlineStr">
-        <is>
-          <t>yeni_durum</t>
-        </is>
-      </c>
-      <c r="E3" s="76" t="inlineStr">
-        <is>
-          <t>tutar</t>
-        </is>
-      </c>
-      <c r="F3" s="76" t="inlineStr">
-        <is>
-          <t>bayrak</t>
-        </is>
-      </c>
-      <c r="G3" s="76" t="inlineStr">
-        <is>
-          <t>not</t>
         </is>
       </c>
     </row>
@@ -26129,6 +26136,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -26138,6 +26149,7 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -13930,7 +13930,7 @@
       <c r="B9" s="355" t="n"/>
       <c r="C9" s="358" t="inlineStr">
         <is>
-          <t>5 yaşındaki bir çocuğun dahi anlayacağı yalınlıkta sistem özeti, kullanım kılavuzu ve finans terimleri sözlüğü.</t>
+          <t>Her kademedeki yöneticinin anında kavrayabileceği yalınlıkta sistem özeti, kullanım kılavuzu ve finans terimleri sözlüğü.</t>
         </is>
       </c>
       <c r="F9" s="355" t="n"/>
@@ -14345,7 +14345,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -14353,7 +14353,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>MASRAF VE KOMİSYONLAR — tahsis, sigorta, komisyon ve diğer finansman maliyetleri.</t>
         </is>
@@ -14978,7 +14978,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>TEMINATLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -14986,7 +14986,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>TEMİNAT YÖNETİMİ — değer, geçerlilik ve kredi bağlantısı.</t>
         </is>
@@ -15652,7 +15652,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>YENI TEKLIFLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -15660,7 +15660,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>YENİ KREDİ TEKLİFLERİ — tutar, faiz, masraf ve aylık taksit karşılaştırması.</t>
         </is>
@@ -16519,7 +16519,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -16527,7 +16527,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>REFİNANSMAN ANALİZİ — aylık taksit rahatlaması ve toplam maliyet.</t>
         </is>
@@ -18406,7 +18406,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>KARAR MOTORU — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -18414,7 +18414,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>KARAR MOTORU — borç yükü, yaklaşan taksit ve öncelikli aksiyon</t>
         </is>
@@ -19240,7 +19240,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -19248,7 +19248,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>SENARYO VE DUYARLILIK ANALİZİ</t>
         </is>
@@ -19509,7 +19509,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>KONTROLLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -19517,7 +19517,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>VERİ KALİTESİ VE SİSTEM SAĞLIĞI</t>
         </is>
@@ -19704,7 +19704,7 @@
     <row r="3" ht="20" customHeight="1" s="50">
       <c r="B3" s="430" t="inlineStr">
         <is>
-          <t>5 Yaşındaki Birine Anlatır Gibi Basit, Sade ve Eksiksiz Finansal Karar Mimarisi · Siemens &amp; Enterprise Standartları</t>
+          <t>Yalın, Sade ve Eksiksiz Finansal Karar Mimarisi &amp; Kullanım Rehberi · Siemens &amp; Enterprise Standartları</t>
         </is>
       </c>
     </row>
@@ -19723,7 +19723,7 @@
       </c>
       <c r="C7" s="375" t="inlineStr">
         <is>
-          <t>GÜNLÜK DİLLE CEVAP (5 YAŞINDA ÇOCUĞA ANLATIR GİBİ)</t>
+          <t>YALIN KURUMSAL AÇIKLAMA</t>
         </is>
       </c>
       <c r="D7" s="375" t="inlineStr">
@@ -20166,7 +20166,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>AYARLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -21169,7 +21169,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>LISTELER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -21177,7 +21177,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>AÇILIR LİSTE KAYNAKLARI</t>
         </is>
@@ -24801,7 +24801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="76" min="1" max="1"/>
@@ -24814,16 +24814,7 @@
           <t>KAPAK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-    </row>
-    <row r="3"/>
+    </row>
     <row r="6" ht="31.5" customHeight="1" s="50">
       <c r="A6" s="78" t="inlineStr">
         <is>
@@ -24945,14 +24936,6 @@
           <t>HIZLI BASLANGIC — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="442" t="inlineStr">
@@ -25620,7 +25603,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>ORNEK VERI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -25628,7 +25611,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>ÖRNEK VERİ — otomasyon ve içe aktarma için yapı</t>
         </is>
@@ -25782,7 +25765,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -25790,7 +25773,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
         </is>
@@ -25962,14 +25945,6 @@
           <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="442" t="inlineStr">
@@ -26162,7 +26137,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
@@ -26170,7 +26145,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>DEĞİŞİKLİK KAYDI</t>
         </is>
@@ -26727,7 +26702,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -26735,7 +26710,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>BANKA TANIMLARI — ilişki, operasyonel durum ve iletişim tek merkezde.</t>
         </is>
@@ -27392,7 +27367,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -27400,7 +27375,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>BANKA LİMİTLERİ — toplam, kullanılan ve kalan limit ile kullanım oranı.</t>
         </is>
@@ -28212,7 +28187,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -28220,7 +28195,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>KREDİ PORTFÖYÜ — sözleşme, bakiye, maliyet, vade ve taksit bilgileri.</t>
         </is>
@@ -29261,7 +29236,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -29269,7 +29244,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>TAKSİT PLANI — dönem bazında anapara, faiz, vergi ve ödeme tarihi.</t>
         </is>
@@ -30254,7 +30229,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="433" t="inlineStr">
+      <c r="A1" s="441" t="inlineStr">
         <is>
           <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
@@ -30262,7 +30237,7 @@
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="435" t="inlineStr">
+      <c r="A3" s="442" t="inlineStr">
         <is>
           <t>ÖDEME TAKVİMİ — yaklaşan taksitler 30 / 60 / 90 gün penceresinde.</t>
         </is>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -3141,6 +3141,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3288,7 +3289,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Endeks / Milyon TL</a:t>
+                  <a:t>Tutar (Milyon TL)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3300,7 +3301,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="t"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -3310,6 +3311,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3320,7 +3322,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>BORÇ DAĞILIMI VE RİSK YOĞUNLAŞMASI</a:t>
+              <a:t>KONSOLİDE RİSK VE BORÇ DAĞILIMI</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3397,6 +3399,10 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+          <showPercent val="1"/>
+        </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="60"/>
       </doughnutChart>
@@ -13359,7 +13365,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5940000" cy="3420000"/>
+    <ext cx="5580000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -13381,7 +13387,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5220000" cy="3420000"/>
+    <ext cx="7200000" cy="3780000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -14331,17 +14337,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="76" min="1" max="2"/>
+    <col width="13.5" customWidth="1" style="76" min="1" max="2"/>
+    <col width="13" customWidth="1" style="50" min="2" max="2"/>
     <col width="24" customWidth="1" style="76" min="3" max="3"/>
     <col width="18" customWidth="1" style="76" min="4" max="4"/>
-    <col width="13" customWidth="1" style="76" min="5" max="5"/>
-    <col width="15" customWidth="1" style="76" min="6" max="6"/>
+    <col width="23.5" customWidth="1" style="76" min="5" max="5"/>
+    <col width="18.5" customWidth="1" style="76" min="6" max="6"/>
     <col width="14" customWidth="1" style="76" min="7" max="7"/>
-    <col width="13" customWidth="1" style="76" min="8" max="8"/>
-    <col width="10" customWidth="1" style="76" min="9" max="9"/>
+    <col width="15.5" customWidth="1" style="76" min="8" max="8"/>
+    <col width="11.5" customWidth="1" style="76" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -14962,19 +14974,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="11" customWidth="1" style="76" min="2" max="2"/>
+    <col width="14.5" customWidth="1" style="76" min="1" max="1"/>
+    <col width="12.5" customWidth="1" style="76" min="2" max="2"/>
     <col width="24" customWidth="1" style="76" min="3" max="3"/>
-    <col width="20" customWidth="1" style="76" min="4" max="4"/>
-    <col width="24" customWidth="1" style="76" min="5" max="5"/>
-    <col width="16" customWidth="1" style="76" min="6" max="6"/>
-    <col width="13" customWidth="1" style="76" min="7" max="7"/>
-    <col width="14" customWidth="1" style="76" min="8" max="8"/>
-    <col width="15" customWidth="1" style="76" min="9" max="9"/>
-    <col width="10" customWidth="1" style="76" min="10" max="10"/>
+    <col width="23.5" customWidth="1" style="76" min="4" max="4"/>
+    <col width="27.5" customWidth="1" style="76" min="5" max="5"/>
+    <col width="20.5" customWidth="1" style="76" min="6" max="6"/>
+    <col width="15.5" customWidth="1" style="76" min="7" max="7"/>
+    <col width="23.5" customWidth="1" style="76" min="8" max="8"/>
+    <col width="23.5" customWidth="1" style="76" min="9" max="9"/>
+    <col width="11.5" customWidth="1" style="76" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -15636,19 +15652,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="15" customWidth="1" style="76" min="2" max="2"/>
+    <col width="13.5" customWidth="1" style="76" min="1" max="1"/>
+    <col width="18.5" customWidth="1" style="76" min="2" max="2"/>
     <col width="24" customWidth="1" style="76" min="3" max="3"/>
     <col width="14" customWidth="1" style="76" min="4" max="4"/>
-    <col width="13" customWidth="1" style="76" min="5" max="5"/>
-    <col width="10" customWidth="1" style="76" min="6" max="6"/>
-    <col width="13" customWidth="1" style="76" min="7" max="7"/>
-    <col width="15" customWidth="1" style="76" min="8" max="9"/>
-    <col width="18" customWidth="1" style="76" min="10" max="10"/>
-    <col width="10" customWidth="1" style="76" min="11" max="11"/>
+    <col width="15.5" customWidth="1" style="76" min="5" max="5"/>
+    <col width="11.5" customWidth="1" style="76" min="6" max="6"/>
+    <col width="16.5" customWidth="1" style="76" min="7" max="7"/>
+    <col width="17.5" customWidth="1" style="76" min="8" max="9"/>
+    <col width="16.5" customWidth="1" style="50" min="9" max="9"/>
+    <col width="21.5" customWidth="1" style="76" min="10" max="10"/>
+    <col width="11.5" customWidth="1" style="76" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -16503,19 +16523,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
-    <col width="15" customWidth="1" style="76" min="2" max="2"/>
-    <col width="20" customWidth="1" style="76" min="3" max="3"/>
-    <col width="20" customWidth="1" style="76" min="4" max="6"/>
-    <col width="18" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="20" customWidth="1" style="76" min="7" max="8"/>
-    <col width="20" customWidth="1" style="50" min="8" max="8"/>
+    <col width="18.5" customWidth="1" style="76" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="76" min="4" max="6"/>
+    <col width="22.5" customWidth="1" style="50" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="50" min="6" max="6"/>
+    <col width="23.5" customWidth="1" style="76" min="7" max="8"/>
+    <col width="24.5" customWidth="1" style="50" min="8" max="8"/>
     <col width="14" customWidth="1" style="76" min="9" max="9"/>
     <col width="14" customWidth="1" style="76" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -25571,6 +25595,26 @@
       <c r="H27" s="250" t="n"/>
       <c r="I27" s="251" t="n"/>
     </row>
+    <row r="28" ht="18" customHeight="1" s="50"/>
+    <row r="29" ht="18" customHeight="1" s="50"/>
+    <row r="30" ht="18" customHeight="1" s="50"/>
+    <row r="31" ht="18" customHeight="1" s="50"/>
+    <row r="32" ht="18" customHeight="1" s="50"/>
+    <row r="33" ht="18" customHeight="1" s="50"/>
+    <row r="34" ht="18" customHeight="1" s="50"/>
+    <row r="35" ht="18" customHeight="1" s="50"/>
+    <row r="36" ht="18" customHeight="1" s="50"/>
+    <row r="37" ht="18" customHeight="1" s="50"/>
+    <row r="38" ht="18" customHeight="1" s="50"/>
+    <row r="39" ht="18" customHeight="1" s="50"/>
+    <row r="40" ht="18" customHeight="1" s="50"/>
+    <row r="41" ht="18" customHeight="1" s="50"/>
+    <row r="42" ht="18" customHeight="1" s="50"/>
+    <row r="43" ht="18" customHeight="1" s="50"/>
+    <row r="44" ht="18" customHeight="1" s="50"/>
+    <row r="45" ht="18" customHeight="1" s="50"/>
+    <row r="46" ht="18" customHeight="1" s="50"/>
+    <row r="47" ht="18" customHeight="1" s="50"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:M2"/>
@@ -26687,18 +26731,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
     <col width="26" customWidth="1" style="76" min="2" max="2"/>
-    <col width="18" customWidth="1" style="76" min="3" max="3"/>
-    <col width="18" customWidth="1" style="76" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="20.5" customWidth="1" style="76" min="4" max="4"/>
     <col width="32" customWidth="1" style="76" min="5" max="5"/>
     <col width="14" customWidth="1" style="76" min="6" max="6"/>
-    <col width="20" customWidth="1" style="76" min="7" max="7"/>
-    <col width="18" customWidth="1" style="76" min="8" max="8"/>
+    <col width="21.5" customWidth="1" style="76" min="7" max="7"/>
+    <col width="18.5" customWidth="1" style="76" min="8" max="8"/>
     <col width="14" customWidth="1" style="76" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -27352,18 +27401,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
     <col width="26" customWidth="1" style="76" min="2" max="2"/>
-    <col width="22" customWidth="1" style="76" min="3" max="3"/>
-    <col width="14" customWidth="1" style="76" min="4" max="4"/>
+    <col width="25.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="15.5" customWidth="1" style="76" min="4" max="4"/>
     <col width="18" customWidth="1" style="76" min="5" max="5"/>
-    <col width="18" customWidth="1" style="76" min="6" max="6"/>
+    <col width="20.5" customWidth="1" style="76" min="6" max="6"/>
     <col width="18" customWidth="1" style="76" min="7" max="7"/>
-    <col width="16" customWidth="1" style="76" min="8" max="8"/>
+    <col width="18.5" customWidth="1" style="76" min="8" max="8"/>
     <col width="14" customWidth="1" style="76" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -28172,13 +28226,13 @@
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
     <col width="26" customWidth="1" style="76" min="2" max="2"/>
-    <col width="18" customWidth="1" style="76" min="3" max="3"/>
-    <col width="24" customWidth="1" style="76" min="4" max="4"/>
-    <col width="14" customWidth="1" style="76" min="5" max="5"/>
-    <col width="18" customWidth="1" style="76" min="6" max="7"/>
+    <col width="19.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="25.5" customWidth="1" style="76" min="4" max="4"/>
+    <col width="15.5" customWidth="1" style="76" min="5" max="5"/>
+    <col width="23.5" customWidth="1" style="76" min="6" max="7"/>
     <col width="18" customWidth="1" style="50" min="7" max="7"/>
     <col width="18" customWidth="1" style="76" min="8" max="8"/>
-    <col width="14" customWidth="1" style="76" min="9" max="9"/>
+    <col width="15.5" customWidth="1" style="76" min="9" max="9"/>
     <col width="13" customWidth="1" style="76" min="10" max="10"/>
     <col width="18" customWidth="1" style="76" min="11" max="11"/>
     <col width="18" customWidth="1" style="76" min="12" max="12"/>
@@ -29218,21 +29272,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="2"/>
     <col width="13" customWidth="1" style="50" min="2" max="2"/>
     <col width="10" customWidth="1" style="76" min="3" max="3"/>
-    <col width="18" customWidth="1" style="76" min="4" max="6"/>
+    <col width="23.5" customWidth="1" style="76" min="4" max="6"/>
     <col width="18" customWidth="1" style="50" min="5" max="5"/>
     <col width="18" customWidth="1" style="50" min="6" max="6"/>
     <col width="14" customWidth="1" style="76" min="7" max="7"/>
     <col width="14" customWidth="1" style="76" min="8" max="8"/>
     <col width="18" customWidth="1" style="76" min="9" max="9"/>
-    <col width="15" customWidth="1" style="76" min="10" max="10"/>
+    <col width="16.5" customWidth="1" style="76" min="10" max="10"/>
     <col width="14" customWidth="1" style="76" min="11" max="11"/>
     <col width="14" customWidth="1" style="76" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
@@ -30216,7 +30272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -30225,7 +30281,14 @@
     <col width="18" customWidth="1" style="76" min="4" max="4"/>
     <col width="14" customWidth="1" style="76" min="5" max="5"/>
     <col width="18" customWidth="1" style="76" min="6" max="6"/>
-    <col width="15" customWidth="1" style="76" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="76" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
+    <col width="13" customWidth="1" style="50" min="12" max="12"/>
+    <col width="13" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -1106,7 +1106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -1770,6 +1770,7 @@
       </top>
       <bottom/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1781,7 +1782,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="455">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2896,6 +2897,40 @@
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="36" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="19" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3301,7 +3336,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="t"/>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -3322,7 +3357,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>KONSOLİDE RİSK VE BORÇ DAĞILIMI</a:t>
+              <a:t>KONSOLİDE BORÇ DAĞILIMI</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3399,10 +3434,6 @@
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="0"/>
-          <showPercent val="1"/>
-        </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="60"/>
       </doughnutChart>
@@ -13362,10 +13393,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5580000" cy="3780000"/>
+    <ext cx="5760000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -13384,10 +13415,10 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3780000"/>
+    <ext cx="6480000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -13826,8 +13857,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" style="50" min="1" max="1"/>
-    <col width="3.7" customWidth="1" style="50" min="2" max="2"/>
-    <col width="10.4" customWidth="1" style="50" min="3" max="3"/>
+    <col width="12" customWidth="1" style="50" min="2" max="2"/>
+    <col width="30" customWidth="1" style="50" min="3" max="3"/>
     <col width="13" customWidth="1" style="50" min="4" max="4"/>
     <col width="13" customWidth="1" style="50" min="5" max="5"/>
     <col width="3.7" customWidth="1" style="50" min="6" max="6"/>
@@ -14068,230 +14099,231 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1" s="50">
-      <c r="B21" s="362" t="inlineStr">
+      <c r="B21" s="443" t="inlineStr">
         <is>
           <t>AŞAMA NO</t>
         </is>
       </c>
-      <c r="C21" s="362" t="inlineStr">
+      <c r="C21" s="444" t="inlineStr">
         <is>
           <t>AŞAMA ADI &amp; KAPSAM</t>
         </is>
       </c>
-      <c r="D21" s="362" t="inlineStr">
-        <is>
-          <t>İŞLEM DETAYI VE MANTIK</t>
-        </is>
-      </c>
-      <c r="E21" s="362" t="inlineStr">
-        <is>
-          <t>KULLANILAN SAYFALAR</t>
-        </is>
-      </c>
-      <c r="F21" s="362" t="inlineStr">
-        <is>
-          <t>DOĞRUDAN ERİŞİM BUTONU</t>
+      <c r="D21" s="444" t="inlineStr">
+        <is>
+          <t>İŞLEM DETAYI VE YALIN MANTIK</t>
+        </is>
+      </c>
+      <c r="N21" s="443" t="inlineStr">
+        <is>
+          <t>İLGİLİ SAYFALAR</t>
+        </is>
+      </c>
+      <c r="P21" s="443" t="inlineStr">
+        <is>
+          <t>HIZLI ERİŞİM</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" s="50">
-      <c r="B22" s="363" t="inlineStr">
+      <c r="B22" s="445" t="inlineStr">
         <is>
           <t>AŞAMA 1</t>
         </is>
       </c>
-      <c r="C22" s="341" t="inlineStr">
+      <c r="C22" s="446" t="inlineStr">
         <is>
           <t>SİSTEM KURULUMU &amp; PARAMETRELER</t>
         </is>
       </c>
-      <c r="D22" s="364" t="inlineStr">
-        <is>
-          <t>Şirket unvanı, raporlama tarihi, serbest nakit ve risk toleranslarını AYARLAR sekmesinden tanımlayın.</t>
-        </is>
-      </c>
-      <c r="E22" s="336" t="n"/>
-      <c r="F22" s="336" t="n"/>
-      <c r="G22" s="336" t="n"/>
-      <c r="H22" s="336" t="n"/>
-      <c r="I22" s="336" t="n"/>
-      <c r="J22" s="336" t="n"/>
-      <c r="K22" s="336" t="n"/>
-      <c r="L22" s="336" t="n"/>
-      <c r="M22" s="337" t="n"/>
-      <c r="N22" s="343" t="inlineStr">
+      <c r="D22" s="447" t="inlineStr">
+        <is>
+          <t>Şirket unvanı, raporlama tarihi, serbest nakit ve risk toleranslarını tanımlayın.</t>
+        </is>
+      </c>
+      <c r="E22" s="303" t="n"/>
+      <c r="F22" s="303" t="n"/>
+      <c r="G22" s="303" t="n"/>
+      <c r="H22" s="303" t="n"/>
+      <c r="I22" s="303" t="n"/>
+      <c r="J22" s="303" t="n"/>
+      <c r="K22" s="303" t="n"/>
+      <c r="L22" s="303" t="n"/>
+      <c r="M22" s="303" t="n"/>
+      <c r="N22" s="448" t="inlineStr">
         <is>
           <t>AYARLAR, LISTELER</t>
         </is>
       </c>
-      <c r="O22" s="337" t="n"/>
-      <c r="P22" s="344" t="inlineStr">
+      <c r="O22" s="303" t="n"/>
+      <c r="P22" s="449" t="inlineStr">
         <is>
           <t>⚙ AYARLAR (#AYARLAR!A1)</t>
         </is>
       </c>
-      <c r="Q22" s="336" t="n"/>
-      <c r="R22" s="337" t="n"/>
+      <c r="Q22" s="303" t="n"/>
+      <c r="R22" s="303" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="50">
-      <c r="B23" s="366" t="inlineStr">
+      <c r="B23" s="450" t="inlineStr">
         <is>
           <t>AŞAMA 2</t>
         </is>
       </c>
-      <c r="C23" s="346" t="inlineStr">
+      <c r="C23" s="451" t="inlineStr">
         <is>
           <t>STRATEJİK KOKPİT &amp; İZLEME</t>
         </is>
       </c>
-      <c r="D23" s="367" t="inlineStr">
-        <is>
-          <t>Kredi portföy büyüklüğü, 30 günlük ödeme baskısı ve likidite erken uyarı radarını tek ekrandan izleyin.</t>
-        </is>
-      </c>
-      <c r="E23" s="336" t="n"/>
-      <c r="F23" s="336" t="n"/>
-      <c r="G23" s="336" t="n"/>
-      <c r="H23" s="336" t="n"/>
-      <c r="I23" s="336" t="n"/>
-      <c r="J23" s="336" t="n"/>
-      <c r="K23" s="336" t="n"/>
-      <c r="L23" s="336" t="n"/>
-      <c r="M23" s="337" t="n"/>
-      <c r="N23" s="348" t="inlineStr">
+      <c r="D23" s="452" t="inlineStr">
+        <is>
+          <t>Kredi portföy büyüklüğü, 30 günlük ödeme baskısı ve likidite radarını tek ekrandan izleyin.</t>
+        </is>
+      </c>
+      <c r="E23" s="303" t="n"/>
+      <c r="F23" s="303" t="n"/>
+      <c r="G23" s="303" t="n"/>
+      <c r="H23" s="303" t="n"/>
+      <c r="I23" s="303" t="n"/>
+      <c r="J23" s="303" t="n"/>
+      <c r="K23" s="303" t="n"/>
+      <c r="L23" s="303" t="n"/>
+      <c r="M23" s="303" t="n"/>
+      <c r="N23" s="453" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="O23" s="337" t="n"/>
-      <c r="P23" s="344" t="inlineStr">
+      <c r="O23" s="303" t="n"/>
+      <c r="P23" s="449" t="inlineStr">
         <is>
           <t>▶ PANO KOKPİTİ (#PANO!A1)</t>
         </is>
       </c>
-      <c r="Q23" s="336" t="n"/>
-      <c r="R23" s="337" t="n"/>
+      <c r="Q23" s="303" t="n"/>
+      <c r="R23" s="303" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="50">
-      <c r="B24" s="363" t="inlineStr">
+      <c r="B24" s="445" t="inlineStr">
         <is>
           <t>AŞAMA 3</t>
         </is>
       </c>
-      <c r="C24" s="341" t="inlineStr">
+      <c r="C24" s="446" t="inlineStr">
         <is>
           <t>PORTFÖY VE TAKSİT GİRİŞİ</t>
         </is>
       </c>
-      <c r="D24" s="364" t="inlineStr">
+      <c r="D24" s="447" t="inlineStr">
         <is>
           <t>Banka limitlerini, çekilen kredileri ve sözleşme amortisman takvimlerini ilgili sayfalara girin.</t>
         </is>
       </c>
-      <c r="E24" s="336" t="n"/>
-      <c r="F24" s="336" t="n"/>
-      <c r="G24" s="336" t="n"/>
-      <c r="H24" s="336" t="n"/>
-      <c r="I24" s="336" t="n"/>
-      <c r="J24" s="336" t="n"/>
-      <c r="K24" s="336" t="n"/>
-      <c r="L24" s="336" t="n"/>
-      <c r="M24" s="337" t="n"/>
-      <c r="N24" s="343" t="inlineStr">
-        <is>
-          <t>GİRDİLER, KREDILER, TAKSIT_PLANI</t>
-        </is>
-      </c>
-      <c r="O24" s="337" t="n"/>
-      <c r="P24" s="344" t="inlineStr">
+      <c r="E24" s="303" t="n"/>
+      <c r="F24" s="303" t="n"/>
+      <c r="G24" s="303" t="n"/>
+      <c r="H24" s="303" t="n"/>
+      <c r="I24" s="303" t="n"/>
+      <c r="J24" s="303" t="n"/>
+      <c r="K24" s="303" t="n"/>
+      <c r="L24" s="303" t="n"/>
+      <c r="M24" s="303" t="n"/>
+      <c r="N24" s="448" t="inlineStr">
+        <is>
+          <t>GİRDİLER, KREDİLER</t>
+        </is>
+      </c>
+      <c r="O24" s="303" t="n"/>
+      <c r="P24" s="449" t="inlineStr">
         <is>
           <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
-      <c r="Q24" s="336" t="n"/>
-      <c r="R24" s="337" t="n"/>
+      <c r="Q24" s="303" t="n"/>
+      <c r="R24" s="303" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="50">
-      <c r="B25" s="366" t="inlineStr">
+      <c r="B25" s="450" t="inlineStr">
         <is>
           <t>AŞAMA 4</t>
         </is>
       </c>
-      <c r="C25" s="346" t="inlineStr">
+      <c r="C25" s="451" t="inlineStr">
         <is>
           <t>REFİNANSMAN VE STRES TESTİ</t>
         </is>
       </c>
-      <c r="D25" s="367" t="inlineStr">
-        <is>
-          <t>Krediyi başka bankaya taşıma durumunda net faiz kârını hesaplayın. -%20 nakit daralması stres testini inceleyin.</t>
-        </is>
-      </c>
-      <c r="E25" s="336" t="n"/>
-      <c r="F25" s="336" t="n"/>
-      <c r="G25" s="336" t="n"/>
-      <c r="H25" s="336" t="n"/>
-      <c r="I25" s="336" t="n"/>
-      <c r="J25" s="336" t="n"/>
-      <c r="K25" s="336" t="n"/>
-      <c r="L25" s="336" t="n"/>
-      <c r="M25" s="337" t="n"/>
-      <c r="N25" s="348" t="inlineStr">
-        <is>
-          <t>REFINANSMAN, YÖNETİM_RAPORU</t>
-        </is>
-      </c>
-      <c r="O25" s="337" t="n"/>
-      <c r="P25" s="344" t="inlineStr">
+      <c r="D25" s="452" t="inlineStr">
+        <is>
+          <t>Krediyi başka bankaya taşıma faiz kârını hesaplayın. -%20 nakit daralması kriz testini inceleyin.</t>
+        </is>
+      </c>
+      <c r="E25" s="303" t="n"/>
+      <c r="F25" s="303" t="n"/>
+      <c r="G25" s="303" t="n"/>
+      <c r="H25" s="303" t="n"/>
+      <c r="I25" s="303" t="n"/>
+      <c r="J25" s="303" t="n"/>
+      <c r="K25" s="303" t="n"/>
+      <c r="L25" s="303" t="n"/>
+      <c r="M25" s="303" t="n"/>
+      <c r="N25" s="453" t="inlineStr">
+        <is>
+          <t>REFİNANSMAN, RAPOR</t>
+        </is>
+      </c>
+      <c r="O25" s="303" t="n"/>
+      <c r="P25" s="449" t="inlineStr">
         <is>
           <t>📊 STRES TESTİ (#YÖNETİM_RAPORU!A1)</t>
         </is>
       </c>
-      <c r="Q25" s="336" t="n"/>
-      <c r="R25" s="337" t="n"/>
+      <c r="Q25" s="303" t="n"/>
+      <c r="R25" s="303" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="50">
-      <c r="B26" s="363" t="inlineStr">
+      <c r="B26" s="445" t="inlineStr">
         <is>
           <t>AŞAMA 5</t>
         </is>
       </c>
-      <c r="C26" s="341" t="inlineStr">
+      <c r="C26" s="446" t="inlineStr">
         <is>
           <t>YÖNETİM KURULU VE BANKA ÇIKTISI</t>
         </is>
       </c>
-      <c r="D26" s="364" t="inlineStr">
+      <c r="D26" s="447" t="inlineStr">
         <is>
           <t>Kredi komiteleri ve yönetim kuruluna sunulacak A4 dikey baskıya hazır kurumsal rapor çıktısını alın.</t>
         </is>
       </c>
-      <c r="E26" s="336" t="n"/>
-      <c r="F26" s="336" t="n"/>
-      <c r="G26" s="336" t="n"/>
-      <c r="H26" s="336" t="n"/>
-      <c r="I26" s="336" t="n"/>
-      <c r="J26" s="336" t="n"/>
-      <c r="K26" s="336" t="n"/>
-      <c r="L26" s="336" t="n"/>
-      <c r="M26" s="337" t="n"/>
-      <c r="N26" s="343" t="inlineStr">
+      <c r="E26" s="303" t="n"/>
+      <c r="F26" s="303" t="n"/>
+      <c r="G26" s="303" t="n"/>
+      <c r="H26" s="303" t="n"/>
+      <c r="I26" s="303" t="n"/>
+      <c r="J26" s="303" t="n"/>
+      <c r="K26" s="303" t="n"/>
+      <c r="L26" s="303" t="n"/>
+      <c r="M26" s="303" t="n"/>
+      <c r="N26" s="448" t="inlineStr">
         <is>
           <t>RAPOR</t>
         </is>
       </c>
-      <c r="O26" s="337" t="n"/>
-      <c r="P26" s="344" t="inlineStr">
+      <c r="O26" s="303" t="n"/>
+      <c r="P26" s="449" t="inlineStr">
         <is>
           <t>📄 A4 RAPORU (#RAPOR!A1)</t>
         </is>
       </c>
-      <c r="Q26" s="336" t="n"/>
-      <c r="R26" s="337" t="n"/>
+      <c r="Q26" s="303" t="n"/>
+      <c r="R26" s="303" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="27">
     <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P21:R21"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:R4"/>
     <mergeCell ref="N25:O25"/>
@@ -14301,14 +14333,16 @@
     <mergeCell ref="D24:M24"/>
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="D23:M23"/>
+    <mergeCell ref="N21:O21"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="D26:M26"/>
     <mergeCell ref="O9:Q12"/>
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="P24:R24"/>
     <mergeCell ref="D22:M22"/>
-    <mergeCell ref="P24:R24"/>
     <mergeCell ref="C9:E12"/>
+    <mergeCell ref="D21:M21"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="P25:R25"/>
@@ -14337,7 +14371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="2"/>
@@ -14974,7 +15008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.5" customWidth="1" style="76" min="1" max="1"/>
@@ -15652,7 +15686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="1"/>
@@ -16523,7 +16557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -25039,7 +25073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -25589,32 +25623,382 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="10" customHeight="1" s="50">
+    <row r="27" ht="14" customHeight="1" s="50">
       <c r="F27" s="249" t="n"/>
       <c r="G27" s="250" t="n"/>
       <c r="H27" s="250" t="n"/>
       <c r="I27" s="251" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="50"/>
-    <row r="29" ht="18" customHeight="1" s="50"/>
-    <row r="30" ht="18" customHeight="1" s="50"/>
-    <row r="31" ht="18" customHeight="1" s="50"/>
-    <row r="32" ht="18" customHeight="1" s="50"/>
-    <row r="33" ht="18" customHeight="1" s="50"/>
-    <row r="34" ht="18" customHeight="1" s="50"/>
-    <row r="35" ht="18" customHeight="1" s="50"/>
-    <row r="36" ht="18" customHeight="1" s="50"/>
-    <row r="37" ht="18" customHeight="1" s="50"/>
-    <row r="38" ht="18" customHeight="1" s="50"/>
-    <row r="39" ht="18" customHeight="1" s="50"/>
-    <row r="40" ht="18" customHeight="1" s="50"/>
-    <row r="41" ht="18" customHeight="1" s="50"/>
-    <row r="42" ht="18" customHeight="1" s="50"/>
-    <row r="43" ht="18" customHeight="1" s="50"/>
-    <row r="44" ht="18" customHeight="1" s="50"/>
-    <row r="45" ht="18" customHeight="1" s="50"/>
-    <row r="46" ht="18" customHeight="1" s="50"/>
-    <row r="47" ht="18" customHeight="1" s="50"/>
+    <row r="28" ht="14" customHeight="1" s="50"/>
+    <row r="29" ht="14" customHeight="1" s="50"/>
+    <row r="30" ht="18" customHeight="1" s="50">
+      <c r="A30" s="454" t="n"/>
+      <c r="B30" s="454" t="n"/>
+      <c r="C30" s="454" t="n"/>
+      <c r="D30" s="454" t="n"/>
+      <c r="E30" s="454" t="n"/>
+      <c r="F30" s="454" t="n"/>
+      <c r="G30" s="454" t="n"/>
+      <c r="H30" s="454" t="n"/>
+      <c r="I30" s="454" t="n"/>
+      <c r="J30" s="454" t="n"/>
+      <c r="K30" s="454" t="n"/>
+      <c r="L30" s="454" t="n"/>
+      <c r="M30" s="454" t="n"/>
+      <c r="N30" s="454" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="50">
+      <c r="A31" s="454" t="n"/>
+      <c r="B31" s="454" t="n"/>
+      <c r="C31" s="454" t="n"/>
+      <c r="D31" s="454" t="n"/>
+      <c r="E31" s="454" t="n"/>
+      <c r="F31" s="454" t="n"/>
+      <c r="G31" s="454" t="n"/>
+      <c r="H31" s="454" t="n"/>
+      <c r="I31" s="454" t="n"/>
+      <c r="J31" s="454" t="n"/>
+      <c r="K31" s="454" t="n"/>
+      <c r="L31" s="454" t="n"/>
+      <c r="M31" s="454" t="n"/>
+      <c r="N31" s="454" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="50">
+      <c r="A32" s="454" t="n"/>
+      <c r="B32" s="454" t="n"/>
+      <c r="C32" s="454" t="n"/>
+      <c r="D32" s="454" t="n"/>
+      <c r="E32" s="454" t="n"/>
+      <c r="F32" s="454" t="n"/>
+      <c r="G32" s="454" t="n"/>
+      <c r="H32" s="454" t="n"/>
+      <c r="I32" s="454" t="n"/>
+      <c r="J32" s="454" t="n"/>
+      <c r="K32" s="454" t="n"/>
+      <c r="L32" s="454" t="n"/>
+      <c r="M32" s="454" t="n"/>
+      <c r="N32" s="454" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="50">
+      <c r="A33" s="454" t="n"/>
+      <c r="B33" s="454" t="n"/>
+      <c r="C33" s="454" t="n"/>
+      <c r="D33" s="454" t="n"/>
+      <c r="E33" s="454" t="n"/>
+      <c r="F33" s="454" t="n"/>
+      <c r="G33" s="454" t="n"/>
+      <c r="H33" s="454" t="n"/>
+      <c r="I33" s="454" t="n"/>
+      <c r="J33" s="454" t="n"/>
+      <c r="K33" s="454" t="n"/>
+      <c r="L33" s="454" t="n"/>
+      <c r="M33" s="454" t="n"/>
+      <c r="N33" s="454" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="50">
+      <c r="A34" s="454" t="n"/>
+      <c r="B34" s="454" t="n"/>
+      <c r="C34" s="454" t="n"/>
+      <c r="D34" s="454" t="n"/>
+      <c r="E34" s="454" t="n"/>
+      <c r="F34" s="454" t="n"/>
+      <c r="G34" s="454" t="n"/>
+      <c r="H34" s="454" t="n"/>
+      <c r="I34" s="454" t="n"/>
+      <c r="J34" s="454" t="n"/>
+      <c r="K34" s="454" t="n"/>
+      <c r="L34" s="454" t="n"/>
+      <c r="M34" s="454" t="n"/>
+      <c r="N34" s="454" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="50">
+      <c r="A35" s="454" t="n"/>
+      <c r="B35" s="454" t="n"/>
+      <c r="C35" s="454" t="n"/>
+      <c r="D35" s="454" t="n"/>
+      <c r="E35" s="454" t="n"/>
+      <c r="F35" s="454" t="n"/>
+      <c r="G35" s="454" t="n"/>
+      <c r="H35" s="454" t="n"/>
+      <c r="I35" s="454" t="n"/>
+      <c r="J35" s="454" t="n"/>
+      <c r="K35" s="454" t="n"/>
+      <c r="L35" s="454" t="n"/>
+      <c r="M35" s="454" t="n"/>
+      <c r="N35" s="454" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="50">
+      <c r="A36" s="454" t="n"/>
+      <c r="B36" s="454" t="n"/>
+      <c r="C36" s="454" t="n"/>
+      <c r="D36" s="454" t="n"/>
+      <c r="E36" s="454" t="n"/>
+      <c r="F36" s="454" t="n"/>
+      <c r="G36" s="454" t="n"/>
+      <c r="H36" s="454" t="n"/>
+      <c r="I36" s="454" t="n"/>
+      <c r="J36" s="454" t="n"/>
+      <c r="K36" s="454" t="n"/>
+      <c r="L36" s="454" t="n"/>
+      <c r="M36" s="454" t="n"/>
+      <c r="N36" s="454" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="50">
+      <c r="A37" s="454" t="n"/>
+      <c r="B37" s="454" t="n"/>
+      <c r="C37" s="454" t="n"/>
+      <c r="D37" s="454" t="n"/>
+      <c r="E37" s="454" t="n"/>
+      <c r="F37" s="454" t="n"/>
+      <c r="G37" s="454" t="n"/>
+      <c r="H37" s="454" t="n"/>
+      <c r="I37" s="454" t="n"/>
+      <c r="J37" s="454" t="n"/>
+      <c r="K37" s="454" t="n"/>
+      <c r="L37" s="454" t="n"/>
+      <c r="M37" s="454" t="n"/>
+      <c r="N37" s="454" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="50">
+      <c r="A38" s="454" t="n"/>
+      <c r="B38" s="454" t="n"/>
+      <c r="C38" s="454" t="n"/>
+      <c r="D38" s="454" t="n"/>
+      <c r="E38" s="454" t="n"/>
+      <c r="F38" s="454" t="n"/>
+      <c r="G38" s="454" t="n"/>
+      <c r="H38" s="454" t="n"/>
+      <c r="I38" s="454" t="n"/>
+      <c r="J38" s="454" t="n"/>
+      <c r="K38" s="454" t="n"/>
+      <c r="L38" s="454" t="n"/>
+      <c r="M38" s="454" t="n"/>
+      <c r="N38" s="454" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="50">
+      <c r="A39" s="454" t="n"/>
+      <c r="B39" s="454" t="n"/>
+      <c r="C39" s="454" t="n"/>
+      <c r="D39" s="454" t="n"/>
+      <c r="E39" s="454" t="n"/>
+      <c r="F39" s="454" t="n"/>
+      <c r="G39" s="454" t="n"/>
+      <c r="H39" s="454" t="n"/>
+      <c r="I39" s="454" t="n"/>
+      <c r="J39" s="454" t="n"/>
+      <c r="K39" s="454" t="n"/>
+      <c r="L39" s="454" t="n"/>
+      <c r="M39" s="454" t="n"/>
+      <c r="N39" s="454" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="50">
+      <c r="A40" s="454" t="n"/>
+      <c r="B40" s="454" t="n"/>
+      <c r="C40" s="454" t="n"/>
+      <c r="D40" s="454" t="n"/>
+      <c r="E40" s="454" t="n"/>
+      <c r="F40" s="454" t="n"/>
+      <c r="G40" s="454" t="n"/>
+      <c r="H40" s="454" t="n"/>
+      <c r="I40" s="454" t="n"/>
+      <c r="J40" s="454" t="n"/>
+      <c r="K40" s="454" t="n"/>
+      <c r="L40" s="454" t="n"/>
+      <c r="M40" s="454" t="n"/>
+      <c r="N40" s="454" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="50">
+      <c r="A41" s="454" t="n"/>
+      <c r="B41" s="454" t="n"/>
+      <c r="C41" s="454" t="n"/>
+      <c r="D41" s="454" t="n"/>
+      <c r="E41" s="454" t="n"/>
+      <c r="F41" s="454" t="n"/>
+      <c r="G41" s="454" t="n"/>
+      <c r="H41" s="454" t="n"/>
+      <c r="I41" s="454" t="n"/>
+      <c r="J41" s="454" t="n"/>
+      <c r="K41" s="454" t="n"/>
+      <c r="L41" s="454" t="n"/>
+      <c r="M41" s="454" t="n"/>
+      <c r="N41" s="454" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="50">
+      <c r="A42" s="454" t="n"/>
+      <c r="B42" s="454" t="n"/>
+      <c r="C42" s="454" t="n"/>
+      <c r="D42" s="454" t="n"/>
+      <c r="E42" s="454" t="n"/>
+      <c r="F42" s="454" t="n"/>
+      <c r="G42" s="454" t="n"/>
+      <c r="H42" s="454" t="n"/>
+      <c r="I42" s="454" t="n"/>
+      <c r="J42" s="454" t="n"/>
+      <c r="K42" s="454" t="n"/>
+      <c r="L42" s="454" t="n"/>
+      <c r="M42" s="454" t="n"/>
+      <c r="N42" s="454" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="50">
+      <c r="A43" s="454" t="n"/>
+      <c r="B43" s="454" t="n"/>
+      <c r="C43" s="454" t="n"/>
+      <c r="D43" s="454" t="n"/>
+      <c r="E43" s="454" t="n"/>
+      <c r="F43" s="454" t="n"/>
+      <c r="G43" s="454" t="n"/>
+      <c r="H43" s="454" t="n"/>
+      <c r="I43" s="454" t="n"/>
+      <c r="J43" s="454" t="n"/>
+      <c r="K43" s="454" t="n"/>
+      <c r="L43" s="454" t="n"/>
+      <c r="M43" s="454" t="n"/>
+      <c r="N43" s="454" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="50">
+      <c r="A44" s="454" t="n"/>
+      <c r="B44" s="454" t="n"/>
+      <c r="C44" s="454" t="n"/>
+      <c r="D44" s="454" t="n"/>
+      <c r="E44" s="454" t="n"/>
+      <c r="F44" s="454" t="n"/>
+      <c r="G44" s="454" t="n"/>
+      <c r="H44" s="454" t="n"/>
+      <c r="I44" s="454" t="n"/>
+      <c r="J44" s="454" t="n"/>
+      <c r="K44" s="454" t="n"/>
+      <c r="L44" s="454" t="n"/>
+      <c r="M44" s="454" t="n"/>
+      <c r="N44" s="454" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="50">
+      <c r="A45" s="454" t="n"/>
+      <c r="B45" s="454" t="n"/>
+      <c r="C45" s="454" t="n"/>
+      <c r="D45" s="454" t="n"/>
+      <c r="E45" s="454" t="n"/>
+      <c r="F45" s="454" t="n"/>
+      <c r="G45" s="454" t="n"/>
+      <c r="H45" s="454" t="n"/>
+      <c r="I45" s="454" t="n"/>
+      <c r="J45" s="454" t="n"/>
+      <c r="K45" s="454" t="n"/>
+      <c r="L45" s="454" t="n"/>
+      <c r="M45" s="454" t="n"/>
+      <c r="N45" s="454" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="50">
+      <c r="A46" s="454" t="n"/>
+      <c r="B46" s="454" t="n"/>
+      <c r="C46" s="454" t="n"/>
+      <c r="D46" s="454" t="n"/>
+      <c r="E46" s="454" t="n"/>
+      <c r="F46" s="454" t="n"/>
+      <c r="G46" s="454" t="n"/>
+      <c r="H46" s="454" t="n"/>
+      <c r="I46" s="454" t="n"/>
+      <c r="J46" s="454" t="n"/>
+      <c r="K46" s="454" t="n"/>
+      <c r="L46" s="454" t="n"/>
+      <c r="M46" s="454" t="n"/>
+      <c r="N46" s="454" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="50">
+      <c r="A47" s="454" t="n"/>
+      <c r="B47" s="454" t="n"/>
+      <c r="C47" s="454" t="n"/>
+      <c r="D47" s="454" t="n"/>
+      <c r="E47" s="454" t="n"/>
+      <c r="F47" s="454" t="n"/>
+      <c r="G47" s="454" t="n"/>
+      <c r="H47" s="454" t="n"/>
+      <c r="I47" s="454" t="n"/>
+      <c r="J47" s="454" t="n"/>
+      <c r="K47" s="454" t="n"/>
+      <c r="L47" s="454" t="n"/>
+      <c r="M47" s="454" t="n"/>
+      <c r="N47" s="454" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1" s="50">
+      <c r="A48" s="454" t="n"/>
+      <c r="B48" s="454" t="n"/>
+      <c r="C48" s="454" t="n"/>
+      <c r="D48" s="454" t="n"/>
+      <c r="E48" s="454" t="n"/>
+      <c r="F48" s="454" t="n"/>
+      <c r="G48" s="454" t="n"/>
+      <c r="H48" s="454" t="n"/>
+      <c r="I48" s="454" t="n"/>
+      <c r="J48" s="454" t="n"/>
+      <c r="K48" s="454" t="n"/>
+      <c r="L48" s="454" t="n"/>
+      <c r="M48" s="454" t="n"/>
+      <c r="N48" s="454" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="50">
+      <c r="A49" s="454" t="n"/>
+      <c r="B49" s="454" t="n"/>
+      <c r="C49" s="454" t="n"/>
+      <c r="D49" s="454" t="n"/>
+      <c r="E49" s="454" t="n"/>
+      <c r="F49" s="454" t="n"/>
+      <c r="G49" s="454" t="n"/>
+      <c r="H49" s="454" t="n"/>
+      <c r="I49" s="454" t="n"/>
+      <c r="J49" s="454" t="n"/>
+      <c r="K49" s="454" t="n"/>
+      <c r="L49" s="454" t="n"/>
+      <c r="M49" s="454" t="n"/>
+      <c r="N49" s="454" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1" s="50">
+      <c r="A50" s="454" t="n"/>
+      <c r="B50" s="454" t="n"/>
+      <c r="C50" s="454" t="n"/>
+      <c r="D50" s="454" t="n"/>
+      <c r="E50" s="454" t="n"/>
+      <c r="F50" s="454" t="n"/>
+      <c r="G50" s="454" t="n"/>
+      <c r="H50" s="454" t="n"/>
+      <c r="I50" s="454" t="n"/>
+      <c r="J50" s="454" t="n"/>
+      <c r="K50" s="454" t="n"/>
+      <c r="L50" s="454" t="n"/>
+      <c r="M50" s="454" t="n"/>
+      <c r="N50" s="454" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1" s="50">
+      <c r="A51" s="454" t="n"/>
+      <c r="B51" s="454" t="n"/>
+      <c r="C51" s="454" t="n"/>
+      <c r="D51" s="454" t="n"/>
+      <c r="E51" s="454" t="n"/>
+      <c r="F51" s="454" t="n"/>
+      <c r="G51" s="454" t="n"/>
+      <c r="H51" s="454" t="n"/>
+      <c r="I51" s="454" t="n"/>
+      <c r="J51" s="454" t="n"/>
+      <c r="K51" s="454" t="n"/>
+      <c r="L51" s="454" t="n"/>
+      <c r="M51" s="454" t="n"/>
+      <c r="N51" s="454" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="50">
+      <c r="A52" s="454" t="n"/>
+      <c r="B52" s="454" t="n"/>
+      <c r="C52" s="454" t="n"/>
+      <c r="D52" s="454" t="n"/>
+      <c r="E52" s="454" t="n"/>
+      <c r="F52" s="454" t="n"/>
+      <c r="G52" s="454" t="n"/>
+      <c r="H52" s="454" t="n"/>
+      <c r="I52" s="454" t="n"/>
+      <c r="J52" s="454" t="n"/>
+      <c r="K52" s="454" t="n"/>
+      <c r="L52" s="454" t="n"/>
+      <c r="M52" s="454" t="n"/>
+      <c r="N52" s="454" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:M2"/>
@@ -26731,7 +27115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -27401,7 +27785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -29272,7 +29656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="2"/>
@@ -30272,7 +30656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -1782,7 +1782,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="455">
+  <cellXfs count="457">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2931,6 +2931,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3176,7 +3182,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -3324,7 +3329,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Tutar (Milyon TL)</a:t>
+                  <a:t>Tutar / Endeks</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -3346,7 +3351,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -13853,11 +13857,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" style="50" min="1" max="1"/>
-    <col width="12" customWidth="1" style="50" min="2" max="2"/>
+    <col width="114.5" customWidth="1" style="50" min="2" max="2"/>
     <col width="30" customWidth="1" style="50" min="3" max="3"/>
     <col width="13" customWidth="1" style="50" min="4" max="4"/>
     <col width="13" customWidth="1" style="50" min="5" max="5"/>
@@ -14090,6 +14094,7 @@
       <c r="Q16" s="355" t="n"/>
       <c r="R16" s="355" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18" ht="14" customHeight="1" s="50"/>
     <row r="19" ht="28" customHeight="1" s="50">
       <c r="B19" s="361" t="inlineStr">
@@ -14098,6 +14103,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="26" customHeight="1" s="50">
       <c r="B21" s="443" t="inlineStr">
         <is>
@@ -14141,28 +14147,28 @@
           <t>Şirket unvanı, raporlama tarihi, serbest nakit ve risk toleranslarını tanımlayın.</t>
         </is>
       </c>
-      <c r="E22" s="303" t="n"/>
-      <c r="F22" s="303" t="n"/>
-      <c r="G22" s="303" t="n"/>
-      <c r="H22" s="303" t="n"/>
-      <c r="I22" s="303" t="n"/>
-      <c r="J22" s="303" t="n"/>
-      <c r="K22" s="303" t="n"/>
-      <c r="L22" s="303" t="n"/>
-      <c r="M22" s="303" t="n"/>
+      <c r="E22" s="336" t="n"/>
+      <c r="F22" s="336" t="n"/>
+      <c r="G22" s="336" t="n"/>
+      <c r="H22" s="336" t="n"/>
+      <c r="I22" s="336" t="n"/>
+      <c r="J22" s="336" t="n"/>
+      <c r="K22" s="336" t="n"/>
+      <c r="L22" s="336" t="n"/>
+      <c r="M22" s="337" t="n"/>
       <c r="N22" s="448" t="inlineStr">
         <is>
           <t>AYARLAR, LISTELER</t>
         </is>
       </c>
-      <c r="O22" s="303" t="n"/>
+      <c r="O22" s="337" t="n"/>
       <c r="P22" s="449" t="inlineStr">
         <is>
           <t>⚙ AYARLAR (#AYARLAR!A1)</t>
         </is>
       </c>
-      <c r="Q22" s="303" t="n"/>
-      <c r="R22" s="303" t="n"/>
+      <c r="Q22" s="336" t="n"/>
+      <c r="R22" s="337" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="50">
       <c r="B23" s="450" t="inlineStr">
@@ -14180,28 +14186,28 @@
           <t>Kredi portföy büyüklüğü, 30 günlük ödeme baskısı ve likidite radarını tek ekrandan izleyin.</t>
         </is>
       </c>
-      <c r="E23" s="303" t="n"/>
-      <c r="F23" s="303" t="n"/>
-      <c r="G23" s="303" t="n"/>
-      <c r="H23" s="303" t="n"/>
-      <c r="I23" s="303" t="n"/>
-      <c r="J23" s="303" t="n"/>
-      <c r="K23" s="303" t="n"/>
-      <c r="L23" s="303" t="n"/>
-      <c r="M23" s="303" t="n"/>
+      <c r="E23" s="336" t="n"/>
+      <c r="F23" s="336" t="n"/>
+      <c r="G23" s="336" t="n"/>
+      <c r="H23" s="336" t="n"/>
+      <c r="I23" s="336" t="n"/>
+      <c r="J23" s="336" t="n"/>
+      <c r="K23" s="336" t="n"/>
+      <c r="L23" s="336" t="n"/>
+      <c r="M23" s="337" t="n"/>
       <c r="N23" s="453" t="inlineStr">
         <is>
           <t>PANO</t>
         </is>
       </c>
-      <c r="O23" s="303" t="n"/>
+      <c r="O23" s="337" t="n"/>
       <c r="P23" s="449" t="inlineStr">
         <is>
           <t>▶ PANO KOKPİTİ (#PANO!A1)</t>
         </is>
       </c>
-      <c r="Q23" s="303" t="n"/>
-      <c r="R23" s="303" t="n"/>
+      <c r="Q23" s="336" t="n"/>
+      <c r="R23" s="337" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="50">
       <c r="B24" s="445" t="inlineStr">
@@ -14219,28 +14225,28 @@
           <t>Banka limitlerini, çekilen kredileri ve sözleşme amortisman takvimlerini ilgili sayfalara girin.</t>
         </is>
       </c>
-      <c r="E24" s="303" t="n"/>
-      <c r="F24" s="303" t="n"/>
-      <c r="G24" s="303" t="n"/>
-      <c r="H24" s="303" t="n"/>
-      <c r="I24" s="303" t="n"/>
-      <c r="J24" s="303" t="n"/>
-      <c r="K24" s="303" t="n"/>
-      <c r="L24" s="303" t="n"/>
-      <c r="M24" s="303" t="n"/>
+      <c r="E24" s="336" t="n"/>
+      <c r="F24" s="336" t="n"/>
+      <c r="G24" s="336" t="n"/>
+      <c r="H24" s="336" t="n"/>
+      <c r="I24" s="336" t="n"/>
+      <c r="J24" s="336" t="n"/>
+      <c r="K24" s="336" t="n"/>
+      <c r="L24" s="336" t="n"/>
+      <c r="M24" s="337" t="n"/>
       <c r="N24" s="448" t="inlineStr">
         <is>
           <t>GİRDİLER, KREDİLER</t>
         </is>
       </c>
-      <c r="O24" s="303" t="n"/>
+      <c r="O24" s="337" t="n"/>
       <c r="P24" s="449" t="inlineStr">
         <is>
           <t>📋 GİRİŞLERİ DÜZENLE (#GİRDİLER!A1)</t>
         </is>
       </c>
-      <c r="Q24" s="303" t="n"/>
-      <c r="R24" s="303" t="n"/>
+      <c r="Q24" s="336" t="n"/>
+      <c r="R24" s="337" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="50">
       <c r="B25" s="450" t="inlineStr">
@@ -14258,28 +14264,28 @@
           <t>Krediyi başka bankaya taşıma faiz kârını hesaplayın. -%20 nakit daralması kriz testini inceleyin.</t>
         </is>
       </c>
-      <c r="E25" s="303" t="n"/>
-      <c r="F25" s="303" t="n"/>
-      <c r="G25" s="303" t="n"/>
-      <c r="H25" s="303" t="n"/>
-      <c r="I25" s="303" t="n"/>
-      <c r="J25" s="303" t="n"/>
-      <c r="K25" s="303" t="n"/>
-      <c r="L25" s="303" t="n"/>
-      <c r="M25" s="303" t="n"/>
+      <c r="E25" s="336" t="n"/>
+      <c r="F25" s="336" t="n"/>
+      <c r="G25" s="336" t="n"/>
+      <c r="H25" s="336" t="n"/>
+      <c r="I25" s="336" t="n"/>
+      <c r="J25" s="336" t="n"/>
+      <c r="K25" s="336" t="n"/>
+      <c r="L25" s="336" t="n"/>
+      <c r="M25" s="337" t="n"/>
       <c r="N25" s="453" t="inlineStr">
         <is>
           <t>REFİNANSMAN, RAPOR</t>
         </is>
       </c>
-      <c r="O25" s="303" t="n"/>
+      <c r="O25" s="337" t="n"/>
       <c r="P25" s="449" t="inlineStr">
         <is>
           <t>📊 STRES TESTİ (#YÖNETİM_RAPORU!A1)</t>
         </is>
       </c>
-      <c r="Q25" s="303" t="n"/>
-      <c r="R25" s="303" t="n"/>
+      <c r="Q25" s="336" t="n"/>
+      <c r="R25" s="337" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="50">
       <c r="B26" s="445" t="inlineStr">
@@ -14297,28 +14303,28 @@
           <t>Kredi komiteleri ve yönetim kuruluna sunulacak A4 dikey baskıya hazır kurumsal rapor çıktısını alın.</t>
         </is>
       </c>
-      <c r="E26" s="303" t="n"/>
-      <c r="F26" s="303" t="n"/>
-      <c r="G26" s="303" t="n"/>
-      <c r="H26" s="303" t="n"/>
-      <c r="I26" s="303" t="n"/>
-      <c r="J26" s="303" t="n"/>
-      <c r="K26" s="303" t="n"/>
-      <c r="L26" s="303" t="n"/>
-      <c r="M26" s="303" t="n"/>
+      <c r="E26" s="336" t="n"/>
+      <c r="F26" s="336" t="n"/>
+      <c r="G26" s="336" t="n"/>
+      <c r="H26" s="336" t="n"/>
+      <c r="I26" s="336" t="n"/>
+      <c r="J26" s="336" t="n"/>
+      <c r="K26" s="336" t="n"/>
+      <c r="L26" s="336" t="n"/>
+      <c r="M26" s="337" t="n"/>
       <c r="N26" s="448" t="inlineStr">
         <is>
           <t>RAPOR</t>
         </is>
       </c>
-      <c r="O26" s="303" t="n"/>
+      <c r="O26" s="337" t="n"/>
       <c r="P26" s="449" t="inlineStr">
         <is>
           <t>📄 A4 RAPORU (#RAPOR!A1)</t>
         </is>
       </c>
-      <c r="Q26" s="303" t="n"/>
-      <c r="R26" s="303" t="n"/>
+      <c r="Q26" s="336" t="n"/>
+      <c r="R26" s="337" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -14371,7 +14377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="2"/>
@@ -14391,15 +14397,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>MASRAF VE KOMİSYONLAR — tahsis, sigorta, komisyon ve diğer finansman maliyetleri.</t>
         </is>
@@ -15008,7 +15022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.5" customWidth="1" style="76" min="1" max="1"/>
@@ -15028,15 +15042,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>TEMINATLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>TEMİNAT YÖNETİMİ — değer, geçerlilik ve kredi bağlantısı.</t>
         </is>
@@ -15686,7 +15709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="1"/>
@@ -15706,15 +15729,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>YENI TEKLIFLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>YENİ KREDİ TEKLİFLERİ — tutar, faiz, masraf ve aylık taksit karşılaştırması.</t>
         </is>
@@ -16557,7 +16590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -16577,15 +16610,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>REFİNANSMAN ANALİZİ — aylık taksit rahatlaması ve toplam maliyet.</t>
         </is>
@@ -17944,7 +17986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -18184,6 +18226,7 @@
       <c r="K15" s="268" t="n"/>
       <c r="L15" s="269" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="61" t="inlineStr">
         <is>
@@ -18191,6 +18234,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="156" t="inlineStr">
         <is>
@@ -18271,19 +18315,36 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="44" customWidth="1" style="76" min="1" max="1"/>
+    <col width="96.5" customWidth="1" style="76" min="1" max="1"/>
     <col width="30" customWidth="1" style="76" min="2" max="2"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>RAPOR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" s="50">
-      <c r="A3" s="83" t="inlineStr">
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="50">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>FİNANSMAN KOMİTESİ RAPORU</t>
         </is>
@@ -18322,6 +18383,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="50">
       <c r="A8" s="84" t="inlineStr">
         <is>
@@ -18395,6 +18457,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="50">
       <c r="A16" s="84" t="inlineStr">
         <is>
@@ -18423,6 +18486,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="24.75" customHeight="1" s="50">
       <c r="A21" s="82" t="inlineStr">
         <is>
@@ -18432,8 +18496,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
@@ -18456,23 +18521,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="38" customWidth="1" style="76" min="1" max="1"/>
-    <col width="26" customWidth="1" style="76" min="2" max="2"/>
+    <col width="144.5" customWidth="1" style="76" min="1" max="1"/>
+    <col width="31.5" customWidth="1" style="76" min="2" max="2"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>KARAR MOTORU — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>KARAR MOTORU — borç yükü, yaklaşan taksit ve öncelikli aksiyon</t>
         </is>
@@ -18644,6 +18725,8 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="36.75" customHeight="1" s="50">
       <c r="A22" s="82" t="inlineStr">
         <is>
@@ -18709,17 +18792,31 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="76" min="1" max="1"/>
-    <col width="30" customWidth="1" style="76" min="2" max="2"/>
+    <col width="45.5" customWidth="1" style="76" min="2" max="2"/>
     <col width="95" customWidth="1" style="76" min="3" max="3"/>
     <col width="18" customWidth="1" style="76" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="50">
-      <c r="A1" s="77" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>MOTOR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
@@ -18728,6 +18825,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
@@ -18955,6 +19053,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="50">
       <c r="A26" s="105" t="inlineStr">
         <is>
@@ -19021,6 +19120,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="15" customHeight="1" s="50">
       <c r="A33" s="105" t="inlineStr">
         <is>
@@ -19261,6 +19361,8 @@
         <v/>
       </c>
     </row>
+    <row r="49"/>
+    <row r="50"/>
     <row r="51" ht="19.5" customHeight="1" s="50">
       <c r="A51" s="103" t="inlineStr">
         <is>
@@ -19271,7 +19373,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A51:AN51"/>
     <mergeCell ref="A2:AN2"/>
   </mergeCells>
@@ -19289,24 +19391,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
-    <col width="18" customWidth="1" style="76" min="2" max="3"/>
+    <col width="22.5" customWidth="1" style="76" min="2" max="3"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
     <col width="20" customWidth="1" style="76" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>SENARYO VE DUYARLILIK ANALİZİ</t>
         </is>
@@ -19346,6 +19463,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="84" t="inlineStr">
         <is>
@@ -19429,6 +19547,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="84" t="inlineStr">
         <is>
@@ -19559,29 +19678,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
     <col width="24" customWidth="1" style="76" min="2" max="2"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>KONTROLLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>VERİ KALİTESİ VE SİSTEM SAĞLIĞI</t>
         </is>
       </c>
     </row>
     <row r="4" ht="10" customHeight="1" s="50"/>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="50">
       <c r="A6" s="100" t="inlineStr">
         <is>
@@ -19681,6 +19819,9 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="36.75" customHeight="1" s="50">
       <c r="A18" s="82" t="inlineStr">
         <is>
@@ -19741,17 +19882,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="24" customWidth="1" style="50" min="2" max="2"/>
+    <col width="47.5" customWidth="1" style="50" min="2" max="2"/>
     <col width="32" customWidth="1" style="50" min="3" max="3"/>
     <col width="40" customWidth="1" style="50" min="4" max="4"/>
     <col width="24" customWidth="1" style="50" min="5" max="5"/>
     <col width="18" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="36" customHeight="1" s="50">
       <c r="B2" s="429" t="inlineStr">
         <is>
@@ -19766,6 +19912,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="50">
       <c r="B5" s="373" t="inlineStr">
         <is>
@@ -19773,6 +19920,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1" s="50">
       <c r="B7" s="374" t="inlineStr">
         <is>
@@ -19861,6 +20009,8 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="50">
       <c r="B13" s="373" t="inlineStr">
         <is>
@@ -19868,6 +20018,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="50">
       <c r="B15" s="374" t="inlineStr">
         <is>
@@ -20022,6 +20173,8 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="24" customHeight="1" s="50">
       <c r="B24" s="373" t="inlineStr">
         <is>
@@ -20029,6 +20182,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="24" customHeight="1" s="50">
       <c r="B26" s="374" t="inlineStr">
         <is>
@@ -20214,8 +20368,11 @@
     <col width="42" customWidth="1" style="76" min="2" max="2"/>
     <col width="12" customWidth="1" style="76" min="3" max="3"/>
     <col width="56" customWidth="1" style="76" min="4" max="4"/>
-    <col width="20" customWidth="1" style="76" min="5" max="5"/>
+    <col width="20.5" customWidth="1" style="76" min="5" max="5"/>
     <col width="14" customWidth="1" style="76" min="6" max="7"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
     <col width="16" customWidth="1" style="76" min="10" max="10"/>
     <col width="13" customWidth="1" style="76" min="11" max="11"/>
     <col width="28" customWidth="1" style="76" min="12" max="12"/>
@@ -20224,11 +20381,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>AYARLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
@@ -20237,6 +20402,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="10" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
@@ -20344,6 +20510,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="50">
       <c r="A12" s="104" t="inlineStr">
         <is>
@@ -21053,6 +21220,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="50">
       <c r="J34" s="76" t="inlineStr">
         <is>
@@ -21208,34 +21376,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="76" min="1" max="1"/>
     <col width="3" customWidth="1" style="76" min="2" max="2"/>
     <col width="26" customWidth="1" style="76" min="3" max="3"/>
     <col width="3" customWidth="1" style="76" min="4" max="4"/>
-    <col width="14" customWidth="1" style="76" min="5" max="5"/>
+    <col width="15.5" customWidth="1" style="76" min="5" max="5"/>
     <col width="3" customWidth="1" style="76" min="6" max="6"/>
-    <col width="16" customWidth="1" style="76" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="76" min="7" max="7"/>
     <col width="3" customWidth="1" style="76" min="8" max="8"/>
-    <col width="16" customWidth="1" style="76" min="9" max="9"/>
+    <col width="17.5" customWidth="1" style="76" min="9" max="9"/>
     <col width="3" customWidth="1" style="76" min="10" max="10"/>
-    <col width="22" customWidth="1" style="76" min="11" max="11"/>
+    <col width="23.5" customWidth="1" style="76" min="11" max="11"/>
     <col width="3" customWidth="1" style="76" min="12" max="12"/>
     <col width="14" customWidth="1" style="76" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>LISTELER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
+      <c r="M1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>AÇILIR LİSTE KAYNAKLARI</t>
         </is>
@@ -21445,20 +21626,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="50" min="1" max="1"/>
-    <col width="78" customWidth="1" style="50" min="2" max="2"/>
+    <col width="147.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="201" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="202" t="inlineStr">
         <is>
@@ -21723,6 +21921,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="50">
       <c r="A26" s="205" t="inlineStr">
         <is>
@@ -21821,7 +22020,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21834,25 +22033,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="50" min="1" max="1"/>
-    <col width="24" customWidth="1" style="50" min="2" max="2"/>
-    <col width="22" customWidth="1" style="50" min="3" max="3"/>
-    <col width="27" customWidth="1" style="50" min="4" max="4"/>
-    <col width="29" customWidth="1" style="50" min="5" max="5"/>
-    <col width="20" customWidth="1" style="50" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="50" min="3" max="3"/>
+    <col width="48.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="43.5" customWidth="1" style="50" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="50" min="6" max="6"/>
     <col width="21" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="206" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="207" t="inlineStr">
         <is>
@@ -22312,7 +22523,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22325,22 +22536,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="50" min="1" max="1"/>
-    <col width="52" customWidth="1" style="50" min="2" max="2"/>
-    <col width="34" customWidth="1" style="50" min="3" max="3"/>
+    <col width="89.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="34.5" customWidth="1" style="50" min="3" max="3"/>
     <col width="16" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="209" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="210" t="inlineStr">
         <is>
@@ -23052,7 +23278,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23065,24 +23291,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="50" min="1" max="1"/>
-    <col width="36" customWidth="1" style="50" min="2" max="2"/>
-    <col width="48" customWidth="1" style="50" min="3" max="3"/>
-    <col width="34" customWidth="1" style="50" min="4" max="4"/>
-    <col width="30" customWidth="1" style="50" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="50" min="1" max="1"/>
+    <col width="71.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="160.5" customWidth="1" style="50" min="3" max="3"/>
+    <col width="70.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="50.5" customWidth="1" style="50" min="5" max="5"/>
     <col width="16" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="214" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -23725,7 +23964,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23738,24 +23977,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="50" min="1" max="1"/>
-    <col width="40" customWidth="1" style="50" min="2" max="2"/>
-    <col width="50" customWidth="1" style="50" min="3" max="3"/>
-    <col width="30" customWidth="1" style="50" min="4" max="4"/>
-    <col width="28" customWidth="1" style="50" min="5" max="5"/>
-    <col width="26" customWidth="1" style="50" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="50" min="1" max="1"/>
+    <col width="60.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="50" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="39.5" customWidth="1" style="50" min="5" max="5"/>
+    <col width="27.5" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="218" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="219" t="inlineStr">
         <is>
@@ -24270,7 +24522,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24283,23 +24535,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="50" min="1" max="1"/>
-    <col width="32" customWidth="1" style="50" min="2" max="2"/>
-    <col width="54" customWidth="1" style="50" min="3" max="3"/>
-    <col width="34" customWidth="1" style="50" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="50" min="1" max="1"/>
+    <col width="41.5" customWidth="1" style="50" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="50" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="50" min="5" max="5"/>
     <col width="16" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="50">
-      <c r="A1" s="221" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="50">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="222" t="inlineStr">
         <is>
@@ -24846,7 +25112,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24859,20 +25125,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="76" min="1" max="1"/>
     <col width="22" customWidth="1" style="76" min="2" max="7"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
+    <col width="13" customWidth="1" style="50" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>KAPAK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="31.5" customHeight="1" s="50">
       <c r="A6" s="78" t="inlineStr">
         <is>
@@ -24887,6 +25175,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="80" t="inlineStr">
         <is>
@@ -24901,6 +25190,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="50">
       <c r="A12" s="80" t="inlineStr">
         <is>
@@ -24915,6 +25205,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="80" t="inlineStr">
         <is>
@@ -24943,6 +25234,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="50">
       <c r="A20" s="80" t="inlineStr">
         <is>
@@ -24957,6 +25249,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="50">
       <c r="A23" s="82" t="inlineStr">
         <is>
@@ -24967,7 +25260,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -24985,16 +25278,34 @@
   <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="80" customWidth="1" style="76" min="1" max="1"/>
+    <col width="225.5" customWidth="1" style="76" min="1" max="1"/>
+    <col width="13" customWidth="1" style="50" min="2" max="2"/>
+    <col width="13" customWidth="1" style="50" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="442" t="inlineStr">
         <is>
@@ -25002,6 +25313,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="50">
       <c r="A5" s="84" t="inlineStr">
         <is>
@@ -25016,6 +25328,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="50">
       <c r="A8" s="84" t="inlineStr">
         <is>
@@ -25030,6 +25343,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="50">
       <c r="A11" s="84" t="inlineStr">
         <is>
@@ -25044,6 +25358,9 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="50">
       <c r="A16" s="82" t="inlineStr">
         <is>
@@ -25073,22 +25390,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
+    <col width="71.5" customWidth="1" style="50" min="2" max="2"/>
     <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="14" customWidth="1" style="50" min="5" max="5"/>
+    <col width="16.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="42.5" customWidth="1" style="50" min="5" max="5"/>
     <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="10" customWidth="1" style="50" min="7" max="7"/>
-    <col width="30" customWidth="1" style="50" min="8" max="8"/>
+    <col width="17.5" customWidth="1" style="50" min="7" max="7"/>
+    <col width="75.5" customWidth="1" style="50" min="8" max="8"/>
     <col width="16" customWidth="1" style="50" min="9" max="9"/>
-    <col width="16" customWidth="1" style="50" min="10" max="10"/>
-    <col width="10" customWidth="1" style="50" min="11" max="11"/>
+    <col width="29.5" customWidth="1" style="50" min="10" max="10"/>
+    <col width="136.5" customWidth="1" style="50" min="11" max="11"/>
     <col width="26" customWidth="1" style="50" min="12" max="12"/>
-    <col width="10" customWidth="1" style="50" min="13" max="13"/>
+    <col width="21.5" customWidth="1" style="50" min="13" max="13"/>
+    <col width="13" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1" s="50">
@@ -26022,24 +26340,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="76" min="1" max="1"/>
-    <col width="40" customWidth="1" style="76" min="2" max="2"/>
-    <col width="42" customWidth="1" style="76" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="76" min="2" max="2"/>
+    <col width="44.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>ORNEK VERI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>ÖRNEK VERİ — otomasyon ve içe aktarma için yapı</t>
         </is>
@@ -26184,24 +26517,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="76" min="1" max="1"/>
+    <col width="81.5" customWidth="1" style="76" min="1" max="1"/>
     <col width="20" customWidth="1" style="76" min="2" max="2"/>
     <col width="18" customWidth="1" style="76" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
         </is>
@@ -26330,6 +26678,9 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16" ht="24.75" customHeight="1" s="50">
       <c r="A16" s="82" t="inlineStr">
         <is>
@@ -26356,24 +26707,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="76" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="76" min="1" max="1"/>
     <col width="16" customWidth="1" style="76" min="2" max="2"/>
     <col width="14" customWidth="1" style="76" min="3" max="4"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
     <col width="10" customWidth="1" style="76" min="5" max="5"/>
-    <col width="14" customWidth="1" style="76" min="6" max="6"/>
-    <col width="40" customWidth="1" style="76" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="76" min="6" max="6"/>
+    <col width="40.5" customWidth="1" style="76" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="442" t="inlineStr">
         <is>
@@ -26521,6 +26885,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="76" t="inlineStr">
         <is>
@@ -26556,24 +26921,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
-    <col width="14" customWidth="1" style="76" min="2" max="2"/>
-    <col width="90" customWidth="1" style="76" min="3" max="3"/>
+    <col width="14.5" customWidth="1" style="76" min="2" max="2"/>
+    <col width="98.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="13" customWidth="1" style="50" min="4" max="4"/>
+    <col width="13" customWidth="1" style="50" min="5" max="5"/>
+    <col width="13" customWidth="1" style="50" min="6" max="6"/>
+    <col width="13" customWidth="1" style="50" min="7" max="7"/>
+    <col width="13" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>DEĞİŞİKLİK KAYDI</t>
         </is>
@@ -26633,18 +27013,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
+    <col width="40.5" customWidth="1" style="50" min="2" max="2"/>
     <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="36" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="20" customWidth="1" style="50" min="7" max="7"/>
-    <col width="16" customWidth="1" style="50" min="8" max="8"/>
-    <col width="18" customWidth="1" style="50" min="9" max="9"/>
+    <col width="40.5" customWidth="1" style="50" min="4" max="4"/>
+    <col width="21.5" customWidth="1" style="50" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="50" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="50" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="50" min="8" max="8"/>
+    <col width="19.5" customWidth="1" style="50" min="9" max="9"/>
+    <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1" s="50">
@@ -27115,7 +27496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -27135,15 +27516,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>BANKA TANIMLARI — ilişki, operasyonel durum ve iletişim tek merkezde.</t>
         </is>
@@ -27785,7 +28174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -27805,15 +28194,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>BANKA LİMİTLERİ — toplam, kullanılan ve kalan limit ile kullanım oranı.</t>
         </is>
@@ -28605,7 +29002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -28622,18 +29019,32 @@
     <col width="18" customWidth="1" style="76" min="12" max="12"/>
     <col width="28" customWidth="1" style="76" min="13" max="13"/>
     <col width="14" customWidth="1" style="76" min="14" max="14"/>
+    <col width="13" customWidth="1" style="50" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
+      <c r="M1" s="434" t="n"/>
+      <c r="N1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>KREDİ PORTFÖYÜ — sözleşme, bakiye, maliyet, vade ve taksit bilgileri.</t>
         </is>
@@ -29656,7 +30067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="2"/>
@@ -29676,15 +30087,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
+      <c r="J1" s="434" t="n"/>
+      <c r="K1" s="434" t="n"/>
+      <c r="L1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>TAKSİT PLANI — dönem bazında anapara, faiz, vergi ve ödeme tarihi.</t>
         </is>
@@ -30656,7 +31078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -30676,15 +31098,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="50">
-      <c r="A1" s="441" t="inlineStr">
+      <c r="A1" s="455" t="inlineStr">
         <is>
           <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="434" t="n"/>
+      <c r="C1" s="434" t="n"/>
+      <c r="D1" s="434" t="n"/>
+      <c r="E1" s="434" t="n"/>
+      <c r="F1" s="434" t="n"/>
+      <c r="G1" s="434" t="n"/>
+      <c r="H1" s="434" t="n"/>
+      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>ÖDEME TAKVİMİ — yaklaşan taksitler 30 / 60 / 90 gün penceresinde.</t>
         </is>

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -13857,7 +13857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" style="50" min="1" max="1"/>
@@ -14377,7 +14377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="2"/>
@@ -14402,14 +14402,6 @@
           <t>MASRAF KOMISYON — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -15022,7 +15014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.5" customWidth="1" style="76" min="1" max="1"/>
@@ -15047,15 +15039,6 @@
           <t>TEMINATLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -15709,7 +15692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.5" customWidth="1" style="76" min="1" max="1"/>
@@ -15734,16 +15717,6 @@
           <t>YENI TEKLIFLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -16590,7 +16563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -16615,15 +16588,6 @@
           <t>REFINANSMAN — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -17986,7 +17950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -18153,7 +18117,7 @@
       <c r="C11" s="411" t="n"/>
       <c r="D11" s="411" t="n"/>
       <c r="E11" s="425">
-        <f>YUVARLA(KARAR_MOTORU!B7/MAX(1,SerbestNakit*0.8); 2)</f>
+        <f>ROUND(KARAR_MOTORU!B7/MAX(1,SerbestNakit*0.8), 2)</f>
         <v/>
       </c>
       <c r="F11" s="412" t="n"/>
@@ -18165,7 +18129,7 @@
       <c r="I11" s="411" t="n"/>
       <c r="J11" s="411" t="n"/>
       <c r="K11" s="426">
-        <f>YUVARLA(KARAR_MOTORU!B14; 2)</f>
+        <f>ROUND(KARAR_MOTORU!B14, 2)</f>
         <v/>
       </c>
       <c r="L11" s="412" t="n"/>
@@ -18312,7 +18276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="96.5" customWidth="1" style="76" min="1" max="1"/>
@@ -18333,14 +18297,6 @@
           <t>RAPOR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -18521,7 +18477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="144.5" customWidth="1" style="76" min="1" max="1"/>
@@ -18542,14 +18498,6 @@
           <t>KARAR MOTORU — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -18699,7 +18647,7 @@
         </is>
       </c>
       <c r="B17" s="102">
-        <f>IF(B15="DURDUR","Ödeme baskısını düşürün: erken kapama, refinansman veya ek limit değerlendirin",IF(B15="İNCELE","Döviz uyumu ve kaldıraç eşiklerini gözden geçirin, aday teklifleri müzakereye alın","Borç yapısı sürdürülebilir: ödeme takvimini düzenli izleyin"))</f>
+        <f>IF(B15="DURDUR","Ödeme baskısını düşürün: erken kapama, refinansman veya ek limit değerlendirin",IF(B15="İNCELE","Döviz uyumu AND kaldıraç eşiklerini gözden geçirin, aday teklifleri müzakereye alın","Borç yapısı sürdürülebilir: ödeme takvimini düzenli izleyin"))</f>
         <v/>
       </c>
     </row>
@@ -18809,14 +18757,6 @@
           <t>MOTOR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
@@ -19132,7 +19072,7 @@
         <v/>
       </c>
       <c r="C33" s="109">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Vadesi geçmiş taksit sayısı "&amp;modulT1VadeGecmis,IF(modulT1VadeGecmis&gt;0,"gecikmiş taksitler faiz ve itibar riski yaratıyor, ödeme önceliği verin","vadesi geçmiş taksit yok"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Vadesi geçmiş taksit sayısı "&amp;modulT1VadeGecmis,IF(modulT1VadeGecmis&gt;0,"gecikmiş taksitler faiz AND itibar riski yaratıyor, ödeme önceliği verin","vadesi geçmiş taksit yok"))</f>
         <v/>
       </c>
     </row>
@@ -19237,7 +19177,7 @@
         <v/>
       </c>
       <c r="C40" s="109">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Duyarlılık değişkenlerinin en yüksek etkisi "&amp;TEXT(modulO2TornadoZirve,"#,##0")&amp;" TL",IF(modulO2TornadoZirve&gt;KARAR_MOTORU!$B$7,"tek değişken senaryoyu değiştirebilir, kur ve faiz riskini yönetin","duyarlılık etkisi sınırlı"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Duyarlılık değişkenlerinin en yüksek etkisi "&amp;TEXT(modulO2TornadoZirve,"#,##0")&amp;" TL",IF(modulO2TornadoZirve&gt;KARAR_MOTORU!$B$7,"tek değişken senaryoyu değiştirebilir, kur AND faiz riskini yönetin","duyarlılık etkisi sınırlı"))</f>
         <v/>
       </c>
     </row>
@@ -19357,7 +19297,7 @@
         <v/>
       </c>
       <c r="C48" s="109">
-        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"I7: Nakit açığı köprüsü "&amp;TEXT(modulI7NakitAcigi,"#,##0")&amp;" TL",IF(modulI7NakitAcigi&gt;0,"30 günlük yük serbest nakdi aşıyor, tahsilat ve limit imkânını hızlandırın","nakit açığı yok"))</f>
+        <f>_xlfn.TEXTJOIN(" | ",TRUE(),"I7: Nakit açığı köprüsü "&amp;TEXT(modulI7NakitAcigi,"#,##0")&amp;" TL",IF(modulI7NakitAcigi&gt;0,"30 günlük yük serbest nakdi aşıyor, tahsilat AND limit imkânını hızlandırın","nakit açığı yok"))</f>
         <v/>
       </c>
     </row>
@@ -19391,7 +19331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
@@ -19412,14 +19352,6 @@
           <t>SENARYO DUYARLILIK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -19678,7 +19610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="76" min="1" max="1"/>
@@ -19700,15 +19632,6 @@
           <t>KONTROLLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -19882,7 +19805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -20386,14 +20309,6 @@
           <t>AYARLAR — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50">
       <c r="A2" s="103" t="inlineStr">
@@ -21376,7 +21291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="76" min="1" max="1"/>
@@ -21401,18 +21316,6 @@
           <t>LISTELER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
-      <c r="M1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -21626,7 +21529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="50" min="1" max="1"/>
@@ -21647,14 +21550,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -22033,7 +21928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="50" min="1" max="1"/>
@@ -22054,14 +21949,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -22536,7 +22423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="50" min="1" max="1"/>
@@ -22557,14 +22444,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -23291,7 +23170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" style="50" min="1" max="1"/>
@@ -23312,14 +23191,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -23977,7 +23848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" style="50" min="1" max="1"/>
@@ -23998,14 +23869,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -24535,7 +24398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="50" min="1" max="1"/>
@@ -24556,14 +24419,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
@@ -25125,7 +24980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="76" min="1" max="1"/>
@@ -25147,15 +25002,6 @@
           <t>KAPAK — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3"/>
@@ -25296,18 +25142,10 @@
           <t>HIZLI BASLANGIC — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>3 ADIMDA SİSTEM</t>
         </is>
@@ -25390,7 +25228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -26340,7 +26178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="76" min="1" max="1"/>
@@ -26361,14 +26199,6 @@
           <t>ORNEK VERI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -26517,7 +26347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="81.5" customWidth="1" style="76" min="1" max="1"/>
@@ -26538,14 +26368,6 @@
           <t>TESTLER — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -26707,7 +26529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.5" customWidth="1" style="76" min="1" max="1"/>
@@ -26728,18 +26550,10 @@
           <t>AKIS — BankaKrediVeTaksitTakipSistemi</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
-      <c r="A3" s="442" t="inlineStr">
+      <c r="A3" s="456" t="inlineStr">
         <is>
           <t>islem_id</t>
         </is>
@@ -26921,7 +26735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="76" min="1" max="1"/>
@@ -26942,14 +26756,6 @@
           <t>DEGISIKLIK KAYDI — BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -27013,7 +26819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -27496,7 +27302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -27521,14 +27327,6 @@
           <t>BANKALAR — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -28174,7 +27972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -28199,14 +27997,6 @@
           <t>LIMITLER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -29002,7 +28792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="1"/>
@@ -29028,19 +28818,6 @@
           <t>KREDILER — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
-      <c r="M1" s="434" t="n"/>
-      <c r="N1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -30067,7 +29844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13" customWidth="1" style="76" min="1" max="2"/>
@@ -30092,17 +29869,6 @@
           <t>TAKSIT_PLANI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
-      <c r="J1" s="434" t="n"/>
-      <c r="K1" s="434" t="n"/>
-      <c r="L1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -31078,7 +30844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="76" min="1" max="1"/>
@@ -31103,14 +30869,6 @@
           <t>ODEME_TAKVIMI — KURUMSAL BANKA VE BORÇ YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="434" t="n"/>
-      <c r="C1" s="434" t="n"/>
-      <c r="D1" s="434" t="n"/>
-      <c r="E1" s="434" t="n"/>
-      <c r="F1" s="434" t="n"/>
-      <c r="G1" s="434" t="n"/>
-      <c r="H1" s="434" t="n"/>
-      <c r="I1" s="434" t="n"/>
     </row>
     <row r="2" ht="7.8" customHeight="1" s="50"/>
     <row r="3" ht="22" customHeight="1" s="50">
@@ -31180,7 +30938,7 @@
         <v/>
       </c>
       <c r="F6" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",IF(TAKSIT_PLANI!$K6&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K6&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K6&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A6),"",IF(TAKSIT_PLANI!$K6&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K6&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K6&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G6" s="311">
@@ -31210,7 +30968,7 @@
         <v/>
       </c>
       <c r="F7" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",IF(TAKSIT_PLANI!$K7&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K7&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K7&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A7),"",IF(TAKSIT_PLANI!$K7&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K7&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K7&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G7" s="315">
@@ -31240,7 +30998,7 @@
         <v/>
       </c>
       <c r="F8" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",IF(TAKSIT_PLANI!$K8&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K8&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K8&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A8),"",IF(TAKSIT_PLANI!$K8&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K8&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K8&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G8" s="311">
@@ -31270,7 +31028,7 @@
         <v/>
       </c>
       <c r="F9" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",IF(TAKSIT_PLANI!$K9&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K9&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K9&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A9),"",IF(TAKSIT_PLANI!$K9&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K9&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K9&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G9" s="315">
@@ -31300,7 +31058,7 @@
         <v/>
       </c>
       <c r="F10" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",IF(TAKSIT_PLANI!$K10&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K10&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K10&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A10),"",IF(TAKSIT_PLANI!$K10&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K10&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K10&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G10" s="311">
@@ -31330,7 +31088,7 @@
         <v/>
       </c>
       <c r="F11" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",IF(TAKSIT_PLANI!$K11&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K11&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K11&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A11),"",IF(TAKSIT_PLANI!$K11&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K11&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K11&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G11" s="315">
@@ -31360,7 +31118,7 @@
         <v/>
       </c>
       <c r="F12" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",IF(TAKSIT_PLANI!$K12&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K12&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K12&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A12),"",IF(TAKSIT_PLANI!$K12&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K12&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K12&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G12" s="311">
@@ -31390,7 +31148,7 @@
         <v/>
       </c>
       <c r="F13" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",IF(TAKSIT_PLANI!$K13&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K13&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K13&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A13),"",IF(TAKSIT_PLANI!$K13&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K13&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K13&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G13" s="315">
@@ -31420,7 +31178,7 @@
         <v/>
       </c>
       <c r="F14" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",IF(TAKSIT_PLANI!$K14&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K14&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K14&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A14),"",IF(TAKSIT_PLANI!$K14&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K14&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K14&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G14" s="311">
@@ -31450,7 +31208,7 @@
         <v/>
       </c>
       <c r="F15" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",IF(TAKSIT_PLANI!$K15&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K15&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K15&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A15),"",IF(TAKSIT_PLANI!$K15&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K15&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K15&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G15" s="315">
@@ -31480,7 +31238,7 @@
         <v/>
       </c>
       <c r="F16" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",IF(TAKSIT_PLANI!$K16&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K16&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K16&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A16),"",IF(TAKSIT_PLANI!$K16&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K16&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K16&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G16" s="311">
@@ -31510,7 +31268,7 @@
         <v/>
       </c>
       <c r="F17" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",IF(TAKSIT_PLANI!$K17&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K17&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K17&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A17),"",IF(TAKSIT_PLANI!$K17&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K17&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K17&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G17" s="315">
@@ -31540,7 +31298,7 @@
         <v/>
       </c>
       <c r="F18" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",IF(TAKSIT_PLANI!$K18&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K18&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K18&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A18),"",IF(TAKSIT_PLANI!$K18&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K18&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K18&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G18" s="311">
@@ -31570,7 +31328,7 @@
         <v/>
       </c>
       <c r="F19" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",IF(TAKSIT_PLANI!$K19&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K19&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K19&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A19),"",IF(TAKSIT_PLANI!$K19&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K19&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K19&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G19" s="315">
@@ -31600,7 +31358,7 @@
         <v/>
       </c>
       <c r="F20" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",IF(TAKSIT_PLANI!$K20&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K20&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K20&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A20),"",IF(TAKSIT_PLANI!$K20&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K20&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K20&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G20" s="311">
@@ -31630,7 +31388,7 @@
         <v/>
       </c>
       <c r="F21" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",IF(TAKSIT_PLANI!$K21&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K21&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K21&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A21),"",IF(TAKSIT_PLANI!$K21&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K21&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K21&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G21" s="315">
@@ -31660,7 +31418,7 @@
         <v/>
       </c>
       <c r="F22" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",IF(TAKSIT_PLANI!$K22&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K22&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K22&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A22),"",IF(TAKSIT_PLANI!$K22&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K22&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K22&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G22" s="311">
@@ -31690,7 +31448,7 @@
         <v/>
       </c>
       <c r="F23" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",IF(TAKSIT_PLANI!$K23&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K23&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K23&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A23),"",IF(TAKSIT_PLANI!$K23&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K23&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K23&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G23" s="315">
@@ -31720,7 +31478,7 @@
         <v/>
       </c>
       <c r="F24" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",IF(TAKSIT_PLANI!$K24&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K24&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K24&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A24),"",IF(TAKSIT_PLANI!$K24&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K24&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K24&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G24" s="311">
@@ -31750,7 +31508,7 @@
         <v/>
       </c>
       <c r="F25" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",IF(TAKSIT_PLANI!$K25&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K25&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K25&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A25),"",IF(TAKSIT_PLANI!$K25&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K25&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K25&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G25" s="315">
@@ -31780,7 +31538,7 @@
         <v/>
       </c>
       <c r="F26" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",IF(TAKSIT_PLANI!$K26&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K26&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K26&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A26),"",IF(TAKSIT_PLANI!$K26&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K26&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K26&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G26" s="311">
@@ -31810,7 +31568,7 @@
         <v/>
       </c>
       <c r="F27" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",IF(TAKSIT_PLANI!$K27&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K27&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K27&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A27),"",IF(TAKSIT_PLANI!$K27&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K27&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K27&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G27" s="315">
@@ -31840,7 +31598,7 @@
         <v/>
       </c>
       <c r="F28" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",IF(TAKSIT_PLANI!$K28&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K28&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K28&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A28),"",IF(TAKSIT_PLANI!$K28&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K28&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K28&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G28" s="311">
@@ -31870,7 +31628,7 @@
         <v/>
       </c>
       <c r="F29" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",IF(TAKSIT_PLANI!$K29&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K29&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K29&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A29),"",IF(TAKSIT_PLANI!$K29&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K29&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K29&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G29" s="315">
@@ -31900,7 +31658,7 @@
         <v/>
       </c>
       <c r="F30" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",IF(TAKSIT_PLANI!$K30&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K30&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K30&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A30),"",IF(TAKSIT_PLANI!$K30&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K30&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K30&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G30" s="311">
@@ -31930,7 +31688,7 @@
         <v/>
       </c>
       <c r="F31" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",IF(TAKSIT_PLANI!$K31&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K31&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K31&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A31),"",IF(TAKSIT_PLANI!$K31&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K31&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K31&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G31" s="315">
@@ -31960,7 +31718,7 @@
         <v/>
       </c>
       <c r="F32" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",IF(TAKSIT_PLANI!$K32&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K32&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K32&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A32),"",IF(TAKSIT_PLANI!$K32&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K32&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K32&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G32" s="311">
@@ -31990,7 +31748,7 @@
         <v/>
       </c>
       <c r="F33" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",IF(TAKSIT_PLANI!$K33&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K33&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K33&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A33),"",IF(TAKSIT_PLANI!$K33&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K33&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K33&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G33" s="315">
@@ -32020,7 +31778,7 @@
         <v/>
       </c>
       <c r="F34" s="311">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",IF(TAKSIT_PLANI!$K34&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K34&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K34&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A34),"",IF(TAKSIT_PLANI!$K34&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K34&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K34&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G34" s="311">
@@ -32050,7 +31808,7 @@
         <v/>
       </c>
       <c r="F35" s="315">
-        <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",IF(TAKSIT_PLANI!$K35&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K35&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K35&lt;=60,"31-60 Gün","61 Gün ve Üzeri"))))</f>
+        <f>IF(ISBLANK(TAKSIT_PLANI!$A35),"",IF(TAKSIT_PLANI!$K35&lt;0,"Vadesi Geçmiş",IF(TAKSIT_PLANI!$K35&lt;=30,"0-30 Gün",IF(TAKSIT_PLANI!$K35&lt;=60,"31-60 Gün","61 Gün AND Üzeri"))))</f>
         <v/>
       </c>
       <c r="G35" s="315">

--- a/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/banka-kredi-ve-taksit-takip-sistemi/BankaKrediVeTaksitTakipSistemi.xlsx
@@ -119,7 +119,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="128">
+  <fonts count="159">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -894,8 +894,194 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -1105,8 +1291,26 @@
         <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="65">
+  <borders count="121">
     <border>
       <left/>
       <right/>
@@ -1771,6 +1975,582 @@
       <bottom/>
     </border>
     <border/>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FCA5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1782,7 +2562,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="457">
+  <cellXfs count="580">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2937,6 +3717,261 @@
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="130" fillId="18" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="132" fillId="18" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="130" fillId="18" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="18" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="7" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="7" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="73" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="73" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="142" fillId="7" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="143" fillId="7" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="144" fillId="7" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="150" fillId="17" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="145" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="145" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="151" fillId="17" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="146" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="17" borderId="79" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="148" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="152" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="12" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="157" fillId="11" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="18" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="154" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="18" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="158" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="122" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="155" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="155" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="12" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13857,7 +14892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="B2:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" style="50" min="1" max="1"/>
@@ -14094,7 +15129,6 @@
       <c r="Q16" s="355" t="n"/>
       <c r="R16" s="355" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="14" customHeight="1" s="50"/>
     <row r="19" ht="28" customHeight="1" s="50">
       <c r="B19" s="361" t="inlineStr">
@@ -14103,7 +15137,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="26" customHeight="1" s="50">
       <c r="B21" s="443" t="inlineStr">
         <is>
@@ -17950,31 +18983,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="26" customWidth="1" style="50" min="2" max="2"/>
+    <col width="12" customWidth="1" style="50" min="1" max="1"/>
+    <col width="24" customWidth="1" style="50" min="2" max="2"/>
     <col width="14" customWidth="1" style="50" min="3" max="3"/>
     <col width="14" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="4" customWidth="1" style="50" min="6" max="6"/>
-    <col width="4" customWidth="1" style="50" min="7" max="7"/>
-    <col width="26" customWidth="1" style="50" min="8" max="8"/>
+    <col width="16" customWidth="1" style="50" min="5" max="5"/>
+    <col width="14" customWidth="1" style="50" min="6" max="6"/>
+    <col width="6" customWidth="1" style="50" min="7" max="7"/>
+    <col width="24" customWidth="1" style="50" min="8" max="8"/>
     <col width="14" customWidth="1" style="50" min="9" max="9"/>
     <col width="14" customWidth="1" style="50" min="10" max="10"/>
-    <col width="20" customWidth="1" style="50" min="11" max="11"/>
-    <col width="4" customWidth="1" style="50" min="12" max="12"/>
+    <col width="16" customWidth="1" style="50" min="11" max="11"/>
+    <col width="14" customWidth="1" style="50" min="12" max="12"/>
+    <col width="6" customWidth="1" style="50" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10" customHeight="1" s="50">
-      <c r="A1" s="60" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="50">
+      <c r="A1" s="457" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1" s="50">
+    <row r="2" ht="28" customHeight="1" s="50">
       <c r="B2" s="436" t="inlineStr">
         <is>
           <t>BANKA, KREDİ VE TAKSİT TAKİP SİSTEMİ — FİNANSAL STRES TESTİ</t>
@@ -17982,278 +19016,393 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="437" t="inlineStr">
+      <c r="B3" s="534" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve Hazine Komitesi için Borç Servisi ve Likidite Dayanıklılık Raporu</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="50">
-      <c r="B4" s="438" t="inlineStr">
+      <c r="B4" s="535" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="14" customHeight="1" s="50"/>
-    <row r="6" ht="28" customHeight="1" s="50">
-      <c r="B6" s="439" t="inlineStr">
+    <row r="5" ht="12" customHeight="1" s="50"/>
+    <row r="6" ht="26" customHeight="1" s="50">
+      <c r="B6" s="536" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="290" t="n"/>
-      <c r="D6" s="290" t="n"/>
-      <c r="E6" s="290" t="n"/>
-      <c r="F6" s="291" t="n"/>
-      <c r="H6" s="440" t="inlineStr">
+      <c r="C6" s="566" t="n"/>
+      <c r="D6" s="566" t="n"/>
+      <c r="E6" s="566" t="n"/>
+      <c r="F6" s="567" t="n"/>
+      <c r="H6" s="539" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="290" t="n"/>
-      <c r="J6" s="290" t="n"/>
-      <c r="K6" s="290" t="n"/>
-      <c r="L6" s="291" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1" s="50">
-      <c r="B7" s="418" t="n"/>
-      <c r="C7" s="404" t="n"/>
-      <c r="D7" s="404" t="n"/>
-      <c r="E7" s="404" t="n"/>
-      <c r="F7" s="405" t="n"/>
-      <c r="H7" s="418" t="n"/>
-      <c r="I7" s="404" t="n"/>
-      <c r="J7" s="404" t="n"/>
-      <c r="K7" s="404" t="n"/>
-      <c r="L7" s="405" t="n"/>
+      <c r="I6" s="568" t="n"/>
+      <c r="J6" s="568" t="n"/>
+      <c r="K6" s="568" t="n"/>
+      <c r="L6" s="569" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="50">
+      <c r="B7" s="542" t="n"/>
+      <c r="C7" s="472" t="n"/>
+      <c r="D7" s="472" t="n"/>
+      <c r="E7" s="472" t="n"/>
+      <c r="F7" s="543" t="n"/>
+      <c r="H7" s="544" t="n"/>
+      <c r="I7" s="472" t="n"/>
+      <c r="J7" s="472" t="n"/>
+      <c r="K7" s="472" t="n"/>
+      <c r="L7" s="545" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1" s="50">
-      <c r="B8" s="419" t="inlineStr">
-        <is>
-          <t>Faaliyet Nakit Akışı Daralması:</t>
-        </is>
-      </c>
-      <c r="C8" s="404" t="n"/>
-      <c r="D8" s="404" t="n"/>
-      <c r="E8" s="420" t="inlineStr">
-        <is>
-          <t>-%20.0 (Kriz Modeli)</t>
-        </is>
-      </c>
-      <c r="F8" s="405" t="n"/>
-      <c r="H8" s="419" t="inlineStr">
-        <is>
-          <t>Planlanan Borç Karşılama:</t>
-        </is>
-      </c>
-      <c r="I8" s="404" t="n"/>
-      <c r="J8" s="404" t="n"/>
-      <c r="K8" s="421" t="inlineStr">
+      <c r="B8" s="546" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="472" t="n"/>
+      <c r="D8" s="472" t="n"/>
+      <c r="E8" s="547" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="543" t="n"/>
+      <c r="H8" s="548" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="472" t="n"/>
+      <c r="J8" s="472" t="n"/>
+      <c r="K8" s="549" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="405" t="n"/>
+      <c r="L8" s="545" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1" s="50">
-      <c r="B9" s="419" t="inlineStr">
-        <is>
-          <t>Mevcut 30 Günlük Borç Servisi:</t>
-        </is>
-      </c>
-      <c r="C9" s="404" t="n"/>
-      <c r="D9" s="404" t="n"/>
-      <c r="E9" s="422">
+      <c r="B9" s="546" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="472" t="n"/>
+      <c r="D9" s="472" t="n"/>
+      <c r="E9" s="550">
         <f>KARAR_MOTORU!B7</f>
         <v/>
       </c>
-      <c r="F9" s="405" t="n"/>
-      <c r="H9" s="419" t="inlineStr">
-        <is>
-          <t>Aylık Refinansman Tasarrufu:</t>
-        </is>
-      </c>
-      <c r="I9" s="404" t="n"/>
-      <c r="J9" s="404" t="n"/>
-      <c r="K9" s="422">
+      <c r="F9" s="543" t="n"/>
+      <c r="H9" s="548" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="472" t="n"/>
+      <c r="J9" s="472" t="n"/>
+      <c r="K9" s="550">
         <f>KARAR_MOTORU!B19</f>
         <v/>
       </c>
-      <c r="L9" s="405" t="n"/>
+      <c r="L9" s="545" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1" s="50">
-      <c r="B10" s="419" t="inlineStr">
-        <is>
-          <t>Stres Altında Serbest Nakit:</t>
-        </is>
-      </c>
-      <c r="C10" s="404" t="n"/>
-      <c r="D10" s="404" t="n"/>
-      <c r="E10" s="423">
+      <c r="B10" s="546" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="472" t="n"/>
+      <c r="D10" s="472" t="n"/>
+      <c r="E10" s="551">
         <f>SerbestNakit*0.8</f>
         <v/>
       </c>
-      <c r="F10" s="405" t="n"/>
-      <c r="H10" s="419" t="inlineStr">
-        <is>
-          <t>Konsolide Serbest Nakit:</t>
-        </is>
-      </c>
-      <c r="I10" s="404" t="n"/>
-      <c r="J10" s="404" t="n"/>
-      <c r="K10" s="423">
+      <c r="F10" s="543" t="n"/>
+      <c r="H10" s="548" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="472" t="n"/>
+      <c r="J10" s="472" t="n"/>
+      <c r="K10" s="551">
         <f>SerbestNakit</f>
         <v/>
       </c>
-      <c r="L10" s="405" t="n"/>
+      <c r="L10" s="545" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1" s="50">
-      <c r="B11" s="424" t="inlineStr">
-        <is>
-          <t>Stres Altında Likidite Baskısı:</t>
-        </is>
-      </c>
-      <c r="C11" s="411" t="n"/>
-      <c r="D11" s="411" t="n"/>
-      <c r="E11" s="425">
+      <c r="B11" s="546" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="472" t="n"/>
+      <c r="D11" s="472" t="n"/>
+      <c r="E11" s="552">
         <f>ROUND(KARAR_MOTORU!B7/MAX(1,SerbestNakit*0.8), 2)</f>
         <v/>
       </c>
-      <c r="F11" s="412" t="n"/>
-      <c r="H11" s="424" t="inlineStr">
-        <is>
-          <t>Baz Model Likidite Baskısı:</t>
-        </is>
-      </c>
-      <c r="I11" s="411" t="n"/>
-      <c r="J11" s="411" t="n"/>
-      <c r="K11" s="426">
+      <c r="F11" s="543" t="n"/>
+      <c r="H11" s="548" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="472" t="n"/>
+      <c r="J11" s="472" t="n"/>
+      <c r="K11" s="553">
         <f>ROUND(KARAR_MOTORU!B14, 2)</f>
         <v/>
       </c>
-      <c r="L11" s="412" t="n"/>
-    </row>
-    <row r="12" ht="8" customHeight="1" s="50">
-      <c r="B12" s="129" t="n"/>
-      <c r="C12" s="129" t="n"/>
-      <c r="D12" s="129" t="n"/>
-      <c r="E12" s="129" t="n"/>
-      <c r="F12" s="129" t="n"/>
-      <c r="H12" s="129" t="n"/>
-      <c r="I12" s="129" t="n"/>
-      <c r="J12" s="129" t="n"/>
-      <c r="K12" s="129" t="n"/>
-      <c r="L12" s="129" t="n"/>
-    </row>
-    <row r="13" ht="6" customHeight="1" s="50">
-      <c r="B13" s="129" t="n"/>
-      <c r="C13" s="129" t="n"/>
-      <c r="D13" s="129" t="n"/>
-      <c r="E13" s="129" t="n"/>
-      <c r="F13" s="129" t="n"/>
-      <c r="H13" s="129" t="n"/>
-      <c r="I13" s="129" t="n"/>
-      <c r="J13" s="129" t="n"/>
-      <c r="K13" s="129" t="n"/>
-      <c r="L13" s="129" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1" s="50">
-      <c r="B14" s="198" t="inlineStr">
-        <is>
-          <t>KRİZ SENARYOSUNDA DAHİ TEMERRÜT RİSKİ SIFIR</t>
-        </is>
-      </c>
-      <c r="C14" s="260" t="n"/>
-      <c r="D14" s="260" t="n"/>
-      <c r="E14" s="260" t="n"/>
-      <c r="F14" s="261" t="n"/>
-      <c r="H14" s="199" t="inlineStr">
-        <is>
-          <t>OPTİMUM REFINANSMAN VE NAKİT YÖNETİM REÇETESİ</t>
-        </is>
-      </c>
-      <c r="I14" s="262" t="n"/>
-      <c r="J14" s="262" t="n"/>
-      <c r="K14" s="262" t="n"/>
-      <c r="L14" s="263" t="n"/>
+      <c r="L11" s="545" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="50">
+      <c r="B12" s="542" t="n"/>
+      <c r="C12" s="472" t="n"/>
+      <c r="D12" s="472" t="n"/>
+      <c r="E12" s="472" t="n"/>
+      <c r="F12" s="543" t="n"/>
+      <c r="H12" s="544" t="n"/>
+      <c r="I12" s="472" t="n"/>
+      <c r="J12" s="472" t="n"/>
+      <c r="K12" s="472" t="n"/>
+      <c r="L12" s="545" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="50">
+      <c r="B13" s="542" t="n"/>
+      <c r="C13" s="472" t="n"/>
+      <c r="D13" s="472" t="n"/>
+      <c r="E13" s="472" t="n"/>
+      <c r="F13" s="543" t="n"/>
+      <c r="H13" s="544" t="n"/>
+      <c r="I13" s="472" t="n"/>
+      <c r="J13" s="472" t="n"/>
+      <c r="K13" s="472" t="n"/>
+      <c r="L13" s="545" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="50">
+      <c r="B14" s="554" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="570" t="n"/>
+      <c r="D14" s="570" t="n"/>
+      <c r="E14" s="570" t="n"/>
+      <c r="F14" s="571" t="n"/>
+      <c r="H14" s="557" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="572" t="n"/>
+      <c r="J14" s="572" t="n"/>
+      <c r="K14" s="572" t="n"/>
+      <c r="L14" s="573" t="n"/>
     </row>
     <row r="15" ht="14" customHeight="1" s="50">
-      <c r="B15" s="264" t="n"/>
-      <c r="C15" s="265" t="n"/>
-      <c r="D15" s="265" t="n"/>
-      <c r="E15" s="265" t="n"/>
-      <c r="F15" s="266" t="n"/>
-      <c r="H15" s="267" t="n"/>
-      <c r="I15" s="268" t="n"/>
-      <c r="J15" s="268" t="n"/>
-      <c r="K15" s="268" t="n"/>
-      <c r="L15" s="269" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B15" s="574" t="n"/>
+      <c r="C15" s="575" t="n"/>
+      <c r="D15" s="575" t="n"/>
+      <c r="E15" s="575" t="n"/>
+      <c r="F15" s="576" t="n"/>
+      <c r="H15" s="577" t="n"/>
+      <c r="I15" s="578" t="n"/>
+      <c r="J15" s="578" t="n"/>
+      <c r="K15" s="578" t="n"/>
+      <c r="L15" s="579" t="n"/>
+    </row>
+    <row r="16" ht="10" customHeight="1" s="50"/>
+    <row r="17" ht="26" customHeight="1" s="50">
+      <c r="B17" s="560" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="156" t="inlineStr">
+      <c r="C17" s="463" t="n"/>
+      <c r="D17" s="463" t="n"/>
+      <c r="E17" s="463" t="n"/>
+      <c r="F17" s="463" t="n"/>
+      <c r="G17" s="463" t="n"/>
+      <c r="H17" s="463" t="n"/>
+      <c r="I17" s="463" t="n"/>
+      <c r="J17" s="463" t="n"/>
+      <c r="K17" s="463" t="n"/>
+      <c r="L17" s="511" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="50">
+      <c r="B18" s="561" t="n"/>
+      <c r="C18" s="472" t="n"/>
+      <c r="D18" s="472" t="n"/>
+      <c r="E18" s="472" t="n"/>
+      <c r="F18" s="472" t="n"/>
+      <c r="G18" s="472" t="n"/>
+      <c r="H18" s="472" t="n"/>
+      <c r="I18" s="472" t="n"/>
+      <c r="J18" s="472" t="n"/>
+      <c r="K18" s="472" t="n"/>
+      <c r="L18" s="473" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="50">
+      <c r="B19" s="562" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="200" t="inlineStr">
+      <c r="C19" s="472" t="n"/>
+      <c r="D19" s="472" t="n"/>
+      <c r="E19" s="472" t="n"/>
+      <c r="F19" s="472" t="n"/>
+      <c r="G19" s="472" t="n"/>
+      <c r="H19" s="472" t="n"/>
+      <c r="I19" s="472" t="n"/>
+      <c r="J19" s="472" t="n"/>
+      <c r="K19" s="472" t="n"/>
+      <c r="L19" s="473" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="50">
+      <c r="B20" s="563" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="156" t="inlineStr">
+      <c r="C20" s="472" t="n"/>
+      <c r="D20" s="472" t="n"/>
+      <c r="E20" s="472" t="n"/>
+      <c r="F20" s="472" t="n"/>
+      <c r="G20" s="472" t="n"/>
+      <c r="H20" s="472" t="n"/>
+      <c r="I20" s="472" t="n"/>
+      <c r="J20" s="472" t="n"/>
+      <c r="K20" s="472" t="n"/>
+      <c r="L20" s="473" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="50">
+      <c r="B21" s="562" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="200" t="inlineStr">
+      <c r="C21" s="472" t="n"/>
+      <c r="D21" s="472" t="n"/>
+      <c r="E21" s="472" t="n"/>
+      <c r="F21" s="472" t="n"/>
+      <c r="G21" s="472" t="n"/>
+      <c r="H21" s="472" t="n"/>
+      <c r="I21" s="472" t="n"/>
+      <c r="J21" s="472" t="n"/>
+      <c r="K21" s="472" t="n"/>
+      <c r="L21" s="473" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="50">
+      <c r="B22" s="563" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="156" t="inlineStr">
+      <c r="C22" s="472" t="n"/>
+      <c r="D22" s="472" t="n"/>
+      <c r="E22" s="472" t="n"/>
+      <c r="F22" s="472" t="n"/>
+      <c r="G22" s="472" t="n"/>
+      <c r="H22" s="472" t="n"/>
+      <c r="I22" s="472" t="n"/>
+      <c r="J22" s="472" t="n"/>
+      <c r="K22" s="472" t="n"/>
+      <c r="L22" s="473" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="50">
+      <c r="B23" s="562" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="200" t="inlineStr">
+      <c r="C23" s="472" t="n"/>
+      <c r="D23" s="472" t="n"/>
+      <c r="E23" s="472" t="n"/>
+      <c r="F23" s="472" t="n"/>
+      <c r="G23" s="472" t="n"/>
+      <c r="H23" s="472" t="n"/>
+      <c r="I23" s="472" t="n"/>
+      <c r="J23" s="472" t="n"/>
+      <c r="K23" s="472" t="n"/>
+      <c r="L23" s="473" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="50">
+      <c r="B24" s="563" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="156" t="inlineStr">
+      <c r="C24" s="472" t="n"/>
+      <c r="D24" s="472" t="n"/>
+      <c r="E24" s="472" t="n"/>
+      <c r="F24" s="472" t="n"/>
+      <c r="G24" s="472" t="n"/>
+      <c r="H24" s="472" t="n"/>
+      <c r="I24" s="472" t="n"/>
+      <c r="J24" s="472" t="n"/>
+      <c r="K24" s="472" t="n"/>
+      <c r="L24" s="473" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="50">
+      <c r="B25" s="562" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="200" t="inlineStr">
+      <c r="C25" s="472" t="n"/>
+      <c r="D25" s="472" t="n"/>
+      <c r="E25" s="472" t="n"/>
+      <c r="F25" s="472" t="n"/>
+      <c r="G25" s="472" t="n"/>
+      <c r="H25" s="472" t="n"/>
+      <c r="I25" s="472" t="n"/>
+      <c r="J25" s="472" t="n"/>
+      <c r="K25" s="472" t="n"/>
+      <c r="L25" s="473" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="50">
+      <c r="B26" s="563" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="472" t="n"/>
+      <c r="D26" s="472" t="n"/>
+      <c r="E26" s="472" t="n"/>
+      <c r="F26" s="472" t="n"/>
+      <c r="G26" s="472" t="n"/>
+      <c r="H26" s="472" t="n"/>
+      <c r="I26" s="472" t="n"/>
+      <c r="J26" s="472" t="n"/>
+      <c r="K26" s="472" t="n"/>
+      <c r="L26" s="473" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="50">
+      <c r="B27" s="530" t="n"/>
+      <c r="C27" s="482" t="n"/>
+      <c r="D27" s="482" t="n"/>
+      <c r="E27" s="482" t="n"/>
+      <c r="F27" s="482" t="n"/>
+      <c r="G27" s="482" t="n"/>
+      <c r="H27" s="482" t="n"/>
+      <c r="I27" s="482" t="n"/>
+      <c r="J27" s="482" t="n"/>
+      <c r="K27" s="482" t="n"/>
+      <c r="L27" s="483" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -18298,7 +19447,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="456" t="inlineStr">
         <is>
@@ -18339,7 +19487,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="50">
       <c r="A8" s="84" t="inlineStr">
         <is>
@@ -18413,7 +19560,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="50">
       <c r="A16" s="84" t="inlineStr">
         <is>
@@ -18442,7 +19588,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="24.75" customHeight="1" s="50">
       <c r="A21" s="82" t="inlineStr">
         <is>
@@ -18673,8 +19818,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="36.75" customHeight="1" s="50">
       <c r="A22" s="82" t="inlineStr">
         <is>
@@ -18765,7 +19908,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
@@ -18993,7 +20135,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="50">
       <c r="A26" s="105" t="inlineStr">
         <is>
@@ -19060,7 +20201,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33" ht="15" customHeight="1" s="50">
       <c r="A33" s="105" t="inlineStr">
         <is>
@@ -19301,8 +20441,6 @@
         <v/>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
     <row r="51" ht="19.5" customHeight="1" s="50">
       <c r="A51" s="103" t="inlineStr">
         <is>
@@ -19395,7 +20533,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="84" t="inlineStr">
         <is>
@@ -19479,7 +20616,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="84" t="inlineStr">
         <is>
@@ -19642,7 +20778,6 @@
       </c>
     </row>
     <row r="4" ht="10" customHeight="1" s="50"/>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="50">
       <c r="A6" s="100" t="inlineStr">
         <is>
@@ -19742,9 +20877,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="36.75" customHeight="1" s="50">
       <c r="A18" s="82" t="inlineStr">
         <is>
@@ -19805,7 +20937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="B2:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
@@ -19820,7 +20952,6 @@
     <col width="13" customWidth="1" style="50" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="36" customHeight="1" s="50">
       <c r="B2" s="429" t="inlineStr">
         <is>
@@ -19835,7 +20966,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="50">
       <c r="B5" s="373" t="inlineStr">
         <is>
@@ -19843,7 +20973,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1" s="50">
       <c r="B7" s="374" t="inlineStr">
         <is>
@@ -19932,8 +21061,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="50">
       <c r="B13" s="373" t="inlineStr">
         <is>
@@ -19941,7 +21068,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="50">
       <c r="B15" s="374" t="inlineStr">
         <is>
@@ -20096,8 +21222,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="24" customHeight="1" s="50">
       <c r="B24" s="373" t="inlineStr">
         <is>
@@ -20105,7 +21229,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="24" customHeight="1" s="50">
       <c r="B26" s="374" t="inlineStr">
         <is>
@@ -20317,7 +21440,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="10" customHeight="1" s="50">
       <c r="A4" s="104" t="inlineStr">
         <is>
@@ -20425,7 +21547,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="50">
       <c r="A12" s="104" t="inlineStr">
         <is>
@@ -21135,7 +22256,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="50">
       <c r="J34" s="76" t="inlineStr">
         <is>
@@ -21551,7 +22671,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="202" t="inlineStr">
         <is>
@@ -21816,7 +22935,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="50">
       <c r="A26" s="205" t="inlineStr">
         <is>
@@ -21950,7 +23068,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="207" t="inlineStr">
         <is>
@@ -22445,7 +23562,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="210" t="inlineStr">
         <is>
@@ -23192,7 +24308,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="215" t="inlineStr">
         <is>
@@ -23870,7 +24985,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="219" t="inlineStr">
         <is>
@@ -24420,7 +25534,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="50">
       <c r="A3" s="222" t="inlineStr">
         <is>
@@ -25003,10 +26116,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="31.5" customHeight="1" s="50">
       <c r="A6" s="78" t="inlineStr">
         <is>
@@ -25021,7 +26130,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="80" t="inlineStr">
         <is>
@@ -25036,7 +26144,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="50">
       <c r="A12" s="80" t="inlineStr">
         <is>
@@ -25051,7 +26158,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="50">
       <c r="A15" s="80" t="inlineStr">
         <is>
@@ -25080,7 +26186,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="50">
       <c r="A20" s="80" t="inlineStr">
         <is>
@@ -25095,7 +26200,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="50">
       <c r="A23" s="82" t="inlineStr">
         <is>
@@ -25143,7 +26247,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="456" t="inlineStr">
         <is>
@@ -25151,7 +26254,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="50">
       <c r="A5" s="84" t="inlineStr">
         <is>
@@ -25166,7 +26268,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="50">
       <c r="A8" s="84" t="inlineStr">
         <is>
@@ -25181,7 +26282,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="50">
       <c r="A11" s="84" t="inlineStr">
         <is>
@@ -25196,9 +26296,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="50">
       <c r="A16" s="82" t="inlineStr">
         <is>
@@ -25231,559 +26328,612 @@
   <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3.5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="71.5" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="16.5" customWidth="1" style="50" min="4" max="4"/>
-    <col width="42.5" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="17.5" customWidth="1" style="50" min="7" max="7"/>
-    <col width="75.5" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="9"/>
-    <col width="29.5" customWidth="1" style="50" min="10" max="10"/>
-    <col width="136.5" customWidth="1" style="50" min="11" max="11"/>
-    <col width="26" customWidth="1" style="50" min="12" max="12"/>
-    <col width="21.5" customWidth="1" style="50" min="13" max="13"/>
-    <col width="13" customWidth="1" style="50" min="14" max="14"/>
+    <col width="12" customWidth="1" style="50" min="1" max="1"/>
+    <col width="17" customWidth="1" style="50" min="2" max="2"/>
+    <col width="12" customWidth="1" style="50" min="3" max="3"/>
+    <col width="11" customWidth="1" style="50" min="4" max="4"/>
+    <col width="17" customWidth="1" style="50" min="5" max="5"/>
+    <col width="12" customWidth="1" style="50" min="6" max="6"/>
+    <col width="11" customWidth="1" style="50" min="7" max="7"/>
+    <col width="17" customWidth="1" style="50" min="8" max="8"/>
+    <col width="13" customWidth="1" style="50" min="9" max="9"/>
+    <col width="11" customWidth="1" style="50" min="10" max="10"/>
+    <col width="17" customWidth="1" style="50" min="11" max="11"/>
+    <col width="14" customWidth="1" style="50" min="12" max="12"/>
+    <col width="12" customWidth="1" style="50" min="13" max="13"/>
+    <col width="6" customWidth="1" style="50" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="10" customHeight="1" s="50">
-      <c r="A1" s="60" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="50">
+      <c r="A1" s="457" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="431" t="inlineStr">
-        <is>
-          <t>BANKA, KREDİ VE TAKSİT YÖNETİM MERKEZİ</t>
+    <row r="2" ht="28" customHeight="1" s="50">
+      <c r="B2" s="458" t="inlineStr">
+        <is>
+          <t>BANKA KREDI VE TAKSIT TAKIP SISTEMI</t>
+        </is>
+      </c>
+      <c r="L2" s="459" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="460" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="50">
-      <c r="B3" s="432" t="inlineStr">
-        <is>
-          <t>Konsolide Kredi Portföyü, Aylık Borç Servisi ve Likidite Karar Kokpiti · Canlı Hesaplama</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14" customHeight="1" s="50"/>
+      <c r="B3" s="461" t="inlineStr">
+        <is>
+          <t>CFO &amp; Finans Direktörü Kredi Yönetimi, XIRR Efektif Maliyet ve Arbitraj Kokpiti · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1" s="50"/>
     <row r="5" ht="20" customHeight="1" s="50">
-      <c r="B5" s="398" t="inlineStr">
+      <c r="B5" s="462" t="inlineStr">
         <is>
           <t>TOPLAM KREDİ PORTFÖYÜ</t>
         </is>
       </c>
-      <c r="C5" s="399" t="n"/>
-      <c r="D5" s="400" t="inlineStr">
+      <c r="C5" s="463" t="n"/>
+      <c r="D5" s="464" t="inlineStr">
         <is>
           <t>CANLI BAKİYE</t>
         </is>
       </c>
-      <c r="E5" s="398" t="inlineStr">
+      <c r="E5" s="465" t="inlineStr">
         <is>
           <t>AYLIK BORÇ SERVİSİ (30 GÜN)</t>
         </is>
       </c>
-      <c r="F5" s="399" t="n"/>
-      <c r="G5" s="401" t="inlineStr">
+      <c r="F5" s="463" t="n"/>
+      <c r="G5" s="466" t="inlineStr">
         <is>
           <t>ÖDEME BASKISI</t>
         </is>
       </c>
-      <c r="H5" s="398" t="inlineStr">
+      <c r="H5" s="467" t="inlineStr">
         <is>
           <t>REFİNANSMAN AYLIK RAHATLAMA</t>
         </is>
       </c>
-      <c r="I5" s="399" t="n"/>
-      <c r="J5" s="402">
+      <c r="I5" s="463" t="n"/>
+      <c r="J5" s="468">
         <f>KARAR_MOTORU!B18&amp;" ADAY"</f>
         <v/>
       </c>
-      <c r="K5" s="398" t="inlineStr">
+      <c r="K5" s="469" t="inlineStr">
         <is>
           <t>BORÇLANMA SÜRDÜRÜLEBİLİRLİĞİ</t>
         </is>
       </c>
-      <c r="L5" s="399" t="n"/>
-      <c r="M5" s="400">
+      <c r="L5" s="463" t="n"/>
+      <c r="M5" s="470">
         <f>KARAR_MOTORU!B16</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1" s="50">
-      <c r="B6" s="403" t="n"/>
-      <c r="C6" s="404" t="n"/>
-      <c r="D6" s="405" t="n"/>
-      <c r="E6" s="403" t="n"/>
-      <c r="F6" s="404" t="n"/>
-      <c r="G6" s="405" t="n"/>
-      <c r="H6" s="403" t="n"/>
-      <c r="I6" s="404" t="n"/>
-      <c r="J6" s="405" t="n"/>
-      <c r="K6" s="403" t="n"/>
-      <c r="L6" s="404" t="n"/>
-      <c r="M6" s="405" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" s="50">
-      <c r="B7" s="406">
+      <c r="B6" s="471" t="n"/>
+      <c r="C6" s="472" t="n"/>
+      <c r="D6" s="473" t="n"/>
+      <c r="E6" s="474" t="n"/>
+      <c r="F6" s="472" t="n"/>
+      <c r="G6" s="473" t="n"/>
+      <c r="H6" s="475" t="n"/>
+      <c r="I6" s="472" t="n"/>
+      <c r="J6" s="473" t="n"/>
+      <c r="K6" s="476" t="n"/>
+      <c r="L6" s="472" t="n"/>
+      <c r="M6" s="473" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="50">
+      <c r="B7" s="477">
         <f>KARAR_MOTORU!B5</f>
         <v/>
       </c>
-      <c r="C7" s="404" t="n"/>
-      <c r="D7" s="405" t="n"/>
-      <c r="E7" s="407">
+      <c r="C7" s="472" t="n"/>
+      <c r="D7" s="473" t="n"/>
+      <c r="E7" s="478">
         <f>KARAR_MOTORU!B7</f>
         <v/>
       </c>
-      <c r="F7" s="404" t="n"/>
-      <c r="G7" s="405" t="n"/>
-      <c r="H7" s="408">
+      <c r="F7" s="472" t="n"/>
+      <c r="G7" s="473" t="n"/>
+      <c r="H7" s="479">
         <f>KARAR_MOTORU!B19</f>
         <v/>
       </c>
-      <c r="I7" s="404" t="n"/>
-      <c r="J7" s="405" t="n"/>
-      <c r="K7" s="409">
+      <c r="I7" s="472" t="n"/>
+      <c r="J7" s="473" t="n"/>
+      <c r="K7" s="480">
         <f>KARAR_MOTORU!B15</f>
         <v/>
       </c>
-      <c r="L7" s="404" t="n"/>
-      <c r="M7" s="405" t="n"/>
+      <c r="L7" s="472" t="n"/>
+      <c r="M7" s="473" t="n"/>
     </row>
     <row r="8" ht="6" customHeight="1" s="50">
-      <c r="B8" s="403" t="n"/>
-      <c r="C8" s="404" t="n"/>
-      <c r="D8" s="405" t="n"/>
-      <c r="E8" s="403" t="n"/>
-      <c r="F8" s="404" t="n"/>
-      <c r="G8" s="405" t="n"/>
-      <c r="H8" s="403" t="n"/>
-      <c r="I8" s="404" t="n"/>
-      <c r="J8" s="405" t="n"/>
-      <c r="K8" s="403" t="n"/>
-      <c r="L8" s="404" t="n"/>
-      <c r="M8" s="405" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="50">
-      <c r="B9" s="410" t="inlineStr">
+      <c r="B8" s="471" t="n"/>
+      <c r="C8" s="472" t="n"/>
+      <c r="D8" s="473" t="n"/>
+      <c r="E8" s="474" t="n"/>
+      <c r="F8" s="472" t="n"/>
+      <c r="G8" s="473" t="n"/>
+      <c r="H8" s="475" t="n"/>
+      <c r="I8" s="472" t="n"/>
+      <c r="J8" s="473" t="n"/>
+      <c r="K8" s="476" t="n"/>
+      <c r="L8" s="472" t="n"/>
+      <c r="M8" s="473" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="50">
+      <c r="B9" s="481" t="inlineStr">
         <is>
           <t>↑ Aktif portföy risk hacmi</t>
         </is>
       </c>
-      <c r="C9" s="411" t="n"/>
-      <c r="D9" s="412" t="n"/>
-      <c r="E9" s="413" t="inlineStr">
+      <c r="C9" s="482" t="n"/>
+      <c r="D9" s="483" t="n"/>
+      <c r="E9" s="484" t="inlineStr">
         <is>
           <t>● 30 gün içinde vadesi gelen taksitler</t>
         </is>
       </c>
-      <c r="F9" s="411" t="n"/>
-      <c r="G9" s="412" t="n"/>
-      <c r="H9" s="410" t="inlineStr">
+      <c r="F9" s="482" t="n"/>
+      <c r="G9" s="483" t="n"/>
+      <c r="H9" s="485" t="inlineStr">
         <is>
           <t>✓ Yapılandırma ile aylık nakit kazanımı</t>
         </is>
       </c>
-      <c r="I9" s="411" t="n"/>
-      <c r="J9" s="412" t="n"/>
-      <c r="K9" s="414">
+      <c r="I9" s="482" t="n"/>
+      <c r="J9" s="483" t="n"/>
+      <c r="K9" s="486">
         <f>KARAR_MOTORU!B17</f>
         <v/>
       </c>
-      <c r="L9" s="411" t="n"/>
-      <c r="M9" s="412" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="50"/>
+      <c r="L9" s="482" t="n"/>
+      <c r="M9" s="483" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="50"/>
     <row r="11" ht="24" customHeight="1" s="50">
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="487" t="inlineStr">
         <is>
           <t>BANKA, KREDI VE TAKSIT TAKIP SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="144" t="inlineStr">
+      <c r="F11" s="488" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="74" t="inlineStr">
+      <c r="H11" s="487" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="50">
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="127" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="73" t="inlineStr">
+      <c r="H12" s="127" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1" s="50"/>
-    <row r="14" ht="26" customHeight="1" s="50">
-      <c r="B14" s="145" t="inlineStr">
+    <row r="14" ht="24" customHeight="1" s="50">
+      <c r="B14" s="489" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="145" t="inlineStr">
+      <c r="C14" s="489" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="145" t="inlineStr">
+      <c r="D14" s="489" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="145" t="inlineStr">
+      <c r="E14" s="489" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="146" t="inlineStr">
+      <c r="H14" s="490" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="146" t="inlineStr">
+      <c r="I14" s="491" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="146" t="inlineStr">
+      <c r="J14" s="491" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="146" t="inlineStr">
+      <c r="K14" s="491" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="146" t="inlineStr">
+      <c r="L14" s="491" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
+      <c r="M14" s="491" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1" s="50">
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="276" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="73" t="n">
+      <c r="C15" s="276" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="73" t="n">
+      <c r="D15" s="276" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="73" t="n">
+      <c r="E15" s="276" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="147" t="inlineStr">
+      <c r="H15" s="492" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="227">
+      <c r="I15" s="493">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="228">
+      <c r="J15" s="494">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="149" t="inlineStr">
+      <c r="K15" s="495" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="133" t="inlineStr">
+      <c r="L15" s="496" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
+      <c r="M15" s="497" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1" s="50">
-      <c r="B16" s="73" t="inlineStr">
+      <c r="B16" s="275" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="73" t="n">
+      <c r="C16" s="275" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="73" t="n">
+      <c r="D16" s="275" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="73" t="n">
+      <c r="E16" s="275" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="147" t="inlineStr">
+      <c r="H16" s="498" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="227">
+      <c r="I16" s="499">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="228">
+      <c r="J16" s="500">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="149" t="inlineStr">
+      <c r="K16" s="501" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="130" t="inlineStr">
+      <c r="L16" s="502" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
+      <c r="M16" s="238" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1" s="50">
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="276" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="73" t="n">
+      <c r="C17" s="276" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="73" t="n">
+      <c r="D17" s="276" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="73" t="n">
+      <c r="E17" s="276" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="147" t="inlineStr">
+      <c r="H17" s="492" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="227">
+      <c r="I17" s="493">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="228">
+      <c r="J17" s="494">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="149" t="inlineStr">
+      <c r="K17" s="495" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="150" t="inlineStr">
+      <c r="L17" s="503" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
+      <c r="M17" s="497" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1" s="50">
-      <c r="B18" s="73" t="inlineStr">
+      <c r="B18" s="275" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="73" t="n">
+      <c r="C18" s="275" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="73" t="n">
+      <c r="D18" s="275" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="73" t="n">
+      <c r="E18" s="275" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="147" t="inlineStr">
+      <c r="H18" s="498" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="227">
+      <c r="I18" s="499">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="228">
+      <c r="J18" s="500">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="149" t="inlineStr">
+      <c r="K18" s="501" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="133" t="inlineStr">
+      <c r="L18" s="504" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
+      <c r="M18" s="238" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1" s="50">
-      <c r="B19" s="73" t="inlineStr">
+      <c r="B19" s="276" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="73" t="n">
+      <c r="C19" s="276" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="73" t="n">
+      <c r="D19" s="276" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="73" t="n">
+      <c r="E19" s="276" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="151" t="inlineStr">
+      <c r="H19" s="505" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="506">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="507">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="154" t="inlineStr"/>
-      <c r="L19" s="155" t="inlineStr">
+      <c r="K19" s="508" t="inlineStr"/>
+      <c r="L19" s="509" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="16" customHeight="1" s="50">
-      <c r="B20" s="73" t="inlineStr">
+      <c r="M19" s="509" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="50">
+      <c r="B20" s="275" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="73" t="n">
+      <c r="C20" s="275" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="73" t="n">
+      <c r="D20" s="275" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="73" t="n">
+      <c r="E20" s="275" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1" s="50"/>
+    <row r="21" ht="14" customHeight="1" s="50"/>
     <row r="22" ht="24" customHeight="1" s="50">
-      <c r="B22" s="156" t="inlineStr">
+      <c r="B22" s="510" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="156" t="inlineStr">
+      <c r="C22" s="463" t="n"/>
+      <c r="D22" s="463" t="n"/>
+      <c r="E22" s="511" t="n"/>
+      <c r="F22" s="510" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="157" t="inlineStr">
-        <is>
-          <t>KARAR MOTORU PROTOKOLÜ</t>
-        </is>
-      </c>
-      <c r="L22" s="158" t="n"/>
-      <c r="M22" s="158" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" s="50">
-      <c r="B23" s="58" t="inlineStr">
+      <c r="G22" s="463" t="n"/>
+      <c r="H22" s="463" t="n"/>
+      <c r="I22" s="511" t="n"/>
+      <c r="K22" s="512" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="513" t="n"/>
+      <c r="M22" s="514" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="50">
+      <c r="B23" s="515" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="73" t="inlineStr">
+      <c r="C23" s="472" t="n"/>
+      <c r="D23" s="472" t="n"/>
+      <c r="E23" s="473" t="n"/>
+      <c r="F23" s="516" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="159" t="inlineStr">
+      <c r="G23" s="472" t="n"/>
+      <c r="H23" s="472" t="n"/>
+      <c r="I23" s="517" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="160" t="inlineStr">
-        <is>
-          <t>REFİNANSMAN &amp; LİKİDİTE</t>
-        </is>
-      </c>
-      <c r="L23" s="158" t="n"/>
-      <c r="M23" s="158" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="50">
-      <c r="B24" s="59" t="inlineStr">
+      <c r="K23" s="518" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="519" t="n"/>
+      <c r="M23" s="520" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="50">
+      <c r="B24" s="521" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="73" t="inlineStr">
+      <c r="C24" s="472" t="n"/>
+      <c r="D24" s="472" t="n"/>
+      <c r="E24" s="473" t="n"/>
+      <c r="F24" s="516" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="159" t="inlineStr">
+      <c r="G24" s="472" t="n"/>
+      <c r="H24" s="472" t="n"/>
+      <c r="I24" s="517" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="161" t="inlineStr">
-        <is>
-          <t>Sistem, nakit açığı riskini 30/60/90 günlük pencerelerde izleyerek, borç servisi oranını optimal eşikte tutacak yapılandırma önerir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="50">
-      <c r="B25" s="162" t="inlineStr">
+      <c r="K24" s="522" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+      <c r="M24" s="564" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="50">
+      <c r="B25" s="523" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="58" t="inlineStr">
+      <c r="C25" s="472" t="n"/>
+      <c r="D25" s="472" t="n"/>
+      <c r="E25" s="473" t="n"/>
+      <c r="F25" s="496" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" s="50">
-      <c r="B26" s="163" t="inlineStr">
+      <c r="G25" s="524" t="n"/>
+      <c r="H25" s="524" t="n"/>
+      <c r="I25" s="524" t="n"/>
+      <c r="K25" s="565" t="n"/>
+      <c r="M25" s="564" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="50">
+      <c r="B26" s="526" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="164" t="inlineStr">
+      <c r="C26" s="472" t="n"/>
+      <c r="D26" s="472" t="n"/>
+      <c r="E26" s="473" t="n"/>
+      <c r="F26" s="527" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
-      <c r="G26" s="247" t="n"/>
-      <c r="H26" s="247" t="n"/>
-      <c r="I26" s="248" t="n"/>
-      <c r="K26" s="165" t="inlineStr">
-        <is>
-          <t>REFİNANSMAN ANALİZİNİ GÖR (#REFINANSMAN!A1) &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="14" customHeight="1" s="50">
-      <c r="F27" s="249" t="n"/>
-      <c r="G27" s="250" t="n"/>
-      <c r="H27" s="250" t="n"/>
-      <c r="I27" s="251" t="n"/>
+      <c r="G26" s="290" t="n"/>
+      <c r="H26" s="290" t="n"/>
+      <c r="I26" s="291" t="n"/>
+      <c r="K26" s="529" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+      <c r="L26" s="290" t="n"/>
+      <c r="M26" s="291" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="50">
+      <c r="B27" s="530" t="n"/>
+      <c r="C27" s="482" t="n"/>
+      <c r="D27" s="482" t="n"/>
+      <c r="E27" s="483" t="n"/>
+      <c r="F27" s="294" t="n"/>
+      <c r="G27" s="295" t="n"/>
+      <c r="H27" s="295" t="n"/>
+      <c r="I27" s="296" t="n"/>
+      <c r="K27" s="294" t="n"/>
+      <c r="L27" s="295" t="n"/>
+      <c r="M27" s="296" t="n"/>
     </row>
     <row r="28" ht="14" customHeight="1" s="50"/>
     <row r="29" ht="14" customHeight="1" s="50"/>
@@ -26157,11 +27307,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B2:M2"/>
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
-    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:K2"/>
     <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId1"/>
@@ -26500,9 +27650,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16" ht="24.75" customHeight="1" s="50">
       <c r="A16" s="82" t="inlineStr">
         <is>
@@ -26551,7 +27698,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="50">
       <c r="A3" s="456" t="inlineStr">
         <is>
@@ -26699,7 +27845,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="50">
       <c r="A9" s="76" t="inlineStr">
         <is>
